--- a/multi.xlsx
+++ b/multi.xlsx
@@ -20,15 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="331">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
   <si>
-    <t xml:space="preserve">es</t>
-  </si>
-  <si>
-    <t xml:space="preserve">en</t>
+    <t xml:space="preserve">ES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EN </t>
   </si>
   <si>
     <t xml:space="preserve">lenguajes</t>
@@ -743,6 +743,276 @@
   </si>
   <si>
     <t xml:space="preserve">🤖 Analyzing dish with Artificial Intelligence...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_sin_presion_usuario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 No hay registros de presión arterial para el usuario {user_id}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 No blood pressure records found for user {user_id}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_sin_presion_mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 No hay registros de presión para el mes {mes_str}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 No blood pressure records found for the month {mes_str}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_resumen_presion_titulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 Resumen de Presión Arterial ({mes_str}):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 Blood Pressure Summary ({mes_str}):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_mediciones_registradas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Mediciones registradas: {count}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Recorded measurements: {count}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_prom_alta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Promedio Alta (Sistólica): {alta:.1f} mmHg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Average High (Systolic): {alta:.1f} mmHg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_prom_baja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Promedio Baja (Diastólica): {baja:.1f} mmHg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Average Low (Diastolic): {baja:.1f} mmHg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_prom_pulsaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Promedio Pulsaciones: {pul:.1f} lpm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Average Pulse: {pul:.1f} bpm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_btn_descargar_pdf_presion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📄 Descargar PDF Presión Diaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📄 Download Daily Pressure PDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_inf_no_registros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ No hay registros suficientes para generar el informe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Not enough records to generate the report.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_inf_sin_registros_periodo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ No se encontraron registros cerrados para el período {etiqueta_periodo}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ No closed records found for the period {etiqueta_periodo}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sup_inf_error_ia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ No se pudo generar el informe auditado mediante IA tras los reintentos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Could not generate the AI audited report after retries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_no_comidas_precargadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 No hay comidas predeterminadas registradas en tu lista.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 There are no default meals registered in your list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_adjunto_pdf_comidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\n📄 Te adjuntamos el archivo en PDF completo con todos los macronutrientes a continuación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\n📄 We have attached the complete PDF file with all macronutrients below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_generando_pdf_comidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 Generando tu lista de comidas en PDF directamente...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 Generating your meal list in PDF directly...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_error_gen_pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Ocurrió un error al generar el archivo PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ An error occurred while generating the PDF file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_comida_no_encontrada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ No se encontró ninguna comida registrada con el nombre exacto: &lt;b&gt;{nombre}&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ No registered meal was found with the exact name: &lt;b&gt;{nombre}&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_comida_borrada_exito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ La comida &lt;b&gt;{nombre}&lt;/b&gt; ha sido eliminada exitosamente de tu planilla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ The meal &lt;b&gt;{nombre}&lt;/b&gt; has been successfully deleted from your sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_error_db_borrar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Hubo un error en la base de datos al intentar borrar &lt;b&gt;{nombre}&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ A database error occurred while trying to delete &lt;b&gt;{nombre}&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_como_borrar_comida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\n🗑️ &lt;b&gt;¿Cómo borrar una comida?&lt;/b&gt;\nCopiá el nombre exacto de la lista de arriba y escribí el comando de la siguiente forma:\n&lt;code&gt;/borrarcomida Nombre de la Comida&lt;/code&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\n🗑️ &lt;b&gt;How to delete a meal?&lt;/b&gt;\nCopy the exact name from the list above and type the command like this:\n&lt;code&gt;/delmeal Meal_Name&lt;/code&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_analizando_barra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔍 Analizando código de barras y verificando producto...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔍 Analyzing barcode and verifying product...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_producto_encontrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 Producto encontrado (valores calculados cada 100 g):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 Product found (values calculated per 100 g):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_barra_no_encontrada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Código de barras no encontrado en la base de datos. Intentá ingresarlo como texto o foto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Barcode not found in the database. Try entering it as text or photo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_solic_barra_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⌨️ Por favor, ingresá los números del código de barras con el comando /barra NUMERO:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⌨️ Please enter the barcode numbers with the command /barcode NUMBER:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_analizando_imagen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📸 Analizando imagen...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📸 Analyzing image...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_leyendo_barra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔍 Código de barras detectado. Leyendo números del envase...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔍 Barcode detected. Reading package numbers...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_no_comidas_borrar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 No hay comidas predeterminadas registradas para eliminar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 There are no default meals registered to delete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_error_mostrar_listado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 Ocurrió un error al mostrar el listado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 An error occurred while displaying the list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_error_consulta_barra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error al consultar el código: {e}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error querying the barcode: {e}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_titulo_eliminar_ingestas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🗑️ **Eliminación de Ingestas / Actividades:**\nSeleccioná el día que querés revisar:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🗑️ **Deletion of Meals / Activities:**\nSelect the day you want to review:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_txt_sel_momento_del</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📅 Fecha seleccionada: {fecha}\n\nSeleccioná el momento o actividad que querés revisar para eliminar:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📅 Selected Date: {fecha}\n\nSelect the moment or activity you want to review for deletion:</t>
   </si>
 </sst>
 </file>
@@ -851,8 +1121,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
-  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C1048576"/>
+  <sheetFormatPr defaultColWidth="12.6953125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.95"/>
@@ -1771,6 +2041,471 @@
         <v>240</v>
       </c>
     </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+    </row>
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+    </row>
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+    </row>
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+    </row>
+    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+    </row>
+    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+    </row>
+    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+    </row>
+    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+    </row>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>

--- a/multi.xlsx
+++ b/multi.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2682" uniqueCount="2339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="2349">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -7037,6 +7037,40 @@
   </si>
   <si>
     <t xml:space="preserve">Benvenuti su I A NutriBot, il vostro assistente personale intelligente su Telegram per gestire le vostre abitudini alimentari e la vostra salute in modo semplice e automatizzato. Con questo sistema, non avrete bisogno di complessi fogli di calcolo o tabelle manuali. Potrete registrare tutto ciò che consumate utilizzando il linguaggio naturale: semplicemente scrivendo un messaggio, inviando una nota vocale o scattando una foto del vostro piatto. Il bot calcolerà istantaneamente calorie e macronutrienti. Inoltre, potrete registrare la vostra attività fisica quotidiana, monitorare la pressione sanguigna e visualizzare report e riepiloghi a schermo o in formato PDF. Per consultare l'elenco completo dei comandi rapidi, potete visitare la sezione guida di questa pagina o contattarci in qualsiasi momento nella chat di Telegram. Grazie per la fiducia che riponete in noi per supportare il vostro benessere quotidiano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dec_no_registrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ ¡Todavía no estás registrado!
+Para usar este comando y acceder a tu plan nutricional, necesitás registrarte primero.
+👉 Usá el comando /alta para crear tu perfil en un par de pasos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ You are not registered yet!
+To use this command and access your nutrition plan, you need to sign up first.
+👉 Use the /alta command to create your profile in a couple of steps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dec_cuenta_deshabilitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Tu cuenta ha sido deshabilitada debido a inactividad o baja del sistema. Por favor, contactá al administrador del bot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Your account has been disabled due to inactivity or system removal. Please contact the bot administrator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dec_alerta_req_reg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dec_alerta_cta_dis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Cuenta deshabilitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Account disabled</t>
   </si>
 </sst>
 </file>
@@ -7046,7 +7080,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -7071,6 +7105,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -7119,13 +7161,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7145,8 +7195,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H668"/>
-  <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AMJ1048576"/>
+  <sheetFormatPr defaultColWidth="12.7578125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.95"/>
@@ -16523,18 +16573,1042 @@
       <c r="D667" s="1" t="s">
         <v>2338</v>
       </c>
-    </row>
-    <row r="668" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J667" s="1"/>
+      <c r="P667" s="1"/>
+      <c r="V667" s="1"/>
+      <c r="AB667" s="1"/>
+      <c r="AH667" s="1"/>
+      <c r="AN667" s="1"/>
+      <c r="AT667" s="1"/>
+      <c r="AZ667" s="1"/>
+      <c r="BF667" s="1"/>
+      <c r="BL667" s="1"/>
+      <c r="BR667" s="1"/>
+      <c r="BX667" s="1"/>
+      <c r="CD667" s="1"/>
+      <c r="CJ667" s="1"/>
+      <c r="CP667" s="1"/>
+      <c r="CV667" s="1"/>
+      <c r="DB667" s="1"/>
+      <c r="DH667" s="1"/>
+      <c r="DN667" s="1"/>
+      <c r="DT667" s="1"/>
+      <c r="DZ667" s="1"/>
+      <c r="EF667" s="1"/>
+      <c r="EL667" s="1"/>
+      <c r="ER667" s="1"/>
+      <c r="EX667" s="1"/>
+      <c r="FD667" s="1"/>
+      <c r="FJ667" s="1"/>
+      <c r="FP667" s="1"/>
+      <c r="FV667" s="1"/>
+      <c r="GB667" s="1"/>
+      <c r="GH667" s="1"/>
+      <c r="GN667" s="1"/>
+      <c r="GT667" s="1"/>
+      <c r="GZ667" s="1"/>
+      <c r="HF667" s="1"/>
+      <c r="HL667" s="1"/>
+      <c r="HR667" s="1"/>
+      <c r="HX667" s="1"/>
+      <c r="ID667" s="1"/>
+      <c r="IJ667" s="1"/>
+      <c r="IP667" s="1"/>
+      <c r="IV667" s="1"/>
+      <c r="JB667" s="1"/>
+      <c r="JH667" s="1"/>
+      <c r="JN667" s="1"/>
+      <c r="JT667" s="1"/>
+      <c r="JZ667" s="1"/>
+      <c r="KF667" s="1"/>
+      <c r="KL667" s="1"/>
+      <c r="KR667" s="1"/>
+      <c r="KX667" s="1"/>
+      <c r="LD667" s="1"/>
+      <c r="LJ667" s="1"/>
+      <c r="LP667" s="1"/>
+      <c r="LV667" s="1"/>
+      <c r="MB667" s="1"/>
+      <c r="MH667" s="1"/>
+      <c r="MN667" s="1"/>
+      <c r="MT667" s="1"/>
+      <c r="MZ667" s="1"/>
+      <c r="NF667" s="1"/>
+      <c r="NL667" s="1"/>
+      <c r="NR667" s="1"/>
+      <c r="NX667" s="1"/>
+      <c r="OD667" s="1"/>
+      <c r="OJ667" s="1"/>
+      <c r="OP667" s="1"/>
+      <c r="OV667" s="1"/>
+      <c r="PB667" s="1"/>
+      <c r="PH667" s="1"/>
+      <c r="PN667" s="1"/>
+      <c r="PT667" s="1"/>
+      <c r="PZ667" s="1"/>
+      <c r="QF667" s="1"/>
+      <c r="QL667" s="1"/>
+      <c r="QR667" s="1"/>
+      <c r="QX667" s="1"/>
+      <c r="RD667" s="1"/>
+      <c r="RJ667" s="1"/>
+      <c r="RP667" s="1"/>
+      <c r="RV667" s="1"/>
+      <c r="SB667" s="1"/>
+      <c r="SH667" s="1"/>
+      <c r="SN667" s="1"/>
+      <c r="ST667" s="1"/>
+      <c r="SZ667" s="1"/>
+      <c r="TF667" s="1"/>
+      <c r="TL667" s="1"/>
+      <c r="TR667" s="1"/>
+      <c r="TX667" s="1"/>
+      <c r="UD667" s="1"/>
+      <c r="UJ667" s="1"/>
+      <c r="UP667" s="1"/>
+      <c r="UV667" s="1"/>
+      <c r="VB667" s="1"/>
+      <c r="VH667" s="1"/>
+      <c r="VN667" s="1"/>
+      <c r="VT667" s="1"/>
+      <c r="VZ667" s="1"/>
+      <c r="WF667" s="1"/>
+      <c r="WL667" s="1"/>
+      <c r="WR667" s="1"/>
+      <c r="WX667" s="1"/>
+      <c r="XD667" s="1"/>
+      <c r="XJ667" s="1"/>
+      <c r="XP667" s="1"/>
+      <c r="XV667" s="1"/>
+      <c r="YB667" s="1"/>
+      <c r="YH667" s="1"/>
+      <c r="YN667" s="1"/>
+      <c r="YT667" s="1"/>
+      <c r="YZ667" s="1"/>
+      <c r="ZF667" s="1"/>
+      <c r="ZL667" s="1"/>
+      <c r="ZR667" s="1"/>
+      <c r="ZX667" s="1"/>
+      <c r="AAD667" s="1"/>
+      <c r="AAJ667" s="1"/>
+      <c r="AAP667" s="1"/>
+      <c r="AAV667" s="1"/>
+      <c r="ABB667" s="1"/>
+      <c r="ABH667" s="1"/>
+      <c r="ABN667" s="1"/>
+      <c r="ABT667" s="1"/>
+      <c r="ABZ667" s="1"/>
+      <c r="ACF667" s="1"/>
+      <c r="ACL667" s="1"/>
+      <c r="ACR667" s="1"/>
+      <c r="ACX667" s="1"/>
+      <c r="ADD667" s="1"/>
+      <c r="ADJ667" s="1"/>
+      <c r="ADP667" s="1"/>
+      <c r="ADV667" s="1"/>
+      <c r="AEB667" s="1"/>
+      <c r="AEH667" s="1"/>
+      <c r="AEN667" s="1"/>
+      <c r="AET667" s="1"/>
+      <c r="AEZ667" s="1"/>
+      <c r="AFF667" s="1"/>
+      <c r="AFL667" s="1"/>
+      <c r="AFR667" s="1"/>
+      <c r="AFX667" s="1"/>
+      <c r="AGD667" s="1"/>
+      <c r="AGJ667" s="1"/>
+      <c r="AGP667" s="1"/>
+      <c r="AGV667" s="1"/>
+      <c r="AHB667" s="1"/>
+      <c r="AHH667" s="1"/>
+      <c r="AHN667" s="1"/>
+      <c r="AHT667" s="1"/>
+      <c r="AHZ667" s="1"/>
+      <c r="AIF667" s="1"/>
+      <c r="AIL667" s="1"/>
+      <c r="AIR667" s="1"/>
+      <c r="AIX667" s="1"/>
+      <c r="AJD667" s="1"/>
+      <c r="AJJ667" s="1"/>
+      <c r="AJP667" s="1"/>
+      <c r="AJV667" s="1"/>
+      <c r="AKB667" s="1"/>
+      <c r="AKH667" s="1"/>
+      <c r="AKN667" s="1"/>
+      <c r="AKT667" s="1"/>
+      <c r="AKZ667" s="1"/>
+      <c r="ALF667" s="1"/>
+      <c r="ALL667" s="1"/>
+      <c r="ALR667" s="1"/>
+      <c r="ALX667" s="1"/>
+      <c r="AMD667" s="1"/>
+      <c r="AMJ667" s="1"/>
+    </row>
+    <row r="668" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A668" s="0" t="s">
-        <v>2335</v>
-      </c>
-      <c r="B668" s="0" t="s">
-        <v>2336</v>
-      </c>
-      <c r="C668" s="0" t="s">
-        <v>2337</v>
-      </c>
-    </row>
+        <v>2339</v>
+      </c>
+      <c r="B668" s="2" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C668" s="2" t="s">
+        <v>2341</v>
+      </c>
+      <c r="J668" s="1"/>
+      <c r="P668" s="1"/>
+      <c r="V668" s="1"/>
+      <c r="AB668" s="1"/>
+      <c r="AH668" s="1"/>
+      <c r="AN668" s="1"/>
+      <c r="AT668" s="1"/>
+      <c r="AZ668" s="1"/>
+      <c r="BF668" s="1"/>
+      <c r="BL668" s="1"/>
+      <c r="BR668" s="1"/>
+      <c r="BX668" s="1"/>
+      <c r="CD668" s="1"/>
+      <c r="CJ668" s="1"/>
+      <c r="CP668" s="1"/>
+      <c r="CV668" s="1"/>
+      <c r="DB668" s="1"/>
+      <c r="DH668" s="1"/>
+      <c r="DN668" s="1"/>
+      <c r="DT668" s="1"/>
+      <c r="DZ668" s="1"/>
+      <c r="EF668" s="1"/>
+      <c r="EL668" s="1"/>
+      <c r="ER668" s="1"/>
+      <c r="EX668" s="1"/>
+      <c r="FD668" s="1"/>
+      <c r="FJ668" s="1"/>
+      <c r="FP668" s="1"/>
+      <c r="FV668" s="1"/>
+      <c r="GB668" s="1"/>
+      <c r="GH668" s="1"/>
+      <c r="GN668" s="1"/>
+      <c r="GT668" s="1"/>
+      <c r="GZ668" s="1"/>
+      <c r="HF668" s="1"/>
+      <c r="HL668" s="1"/>
+      <c r="HR668" s="1"/>
+      <c r="HX668" s="1"/>
+      <c r="ID668" s="1"/>
+      <c r="IJ668" s="1"/>
+      <c r="IP668" s="1"/>
+      <c r="IV668" s="1"/>
+      <c r="JB668" s="1"/>
+      <c r="JH668" s="1"/>
+      <c r="JN668" s="1"/>
+      <c r="JT668" s="1"/>
+      <c r="JZ668" s="1"/>
+      <c r="KF668" s="1"/>
+      <c r="KL668" s="1"/>
+      <c r="KR668" s="1"/>
+      <c r="KX668" s="1"/>
+      <c r="LD668" s="1"/>
+      <c r="LJ668" s="1"/>
+      <c r="LP668" s="1"/>
+      <c r="LV668" s="1"/>
+      <c r="MB668" s="1"/>
+      <c r="MH668" s="1"/>
+      <c r="MN668" s="1"/>
+      <c r="MT668" s="1"/>
+      <c r="MZ668" s="1"/>
+      <c r="NF668" s="1"/>
+      <c r="NL668" s="1"/>
+      <c r="NR668" s="1"/>
+      <c r="NX668" s="1"/>
+      <c r="OD668" s="1"/>
+      <c r="OJ668" s="1"/>
+      <c r="OP668" s="1"/>
+      <c r="OV668" s="1"/>
+      <c r="PB668" s="1"/>
+      <c r="PH668" s="1"/>
+      <c r="PN668" s="1"/>
+      <c r="PT668" s="1"/>
+      <c r="PZ668" s="1"/>
+      <c r="QF668" s="1"/>
+      <c r="QL668" s="1"/>
+      <c r="QR668" s="1"/>
+      <c r="QX668" s="1"/>
+      <c r="RD668" s="1"/>
+      <c r="RJ668" s="1"/>
+      <c r="RP668" s="1"/>
+      <c r="RV668" s="1"/>
+      <c r="SB668" s="1"/>
+      <c r="SH668" s="1"/>
+      <c r="SN668" s="1"/>
+      <c r="ST668" s="1"/>
+      <c r="SZ668" s="1"/>
+      <c r="TF668" s="1"/>
+      <c r="TL668" s="1"/>
+      <c r="TR668" s="1"/>
+      <c r="TX668" s="1"/>
+      <c r="UD668" s="1"/>
+      <c r="UJ668" s="1"/>
+      <c r="UP668" s="1"/>
+      <c r="UV668" s="1"/>
+      <c r="VB668" s="1"/>
+      <c r="VH668" s="1"/>
+      <c r="VN668" s="1"/>
+      <c r="VT668" s="1"/>
+      <c r="VZ668" s="1"/>
+      <c r="WF668" s="1"/>
+      <c r="WL668" s="1"/>
+      <c r="WR668" s="1"/>
+      <c r="WX668" s="1"/>
+      <c r="XD668" s="1"/>
+      <c r="XJ668" s="1"/>
+      <c r="XP668" s="1"/>
+      <c r="XV668" s="1"/>
+      <c r="YB668" s="1"/>
+      <c r="YH668" s="1"/>
+      <c r="YN668" s="1"/>
+      <c r="YT668" s="1"/>
+      <c r="YZ668" s="1"/>
+      <c r="ZF668" s="1"/>
+      <c r="ZL668" s="1"/>
+      <c r="ZR668" s="1"/>
+      <c r="ZX668" s="1"/>
+      <c r="AAD668" s="1"/>
+      <c r="AAJ668" s="1"/>
+      <c r="AAP668" s="1"/>
+      <c r="AAV668" s="1"/>
+      <c r="ABB668" s="1"/>
+      <c r="ABH668" s="1"/>
+      <c r="ABN668" s="1"/>
+      <c r="ABT668" s="1"/>
+      <c r="ABZ668" s="1"/>
+      <c r="ACF668" s="1"/>
+      <c r="ACL668" s="1"/>
+      <c r="ACR668" s="1"/>
+      <c r="ACX668" s="1"/>
+      <c r="ADD668" s="1"/>
+      <c r="ADJ668" s="1"/>
+      <c r="ADP668" s="1"/>
+      <c r="ADV668" s="1"/>
+      <c r="AEB668" s="1"/>
+      <c r="AEH668" s="1"/>
+      <c r="AEN668" s="1"/>
+      <c r="AET668" s="1"/>
+      <c r="AEZ668" s="1"/>
+      <c r="AFF668" s="1"/>
+      <c r="AFL668" s="1"/>
+      <c r="AFR668" s="1"/>
+      <c r="AFX668" s="1"/>
+      <c r="AGD668" s="1"/>
+      <c r="AGJ668" s="1"/>
+      <c r="AGP668" s="1"/>
+      <c r="AGV668" s="1"/>
+      <c r="AHB668" s="1"/>
+      <c r="AHH668" s="1"/>
+      <c r="AHN668" s="1"/>
+      <c r="AHT668" s="1"/>
+      <c r="AHZ668" s="1"/>
+      <c r="AIF668" s="1"/>
+      <c r="AIL668" s="1"/>
+      <c r="AIR668" s="1"/>
+      <c r="AIX668" s="1"/>
+      <c r="AJD668" s="1"/>
+      <c r="AJJ668" s="1"/>
+      <c r="AJP668" s="1"/>
+      <c r="AJV668" s="1"/>
+      <c r="AKB668" s="1"/>
+      <c r="AKH668" s="1"/>
+      <c r="AKN668" s="1"/>
+      <c r="AKT668" s="1"/>
+      <c r="AKZ668" s="1"/>
+      <c r="ALF668" s="1"/>
+      <c r="ALL668" s="1"/>
+      <c r="ALR668" s="1"/>
+      <c r="ALX668" s="1"/>
+      <c r="AMD668" s="1"/>
+      <c r="AMJ668" s="1"/>
+    </row>
+    <row r="669" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A669" s="0" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B669" s="0" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C669" s="0" t="s">
+        <v>2344</v>
+      </c>
+      <c r="J669" s="1"/>
+      <c r="P669" s="1"/>
+      <c r="V669" s="1"/>
+      <c r="AB669" s="1"/>
+      <c r="AH669" s="1"/>
+      <c r="AN669" s="1"/>
+      <c r="AT669" s="1"/>
+      <c r="AZ669" s="1"/>
+      <c r="BF669" s="1"/>
+      <c r="BL669" s="1"/>
+      <c r="BR669" s="1"/>
+      <c r="BX669" s="1"/>
+      <c r="CD669" s="1"/>
+      <c r="CJ669" s="1"/>
+      <c r="CP669" s="1"/>
+      <c r="CV669" s="1"/>
+      <c r="DB669" s="1"/>
+      <c r="DH669" s="1"/>
+      <c r="DN669" s="1"/>
+      <c r="DT669" s="1"/>
+      <c r="DZ669" s="1"/>
+      <c r="EF669" s="1"/>
+      <c r="EL669" s="1"/>
+      <c r="ER669" s="1"/>
+      <c r="EX669" s="1"/>
+      <c r="FD669" s="1"/>
+      <c r="FJ669" s="1"/>
+      <c r="FP669" s="1"/>
+      <c r="FV669" s="1"/>
+      <c r="GB669" s="1"/>
+      <c r="GH669" s="1"/>
+      <c r="GN669" s="1"/>
+      <c r="GT669" s="1"/>
+      <c r="GZ669" s="1"/>
+      <c r="HF669" s="1"/>
+      <c r="HL669" s="1"/>
+      <c r="HR669" s="1"/>
+      <c r="HX669" s="1"/>
+      <c r="ID669" s="1"/>
+      <c r="IJ669" s="1"/>
+      <c r="IP669" s="1"/>
+      <c r="IV669" s="1"/>
+      <c r="JB669" s="1"/>
+      <c r="JH669" s="1"/>
+      <c r="JN669" s="1"/>
+      <c r="JT669" s="1"/>
+      <c r="JZ669" s="1"/>
+      <c r="KF669" s="1"/>
+      <c r="KL669" s="1"/>
+      <c r="KR669" s="1"/>
+      <c r="KX669" s="1"/>
+      <c r="LD669" s="1"/>
+      <c r="LJ669" s="1"/>
+      <c r="LP669" s="1"/>
+      <c r="LV669" s="1"/>
+      <c r="MB669" s="1"/>
+      <c r="MH669" s="1"/>
+      <c r="MN669" s="1"/>
+      <c r="MT669" s="1"/>
+      <c r="MZ669" s="1"/>
+      <c r="NF669" s="1"/>
+      <c r="NL669" s="1"/>
+      <c r="NR669" s="1"/>
+      <c r="NX669" s="1"/>
+      <c r="OD669" s="1"/>
+      <c r="OJ669" s="1"/>
+      <c r="OP669" s="1"/>
+      <c r="OV669" s="1"/>
+      <c r="PB669" s="1"/>
+      <c r="PH669" s="1"/>
+      <c r="PN669" s="1"/>
+      <c r="PT669" s="1"/>
+      <c r="PZ669" s="1"/>
+      <c r="QF669" s="1"/>
+      <c r="QL669" s="1"/>
+      <c r="QR669" s="1"/>
+      <c r="QX669" s="1"/>
+      <c r="RD669" s="1"/>
+      <c r="RJ669" s="1"/>
+      <c r="RP669" s="1"/>
+      <c r="RV669" s="1"/>
+      <c r="SB669" s="1"/>
+      <c r="SH669" s="1"/>
+      <c r="SN669" s="1"/>
+      <c r="ST669" s="1"/>
+      <c r="SZ669" s="1"/>
+      <c r="TF669" s="1"/>
+      <c r="TL669" s="1"/>
+      <c r="TR669" s="1"/>
+      <c r="TX669" s="1"/>
+      <c r="UD669" s="1"/>
+      <c r="UJ669" s="1"/>
+      <c r="UP669" s="1"/>
+      <c r="UV669" s="1"/>
+      <c r="VB669" s="1"/>
+      <c r="VH669" s="1"/>
+      <c r="VN669" s="1"/>
+      <c r="VT669" s="1"/>
+      <c r="VZ669" s="1"/>
+      <c r="WF669" s="1"/>
+      <c r="WL669" s="1"/>
+      <c r="WR669" s="1"/>
+      <c r="WX669" s="1"/>
+      <c r="XD669" s="1"/>
+      <c r="XJ669" s="1"/>
+      <c r="XP669" s="1"/>
+      <c r="XV669" s="1"/>
+      <c r="YB669" s="1"/>
+      <c r="YH669" s="1"/>
+      <c r="YN669" s="1"/>
+      <c r="YT669" s="1"/>
+      <c r="YZ669" s="1"/>
+      <c r="ZF669" s="1"/>
+      <c r="ZL669" s="1"/>
+      <c r="ZR669" s="1"/>
+      <c r="ZX669" s="1"/>
+      <c r="AAD669" s="1"/>
+      <c r="AAJ669" s="1"/>
+      <c r="AAP669" s="1"/>
+      <c r="AAV669" s="1"/>
+      <c r="ABB669" s="1"/>
+      <c r="ABH669" s="1"/>
+      <c r="ABN669" s="1"/>
+      <c r="ABT669" s="1"/>
+      <c r="ABZ669" s="1"/>
+      <c r="ACF669" s="1"/>
+      <c r="ACL669" s="1"/>
+      <c r="ACR669" s="1"/>
+      <c r="ACX669" s="1"/>
+      <c r="ADD669" s="1"/>
+      <c r="ADJ669" s="1"/>
+      <c r="ADP669" s="1"/>
+      <c r="ADV669" s="1"/>
+      <c r="AEB669" s="1"/>
+      <c r="AEH669" s="1"/>
+      <c r="AEN669" s="1"/>
+      <c r="AET669" s="1"/>
+      <c r="AEZ669" s="1"/>
+      <c r="AFF669" s="1"/>
+      <c r="AFL669" s="1"/>
+      <c r="AFR669" s="1"/>
+      <c r="AFX669" s="1"/>
+      <c r="AGD669" s="1"/>
+      <c r="AGJ669" s="1"/>
+      <c r="AGP669" s="1"/>
+      <c r="AGV669" s="1"/>
+      <c r="AHB669" s="1"/>
+      <c r="AHH669" s="1"/>
+      <c r="AHN669" s="1"/>
+      <c r="AHT669" s="1"/>
+      <c r="AHZ669" s="1"/>
+      <c r="AIF669" s="1"/>
+      <c r="AIL669" s="1"/>
+      <c r="AIR669" s="1"/>
+      <c r="AIX669" s="1"/>
+      <c r="AJD669" s="1"/>
+      <c r="AJJ669" s="1"/>
+      <c r="AJP669" s="1"/>
+      <c r="AJV669" s="1"/>
+      <c r="AKB669" s="1"/>
+      <c r="AKH669" s="1"/>
+      <c r="AKN669" s="1"/>
+      <c r="AKT669" s="1"/>
+      <c r="AKZ669" s="1"/>
+      <c r="ALF669" s="1"/>
+      <c r="ALL669" s="1"/>
+      <c r="ALR669" s="1"/>
+      <c r="ALX669" s="1"/>
+      <c r="AMD669" s="1"/>
+      <c r="AMJ669" s="1"/>
+    </row>
+    <row r="670" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A670" s="0" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B670" s="0" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C670" s="0" t="s">
+        <v>1344</v>
+      </c>
+      <c r="J670" s="1"/>
+      <c r="P670" s="1"/>
+      <c r="V670" s="1"/>
+      <c r="AB670" s="1"/>
+      <c r="AH670" s="1"/>
+      <c r="AN670" s="1"/>
+      <c r="AT670" s="1"/>
+      <c r="AZ670" s="1"/>
+      <c r="BF670" s="1"/>
+      <c r="BL670" s="1"/>
+      <c r="BR670" s="1"/>
+      <c r="BX670" s="1"/>
+      <c r="CD670" s="1"/>
+      <c r="CJ670" s="1"/>
+      <c r="CP670" s="1"/>
+      <c r="CV670" s="1"/>
+      <c r="DB670" s="1"/>
+      <c r="DH670" s="1"/>
+      <c r="DN670" s="1"/>
+      <c r="DT670" s="1"/>
+      <c r="DZ670" s="1"/>
+      <c r="EF670" s="1"/>
+      <c r="EL670" s="1"/>
+      <c r="ER670" s="1"/>
+      <c r="EX670" s="1"/>
+      <c r="FD670" s="1"/>
+      <c r="FJ670" s="1"/>
+      <c r="FP670" s="1"/>
+      <c r="FV670" s="1"/>
+      <c r="GB670" s="1"/>
+      <c r="GH670" s="1"/>
+      <c r="GN670" s="1"/>
+      <c r="GT670" s="1"/>
+      <c r="GZ670" s="1"/>
+      <c r="HF670" s="1"/>
+      <c r="HL670" s="1"/>
+      <c r="HR670" s="1"/>
+      <c r="HX670" s="1"/>
+      <c r="ID670" s="1"/>
+      <c r="IJ670" s="1"/>
+      <c r="IP670" s="1"/>
+      <c r="IV670" s="1"/>
+      <c r="JB670" s="1"/>
+      <c r="JH670" s="1"/>
+      <c r="JN670" s="1"/>
+      <c r="JT670" s="1"/>
+      <c r="JZ670" s="1"/>
+      <c r="KF670" s="1"/>
+      <c r="KL670" s="1"/>
+      <c r="KR670" s="1"/>
+      <c r="KX670" s="1"/>
+      <c r="LD670" s="1"/>
+      <c r="LJ670" s="1"/>
+      <c r="LP670" s="1"/>
+      <c r="LV670" s="1"/>
+      <c r="MB670" s="1"/>
+      <c r="MH670" s="1"/>
+      <c r="MN670" s="1"/>
+      <c r="MT670" s="1"/>
+      <c r="MZ670" s="1"/>
+      <c r="NF670" s="1"/>
+      <c r="NL670" s="1"/>
+      <c r="NR670" s="1"/>
+      <c r="NX670" s="1"/>
+      <c r="OD670" s="1"/>
+      <c r="OJ670" s="1"/>
+      <c r="OP670" s="1"/>
+      <c r="OV670" s="1"/>
+      <c r="PB670" s="1"/>
+      <c r="PH670" s="1"/>
+      <c r="PN670" s="1"/>
+      <c r="PT670" s="1"/>
+      <c r="PZ670" s="1"/>
+      <c r="QF670" s="1"/>
+      <c r="QL670" s="1"/>
+      <c r="QR670" s="1"/>
+      <c r="QX670" s="1"/>
+      <c r="RD670" s="1"/>
+      <c r="RJ670" s="1"/>
+      <c r="RP670" s="1"/>
+      <c r="RV670" s="1"/>
+      <c r="SB670" s="1"/>
+      <c r="SH670" s="1"/>
+      <c r="SN670" s="1"/>
+      <c r="ST670" s="1"/>
+      <c r="SZ670" s="1"/>
+      <c r="TF670" s="1"/>
+      <c r="TL670" s="1"/>
+      <c r="TR670" s="1"/>
+      <c r="TX670" s="1"/>
+      <c r="UD670" s="1"/>
+      <c r="UJ670" s="1"/>
+      <c r="UP670" s="1"/>
+      <c r="UV670" s="1"/>
+      <c r="VB670" s="1"/>
+      <c r="VH670" s="1"/>
+      <c r="VN670" s="1"/>
+      <c r="VT670" s="1"/>
+      <c r="VZ670" s="1"/>
+      <c r="WF670" s="1"/>
+      <c r="WL670" s="1"/>
+      <c r="WR670" s="1"/>
+      <c r="WX670" s="1"/>
+      <c r="XD670" s="1"/>
+      <c r="XJ670" s="1"/>
+      <c r="XP670" s="1"/>
+      <c r="XV670" s="1"/>
+      <c r="YB670" s="1"/>
+      <c r="YH670" s="1"/>
+      <c r="YN670" s="1"/>
+      <c r="YT670" s="1"/>
+      <c r="YZ670" s="1"/>
+      <c r="ZF670" s="1"/>
+      <c r="ZL670" s="1"/>
+      <c r="ZR670" s="1"/>
+      <c r="ZX670" s="1"/>
+      <c r="AAD670" s="1"/>
+      <c r="AAJ670" s="1"/>
+      <c r="AAP670" s="1"/>
+      <c r="AAV670" s="1"/>
+      <c r="ABB670" s="1"/>
+      <c r="ABH670" s="1"/>
+      <c r="ABN670" s="1"/>
+      <c r="ABT670" s="1"/>
+      <c r="ABZ670" s="1"/>
+      <c r="ACF670" s="1"/>
+      <c r="ACL670" s="1"/>
+      <c r="ACR670" s="1"/>
+      <c r="ACX670" s="1"/>
+      <c r="ADD670" s="1"/>
+      <c r="ADJ670" s="1"/>
+      <c r="ADP670" s="1"/>
+      <c r="ADV670" s="1"/>
+      <c r="AEB670" s="1"/>
+      <c r="AEH670" s="1"/>
+      <c r="AEN670" s="1"/>
+      <c r="AET670" s="1"/>
+      <c r="AEZ670" s="1"/>
+      <c r="AFF670" s="1"/>
+      <c r="AFL670" s="1"/>
+      <c r="AFR670" s="1"/>
+      <c r="AFX670" s="1"/>
+      <c r="AGD670" s="1"/>
+      <c r="AGJ670" s="1"/>
+      <c r="AGP670" s="1"/>
+      <c r="AGV670" s="1"/>
+      <c r="AHB670" s="1"/>
+      <c r="AHH670" s="1"/>
+      <c r="AHN670" s="1"/>
+      <c r="AHT670" s="1"/>
+      <c r="AHZ670" s="1"/>
+      <c r="AIF670" s="1"/>
+      <c r="AIL670" s="1"/>
+      <c r="AIR670" s="1"/>
+      <c r="AIX670" s="1"/>
+      <c r="AJD670" s="1"/>
+      <c r="AJJ670" s="1"/>
+      <c r="AJP670" s="1"/>
+      <c r="AJV670" s="1"/>
+      <c r="AKB670" s="1"/>
+      <c r="AKH670" s="1"/>
+      <c r="AKN670" s="1"/>
+      <c r="AKT670" s="1"/>
+      <c r="AKZ670" s="1"/>
+      <c r="ALF670" s="1"/>
+      <c r="ALL670" s="1"/>
+      <c r="ALR670" s="1"/>
+      <c r="ALX670" s="1"/>
+      <c r="AMD670" s="1"/>
+      <c r="AMJ670" s="1"/>
+    </row>
+    <row r="671" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A671" s="0" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B671" s="0" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C671" s="0" t="s">
+        <v>2348</v>
+      </c>
+      <c r="J671" s="1"/>
+      <c r="P671" s="1"/>
+      <c r="V671" s="1"/>
+      <c r="AB671" s="1"/>
+      <c r="AH671" s="1"/>
+      <c r="AN671" s="1"/>
+      <c r="AT671" s="1"/>
+      <c r="AZ671" s="1"/>
+      <c r="BF671" s="1"/>
+      <c r="BL671" s="1"/>
+      <c r="BR671" s="1"/>
+      <c r="BX671" s="1"/>
+      <c r="CD671" s="1"/>
+      <c r="CJ671" s="1"/>
+      <c r="CP671" s="1"/>
+      <c r="CV671" s="1"/>
+      <c r="DB671" s="1"/>
+      <c r="DH671" s="1"/>
+      <c r="DN671" s="1"/>
+      <c r="DT671" s="1"/>
+      <c r="DZ671" s="1"/>
+      <c r="EF671" s="1"/>
+      <c r="EL671" s="1"/>
+      <c r="ER671" s="1"/>
+      <c r="EX671" s="1"/>
+      <c r="FD671" s="1"/>
+      <c r="FJ671" s="1"/>
+      <c r="FP671" s="1"/>
+      <c r="FV671" s="1"/>
+      <c r="GB671" s="1"/>
+      <c r="GH671" s="1"/>
+      <c r="GN671" s="1"/>
+      <c r="GT671" s="1"/>
+      <c r="GZ671" s="1"/>
+      <c r="HF671" s="1"/>
+      <c r="HL671" s="1"/>
+      <c r="HR671" s="1"/>
+      <c r="HX671" s="1"/>
+      <c r="ID671" s="1"/>
+      <c r="IJ671" s="1"/>
+      <c r="IP671" s="1"/>
+      <c r="IV671" s="1"/>
+      <c r="JB671" s="1"/>
+      <c r="JH671" s="1"/>
+      <c r="JN671" s="1"/>
+      <c r="JT671" s="1"/>
+      <c r="JZ671" s="1"/>
+      <c r="KF671" s="1"/>
+      <c r="KL671" s="1"/>
+      <c r="KR671" s="1"/>
+      <c r="KX671" s="1"/>
+      <c r="LD671" s="1"/>
+      <c r="LJ671" s="1"/>
+      <c r="LP671" s="1"/>
+      <c r="LV671" s="1"/>
+      <c r="MB671" s="1"/>
+      <c r="MH671" s="1"/>
+      <c r="MN671" s="1"/>
+      <c r="MT671" s="1"/>
+      <c r="MZ671" s="1"/>
+      <c r="NF671" s="1"/>
+      <c r="NL671" s="1"/>
+      <c r="NR671" s="1"/>
+      <c r="NX671" s="1"/>
+      <c r="OD671" s="1"/>
+      <c r="OJ671" s="1"/>
+      <c r="OP671" s="1"/>
+      <c r="OV671" s="1"/>
+      <c r="PB671" s="1"/>
+      <c r="PH671" s="1"/>
+      <c r="PN671" s="1"/>
+      <c r="PT671" s="1"/>
+      <c r="PZ671" s="1"/>
+      <c r="QF671" s="1"/>
+      <c r="QL671" s="1"/>
+      <c r="QR671" s="1"/>
+      <c r="QX671" s="1"/>
+      <c r="RD671" s="1"/>
+      <c r="RJ671" s="1"/>
+      <c r="RP671" s="1"/>
+      <c r="RV671" s="1"/>
+      <c r="SB671" s="1"/>
+      <c r="SH671" s="1"/>
+      <c r="SN671" s="1"/>
+      <c r="ST671" s="1"/>
+      <c r="SZ671" s="1"/>
+      <c r="TF671" s="1"/>
+      <c r="TL671" s="1"/>
+      <c r="TR671" s="1"/>
+      <c r="TX671" s="1"/>
+      <c r="UD671" s="1"/>
+      <c r="UJ671" s="1"/>
+      <c r="UP671" s="1"/>
+      <c r="UV671" s="1"/>
+      <c r="VB671" s="1"/>
+      <c r="VH671" s="1"/>
+      <c r="VN671" s="1"/>
+      <c r="VT671" s="1"/>
+      <c r="VZ671" s="1"/>
+      <c r="WF671" s="1"/>
+      <c r="WL671" s="1"/>
+      <c r="WR671" s="1"/>
+      <c r="WX671" s="1"/>
+      <c r="XD671" s="1"/>
+      <c r="XJ671" s="1"/>
+      <c r="XP671" s="1"/>
+      <c r="XV671" s="1"/>
+      <c r="YB671" s="1"/>
+      <c r="YH671" s="1"/>
+      <c r="YN671" s="1"/>
+      <c r="YT671" s="1"/>
+      <c r="YZ671" s="1"/>
+      <c r="ZF671" s="1"/>
+      <c r="ZL671" s="1"/>
+      <c r="ZR671" s="1"/>
+      <c r="ZX671" s="1"/>
+      <c r="AAD671" s="1"/>
+      <c r="AAJ671" s="1"/>
+      <c r="AAP671" s="1"/>
+      <c r="AAV671" s="1"/>
+      <c r="ABB671" s="1"/>
+      <c r="ABH671" s="1"/>
+      <c r="ABN671" s="1"/>
+      <c r="ABT671" s="1"/>
+      <c r="ABZ671" s="1"/>
+      <c r="ACF671" s="1"/>
+      <c r="ACL671" s="1"/>
+      <c r="ACR671" s="1"/>
+      <c r="ACX671" s="1"/>
+      <c r="ADD671" s="1"/>
+      <c r="ADJ671" s="1"/>
+      <c r="ADP671" s="1"/>
+      <c r="ADV671" s="1"/>
+      <c r="AEB671" s="1"/>
+      <c r="AEH671" s="1"/>
+      <c r="AEN671" s="1"/>
+      <c r="AET671" s="1"/>
+      <c r="AEZ671" s="1"/>
+      <c r="AFF671" s="1"/>
+      <c r="AFL671" s="1"/>
+      <c r="AFR671" s="1"/>
+      <c r="AFX671" s="1"/>
+      <c r="AGD671" s="1"/>
+      <c r="AGJ671" s="1"/>
+      <c r="AGP671" s="1"/>
+      <c r="AGV671" s="1"/>
+      <c r="AHB671" s="1"/>
+      <c r="AHH671" s="1"/>
+      <c r="AHN671" s="1"/>
+      <c r="AHT671" s="1"/>
+      <c r="AHZ671" s="1"/>
+      <c r="AIF671" s="1"/>
+      <c r="AIL671" s="1"/>
+      <c r="AIR671" s="1"/>
+      <c r="AIX671" s="1"/>
+      <c r="AJD671" s="1"/>
+      <c r="AJJ671" s="1"/>
+      <c r="AJP671" s="1"/>
+      <c r="AJV671" s="1"/>
+      <c r="AKB671" s="1"/>
+      <c r="AKH671" s="1"/>
+      <c r="AKN671" s="1"/>
+      <c r="AKT671" s="1"/>
+      <c r="AKZ671" s="1"/>
+      <c r="ALF671" s="1"/>
+      <c r="ALL671" s="1"/>
+      <c r="ALR671" s="1"/>
+      <c r="ALX671" s="1"/>
+      <c r="AMD671" s="1"/>
+      <c r="AMJ671" s="1"/>
+    </row>
+    <row r="675" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A675" s="2"/>
+      <c r="B675" s="2"/>
+      <c r="C675" s="2"/>
+    </row>
+    <row r="676" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A676" s="2"/>
+      <c r="B676" s="2"/>
+      <c r="C676" s="2"/>
+    </row>
+    <row r="677" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A677" s="2"/>
+      <c r="B677" s="2"/>
+      <c r="C677" s="2"/>
+    </row>
+    <row r="678" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A678" s="2"/>
+      <c r="B678" s="2"/>
+      <c r="C678" s="2"/>
+    </row>
+    <row r="679" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A679" s="2"/>
+      <c r="B679" s="2"/>
+      <c r="C679" s="2"/>
+    </row>
+    <row r="680" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A680" s="2"/>
+      <c r="B680" s="2"/>
+      <c r="C680" s="2"/>
+    </row>
+    <row r="681" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A681" s="3"/>
+      <c r="B681" s="3"/>
+      <c r="C681" s="3"/>
+    </row>
+    <row r="682" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A682" s="2"/>
+      <c r="B682" s="2"/>
+      <c r="C682" s="2"/>
+    </row>
+    <row r="683" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A683" s="2"/>
+      <c r="B683" s="2"/>
+      <c r="C683" s="2"/>
+    </row>
+    <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A684" s="2"/>
+      <c r="B684" s="2"/>
+      <c r="C684" s="2"/>
+    </row>
+    <row r="685" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A685" s="3"/>
+      <c r="B685" s="3"/>
+      <c r="C685" s="3"/>
+    </row>
+    <row r="686" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A686" s="2"/>
+      <c r="B686" s="2"/>
+      <c r="C686" s="2"/>
+    </row>
+    <row r="687" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A687" s="2"/>
+      <c r="B687" s="2"/>
+      <c r="C687" s="2"/>
+    </row>
+    <row r="688" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A688" s="3"/>
+      <c r="B688" s="3"/>
+      <c r="C688" s="3"/>
+    </row>
+    <row r="689" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A689" s="2"/>
+      <c r="B689" s="2"/>
+      <c r="C689" s="2"/>
+    </row>
+    <row r="690" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A690" s="2"/>
+      <c r="B690" s="2"/>
+      <c r="C690" s="2"/>
+    </row>
+    <row r="691" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A691" s="2"/>
+      <c r="B691" s="2"/>
+      <c r="C691" s="2"/>
+    </row>
+    <row r="692" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A692" s="2"/>
+      <c r="B692" s="2"/>
+      <c r="C692" s="2"/>
+    </row>
+    <row r="693" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A693" s="3"/>
+      <c r="B693" s="3"/>
+      <c r="C693" s="3"/>
+    </row>
+    <row r="694" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A694" s="2"/>
+      <c r="B694" s="2"/>
+      <c r="C694" s="2"/>
+    </row>
+    <row r="695" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A695" s="2"/>
+      <c r="B695" s="2"/>
+      <c r="C695" s="2"/>
+    </row>
+    <row r="696" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A696" s="2"/>
+      <c r="B696" s="2"/>
+      <c r="C696" s="2"/>
+    </row>
+    <row r="697" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A697" s="2"/>
+      <c r="B697" s="2"/>
+      <c r="C697" s="2"/>
+    </row>
+    <row r="698" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A698" s="3"/>
+      <c r="B698" s="3"/>
+      <c r="C698" s="3"/>
+    </row>
+    <row r="699" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A699" s="2"/>
+      <c r="B699" s="2"/>
+      <c r="C699" s="2"/>
+    </row>
+    <row r="700" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A700" s="3"/>
+      <c r="B700" s="3"/>
+      <c r="C700" s="3"/>
+    </row>
+    <row r="701" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A701" s="2"/>
+      <c r="B701" s="2"/>
+      <c r="C701" s="2"/>
+    </row>
+    <row r="702" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A702" s="2"/>
+      <c r="B702" s="2"/>
+      <c r="C702" s="2"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>

--- a/multi.xlsx
+++ b/multi.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2697" uniqueCount="2354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="2361">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -7110,9 +7110,9 @@
 DESCRIPCION,PESO modificando ambos campos
 ,PESO manteniendo descripción
 • Sin IA: Comidas precargadas y actividad física:
-*DESAYUNO: menú completo
-*PIZZA (porcion),4: 4 porciones de pizza
-*TORTA (fraccion x 100g),1.5: 150 g de torta
+- DESAYUNO: menú completo
+- PIZZA (porcion),4: 4 porciones de pizza
+- TORTA (fraccion x 100g),1.5: 150 g de torta
 📌 Métodos de Registro de actividades:
 • Con IA: Texto, 🎤 Notas de voz.
 • Modificación parcial: Editar ingresando calorias
@@ -7150,9 +7150,9 @@
 DESCRIPTION,WEIGHT modifying both fields
 ,WEIGHT keeping description
 • Without AI: Preloaded meals and physical activity:
-*BREAKFAST: full menu
-*PIZZA (portion),4: 4 pizza portions
-*CAKE (fraction x 100g),1.5: 150 g of cake
+- BREAKFAST: full menu
+- PIZZA (portion),4: 4 pizza portions
+- CAKE (fraction x 100g),1.5: 150 g of cake
 📌 Activity Registration Methods:
 • With AI: Text, 🎤 Voice notes.
 • Partial modification: Edit by entering calories.
@@ -7160,6 +7160,27 @@
 • With AI: 📸 Photos.
 • Confirmation: entering clarifying note.
 📄 Attached is the complete User Manual in PDF format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inf_diario_momento_desayuno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inf_diario_momento_almuerzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inf_diario_momento_merienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inf_diario_momento_cena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inf_diario_momento_actividad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actividad Física</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Activity</t>
   </si>
 </sst>
 </file>
@@ -7267,15 +7288,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7407,7 +7428,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="67.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="67.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="12.71"/>
   </cols>
   <sheetData>
@@ -16952,7 +16973,7 @@
       <c r="AMD667" s="2"/>
       <c r="AMJ667" s="2"/>
     </row>
-    <row r="668" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="668" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
         <v>2339</v>
       </c>
@@ -17687,51 +17708,93 @@
         <v>2351</v>
       </c>
     </row>
-    <row r="673" customFormat="false" ht="2017.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A673" s="5" t="s">
+    <row r="673" customFormat="false" ht="1670.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A673" s="4" t="s">
         <v>1241</v>
       </c>
-      <c r="B673" s="5" t="s">
+      <c r="B673" s="3" t="s">
         <v>2352</v>
       </c>
-      <c r="C673" s="5" t="s">
+      <c r="C673" s="3" t="s">
         <v>2353</v>
       </c>
     </row>
     <row r="674" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A674" s="3"/>
-      <c r="B674" s="3"/>
-      <c r="C674" s="3"/>
+      <c r="A674" s="5" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B674" s="6" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C674" s="6" t="s">
+        <v>2178</v>
+      </c>
     </row>
     <row r="675" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A675" s="3"/>
-      <c r="B675" s="3"/>
-      <c r="C675" s="3"/>
+      <c r="A675" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B675" s="6" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C675" s="6" t="s">
+        <v>2182</v>
+      </c>
     </row>
     <row r="676" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A676" s="3"/>
-      <c r="B676" s="3"/>
-      <c r="C676" s="3"/>
+      <c r="A676" s="5" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B676" s="6" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C676" s="6" t="s">
+        <v>2186</v>
+      </c>
     </row>
     <row r="677" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A677" s="3"/>
-      <c r="B677" s="3"/>
-      <c r="C677" s="3"/>
+      <c r="A677" s="5" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B677" s="6" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C677" s="6" t="s">
+        <v>2190</v>
+      </c>
     </row>
     <row r="678" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A678" s="3"/>
-      <c r="B678" s="3"/>
-      <c r="C678" s="3"/>
-    </row>
-    <row r="679" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A679" s="3"/>
-      <c r="B679" s="3"/>
-      <c r="C679" s="3"/>
-    </row>
-    <row r="680" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A680" s="6"/>
-      <c r="B680" s="6"/>
-      <c r="C680" s="6"/>
+      <c r="A678" s="5" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B678" s="6" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C678" s="6" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="679" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A679" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B679" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="C679" s="6" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="680" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A680" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B680" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C680" s="6" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="681" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A681" s="3"/>
@@ -17744,14 +17807,14 @@
       <c r="C682" s="3"/>
     </row>
     <row r="683" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A683" s="3"/>
-      <c r="B683" s="3"/>
-      <c r="C683" s="3"/>
+      <c r="A683" s="4"/>
+      <c r="B683" s="4"/>
+      <c r="C683" s="4"/>
     </row>
     <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A684" s="6"/>
-      <c r="B684" s="6"/>
-      <c r="C684" s="6"/>
+      <c r="A684" s="3"/>
+      <c r="B684" s="3"/>
+      <c r="C684" s="3"/>
     </row>
     <row r="685" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A685" s="3"/>
@@ -17759,14 +17822,14 @@
       <c r="C685" s="3"/>
     </row>
     <row r="686" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A686" s="3"/>
-      <c r="B686" s="3"/>
-      <c r="C686" s="3"/>
+      <c r="A686" s="4"/>
+      <c r="B686" s="4"/>
+      <c r="C686" s="4"/>
     </row>
     <row r="687" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A687" s="6"/>
-      <c r="B687" s="6"/>
-      <c r="C687" s="6"/>
+      <c r="A687" s="3"/>
+      <c r="B687" s="3"/>
+      <c r="C687" s="3"/>
     </row>
     <row r="688" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A688" s="3"/>
@@ -17784,14 +17847,14 @@
       <c r="C690" s="3"/>
     </row>
     <row r="691" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A691" s="3"/>
-      <c r="B691" s="3"/>
-      <c r="C691" s="3"/>
+      <c r="A691" s="4"/>
+      <c r="B691" s="4"/>
+      <c r="C691" s="4"/>
     </row>
     <row r="692" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A692" s="6"/>
-      <c r="B692" s="6"/>
-      <c r="C692" s="6"/>
+      <c r="A692" s="3"/>
+      <c r="B692" s="3"/>
+      <c r="C692" s="3"/>
     </row>
     <row r="693" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A693" s="3"/>
@@ -17809,35 +17872,31 @@
       <c r="C695" s="3"/>
     </row>
     <row r="696" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A696" s="3"/>
-      <c r="B696" s="3"/>
-      <c r="C696" s="3"/>
+      <c r="A696" s="4"/>
+      <c r="B696" s="4"/>
+      <c r="C696" s="4"/>
     </row>
     <row r="697" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A697" s="6"/>
-      <c r="B697" s="6"/>
-      <c r="C697" s="6"/>
+      <c r="A697" s="3"/>
+      <c r="B697" s="3"/>
+      <c r="C697" s="3"/>
     </row>
     <row r="698" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A698" s="3"/>
-      <c r="B698" s="3"/>
-      <c r="C698" s="3"/>
+      <c r="A698" s="4"/>
+      <c r="B698" s="4"/>
+      <c r="C698" s="4"/>
     </row>
     <row r="699" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A699" s="6"/>
-      <c r="B699" s="6"/>
-      <c r="C699" s="6"/>
+      <c r="A699" s="3"/>
+      <c r="B699" s="3"/>
+      <c r="C699" s="3"/>
     </row>
     <row r="700" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
     </row>
-    <row r="701" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A701" s="3"/>
-      <c r="B701" s="3"/>
-      <c r="C701" s="3"/>
-    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/multi.xlsx
+++ b/multi.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="2361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2868" uniqueCount="2474">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -7071,15 +7071,6 @@
   </si>
   <si>
     <t xml:space="preserve">⚠️ Account disabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de la Variable (variables / key)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor en Español (es)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor en Inglés (en)</t>
   </si>
   <si>
     <t xml:space="preserve">👋 ¡Bienvenido a tu Bot Nutricional Personalizado!
@@ -7181,6 +7172,402 @@
   </si>
   <si>
     <t xml:space="preserve">Physical Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👋 ¡Bienvenido a tu Bot Nutricional Personalizado!
+Guía rápida de comandos e ingestas disponibles:
+📌 Comandos Principales:
+• /inicio: Resumen de los comandos y PDF del manual.
+• /alta: Apertura de cuenta ingresando los datos.
+• /presi: Registro y consulta de presión arterial.
+/presi 120,80,70,nota (Completo)
+/presi 120,80,70 (Sin nota)
+/presi 120,80 (Solo presión)
+/presi AAAA-MM Promedio mensual y PDF.
+• /diario: Ingestas del día, detalle nutricional y PDF.
+• /semanal: Estadística semanal (calorías, fibras, etc.).
+• /mensual: Reporte con estimación de peso y PDF.
+• /perfil: Actualización de datos biométricos.
+• /peso: Actualiza el peso del mes (/peso 90).
+• /GET: Actualiza el gasto calórico total (/GET 2150).
+• /eliminar: Borra ingestas seleccionando día.
+• /barra: Ingreso por código de barras (/barra Número).
+• /comidas: Listado predeterminadas y PDF.
+• /receta: Calculadora Web para registrar comidas.
+• /borracomida: Borra comidas de la planilla.
+📌 Métodos de Registro de Ingestas:
+• Con IA: Texto, 🎤 Notas de voz, 📸 Fotos.
+• Sin IA: Comidas precargadas y actividad física.
+📄 Te adjuntamos el Manual de Usuario completo en formato PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👋 Welcome to your Personalized Nutritional Bot!
+Quick guide of available commands and intakes:
+📌 Main Commands:
+• /start: Summary of commands and manual PDF.
+• /alta: Account opening by entering data.
+• /presi: Blood pressure registration and consultation.
+/presi 120,80,70,note (Complete)
+/presi 120,80,70 (Without note)
+/presi 120,80 (Pressure only)
+/presi YYYY-MM Monthly average and PDF.
+• /day: Daily food intake nutritional detail and PDF.
+• /week: Weekly statistics (calories, fiber, etc.).
+• /month: Report with weight estimation and PDF.
+• /perfil: Update biometric data.
+• /peso: Update monthly weight (/peso 90).
+• /GET: Update total caloric expenditure (/GET 2150).
+• /eliminar: Delete intakes by selecting a day.
+• /barra: Barcode entry (/barra Number).
+• /comidas: Default list and PDF.
+• /receta: Web calculator to log meals.
+• /borracomida: Delete meals from the sheet.
+📌 Intake Registration Methods:
+• With AI: Text, 🎤 Voice notes, 📸 Photos.
+• Without AI: Preloaded meals and physical activity.
+📄 Attached is the complete User Manual in PDF format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_alta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comando /inicio (/start): Permite iniciar el proceso de apertura de cuenta y creación de ficha nutricional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Command /start (/inicio): Initiates account creation and nutritional profile setup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_prof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID de Profesional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_prof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validación del Profesional: Ingresar el ID de Telegram del profesional autorizado para asociar y validar la cuenta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Validation: Enter the authorized professional's Telegram ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre y Apellido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificación: Ingresar el nombre o apodo con el que figurará el paciente en el sistema (mínimo 2 caracteres).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identification: Enter patient name or nickname (minimum 2 characters).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_edad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_edad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edad en años: Ingresar un valor numérico válido entre 10 y 110 años.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age in years: Enter a valid numeric value between 10 and 110 years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_sexo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sexo Biológico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biological Sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_sexo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selección por Botón: Elegir entre Masculino (M) o Femenino (F) mediante el teclado interactivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Button Selection: Choose Male (M) or Female (F) via interactive keyboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estatura en centímetros: Ingresar altura en cm (ejemplo: 175 para 1,75 m, con un rango válido de 100 a 230 cm).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Height in cm: Enter height in cm (e.g., 175, range 100 to 230 cm).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_peso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_peso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso en kilogramos: Ingresar el peso actual en kg (ejemplo: 82.5 kg, con un rango válido de 30 a 300 kg).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight in kg: Enter current weight in kg (e.g., 82.5 kg, range 30 to 300 kg).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_cintura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_cintura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perímetro de la cintura: Ingresar la medida en cm (ejemplo: 90 cm) para calcular la contextura corporal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waist perimeter: Enter measurement in cm to calculate body build.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_cuello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_cuello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perímetro del cuello: Ingresar la medida en cm (ejemplo: 40 cm) para calcular la contextura corporal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neck perimeter: Enter measurement in cm to calculate body build.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_ocupacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocupación / Actividad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_ocupacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivel de Actividad: Seleccionar mediante botones el nivel de actividad habitual (Sedentario/Ligero, Moderado o Intenso).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity Level: Select usual activity level via buttons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_cumple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de Nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birth Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_cumple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños: Ingresar la fecha de nacimiento obligatoriamente en formato AAAA-MM-DD (ejemplo: 1985-04-12).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birthday: Enter birth date mandatory in format YYYY-MM-DD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_intensidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intensidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intensity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_intensidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ritmo de avance: Seleccionar el nivel de ritmo para la etapa (Tranquilo, Moderado o Intenso).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progress pace: Select rhythm level (Easy, Moderate, or Intense).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_cancelar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comando /cancelar: Permite abortar el proceso de alta en cualquier momento, limpiando los datos temporales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Command /cancel: Aborts signup process at any time, clearing temporary data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Intake and Activity Registration Methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_ia_texto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texto Libre: Escribí tus alimentos de forma natural detallando porciones. Detallá tu actividad física indicando tipo, duración e intensidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Text: Write your foods naturally detailing portions. Detail your physical activity indicating type, duration, and intensity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_ia_voz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notas de Voz: Dictá tu ingesta o actividad física en una nota de voz; la IA convertirá el audio a texto y procesará los datos nutricionales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voice Notes: Dictate your intake or physical activity in a voice note; AI will convert audio to text and process nutritional data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_ia_foto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotografías de Galería / Cámara: Envía una foto del plato con o sin descripción aclaratoria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gallery / Camera Photos: Send a photo of the plate with or without clarifying description.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Comandos Principales del Sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Main System Commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_barra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/barra: Ingresa un código de barras y se presenta un comestible en fracciones de 100 g.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/barra: Enters a barcode and presents an edible item in 100g fractions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_borra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/borracomida: Permite la eliminación de una comida predeterminada de la planilla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/borracomida: Allows deleting a default meal from the sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_comidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/comidas (/meals): Listado de comidas predeterminadas y descarga de PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/meals (/comidas): List of default meals and PDF download.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/diario (/day): Muestra los consumos del día y descarga el PDF detallado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/day (/diario): Shows day's consumptions and downloads detailed PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_eliminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/eliminar (/delete): Permite eliminar ingestas y actividades seleccionando el día.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/delete (/eliminar): Allows deleting intakes and activities by selecting the day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_get</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/GET: Actualiza el Gasto Energético Total mediante calorías base de 24 horas (ejemplo: /GET 2150).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/GET: Updates Total Energy Expenditure using 24-hour base calories (e.g., /GET 2150).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_inicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/inicio (/start): Presenta la guía rápida de comandos e ingresos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/start (/inicio): Presents the quick guide of commands and inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/mensual (/month): Reporte mensual, calorías, estimación de peso y PDF completo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/month (/mensual): Monthly report, calories, weight estimation, and complete PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_perfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/perfil (/profile): Muestra y gestiona los datos corporales cargados en el sistema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/profile (/perfil): Shows and manages body data loaded in the system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_peso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/peso (/weight): Actualiza el peso registrado para el mes en curso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/weight (/peso): Updates registered weight for the current month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_presi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/presi (/pressure): Registro (/presi ALTA,BAJA,PULSO,NOTA) y consulta mensual (/presi AAAA-MM).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/pressure (/presi): Registration (/presi HIGH,LOW,PULSE,NOTE) and monthly query.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_receta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/receta (/recipe): Acceso directo al módulo de calculadora web de recetas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/recipe (/receta): Direct access to the web recipe calculator module.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/semanal (/week): Estadística semanal de calorías, proteínas y macronutrientes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/week (/semanal): Weekly statistics of calories, proteins, and macronutrients.</t>
   </si>
 </sst>
 </file>
@@ -17697,205 +18084,658 @@
       <c r="AMD671" s="2"/>
       <c r="AMJ671" s="2"/>
     </row>
-    <row r="672" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="672" customFormat="false" ht="1670.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A672" s="4" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B672" s="3" t="s">
         <v>2349</v>
       </c>
-      <c r="B672" s="4" t="s">
+      <c r="C672" s="3" t="s">
         <v>2350</v>
       </c>
-      <c r="C672" s="4" t="s">
+    </row>
+    <row r="673" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A673" s="5" t="s">
         <v>2351</v>
       </c>
-    </row>
-    <row r="673" customFormat="false" ht="1670.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A673" s="4" t="s">
-        <v>1241</v>
-      </c>
-      <c r="B673" s="3" t="s">
-        <v>2352</v>
-      </c>
-      <c r="C673" s="3" t="s">
-        <v>2353</v>
+      <c r="B673" s="6" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C673" s="6" t="s">
+        <v>2178</v>
       </c>
     </row>
     <row r="674" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A674" s="5" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="B674" s="6" t="s">
-        <v>2177</v>
+        <v>2181</v>
       </c>
       <c r="C674" s="6" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="675" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A675" s="5" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="B675" s="6" t="s">
-        <v>2181</v>
+        <v>2185</v>
       </c>
       <c r="C675" s="6" t="s">
-        <v>2182</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="676" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A676" s="5" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
       <c r="B676" s="6" t="s">
-        <v>2185</v>
+        <v>2189</v>
       </c>
       <c r="C676" s="6" t="s">
-        <v>2186</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A677" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B677" s="6" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C677" s="6" t="s">
         <v>2357</v>
       </c>
-      <c r="B677" s="6" t="s">
-        <v>2189</v>
-      </c>
-      <c r="C677" s="6" t="s">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="678" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="678" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A678" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B678" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="C678" s="6" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="679" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A679" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B679" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C679" s="6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="680" customFormat="false" ht="852.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A680" s="6" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B680" s="6" t="s">
         <v>2358</v>
       </c>
-      <c r="B678" s="6" t="s">
+      <c r="C680" s="6" t="s">
         <v>2359</v>
       </c>
-      <c r="C678" s="6" t="s">
+    </row>
+    <row r="681" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A681" s="6" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B681" s="6" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C681" s="6" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="682" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A682" s="6" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B682" s="6" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C682" s="6" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="683" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A683" s="6" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B683" s="6" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C683" s="6" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A684" s="6" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B684" s="6" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C684" s="6" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="685" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A685" s="6" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B685" s="6" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C685" s="6" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="686" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A686" s="6" t="s">
         <v>2360</v>
       </c>
-    </row>
-    <row r="679" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A679" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="B679" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="C679" s="6" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="680" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A680" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="B680" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="C680" s="6" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="681" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A681" s="3"/>
-      <c r="B681" s="3"/>
-      <c r="C681" s="3"/>
-    </row>
-    <row r="682" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A682" s="3"/>
-      <c r="B682" s="3"/>
-      <c r="C682" s="3"/>
-    </row>
-    <row r="683" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A683" s="4"/>
-      <c r="B683" s="4"/>
-      <c r="C683" s="4"/>
-    </row>
-    <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A684" s="3"/>
-      <c r="B684" s="3"/>
-      <c r="C684" s="3"/>
-    </row>
-    <row r="685" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A685" s="3"/>
-      <c r="B685" s="3"/>
-      <c r="C685" s="3"/>
-    </row>
-    <row r="686" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A686" s="4"/>
-      <c r="B686" s="4"/>
-      <c r="C686" s="4"/>
+      <c r="B686" s="6" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C686" s="6" t="s">
+        <v>2362</v>
+      </c>
     </row>
     <row r="687" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A687" s="3"/>
-      <c r="B687" s="3"/>
-      <c r="C687" s="3"/>
-    </row>
-    <row r="688" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A688" s="3"/>
-      <c r="B688" s="3"/>
-      <c r="C688" s="3"/>
+      <c r="A687" s="6" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B687" s="6" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C687" s="6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="688" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A688" s="6" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B688" s="6" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C688" s="6" t="s">
+        <v>2367</v>
+      </c>
     </row>
     <row r="689" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A689" s="3"/>
-      <c r="B689" s="3"/>
-      <c r="C689" s="3"/>
-    </row>
-    <row r="690" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A690" s="3"/>
-      <c r="B690" s="3"/>
-      <c r="C690" s="3"/>
+      <c r="A689" s="6" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B689" s="6" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C689" s="6" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="690" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A690" s="6" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B690" s="6" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C690" s="6" t="s">
+        <v>2373</v>
+      </c>
     </row>
     <row r="691" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A691" s="4"/>
-      <c r="B691" s="4"/>
-      <c r="C691" s="4"/>
-    </row>
-    <row r="692" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A692" s="3"/>
-      <c r="B692" s="3"/>
-      <c r="C692" s="3"/>
+      <c r="A691" s="6" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B691" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C691" s="6" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="692" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A692" s="6" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B692" s="6" t="s">
+        <v>2376</v>
+      </c>
+      <c r="C692" s="6" t="s">
+        <v>2377</v>
+      </c>
     </row>
     <row r="693" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A693" s="3"/>
-      <c r="B693" s="3"/>
-      <c r="C693" s="3"/>
-    </row>
-    <row r="694" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A694" s="3"/>
-      <c r="B694" s="3"/>
-      <c r="C694" s="3"/>
+      <c r="A693" s="6" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B693" s="6" t="s">
+        <v>2379</v>
+      </c>
+      <c r="C693" s="6" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="694" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A694" s="6" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B694" s="6" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C694" s="6" t="s">
+        <v>2383</v>
+      </c>
     </row>
     <row r="695" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A695" s="3"/>
-      <c r="B695" s="3"/>
-      <c r="C695" s="3"/>
-    </row>
-    <row r="696" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A696" s="4"/>
-      <c r="B696" s="4"/>
-      <c r="C696" s="4"/>
+      <c r="A695" s="6" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B695" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C695" s="6" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="696" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A696" s="6" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B696" s="6" t="s">
+        <v>2386</v>
+      </c>
+      <c r="C696" s="6" t="s">
+        <v>2387</v>
+      </c>
     </row>
     <row r="697" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A697" s="3"/>
-      <c r="B697" s="3"/>
-      <c r="C697" s="3"/>
-    </row>
-    <row r="698" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A698" s="4"/>
-      <c r="B698" s="4"/>
-      <c r="C698" s="4"/>
+      <c r="A697" s="6" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B697" s="6" t="s">
+        <v>2389</v>
+      </c>
+      <c r="C697" s="6" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="698" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A698" s="6" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B698" s="6" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C698" s="6" t="s">
+        <v>2393</v>
+      </c>
     </row>
     <row r="699" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A699" s="3"/>
-      <c r="B699" s="3"/>
-      <c r="C699" s="3"/>
-    </row>
-    <row r="700" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A700" s="3"/>
-      <c r="B700" s="3"/>
-      <c r="C700" s="3"/>
-    </row>
+      <c r="A699" s="6" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B699" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C699" s="6" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="700" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A700" s="6" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B700" s="6" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C700" s="6" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="701" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A701" s="6" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B701" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C701" s="6" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="702" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A702" s="6" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B702" s="6" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C702" s="6" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="703" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A703" s="6" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B703" s="6" t="s">
+        <v>2403</v>
+      </c>
+      <c r="C703" s="6" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="704" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A704" s="6" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B704" s="6" t="s">
+        <v>2406</v>
+      </c>
+      <c r="C704" s="6" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="705" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A705" s="6" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B705" s="6" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C705" s="6" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="706" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A706" s="6" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B706" s="6" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C706" s="6" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="707" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A707" s="6" t="s">
+        <v>2414</v>
+      </c>
+      <c r="B707" s="6" t="s">
+        <v>2415</v>
+      </c>
+      <c r="C707" s="6" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="708" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A708" s="6" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B708" s="6" t="s">
+        <v>2418</v>
+      </c>
+      <c r="C708" s="6" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="709" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A709" s="6" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B709" s="6" t="s">
+        <v>2421</v>
+      </c>
+      <c r="C709" s="6" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="710" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A710" s="6" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B710" s="6" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C710" s="6" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="711" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A711" s="6" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B711" s="6" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C711" s="6" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="712" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A712" s="6" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B712" s="6" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C712" s="6" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="713" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A713" s="6" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B713" s="6" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C713" s="6" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="714" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A714" s="6" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B714" s="6" t="s">
+        <v>2431</v>
+      </c>
+      <c r="C714" s="6" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="715" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A715" s="6" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B715" s="6" t="s">
+        <v>2433</v>
+      </c>
+      <c r="C715" s="6" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="716" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A716" s="6" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B716" s="6" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C716" s="6" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="717" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A717" s="6" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B717" s="6" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C717" s="6" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="718" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A718" s="6" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B718" s="6" t="s">
+        <v>2436</v>
+      </c>
+      <c r="C718" s="6" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="719" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A719" s="6" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B719" s="6" t="s">
+        <v>2439</v>
+      </c>
+      <c r="C719" s="6" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="720" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A720" s="6" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B720" s="6" t="s">
+        <v>2442</v>
+      </c>
+      <c r="C720" s="6" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="721" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A721" s="6" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B721" s="6" t="s">
+        <v>2445</v>
+      </c>
+      <c r="C721" s="6" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="722" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A722" s="6" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B722" s="6" t="s">
+        <v>2448</v>
+      </c>
+      <c r="C722" s="6" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="723" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A723" s="6" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B723" s="6" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C723" s="6" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="724" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A724" s="6" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B724" s="6" t="s">
+        <v>2454</v>
+      </c>
+      <c r="C724" s="6" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="725" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A725" s="6" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B725" s="6" t="s">
+        <v>2457</v>
+      </c>
+      <c r="C725" s="6" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="726" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A726" s="6" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B726" s="6" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C726" s="6" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="727" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A727" s="6" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B727" s="6" t="s">
+        <v>2463</v>
+      </c>
+      <c r="C727" s="6" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="728" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A728" s="6" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B728" s="6" t="s">
+        <v>2466</v>
+      </c>
+      <c r="C728" s="6" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="729" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A729" s="6" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B729" s="6" t="s">
+        <v>2469</v>
+      </c>
+      <c r="C729" s="6" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="730" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A730" s="6" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B730" s="6" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C730" s="6" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/multi.xlsx
+++ b/multi.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2868" uniqueCount="2474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2916" uniqueCount="2502">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -7568,6 +7568,90 @@
   </si>
   <si>
     <t xml:space="preserve">/week (/semanal): Weekly statistics of calories, proteins, and macronutrients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solic_nueva_altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📏 Por favor, ingresá tu nueva altura en cm (ej: 175):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📏 Please enter your new height in cm (e.g., 175):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solic_nuevo_nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👤 Por favor, ingresá tu nuevo Nombre y Apellido:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👤 Please enter your new First and Last Name:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 Please enter your new professional's Telegram ID:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎯 Seleccioná tu nuevo ritmo de dieta (1, 2 o 3):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎯 Select your new diet pace (1, 2, or 3):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solic_elegir_ocupacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏃 Seleccioná tu nuevo nivel de ocupación / actividad:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏃 Select your new occupation / activity level:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Diet pace successfully updated to {ritmo}!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perfil_error_actualizar_ritmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error al actualizar el ritmo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error updating pace.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perfil_ocupacion_actualizada_ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Ocupación actualizada correctamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Occupation successfully updated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perfil_error_actualizar_ocupacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error al actualizar la ocupación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error updating occupation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peso_consulta_actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ Peso actual registrado ({mes_actual}): {peso_actual:.1f} kg\n\nPara actualizarlo, escribí:\n/peso [nuevo_peso] (ejemplo: /peso 82.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ Current registered weight ({mes_actual}): {peso_actual:.1f} kg\n\nTo update it, type:\n/weight [new_weight] (e.g., /weight  82.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peso_no_registrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ No tenés un peso registrado para este mes.\n\nPara registrarlo, escribí:\n/peso [tu_peso] (ejemplo: /peso 82.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ You don't have a weight registered for this month.\n\nTo register it, type:\n/weight [your_weight] (e.g., /weight 82.5)</t>
   </si>
 </sst>
 </file>
@@ -18733,6 +18817,183 @@
         <v>2473</v>
       </c>
     </row>
+    <row r="731" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A731" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B731" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C731" s="6" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="732" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A732" s="6" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B732" s="6" t="s">
+        <v>2475</v>
+      </c>
+      <c r="C732" s="6" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="733" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A733" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B733" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C733" s="6" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="734" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A734" s="6" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B734" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C734" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="735" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A735" s="6" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B735" s="6" t="s">
+        <v>2478</v>
+      </c>
+      <c r="C735" s="6" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="736" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A736" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B736" s="6" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C736" s="6" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="737" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A737" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B737" s="6" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C737" s="6" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="738" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A738" s="6" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B738" s="6" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C738" s="6" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="739" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A739" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B739" s="6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C739" s="6" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="740" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A740" s="6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B740" s="6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C740" s="6" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="741" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A741" s="6" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B741" s="6" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C741" s="6" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="742" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A742" s="6" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B742" s="6" t="s">
+        <v>2491</v>
+      </c>
+      <c r="C742" s="6" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="743" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A743" s="6" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B743" s="6" t="s">
+        <v>2494</v>
+      </c>
+      <c r="C743" s="6" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="744" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A744" s="6" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B744" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C744" s="6" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="745" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A745" s="6" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B745" s="6" t="s">
+        <v>2497</v>
+      </c>
+      <c r="C745" s="6" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="746" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A746" s="6" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B746" s="6" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C746" s="6" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/multi.xlsx
+++ b/multi.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2916" uniqueCount="2502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3302" uniqueCount="2572">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -3743,18 +3743,6 @@
   </si>
   <si>
     <t xml:space="preserve">⚠️ An error occurred while saving to the database: {e}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">start_mensaje_bienvenida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👋 ¡Bienvenido a tu Bot Nutricional Personalizado!\n\nGuía rápida de comandos...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👋 Welcome to your Personalized Nutritional Bot!\n\nQuick guide to commands...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👋 Benvenuto nel tuo Bot Nutrizione Personalizzata!\n\nGuida rapida ai comandi...</t>
   </si>
   <si>
     <t xml:space="preserve">pdf_titulo_principal</t>
@@ -7071,6 +7059,681 @@
   </si>
   <si>
     <t xml:space="preserve">⚠️ Account disabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inf_diario_momento_desayuno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inf_diario_momento_almuerzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inf_diario_momento_merienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inf_diario_momento_cena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inf_diario_momento_actividad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actividad Física</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_alta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comando /inicio (/start): Permite iniciar el proceso de apertura de cuenta y creación de ficha nutricional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Command /start (/inicio): Initiates account creation and nutritional profile setup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_prof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID de Profesional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_prof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validación del Profesional: Ingresar el ID de Telegram del profesional autorizado para asociar y validar la cuenta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Validation: Enter the authorized professional's Telegram ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre y Apellido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificación: Ingresar el nombre o apodo con el que figurará el paciente en el sistema (mínimo 2 caracteres).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identification: Enter patient name or nickname (minimum 2 characters).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_edad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_edad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edad en años: Ingresar un valor numérico válido entre 10 y 110 años.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age in years: Enter a valid numeric value between 10 and 110 years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_sexo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sexo Biológico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biological Sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_sexo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selección por Botón: Elegir entre Masculino (M) o Femenino (F) mediante el teclado interactivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Button Selection: Choose Male (M) or Female (F) via interactive keyboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estatura en centímetros: Ingresar altura en cm (ejemplo: 175 para 1,75 m, con un rango válido de 100 a 230 cm).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Height in cm: Enter height in cm (e.g., 175, range 100 to 230 cm).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_peso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_peso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso en kilogramos: Ingresar el peso actual en kg (ejemplo: 82.5 kg, con un rango válido de 30 a 300 kg).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight in kg: Enter current weight in kg (e.g., 82.5 kg, range 30 to 300 kg).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_cintura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_cintura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perímetro de la cintura: Ingresar la medida en cm (ejemplo: 90 cm) para calcular la contextura corporal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waist perimeter: Enter measurement in cm to calculate body build.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_cuello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_cuello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perímetro del cuello: Ingresar la medida en cm (ejemplo: 40 cm) para calcular la contextura corporal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neck perimeter: Enter measurement in cm to calculate body build.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_ocupacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocupación / Actividad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_ocupacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivel de Actividad: Seleccionar mediante botones el nivel de actividad habitual (Sedentario/Ligero, Moderado o Intenso).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity Level: Select usual activity level via buttons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_cumple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de Nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birth Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_cumple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños: Ingresar la fecha de nacimiento obligatoriamente en formato AAAA-MM-DD (ejemplo: 1985-04-12).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birthday: Enter birth date mandatory in format YYYY-MM-DD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_lbl_intensidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intensidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intensity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_intensidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ritmo de avance: Seleccionar el nivel de ritmo para la etapa (Tranquilo, Moderado o Intenso).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progress pace: Select rhythm level (Easy, Moderate, or Intense).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_cancelar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comando /cancelar: Permite abortar el proceso de alta en cualquier momento, limpiando los datos temporales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Command /cancel: Aborts signup process at any time, clearing temporary data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Intake and Activity Registration Methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_ia_texto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texto Libre: Escribí tus alimentos de forma natural detallando porciones. Detallá tu actividad física indicando tipo, duración e intensidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Text: Write your foods naturally detailing portions. Detail your physical activity indicating type, duration, and intensity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_ia_voz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notas de Voz: Dictá tu ingesta o actividad física en una nota de voz; la IA convertirá el audio a texto y procesará los datos nutricionales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voice Notes: Dictate your intake or physical activity in a voice note; AI will convert audio to text and process nutritional data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_ia_foto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotografías de Galería / Cámara: Envía una foto del plato con o sin descripción aclaratoria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gallery / Camera Photos: Send a photo of the plate with or without clarifying description.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Comandos Principales del Sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Main System Commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_barra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/barra: Ingresa un código de barras y se presenta un comestible en fracciones de 100 g.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/barra: Enters a barcode and presents an edible item in 100g fractions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_borra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/borracomida: Permite la eliminación de una comida predeterminada de la planilla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/borracomida: Allows deleting a default meal from the sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_comidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/comidas (/meals): Listado de comidas predeterminadas y descarga de PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/meals (/comidas): List of default meals and PDF download.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/diario (/day): Muestra los consumos del día y descarga el PDF detallado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/day (/diario): Shows day's consumptions and downloads detailed PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_eliminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/eliminar (/delete): Permite eliminar ingestas y actividades seleccionando el día.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/delete (/eliminar): Allows deleting intakes and activities by selecting the day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_get</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/GET: Actualiza el Gasto Energético Total mediante calorías base de 24 horas (ejemplo: /GET 2150).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/GET: Updates Total Energy Expenditure using 24-hour base calories (e.g., /GET 2150).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_inicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/inicio (/start): Presenta la guía rápida de comandos e ingresos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/start (/inicio): Presents the quick guide of commands and inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/mensual (/month): Reporte mensual, calorías, estimación de peso y PDF completo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/month (/mensual): Monthly report, calories, weight estimation, and complete PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_perfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/perfil (/profile): Muestra y gestiona los datos corporales cargados en el sistema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/profile (/perfil): Shows and manages body data loaded in the system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_peso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/peso (/weight): Actualiza el peso registrado para el mes en curso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/weight (/peso): Updates registered weight for the current month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_presi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/presi (/pressure): Registro (/presi ALTA,BAJA,PULSO,NOTA) y consulta mensual (/presi AAAA-MM).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/pressure (/presi): Registration (/presi HIGH,LOW,PULSE,NOTE) and monthly query.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_receta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/receta (/recipe): Acceso directo al módulo de calculadora web de recetas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/recipe (/receta): Direct access to the web recipe calculator module.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_cmd_semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/semanal (/week): Estadística semanal de calorías, proteínas y macronutrientes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/week (/semanal): Weekly statistics of calories, proteins, and macronutrients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solic_nueva_altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📏 Por favor, ingresá tu nueva altura en cm (ej: 175):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📏 Please enter your new height in cm (e.g., 175):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solic_nuevo_nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👤 Por favor, ingresá tu nuevo Nombre y Apellido:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👤 Please enter your new First and Last Name:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 Please enter your new professional's Telegram ID:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎯 Seleccioná tu nuevo ritmo de dieta (1, 2 o 3):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎯 Select your new diet pace (1, 2, or 3):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solic_elegir_ocupacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏃 Seleccioná tu nuevo nivel de ocupación / actividad:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏃 Select your new occupation / activity level:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Diet pace successfully updated to {ritmo}!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perfil_error_actualizar_ritmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error al actualizar el ritmo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error updating pace.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perfil_ocupacion_actualizada_ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Ocupación actualizada correctamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Occupation successfully updated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perfil_error_actualizar_ocupacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error al actualizar la ocupación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error updating occupation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peso_consulta_actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ Peso actual registrado ({mes_actual}): {peso_actual:.1f} kg\n\nPara actualizarlo, escribí:\n/peso [nuevo_peso] (ejemplo: /peso 82.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ Current registered weight ({mes_actual}): {peso_actual:.1f} kg\n\nTo update it, type:\n/weight [new_weight] (e.g., /weight  82.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peso_no_registrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ No tenés un peso registrado para este mes.\n\nPara registrarlo, escribí:\n/peso [tu_peso] (ejemplo: /peso 82.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ You don't have a weight registered for this month.\n\nTo register it, type:\n/weight [your_weight] (e.g., /weight 82.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comando de Inicio de Registro: Permite iniciar el proceso de apertura de cuenta y creación de ficha nutricional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registration Start Command: Initiates the account opening and nutritional profile creation process.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Validation: Enter the authorized professional's Telegram ID to link and validate the account.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name and Surname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identification: Enter the name or nickname under which the patient will appear in the system (minimum 2 characters).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age in years: Enter a valid numerical value between 10 and 110 years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Button Selection: Choose between Male (M) or Female (F) using the interactive keyboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Height in centimeters: Enter height in cm (e.g., 175 for 1.75 m, valid range 100 to 230 cm).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight in kilograms: Enter current weight in kg (e.g., 82.5 kg, valid range 30 to 300 kg).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waist perimeter: Enter measurement in cm (e.g., 90 cm) to calculate body frame.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neck perimeter: Enter measurement in cm (e.g., 40 cm) to calculate body frame.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupation / Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity Level: Select habitual activity level via buttons (Sedentary/Light, Moderate, or Intense).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date of Birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birthday: Mandatory date of birth entry in format YYYY-MM-DD (e.g., 1985-04-12).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pace/Rhythm: Select the stage pace level (Steady, Moderate, or Intense).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancelar Registro: Permite abortar el proceso de alta en cualquier momento, limpiando los datos temporales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel Registration: Aborts the registration process at any time and clears temporary data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Text: Write your meals naturally detailing portions. Detail physical activity indicating type, duration, and intensity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voice Notes: Dictate your intake or activity via voice note; AI will convert audio to text and process nutritional data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_ia_edicion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proceso de Edición y Confirmación de ingestas:• Momento: Desayuno, Almuerzo, Merienda o Cena.• Edición parcial: Seleccioná ítem por ítem enviando una nueva descripción, ,nuevo peso o nueva descripción,nuevo peso.• Fecha y Guardado: Confirmá la fecha del consumo para asentar en tu planilla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intake Editing &amp; Confirmation Process:• Meal Time: Breakfast, Lunch, Snack, or Dinner.• Partial Edit: Select item by item sending a new description, ,new weight, or new description,new weight.• Date &amp; Save: Confirm consumption date to record in your spreadsheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_ia_actividad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proceso de Edición y Confirmación de actividades:• Momento: Actividad.• Edición parcial: Ingresar un nuevo valor de las calorías quemadas.• Fecha y Guardado: Confirmá para asentar en tu planilla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity Editing &amp; Confirmation Process:• Meal Time: Activity.• Partial Edit: Enter a new burned calories value.• Date &amp; Save: Confirm to record in your spreadsheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_reg_plantilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plantilla de Comidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meal Template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_plantilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• *DESAYUNO,1 Ingresa 1 unidad.• *PIZZA,4 Registra 4 porciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• *BREAKFAST,1 Logs 1 unit.• *PIZZA,4 Logs 4 portions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_reg_barra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código de barras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barcode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_desc_barra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• /barra 7790742363107Ingresá el EAN del producto para consultar fracciones de 100 g.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• /barra 7790742363107Enter product EAN to check 100g fractions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allows uploading prepared recipes or habitual food combinations directly into your personal spreadsheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_receta_ej1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ejemplo 1: Combinación (DESAYUNO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example 1: Combination (BREAKFAST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf_receta_ej2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ejemplo 2: Receta Elaborada (TORTA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example 2: Prepared Recipe (CAKE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código de barras: Ingresa un código de barras y se presenta un comestible en fracciones de 100 g.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barcode: Enter barcode to check product in 100g fractions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borra una comida: Permite la eliminación de una comida predeterminada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete meal: Allows removing a preloaded meal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planilla de comidas: Listado de comidas predeterminadas y descarga de PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meal sheet: List of preloaded meals and PDF download.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumen diario: Muestra los consumos del día y descarga el PDF detallado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily summary: Displays day's intake and detailed PDF download.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrar registros: Permite eliminar ingestas y actividades seleccionando el día.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete records: Allows deleting intakes and activities by selecting the day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasto Energético Total: Actualiza el GET mediante calorías base de 24 horas (ejemplo: /GET 2150).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Energy Expenditure: Updates TEE via 24-hour base calories (e.g., /GET 2150).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guía principal: Presenta la guía rápida de comandos e ingresos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main guide: Displays quick guide of commands and inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumen mensual: Reporte mensual, calorías, estimación de peso y PDF completo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly summary: Monthly report, calories, weight estimation, and complete PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datos biométricos: Muestra los datos corporales cargados en el sistema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biometric data: Displays body data loaded in the system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actualización del peso: Aktualiza el peso registrado para el mes en curso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight update: Updates registered weight for the current month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presión arterial: Registro (/presi ALTA,BAJA,PULSO,NOTA) y consulta mensual (/presi AAAA-MM).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood pressure: Registration (/presi HIGH,LOW,PULSE,NOTE) and monthly query (/presi YYYY-MM).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculadora nutricional: Acceso directo al módulo de recetas web.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nutritional calculator: Direct access to the web recipe module.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promedio semanal: Estadística semanal de calorías, proteínas y macronutrientes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly average: Weekly statistics of calories, proteins, and macronutrients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de la Variable (key)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor en Español (es)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor en Inglés (en)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actualización del peso: Actualiza el peso registrado para el mes en curso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start_mensaje_bienvenida</t>
   </si>
   <si>
     <t xml:space="preserve">👋 ¡Bienvenido a tu Bot Nutricional Personalizado!
@@ -7101,103 +7764,15 @@
 DESCRIPCION,PESO modificando ambos campos
 ,PESO manteniendo descripción
 • Sin IA: Comidas precargadas y actividad física:
-- DESAYUNO: menú completo
-- PIZZA (porcion),4: 4 porciones de pizza
-- TORTA (fraccion x 100g),1.5: 150 g de torta
+*DESAYUNO: menú completo
+*PIZZA (porcion),4: 4 porciones de pizza
+*TORTA (fraccion x 100g),1.5: 150 g de torta
 📌 Métodos de Registro de actividades:
 • Con IA: Texto, 🎤 Notas de voz.
 • Modificación parcial: Editar ingresando calorias
 📌 Métodos de Registro de Presion
 • Con IA: 📸 Fotos .
 • Confirmacion: ingresando nota aclaratoria
-📄 Te adjuntamos el Manual de Usuario completo en formato PDF.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👋 Welcome to your Personalized Nutritional Bot!
-Quick guide of available commands and intakes:
-📌 Main Commands:
-• /inicio: Summary of commands and manual PDF.
-• /alta: Account opening by entering data.
-• /presi: Blood pressure registration and consultation.
-/presi 120,80,70,note (Complete)
-/presi 120,80,70 (Without note)
-/presi 120,80 (Pressure only)
-/presi YYYY-MM Monthly average and PDF.
-• /diario: Daily food intake nutritional detail and PDF.
-• /semanal: Weekly statistics (calories, fiber, etc.).
-• /mensual: Report with weight estimation and PDF.
-• /perfil: Update biometric data.
-• /peso: Update monthly weight /peso 90.
-• /GET: Update total caloric expenditure /GET 2150.
-• /eliminar: Delete intakes by selecting a day.
-• /barra: Barcode entry /barra Number.
-• /comidas: Default list and PDF.
-• /receta: Web calculator to log meals.
-• /borracomida: Delete meals from the sheet.
-📌 Intake Registration Methods:
-• With AI: Text, 🎤 Voice notes, 📸 Photos.
-• Partial modification: Edit by item and resend to AI
-DESCRIPTION keeping weight
-DESCRIPTION,WEIGHT modifying both fields
-,WEIGHT keeping description
-• Without AI: Preloaded meals and physical activity:
-- BREAKFAST: full menu
-- PIZZA (portion),4: 4 pizza portions
-- CAKE (fraction x 100g),1.5: 150 g of cake
-📌 Activity Registration Methods:
-• With AI: Text, 🎤 Voice notes.
-• Partial modification: Edit by entering calories.
-📌 Blood Pressure Registration Methods
-• With AI: 📸 Photos.
-• Confirmation: entering clarifying note.
-📄 Attached is the complete User Manual in PDF format.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inf_diario_momento_desayuno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inf_diario_momento_almuerzo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inf_diario_momento_merienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inf_diario_momento_cena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inf_diario_momento_actividad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actividad Física</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical Activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👋 ¡Bienvenido a tu Bot Nutricional Personalizado!
-Guía rápida de comandos e ingestas disponibles:
-📌 Comandos Principales:
-• /inicio: Resumen de los comandos y PDF del manual.
-• /alta: Apertura de cuenta ingresando los datos.
-• /presi: Registro y consulta de presión arterial.
-/presi 120,80,70,nota (Completo)
-/presi 120,80,70 (Sin nota)
-/presi 120,80 (Solo presión)
-/presi AAAA-MM Promedio mensual y PDF.
-• /diario: Ingestas del día, detalle nutricional y PDF.
-• /semanal: Estadística semanal (calorías, fibras, etc.).
-• /mensual: Reporte con estimación de peso y PDF.
-• /perfil: Actualización de datos biométricos.
-• /peso: Actualiza el peso del mes (/peso 90).
-• /GET: Actualiza el gasto calórico total (/GET 2150).
-• /eliminar: Borra ingestas seleccionando día.
-• /barra: Ingreso por código de barras (/barra Número).
-• /comidas: Listado predeterminadas y PDF.
-• /receta: Calculadora Web para registrar comidas.
-• /borracomida: Borra comidas de la planilla.
-📌 Métodos de Registro de Ingestas:
-• Con IA: Texto, 🎤 Notas de voz, 📸 Fotos.
-• Sin IA: Comidas precargadas y actividad física.
 📄 Te adjuntamos el Manual de Usuario completo en formato PDF.</t>
   </si>
   <si>
@@ -7214,444 +7789,31 @@
 • /day: Daily food intake nutritional detail and PDF.
 • /week: Weekly statistics (calories, fiber, etc.).
 • /month: Report with weight estimation and PDF.
-• /perfil: Update biometric data.
-• /peso: Update monthly weight (/peso 90).
-• /GET: Update total caloric expenditure (/GET 2150).
-• /eliminar: Delete intakes by selecting a day.
-• /barra: Barcode entry (/barra Number).
-• /comidas: Default list and PDF.
-• /receta: Web calculator to log meals.
-• /borracomida: Delete meals from the sheet.
+• /profile: Update biometric data.
+• /weight: Update monthly weight /peso 90.
+• /GET: Update total caloric expenditure /GET 2150.
+• /delete: Delete intakes by selecting a day.
+• /barcode: Barcode entry /barcode Number.
+• /meals: Default list and PDF.
+• /recipe: Web calculator to log meals.
+• /delmeal: Delete meals from the sheet.
 📌 Intake Registration Methods:
 • With AI: Text, 🎤 Voice notes, 📸 Photos.
-• Without AI: Preloaded meals and physical activity.
+• Partial modification: Edit by item and resend to AI
+DESCRIPTION keeping weight
+DESCRIPTION,WEIGHT modifying both fields
+,WEIGHT keeping description
+• Without AI: Preloaded meals and physical activity:
+*BREAKFAST: full menu
+*PIZZA (portion),4: 4 pizza portions
+*CAKE (fraction x 100g),1.5: 150 g of cake
+📌 Activity Registration Methods:
+• With AI: Text, 🎤 Voice notes.
+• Partial modification: Edit by entering calories.
+📌 Blood Pressure Registration Methods
+• With AI: 📸 Photos.
+• Confirmation: entering clarifying note.
 📄 Attached is the complete User Manual in PDF format.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_alta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comando /inicio (/start): Permite iniciar el proceso de apertura de cuenta y creación de ficha nutricional.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Command /start (/inicio): Initiates account creation and nutritional profile setup.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_prof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID de Profesional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_prof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validación del Profesional: Ingresar el ID de Telegram del profesional autorizado para asociar y validar la cuenta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional Validation: Enter the authorized professional's Telegram ID.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre y Apellido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identificación: Ingresar el nombre o apodo con el que figurará el paciente en el sistema (mínimo 2 caracteres).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identification: Enter patient name or nickname (minimum 2 characters).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_edad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_edad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edad en años: Ingresar un valor numérico válido entre 10 y 110 años.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age in years: Enter a valid numeric value between 10 and 110 years.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_sexo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sexo Biológico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biological Sex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_sexo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selección por Botón: Elegir entre Masculino (M) o Femenino (F) mediante el teclado interactivo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Button Selection: Choose Male (M) or Female (F) via interactive keyboard.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_altura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_altura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estatura en centímetros: Ingresar altura en cm (ejemplo: 175 para 1,75 m, con un rango válido de 100 a 230 cm).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Height in cm: Enter height in cm (e.g., 175, range 100 to 230 cm).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_peso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peso Actual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_peso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peso en kilogramos: Ingresar el peso actual en kg (ejemplo: 82.5 kg, con un rango válido de 30 a 300 kg).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight in kg: Enter current weight in kg (e.g., 82.5 kg, range 30 to 300 kg).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_cintura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_cintura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perímetro de la cintura: Ingresar la medida en cm (ejemplo: 90 cm) para calcular la contextura corporal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waist perimeter: Enter measurement in cm to calculate body build.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_cuello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_cuello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perímetro del cuello: Ingresar la medida en cm (ejemplo: 40 cm) para calcular la contextura corporal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neck perimeter: Enter measurement in cm to calculate body build.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_ocupacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ocupación / Actividad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activity Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_ocupacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nivel de Actividad: Seleccionar mediante botones el nivel de actividad habitual (Sedentario/Ligero, Moderado o Intenso).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activity Level: Select usual activity level via buttons.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_cumple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de Nacimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Birth Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_cumple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumpleaños: Ingresar la fecha de nacimiento obligatoriamente en formato AAAA-MM-DD (ejemplo: 1985-04-12).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Birthday: Enter birth date mandatory in format YYYY-MM-DD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_lbl_intensidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intensidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intensity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_intensidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ritmo de avance: Seleccionar el nivel de ritmo para la etapa (Tranquilo, Moderado o Intenso).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progress pace: Select rhythm level (Easy, Moderate, or Intense).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_desc_cancelar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comando /cancelar: Permite abortar el proceso de alta en cualquier momento, limpiando los datos temporales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Command /cancel: Aborts signup process at any time, clearing temporary data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Intake and Activity Registration Methods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_ia_texto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texto Libre: Escribí tus alimentos de forma natural detallando porciones. Detallá tu actividad física indicando tipo, duración e intensidad.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Text: Write your foods naturally detailing portions. Detail your physical activity indicating type, duration, and intensity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_ia_voz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notas de Voz: Dictá tu ingesta o actividad física en una nota de voz; la IA convertirá el audio a texto y procesará los datos nutricionales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voice Notes: Dictate your intake or physical activity in a voice note; AI will convert audio to text and process nutritional data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_ia_foto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotografías de Galería / Cámara: Envía una foto del plato con o sin descripción aclaratoria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gallery / Camera Photos: Send a photo of the plate with or without clarifying description.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Comandos Principales del Sistema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Main System Commands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_barra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/barra: Ingresa un código de barras y se presenta un comestible en fracciones de 100 g.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/barra: Enters a barcode and presents an edible item in 100g fractions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_borra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/borracomida: Permite la eliminación de una comida predeterminada de la planilla.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/borracomida: Allows deleting a default meal from the sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_comidas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/comidas (/meals): Listado de comidas predeterminadas y descarga de PDF.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/meals (/comidas): List of default meals and PDF download.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_dia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/diario (/day): Muestra los consumos del día y descarga el PDF detallado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/day (/diario): Shows day's consumptions and downloads detailed PDF.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_eliminar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/eliminar (/delete): Permite eliminar ingestas y actividades seleccionando el día.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/delete (/eliminar): Allows deleting intakes and activities by selecting the day.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_get</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/GET: Actualiza el Gasto Energético Total mediante calorías base de 24 horas (ejemplo: /GET 2150).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/GET: Updates Total Energy Expenditure using 24-hour base calories (e.g., /GET 2150).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_inicio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/inicio (/start): Presenta la guía rápida de comandos e ingresos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/start (/inicio): Presents the quick guide of commands and inputs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/mensual (/month): Reporte mensual, calorías, estimación de peso y PDF completo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/month (/mensual): Monthly report, calories, weight estimation, and complete PDF.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/perfil (/profile): Muestra y gestiona los datos corporales cargados en el sistema.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/profile (/perfil): Shows and manages body data loaded in the system.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_peso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/peso (/weight): Actualiza el peso registrado para el mes en curso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/weight (/peso): Updates registered weight for the current month.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_presi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/presi (/pressure): Registro (/presi ALTA,BAJA,PULSO,NOTA) y consulta mensual (/presi AAAA-MM).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/pressure (/presi): Registration (/presi HIGH,LOW,PULSE,NOTE) and monthly query.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_receta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/receta (/recipe): Acceso directo al módulo de calculadora web de recetas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/recipe (/receta): Direct access to the web recipe calculator module.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_cmd_semana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/semanal (/week): Estadística semanal de calorías, proteínas y macronutrientes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/week (/semanal): Weekly statistics of calories, proteins, and macronutrients.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">solic_nueva_altura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📏 Por favor, ingresá tu nueva altura en cm (ej: 175):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📏 Please enter your new height in cm (e.g., 175):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">solic_nuevo_nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👤 Por favor, ingresá tu nuevo Nombre y Apellido:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👤 Please enter your new First and Last Name:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🩺 Please enter your new professional's Telegram ID:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🎯 Seleccioná tu nuevo ritmo de dieta (1, 2 o 3):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🎯 Select your new diet pace (1, 2, or 3):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">solic_elegir_ocupacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🏃 Seleccioná tu nuevo nivel de ocupación / actividad:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🏃 Select your new occupation / activity level:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✅ Diet pace successfully updated to {ritmo}!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">perfil_error_actualizar_ritmo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">❌ Error al actualizar el ritmo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">❌ Error updating pace.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">perfil_ocupacion_actualizada_ok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✅ Ocupación actualizada correctamente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✅ Occupation successfully updated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">perfil_error_actualizar_ocupacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">❌ Error al actualizar la ocupación.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">❌ Error updating occupation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peso_consulta_actual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚖️ Peso actual registrado ({mes_actual}): {peso_actual:.1f} kg\n\nPara actualizarlo, escribí:\n/peso [nuevo_peso] (ejemplo: /peso 82.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚖️ Current registered weight ({mes_actual}): {peso_actual:.1f} kg\n\nTo update it, type:\n/weight [new_weight] (e.g., /weight  82.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peso_no_registrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ No tenés un peso registrado para este mes.\n\nPara registrarlo, escribí:\n/peso [tu_peso] (ejemplo: /peso 82.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ You don't have a weight registered for this month.\n\nTo register it, type:\n/weight [your_weight] (e.g., /weight 82.5)</t>
   </si>
 </sst>
 </file>
@@ -7742,7 +7904,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7756,10 +7918,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -13029,21 +13187,21 @@
         <v>1255</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B365" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="B365" s="1" t="s">
+      <c r="C365" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="C365" s="1" t="s">
+      <c r="D365" s="2" t="s">
         <v>1259</v>
-      </c>
-      <c r="D365" s="2" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13183,49 +13341,49 @@
         <v>1298</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>1301</v>
+        <v>1257</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>1302</v>
+        <v>1258</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>1301</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>1261</v>
+        <v>86</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>1262</v>
+        <v>87</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>1263</v>
+        <v>88</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D378" s="2" t="s">
         <v>1304</v>
-      </c>
-      <c r="B378" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C378" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D378" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13261,27 +13419,27 @@
         <v>1313</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>1314</v>
+        <v>660</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>1315</v>
+        <v>1178</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>1316</v>
+        <v>662</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D382" s="2" t="s">
         <v>1317</v>
-      </c>
-      <c r="B382" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="C382" s="1" t="s">
-        <v>1178</v>
-      </c>
-      <c r="D382" s="2" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13541,41 +13699,41 @@
         <v>1390</v>
       </c>
       <c r="B401" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C401" s="1" t="s">
         <v>1391</v>
       </c>
-      <c r="C401" s="1" t="s">
-        <v>1392</v>
-      </c>
       <c r="D401" s="2" t="s">
-        <v>1393</v>
+        <v>369</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C403" s="1" t="s">
         <v>1396</v>
       </c>
-      <c r="B403" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="C403" s="1" t="s">
+      <c r="D403" s="2" t="s">
         <v>1397</v>
-      </c>
-      <c r="D403" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13754,24 +13912,24 @@
         <v>1447</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>1448</v>
+        <v>208</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>1449</v>
+        <v>209</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C417" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="B417" s="1" t="s">
+      <c r="D417" s="2" t="s">
         <v>1451</v>
-      </c>
-      <c r="C417" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D417" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13849,27 +14007,27 @@
         <v>1472</v>
       </c>
       <c r="B423" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C423" s="1" t="s">
         <v>1473</v>
       </c>
-      <c r="C423" s="1" t="s">
-        <v>1474</v>
-      </c>
       <c r="D423" s="2" t="s">
-        <v>1475</v>
+        <v>237</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C424" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="B424" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C424" s="1" t="s">
+      <c r="D424" s="2" t="s">
         <v>1477</v>
-      </c>
-      <c r="D424" s="2" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14003,27 +14161,27 @@
         <v>1514</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>1515</v>
+        <v>275</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>1516</v>
+        <v>276</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1517</v>
+        <v>277</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D435" s="2" t="s">
         <v>1518</v>
-      </c>
-      <c r="B435" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C435" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="D435" s="2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14283,125 +14441,125 @@
         <v>1591</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>1592</v>
+        <v>676</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>1593</v>
+        <v>677</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1594</v>
+        <v>678</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>684</v>
+        <v>612</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>685</v>
+        <v>612</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>684</v>
+        <v>612</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>612</v>
+        <v>688</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>612</v>
+        <v>688</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>612</v>
+        <v>689</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>693</v>
+        <v>177</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>177</v>
+        <v>699</v>
       </c>
     </row>
     <row r="462" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C462" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D462" s="2" t="s">
         <v>1602</v>
-      </c>
-      <c r="B462" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="C462" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="D462" s="2" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14667,21 +14825,21 @@
         <v>1677</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B482" s="1" t="s">
         <v>1679</v>
       </c>
-      <c r="B482" s="1" t="s">
+      <c r="C482" s="1" t="s">
         <v>1680</v>
       </c>
-      <c r="C482" s="1" t="s">
+      <c r="D482" s="2" t="s">
         <v>1681</v>
-      </c>
-      <c r="D482" s="2" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14857,125 +15015,125 @@
         <v>1730</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>1731</v>
+        <v>602</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>1732</v>
+        <v>839</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>1733</v>
+        <v>602</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>839</v>
+        <v>606</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C503" s="1" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D503" s="2" t="s">
         <v>1741</v>
-      </c>
-      <c r="B503" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="D503" s="2" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15109,27 +15267,27 @@
         <v>1778</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>1779</v>
+        <v>1699</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>1780</v>
+        <v>1700</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>1781</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C514" s="1" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D514" s="2" t="s">
         <v>1782</v>
-      </c>
-      <c r="B514" s="1" t="s">
-        <v>1703</v>
-      </c>
-      <c r="C514" s="1" t="s">
-        <v>1704</v>
-      </c>
-      <c r="D514" s="2" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15235,27 +15393,27 @@
         <v>1811</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1812</v>
+        <v>706</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>1813</v>
+        <v>707</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>1814</v>
+        <v>708</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D523" s="2" t="s">
         <v>1815</v>
-      </c>
-      <c r="B523" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="C523" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="D523" s="2" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15277,83 +15435,83 @@
         <v>1820</v>
       </c>
       <c r="B525" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="C525" s="1" t="s">
         <v>1821</v>
       </c>
-      <c r="C525" s="1" t="s">
-        <v>1822</v>
-      </c>
       <c r="D525" s="2" t="s">
-        <v>1823</v>
+        <v>720</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>718</v>
+        <v>762</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>1825</v>
+        <v>763</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>720</v>
+        <v>764</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D527" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>771</v>
+        <v>624</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C530" s="1" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D530" s="2" t="s">
         <v>1829</v>
-      </c>
-      <c r="B530" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="C530" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="D530" s="2" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15389,27 +15547,27 @@
         <v>1838</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>1839</v>
+        <v>746</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>1840</v>
+        <v>747</v>
       </c>
       <c r="D533" s="2" t="s">
-        <v>1841</v>
+        <v>748</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C534" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D534" s="2" t="s">
         <v>1842</v>
-      </c>
-      <c r="B534" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="C534" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="D534" s="2" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15417,83 +15575,83 @@
         <v>1843</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>1844</v>
+        <v>754</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>1845</v>
+        <v>755</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>1846</v>
+        <v>756</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
-        <v>1847</v>
+        <v>1844</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="D536" s="2" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>1849</v>
+        <v>1846</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D538" s="2" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>1850</v>
+        <v>1847</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>771</v>
+        <v>624</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D540" s="2" t="s">
         <v>1851</v>
-      </c>
-      <c r="B540" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="C540" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="D540" s="2" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15501,27 +15659,27 @@
         <v>1852</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>1853</v>
+        <v>1652</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>1854</v>
+        <v>1653</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>1855</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D542" s="2" t="s">
         <v>1856</v>
-      </c>
-      <c r="B542" s="1" t="s">
-        <v>1656</v>
-      </c>
-      <c r="C542" s="1" t="s">
-        <v>1657</v>
-      </c>
-      <c r="D542" s="2" t="s">
-        <v>1658</v>
       </c>
     </row>
     <row r="543" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15543,41 +15701,41 @@
         <v>1861</v>
       </c>
       <c r="B544" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C544" s="1" t="s">
         <v>1862</v>
       </c>
-      <c r="C544" s="1" t="s">
-        <v>1863</v>
-      </c>
       <c r="D544" s="2" t="s">
-        <v>1864</v>
+        <v>600</v>
       </c>
     </row>
     <row r="545" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>598</v>
+        <v>758</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>1866</v>
+        <v>759</v>
       </c>
       <c r="D545" s="2" t="s">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="546" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D546" s="2" t="s">
         <v>1867</v>
-      </c>
-      <c r="B546" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="C546" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="D546" s="2" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15686,24 +15844,24 @@
         <v>1897</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>1898</v>
+        <v>1785</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>1899</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="555" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C555" s="1" t="s">
         <v>1900</v>
       </c>
-      <c r="B555" s="1" t="s">
+      <c r="D555" s="2" t="s">
         <v>1901</v>
-      </c>
-      <c r="C555" s="1" t="s">
-        <v>1789</v>
-      </c>
-      <c r="D555" s="2" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15963,41 +16121,41 @@
         <v>1974</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1975</v>
+        <v>984</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>1976</v>
+        <v>985</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>1977</v>
+        <v>986</v>
       </c>
     </row>
     <row r="575" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="576" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C576" s="1" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D576" s="2" t="s">
         <v>1979</v>
-      </c>
-      <c r="B576" s="1" t="s">
-        <v>988</v>
-      </c>
-      <c r="C576" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="D576" s="2" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="577" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16467,27 +16625,27 @@
         <v>2112</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>2113</v>
+        <v>1503</v>
       </c>
       <c r="C610" s="1" t="s">
-        <v>2114</v>
+        <v>1504</v>
       </c>
       <c r="D610" s="2" t="s">
-        <v>2115</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="611" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="C611" s="1" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D611" s="2" t="s">
         <v>2116</v>
-      </c>
-      <c r="B611" s="1" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C611" s="1" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D611" s="2" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="612" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16596,18 +16754,18 @@
         <v>2146</v>
       </c>
       <c r="C619" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D619" s="2" t="s">
         <v>2147</v>
-      </c>
-      <c r="D619" s="2" t="s">
-        <v>2148</v>
       </c>
     </row>
     <row r="620" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B620" s="1" t="s">
         <v>2149</v>
-      </c>
-      <c r="B620" s="1" t="s">
-        <v>2150</v>
       </c>
       <c r="C620" s="1" t="s">
         <v>2150</v>
@@ -16739,21 +16897,21 @@
         <v>2186</v>
       </c>
       <c r="D629" s="2" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="630" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B630" s="1" t="s">
         <v>2188</v>
       </c>
-      <c r="B630" s="1" t="s">
+      <c r="C630" s="1" t="s">
         <v>2189</v>
       </c>
-      <c r="C630" s="1" t="s">
+      <c r="D630" s="2" t="s">
         <v>2190</v>
-      </c>
-      <c r="D630" s="2" t="s">
-        <v>2189</v>
       </c>
     </row>
     <row r="631" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17259,19 +17417,186 @@
       <c r="D666" s="2" t="s">
         <v>2334</v>
       </c>
-    </row>
-    <row r="667" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J666" s="2"/>
+      <c r="P666" s="2"/>
+      <c r="V666" s="2"/>
+      <c r="AB666" s="2"/>
+      <c r="AH666" s="2"/>
+      <c r="AN666" s="2"/>
+      <c r="AT666" s="2"/>
+      <c r="AZ666" s="2"/>
+      <c r="BF666" s="2"/>
+      <c r="BL666" s="2"/>
+      <c r="BR666" s="2"/>
+      <c r="BX666" s="2"/>
+      <c r="CD666" s="2"/>
+      <c r="CJ666" s="2"/>
+      <c r="CP666" s="2"/>
+      <c r="CV666" s="2"/>
+      <c r="DB666" s="2"/>
+      <c r="DH666" s="2"/>
+      <c r="DN666" s="2"/>
+      <c r="DT666" s="2"/>
+      <c r="DZ666" s="2"/>
+      <c r="EF666" s="2"/>
+      <c r="EL666" s="2"/>
+      <c r="ER666" s="2"/>
+      <c r="EX666" s="2"/>
+      <c r="FD666" s="2"/>
+      <c r="FJ666" s="2"/>
+      <c r="FP666" s="2"/>
+      <c r="FV666" s="2"/>
+      <c r="GB666" s="2"/>
+      <c r="GH666" s="2"/>
+      <c r="GN666" s="2"/>
+      <c r="GT666" s="2"/>
+      <c r="GZ666" s="2"/>
+      <c r="HF666" s="2"/>
+      <c r="HL666" s="2"/>
+      <c r="HR666" s="2"/>
+      <c r="HX666" s="2"/>
+      <c r="ID666" s="2"/>
+      <c r="IJ666" s="2"/>
+      <c r="IP666" s="2"/>
+      <c r="IV666" s="2"/>
+      <c r="JB666" s="2"/>
+      <c r="JH666" s="2"/>
+      <c r="JN666" s="2"/>
+      <c r="JT666" s="2"/>
+      <c r="JZ666" s="2"/>
+      <c r="KF666" s="2"/>
+      <c r="KL666" s="2"/>
+      <c r="KR666" s="2"/>
+      <c r="KX666" s="2"/>
+      <c r="LD666" s="2"/>
+      <c r="LJ666" s="2"/>
+      <c r="LP666" s="2"/>
+      <c r="LV666" s="2"/>
+      <c r="MB666" s="2"/>
+      <c r="MH666" s="2"/>
+      <c r="MN666" s="2"/>
+      <c r="MT666" s="2"/>
+      <c r="MZ666" s="2"/>
+      <c r="NF666" s="2"/>
+      <c r="NL666" s="2"/>
+      <c r="NR666" s="2"/>
+      <c r="NX666" s="2"/>
+      <c r="OD666" s="2"/>
+      <c r="OJ666" s="2"/>
+      <c r="OP666" s="2"/>
+      <c r="OV666" s="2"/>
+      <c r="PB666" s="2"/>
+      <c r="PH666" s="2"/>
+      <c r="PN666" s="2"/>
+      <c r="PT666" s="2"/>
+      <c r="PZ666" s="2"/>
+      <c r="QF666" s="2"/>
+      <c r="QL666" s="2"/>
+      <c r="QR666" s="2"/>
+      <c r="QX666" s="2"/>
+      <c r="RD666" s="2"/>
+      <c r="RJ666" s="2"/>
+      <c r="RP666" s="2"/>
+      <c r="RV666" s="2"/>
+      <c r="SB666" s="2"/>
+      <c r="SH666" s="2"/>
+      <c r="SN666" s="2"/>
+      <c r="ST666" s="2"/>
+      <c r="SZ666" s="2"/>
+      <c r="TF666" s="2"/>
+      <c r="TL666" s="2"/>
+      <c r="TR666" s="2"/>
+      <c r="TX666" s="2"/>
+      <c r="UD666" s="2"/>
+      <c r="UJ666" s="2"/>
+      <c r="UP666" s="2"/>
+      <c r="UV666" s="2"/>
+      <c r="VB666" s="2"/>
+      <c r="VH666" s="2"/>
+      <c r="VN666" s="2"/>
+      <c r="VT666" s="2"/>
+      <c r="VZ666" s="2"/>
+      <c r="WF666" s="2"/>
+      <c r="WL666" s="2"/>
+      <c r="WR666" s="2"/>
+      <c r="WX666" s="2"/>
+      <c r="XD666" s="2"/>
+      <c r="XJ666" s="2"/>
+      <c r="XP666" s="2"/>
+      <c r="XV666" s="2"/>
+      <c r="YB666" s="2"/>
+      <c r="YH666" s="2"/>
+      <c r="YN666" s="2"/>
+      <c r="YT666" s="2"/>
+      <c r="YZ666" s="2"/>
+      <c r="ZF666" s="2"/>
+      <c r="ZL666" s="2"/>
+      <c r="ZR666" s="2"/>
+      <c r="ZX666" s="2"/>
+      <c r="AAD666" s="2"/>
+      <c r="AAJ666" s="2"/>
+      <c r="AAP666" s="2"/>
+      <c r="AAV666" s="2"/>
+      <c r="ABB666" s="2"/>
+      <c r="ABH666" s="2"/>
+      <c r="ABN666" s="2"/>
+      <c r="ABT666" s="2"/>
+      <c r="ABZ666" s="2"/>
+      <c r="ACF666" s="2"/>
+      <c r="ACL666" s="2"/>
+      <c r="ACR666" s="2"/>
+      <c r="ACX666" s="2"/>
+      <c r="ADD666" s="2"/>
+      <c r="ADJ666" s="2"/>
+      <c r="ADP666" s="2"/>
+      <c r="ADV666" s="2"/>
+      <c r="AEB666" s="2"/>
+      <c r="AEH666" s="2"/>
+      <c r="AEN666" s="2"/>
+      <c r="AET666" s="2"/>
+      <c r="AEZ666" s="2"/>
+      <c r="AFF666" s="2"/>
+      <c r="AFL666" s="2"/>
+      <c r="AFR666" s="2"/>
+      <c r="AFX666" s="2"/>
+      <c r="AGD666" s="2"/>
+      <c r="AGJ666" s="2"/>
+      <c r="AGP666" s="2"/>
+      <c r="AGV666" s="2"/>
+      <c r="AHB666" s="2"/>
+      <c r="AHH666" s="2"/>
+      <c r="AHN666" s="2"/>
+      <c r="AHT666" s="2"/>
+      <c r="AHZ666" s="2"/>
+      <c r="AIF666" s="2"/>
+      <c r="AIL666" s="2"/>
+      <c r="AIR666" s="2"/>
+      <c r="AIX666" s="2"/>
+      <c r="AJD666" s="2"/>
+      <c r="AJJ666" s="2"/>
+      <c r="AJP666" s="2"/>
+      <c r="AJV666" s="2"/>
+      <c r="AKB666" s="2"/>
+      <c r="AKH666" s="2"/>
+      <c r="AKN666" s="2"/>
+      <c r="AKT666" s="2"/>
+      <c r="AKZ666" s="2"/>
+      <c r="ALF666" s="2"/>
+      <c r="ALL666" s="2"/>
+      <c r="ALR666" s="2"/>
+      <c r="ALX666" s="2"/>
+      <c r="AMD666" s="2"/>
+      <c r="AMJ666" s="2"/>
+    </row>
+    <row r="667" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A667" s="1" t="s">
         <v>2335</v>
       </c>
-      <c r="B667" s="1" t="s">
+      <c r="B667" s="3" t="s">
         <v>2336</v>
       </c>
-      <c r="C667" s="1" t="s">
+      <c r="C667" s="3" t="s">
         <v>2337</v>
-      </c>
-      <c r="D667" s="2" t="s">
-        <v>2338</v>
       </c>
       <c r="J667" s="2"/>
       <c r="P667" s="2"/>
@@ -17444,15 +17769,15 @@
       <c r="AMD667" s="2"/>
       <c r="AMJ667" s="2"/>
     </row>
-    <row r="668" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="668" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B668" s="1" t="s">
         <v>2339</v>
       </c>
-      <c r="B668" s="3" t="s">
+      <c r="C668" s="1" t="s">
         <v>2340</v>
-      </c>
-      <c r="C668" s="3" t="s">
-        <v>2341</v>
       </c>
       <c r="J668" s="2"/>
       <c r="P668" s="2"/>
@@ -17627,13 +17952,13 @@
     </row>
     <row r="669" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A669" s="1" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>2343</v>
+        <v>1339</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>2344</v>
+        <v>1340</v>
       </c>
       <c r="J669" s="2"/>
       <c r="P669" s="2"/>
@@ -17808,13 +18133,13 @@
     </row>
     <row r="670" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A670" s="1" t="s">
-        <v>2345</v>
+        <v>2342</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1343</v>
+        <v>2343</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>1344</v>
+        <v>2344</v>
       </c>
       <c r="J670" s="2"/>
       <c r="P670" s="2"/>
@@ -17988,1011 +18313,2266 @@
       <c r="AMJ670" s="2"/>
     </row>
     <row r="671" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A671" s="1" t="s">
+      <c r="A671" s="4" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B671" s="5" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C671" s="5" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="672" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A672" s="4" t="s">
         <v>2346</v>
       </c>
-      <c r="B671" s="1" t="s">
+      <c r="B672" s="5" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C672" s="5" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="673" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A673" s="4" t="s">
         <v>2347</v>
       </c>
-      <c r="C671" s="1" t="s">
+      <c r="B673" s="5" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C673" s="5" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="674" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A674" s="4" t="s">
         <v>2348</v>
       </c>
-      <c r="J671" s="2"/>
-      <c r="P671" s="2"/>
-      <c r="V671" s="2"/>
-      <c r="AB671" s="2"/>
-      <c r="AH671" s="2"/>
-      <c r="AN671" s="2"/>
-      <c r="AT671" s="2"/>
-      <c r="AZ671" s="2"/>
-      <c r="BF671" s="2"/>
-      <c r="BL671" s="2"/>
-      <c r="BR671" s="2"/>
-      <c r="BX671" s="2"/>
-      <c r="CD671" s="2"/>
-      <c r="CJ671" s="2"/>
-      <c r="CP671" s="2"/>
-      <c r="CV671" s="2"/>
-      <c r="DB671" s="2"/>
-      <c r="DH671" s="2"/>
-      <c r="DN671" s="2"/>
-      <c r="DT671" s="2"/>
-      <c r="DZ671" s="2"/>
-      <c r="EF671" s="2"/>
-      <c r="EL671" s="2"/>
-      <c r="ER671" s="2"/>
-      <c r="EX671" s="2"/>
-      <c r="FD671" s="2"/>
-      <c r="FJ671" s="2"/>
-      <c r="FP671" s="2"/>
-      <c r="FV671" s="2"/>
-      <c r="GB671" s="2"/>
-      <c r="GH671" s="2"/>
-      <c r="GN671" s="2"/>
-      <c r="GT671" s="2"/>
-      <c r="GZ671" s="2"/>
-      <c r="HF671" s="2"/>
-      <c r="HL671" s="2"/>
-      <c r="HR671" s="2"/>
-      <c r="HX671" s="2"/>
-      <c r="ID671" s="2"/>
-      <c r="IJ671" s="2"/>
-      <c r="IP671" s="2"/>
-      <c r="IV671" s="2"/>
-      <c r="JB671" s="2"/>
-      <c r="JH671" s="2"/>
-      <c r="JN671" s="2"/>
-      <c r="JT671" s="2"/>
-      <c r="JZ671" s="2"/>
-      <c r="KF671" s="2"/>
-      <c r="KL671" s="2"/>
-      <c r="KR671" s="2"/>
-      <c r="KX671" s="2"/>
-      <c r="LD671" s="2"/>
-      <c r="LJ671" s="2"/>
-      <c r="LP671" s="2"/>
-      <c r="LV671" s="2"/>
-      <c r="MB671" s="2"/>
-      <c r="MH671" s="2"/>
-      <c r="MN671" s="2"/>
-      <c r="MT671" s="2"/>
-      <c r="MZ671" s="2"/>
-      <c r="NF671" s="2"/>
-      <c r="NL671" s="2"/>
-      <c r="NR671" s="2"/>
-      <c r="NX671" s="2"/>
-      <c r="OD671" s="2"/>
-      <c r="OJ671" s="2"/>
-      <c r="OP671" s="2"/>
-      <c r="OV671" s="2"/>
-      <c r="PB671" s="2"/>
-      <c r="PH671" s="2"/>
-      <c r="PN671" s="2"/>
-      <c r="PT671" s="2"/>
-      <c r="PZ671" s="2"/>
-      <c r="QF671" s="2"/>
-      <c r="QL671" s="2"/>
-      <c r="QR671" s="2"/>
-      <c r="QX671" s="2"/>
-      <c r="RD671" s="2"/>
-      <c r="RJ671" s="2"/>
-      <c r="RP671" s="2"/>
-      <c r="RV671" s="2"/>
-      <c r="SB671" s="2"/>
-      <c r="SH671" s="2"/>
-      <c r="SN671" s="2"/>
-      <c r="ST671" s="2"/>
-      <c r="SZ671" s="2"/>
-      <c r="TF671" s="2"/>
-      <c r="TL671" s="2"/>
-      <c r="TR671" s="2"/>
-      <c r="TX671" s="2"/>
-      <c r="UD671" s="2"/>
-      <c r="UJ671" s="2"/>
-      <c r="UP671" s="2"/>
-      <c r="UV671" s="2"/>
-      <c r="VB671" s="2"/>
-      <c r="VH671" s="2"/>
-      <c r="VN671" s="2"/>
-      <c r="VT671" s="2"/>
-      <c r="VZ671" s="2"/>
-      <c r="WF671" s="2"/>
-      <c r="WL671" s="2"/>
-      <c r="WR671" s="2"/>
-      <c r="WX671" s="2"/>
-      <c r="XD671" s="2"/>
-      <c r="XJ671" s="2"/>
-      <c r="XP671" s="2"/>
-      <c r="XV671" s="2"/>
-      <c r="YB671" s="2"/>
-      <c r="YH671" s="2"/>
-      <c r="YN671" s="2"/>
-      <c r="YT671" s="2"/>
-      <c r="YZ671" s="2"/>
-      <c r="ZF671" s="2"/>
-      <c r="ZL671" s="2"/>
-      <c r="ZR671" s="2"/>
-      <c r="ZX671" s="2"/>
-      <c r="AAD671" s="2"/>
-      <c r="AAJ671" s="2"/>
-      <c r="AAP671" s="2"/>
-      <c r="AAV671" s="2"/>
-      <c r="ABB671" s="2"/>
-      <c r="ABH671" s="2"/>
-      <c r="ABN671" s="2"/>
-      <c r="ABT671" s="2"/>
-      <c r="ABZ671" s="2"/>
-      <c r="ACF671" s="2"/>
-      <c r="ACL671" s="2"/>
-      <c r="ACR671" s="2"/>
-      <c r="ACX671" s="2"/>
-      <c r="ADD671" s="2"/>
-      <c r="ADJ671" s="2"/>
-      <c r="ADP671" s="2"/>
-      <c r="ADV671" s="2"/>
-      <c r="AEB671" s="2"/>
-      <c r="AEH671" s="2"/>
-      <c r="AEN671" s="2"/>
-      <c r="AET671" s="2"/>
-      <c r="AEZ671" s="2"/>
-      <c r="AFF671" s="2"/>
-      <c r="AFL671" s="2"/>
-      <c r="AFR671" s="2"/>
-      <c r="AFX671" s="2"/>
-      <c r="AGD671" s="2"/>
-      <c r="AGJ671" s="2"/>
-      <c r="AGP671" s="2"/>
-      <c r="AGV671" s="2"/>
-      <c r="AHB671" s="2"/>
-      <c r="AHH671" s="2"/>
-      <c r="AHN671" s="2"/>
-      <c r="AHT671" s="2"/>
-      <c r="AHZ671" s="2"/>
-      <c r="AIF671" s="2"/>
-      <c r="AIL671" s="2"/>
-      <c r="AIR671" s="2"/>
-      <c r="AIX671" s="2"/>
-      <c r="AJD671" s="2"/>
-      <c r="AJJ671" s="2"/>
-      <c r="AJP671" s="2"/>
-      <c r="AJV671" s="2"/>
-      <c r="AKB671" s="2"/>
-      <c r="AKH671" s="2"/>
-      <c r="AKN671" s="2"/>
-      <c r="AKT671" s="2"/>
-      <c r="AKZ671" s="2"/>
-      <c r="ALF671" s="2"/>
-      <c r="ALL671" s="2"/>
-      <c r="ALR671" s="2"/>
-      <c r="ALX671" s="2"/>
-      <c r="AMD671" s="2"/>
-      <c r="AMJ671" s="2"/>
-    </row>
-    <row r="672" customFormat="false" ht="1670.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A672" s="4" t="s">
-        <v>1241</v>
-      </c>
-      <c r="B672" s="3" t="s">
+      <c r="B674" s="5" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C674" s="5" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="675" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A675" s="4" t="s">
         <v>2349</v>
       </c>
-      <c r="C672" s="3" t="s">
+      <c r="B675" s="5" t="s">
         <v>2350</v>
       </c>
-    </row>
-    <row r="673" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A673" s="5" t="s">
+      <c r="C675" s="5" t="s">
         <v>2351</v>
       </c>
-      <c r="B673" s="6" t="s">
-        <v>2177</v>
-      </c>
-      <c r="C673" s="6" t="s">
-        <v>2178</v>
-      </c>
-    </row>
-    <row r="674" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A674" s="5" t="s">
-        <v>2352</v>
-      </c>
-      <c r="B674" s="6" t="s">
-        <v>2181</v>
-      </c>
-      <c r="C674" s="6" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="675" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A675" s="5" t="s">
-        <v>2353</v>
-      </c>
-      <c r="B675" s="6" t="s">
-        <v>2185</v>
-      </c>
-      <c r="C675" s="6" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="676" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A676" s="5" t="s">
-        <v>2354</v>
-      </c>
-      <c r="B676" s="6" t="s">
-        <v>2189</v>
-      </c>
-      <c r="C676" s="6" t="s">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="677" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A677" s="5" t="s">
-        <v>2355</v>
-      </c>
-      <c r="B677" s="6" t="s">
-        <v>2356</v>
-      </c>
-      <c r="C677" s="6" t="s">
-        <v>2357</v>
+    </row>
+    <row r="676" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A676" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B676" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C676" s="5" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="677" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A677" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="B677" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C677" s="5" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="678" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A678" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="B678" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="C678" s="6" t="s">
-        <v>464</v>
+        <v>1241</v>
+      </c>
+      <c r="B678" s="5" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C678" s="5" t="s">
+        <v>1243</v>
       </c>
     </row>
     <row r="679" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A679" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="B679" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="C679" s="6" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="680" customFormat="false" ht="852.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A680" s="6" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B679" s="5" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C679" s="5" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="680" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A680" s="5" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B680" s="5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C680" s="5" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="681" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A681" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B681" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C681" s="5" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="682" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A682" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B682" s="5" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C682" s="5" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="683" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A683" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B683" s="5" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C683" s="5" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A684" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B684" s="5" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C684" s="5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="685" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A685" s="5" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B685" s="5" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C685" s="5" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="686" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A686" s="5" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B686" s="5" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C686" s="5" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="687" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A687" s="5" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B687" s="5" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C687" s="5" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="688" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A688" s="5" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B688" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C688" s="5" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="689" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A689" s="5" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B689" s="5" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C689" s="5" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="690" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A690" s="5" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B690" s="5" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C690" s="5" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="691" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A691" s="5" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B691" s="5" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C691" s="5" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="692" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A692" s="5" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B692" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C692" s="5" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="693" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A693" s="5" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B693" s="5" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C693" s="5" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="694" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A694" s="5" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B694" s="5" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C694" s="5" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="695" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A695" s="5" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B695" s="5" t="s">
+        <v>2384</v>
+      </c>
+      <c r="C695" s="5" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="696" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A696" s="5" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B696" s="5" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C696" s="5" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="697" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A697" s="5" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B697" s="5" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C697" s="5" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="698" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A698" s="5" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B698" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C698" s="5" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="699" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A699" s="5" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B699" s="5" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C699" s="5" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="700" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A700" s="5" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B700" s="5" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C700" s="5" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="701" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A701" s="5" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B701" s="5" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C701" s="5" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="702" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A702" s="5" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B702" s="5" t="s">
+        <v>2401</v>
+      </c>
+      <c r="C702" s="5" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="703" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A703" s="5" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B703" s="5" t="s">
+        <v>2404</v>
+      </c>
+      <c r="C703" s="5" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="704" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A704" s="5" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B704" s="5" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C704" s="5" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="705" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A705" s="5" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B705" s="5" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C705" s="5" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="706" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A706" s="5" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B706" s="5" t="s">
+        <v>2413</v>
+      </c>
+      <c r="C706" s="5" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="707" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A707" s="5" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B707" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C707" s="5" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="708" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A708" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B708" s="5" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C708" s="5" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="709" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A709" s="5" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B709" s="5" t="s">
+        <v>2417</v>
+      </c>
+      <c r="C709" s="5" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="710" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A710" s="5" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B710" s="5" t="s">
+        <v>2420</v>
+      </c>
+      <c r="C710" s="5" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="711" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A711" s="5" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B711" s="5" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C711" s="5" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="712" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A712" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B712" s="5" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C712" s="5" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="713" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A713" s="5" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B713" s="5" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C713" s="5" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="714" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A714" s="5" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B714" s="5" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C714" s="5" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="715" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A715" s="5" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B715" s="5" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C715" s="5" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="716" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A716" s="5" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B716" s="5" t="s">
+        <v>2431</v>
+      </c>
+      <c r="C716" s="5" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="717" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A717" s="5" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B717" s="5" t="s">
+        <v>2434</v>
+      </c>
+      <c r="C717" s="5" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="718" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A718" s="5" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B718" s="5" t="s">
+        <v>2437</v>
+      </c>
+      <c r="C718" s="5" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="719" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A719" s="5" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B719" s="5" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C719" s="5" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="720" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A720" s="5" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B720" s="5" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C720" s="5" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="721" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A721" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B721" s="5" t="s">
+        <v>2446</v>
+      </c>
+      <c r="C721" s="5" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="722" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A722" s="5" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B722" s="5" t="s">
+        <v>2449</v>
+      </c>
+      <c r="C722" s="5" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="723" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A723" s="5" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B723" s="5" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C723" s="5" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="724" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A724" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B724" s="5" t="s">
+        <v>2455</v>
+      </c>
+      <c r="C724" s="5" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="725" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A725" s="5" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B725" s="5" t="s">
+        <v>2458</v>
+      </c>
+      <c r="C725" s="5" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="726" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A726" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B726" s="5" t="s">
+        <v>2461</v>
+      </c>
+      <c r="C726" s="5" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="727" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A727" s="5" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B727" s="5" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C727" s="5" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="728" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A728" s="5" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B728" s="5" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C728" s="5" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="729" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A729" s="5" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B729" s="5" t="s">
+        <v>2467</v>
+      </c>
+      <c r="C729" s="5" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="730" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A730" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B730" s="5" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C730" s="5" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="731" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A731" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B731" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C731" s="5" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="732" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A732" s="5" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B732" s="5" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C732" s="5" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="733" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A733" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B733" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C733" s="5" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="734" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A734" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B734" s="5" t="s">
+        <v>2473</v>
+      </c>
+      <c r="C734" s="5" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="735" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A735" s="5" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B735" s="5" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C735" s="5" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="736" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A736" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B736" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C736" s="5" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="737" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A737" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B737" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C737" s="5" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="738" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A738" s="5" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B738" s="5" t="s">
+        <v>2480</v>
+      </c>
+      <c r="C738" s="5" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="739" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A739" s="5" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B739" s="5" t="s">
+        <v>2483</v>
+      </c>
+      <c r="C739" s="5" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="740" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A740" s="5" t="s">
+        <v>2485</v>
+      </c>
+      <c r="B740" s="5" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C740" s="5" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="741" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A741" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B741" s="5" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C741" s="5" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="742" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A742" s="5" t="s">
+        <v>2488</v>
+      </c>
+      <c r="B742" s="5" t="s">
+        <v>2489</v>
+      </c>
+      <c r="C742" s="5" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="743" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A743" s="5" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B743" s="5" t="s">
+        <v>2492</v>
+      </c>
+      <c r="C743" s="5" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="744" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A744" s="5" t="s">
         <v>1241</v>
       </c>
-      <c r="B680" s="6" t="s">
+      <c r="B744" s="5" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C744" s="5" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="745" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A745" s="5" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B745" s="5" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C745" s="5" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="746" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A746" s="5" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B746" s="5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C746" s="5" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="747" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A747" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B747" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C747" s="5" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="748" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A748" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B748" s="5" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C748" s="5" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="749" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A749" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B749" s="4" t="s">
+        <v>2494</v>
+      </c>
+      <c r="C749" s="4" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="750" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A750" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B750" s="5" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C750" s="5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="751" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A751" s="5" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B751" s="4" t="s">
         <v>2358</v>
       </c>
-      <c r="C680" s="6" t="s">
-        <v>2359</v>
-      </c>
-    </row>
-    <row r="681" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A681" s="6" t="s">
+      <c r="C751" s="4" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="752" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A752" s="5" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B752" s="5" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C752" s="5" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="753" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A753" s="5" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B753" s="4" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C753" s="4" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="754" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A754" s="5" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B754" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C754" s="5" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="755" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A755" s="5" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B755" s="4" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C755" s="4" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="756" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A756" s="5" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B756" s="5" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C756" s="5" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="757" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A757" s="5" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B757" s="4" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C757" s="4" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="758" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A758" s="5" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B758" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C758" s="5" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="759" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A759" s="5" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B759" s="4" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C759" s="4" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="760" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A760" s="5" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B760" s="5" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C760" s="5" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="761" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A761" s="5" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B761" s="4" t="s">
+        <v>2384</v>
+      </c>
+      <c r="C761" s="4" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="762" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A762" s="5" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B762" s="5" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C762" s="5" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="763" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A763" s="5" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B763" s="4" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C763" s="4" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="764" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A764" s="5" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B764" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C764" s="5" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="765" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A765" s="5" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B765" s="4" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C765" s="4" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="766" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A766" s="5" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B766" s="5" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C766" s="5" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="767" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A767" s="5" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B767" s="4" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C767" s="4" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="768" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A768" s="5" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B768" s="5" t="s">
+        <v>2401</v>
+      </c>
+      <c r="C768" s="5" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="769" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A769" s="5" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B769" s="4" t="s">
+        <v>2404</v>
+      </c>
+      <c r="C769" s="4" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="770" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A770" s="5" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B770" s="5" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C770" s="5" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="771" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A771" s="5" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B771" s="4" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C771" s="4" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="772" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A772" s="5" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B772" s="4" t="s">
+        <v>2510</v>
+      </c>
+      <c r="C772" s="4" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="773" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A773" s="5" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B773" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C773" s="5" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="774" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A774" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B774" s="5" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C774" s="5" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="775" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A775" s="5" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B775" s="4" t="s">
+        <v>2417</v>
+      </c>
+      <c r="C775" s="4" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="776" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A776" s="5" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B776" s="4" t="s">
+        <v>2420</v>
+      </c>
+      <c r="C776" s="4" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="777" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A777" s="5" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B777" s="4" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C777" s="4" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="778" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A778" s="5" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B778" s="4" t="s">
+        <v>2515</v>
+      </c>
+      <c r="C778" s="4" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="779" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A779" s="5" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B779" s="4" t="s">
+        <v>2518</v>
+      </c>
+      <c r="C779" s="4" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="780" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A780" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B780" s="5" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C780" s="5" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="781" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A781" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B781" s="5" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C781" s="5" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="782" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A782" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B782" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C782" s="5" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="783" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A783" s="5" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B783" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C783" s="5" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="784" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A784" s="5" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B784" s="4" t="s">
+        <v>2521</v>
+      </c>
+      <c r="C784" s="4" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="785" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A785" s="5" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B785" s="5" t="s">
+        <v>2524</v>
+      </c>
+      <c r="C785" s="5" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="786" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A786" s="5" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B786" s="4" t="s">
+        <v>2527</v>
+      </c>
+      <c r="C786" s="4" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="787" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A787" s="5" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B787" s="5" t="s">
+        <v>2530</v>
+      </c>
+      <c r="C787" s="5" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="788" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A788" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B788" s="5" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C788" s="5" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="789" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A789" s="5" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B789" s="5" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C789" s="5" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="790" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A790" s="5" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B790" s="5" t="s">
+        <v>2534</v>
+      </c>
+      <c r="C790" s="5" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="791" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A791" s="5" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B791" s="5" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C791" s="5" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="792" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A792" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B792" s="5" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C792" s="5" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="793" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A793" s="5" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B793" s="5" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C793" s="5" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="794" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A794" s="5" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B794" s="5" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C794" s="5" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="795" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A795" s="5" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B795" s="4" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C795" s="4" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="796" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A796" s="5" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B796" s="4" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C796" s="4" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="797" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A797" s="5" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B797" s="4" t="s">
+        <v>2543</v>
+      </c>
+      <c r="C797" s="4" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="798" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A798" s="5" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B798" s="4" t="s">
+        <v>2545</v>
+      </c>
+      <c r="C798" s="4" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="799" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A799" s="5" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B799" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="C799" s="4" t="s">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="800" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A800" s="5" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B800" s="4" t="s">
+        <v>2549</v>
+      </c>
+      <c r="C800" s="4" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="801" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A801" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B801" s="4" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C801" s="4" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="802" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A802" s="5" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B802" s="4" t="s">
+        <v>2553</v>
+      </c>
+      <c r="C802" s="4" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="803" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A803" s="5" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B803" s="4" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C803" s="4" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="804" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A804" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B804" s="4" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C804" s="4" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="805" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A805" s="5" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B805" s="4" t="s">
+        <v>2559</v>
+      </c>
+      <c r="C805" s="4" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="806" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A806" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B806" s="4" t="s">
+        <v>2561</v>
+      </c>
+      <c r="C806" s="4" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="807" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A807" s="5" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B807" s="4" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C807" s="4" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="808" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A808" s="5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B808" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C808" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="810" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A810" s="4" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B810" s="4" t="s">
+        <v>2566</v>
+      </c>
+      <c r="C810" s="4" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="811" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A811" s="5" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B811" s="5" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C811" s="5" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="812" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A812" s="5" t="s">
         <v>1245</v>
       </c>
-      <c r="B681" s="6" t="s">
+      <c r="B812" s="5" t="s">
         <v>1246</v>
       </c>
-      <c r="C681" s="6" t="s">
+      <c r="C812" s="5" t="s">
         <v>1247</v>
       </c>
     </row>
-    <row r="682" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A682" s="6" t="s">
+    <row r="813" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A813" s="5" t="s">
         <v>1249</v>
       </c>
-      <c r="B682" s="6" t="s">
+      <c r="B813" s="5" t="s">
         <v>1250</v>
       </c>
-      <c r="C682" s="6" t="s">
+      <c r="C813" s="5" t="s">
         <v>1251</v>
       </c>
     </row>
-    <row r="683" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A683" s="6" t="s">
+    <row r="814" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A814" s="5" t="s">
         <v>1253</v>
       </c>
-      <c r="B683" s="6" t="s">
+      <c r="B814" s="5" t="s">
         <v>1254</v>
       </c>
-      <c r="C683" s="6" t="s">
+      <c r="C814" s="5" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A684" s="6" t="s">
+    <row r="815" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A815" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B815" s="5" t="s">
         <v>1257</v>
       </c>
-      <c r="B684" s="6" t="s">
+      <c r="C815" s="5" t="s">
         <v>1258</v>
       </c>
-      <c r="C684" s="6" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="685" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A685" s="6" t="s">
+    </row>
+    <row r="816" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A816" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B816" s="4" t="s">
+        <v>2494</v>
+      </c>
+      <c r="C816" s="4" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="817" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A817" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B817" s="5" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C817" s="5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="818" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A818" s="5" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B818" s="4" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C818" s="4" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="819" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A819" s="5" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B819" s="5" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C819" s="5" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="820" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A820" s="5" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B820" s="4" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C820" s="4" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="821" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A821" s="5" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B821" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C821" s="5" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="822" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A822" s="5" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B822" s="4" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C822" s="4" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="823" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A823" s="5" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B823" s="5" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C823" s="5" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="824" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A824" s="5" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B824" s="4" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C824" s="4" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="825" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A825" s="5" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B825" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C825" s="5" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="826" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A826" s="5" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B826" s="4" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C826" s="4" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="827" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A827" s="5" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B827" s="5" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C827" s="5" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="828" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A828" s="5" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B828" s="4" t="s">
+        <v>2384</v>
+      </c>
+      <c r="C828" s="4" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="829" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A829" s="5" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B829" s="5" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C829" s="5" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="830" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A830" s="5" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B830" s="4" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C830" s="4" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="831" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A831" s="5" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B831" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C831" s="5" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="832" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A832" s="5" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B832" s="4" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C832" s="4" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="833" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A833" s="5" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B833" s="5" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C833" s="5" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="834" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A834" s="5" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B834" s="4" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C834" s="4" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="835" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A835" s="5" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B835" s="5" t="s">
+        <v>2401</v>
+      </c>
+      <c r="C835" s="5" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="836" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A836" s="5" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B836" s="4" t="s">
+        <v>2404</v>
+      </c>
+      <c r="C836" s="4" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="837" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A837" s="5" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B837" s="5" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C837" s="5" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="838" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A838" s="5" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B838" s="4" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C838" s="4" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="839" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A839" s="5" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B839" s="4" t="s">
+        <v>2510</v>
+      </c>
+      <c r="C839" s="4" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="840" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A840" s="5" t="s">
         <v>1260</v>
       </c>
-      <c r="B685" s="6" t="s">
+      <c r="B840" s="5" t="s">
         <v>1261</v>
       </c>
-      <c r="C685" s="6" t="s">
+      <c r="C840" s="5" t="s">
         <v>1262</v>
       </c>
     </row>
-    <row r="686" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A686" s="6" t="s">
-        <v>2360</v>
-      </c>
-      <c r="B686" s="6" t="s">
-        <v>2361</v>
-      </c>
-      <c r="C686" s="6" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="687" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A687" s="6" t="s">
-        <v>2363</v>
-      </c>
-      <c r="B687" s="6" t="s">
-        <v>2364</v>
-      </c>
-      <c r="C687" s="6" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="688" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A688" s="6" t="s">
-        <v>2365</v>
-      </c>
-      <c r="B688" s="6" t="s">
-        <v>2366</v>
-      </c>
-      <c r="C688" s="6" t="s">
-        <v>2367</v>
-      </c>
-    </row>
-    <row r="689" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A689" s="6" t="s">
-        <v>2368</v>
-      </c>
-      <c r="B689" s="6" t="s">
-        <v>2369</v>
-      </c>
-      <c r="C689" s="6" t="s">
-        <v>2370</v>
-      </c>
-    </row>
-    <row r="690" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A690" s="6" t="s">
-        <v>2371</v>
-      </c>
-      <c r="B690" s="6" t="s">
-        <v>2372</v>
-      </c>
-      <c r="C690" s="6" t="s">
-        <v>2373</v>
-      </c>
-    </row>
-    <row r="691" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A691" s="6" t="s">
-        <v>2374</v>
-      </c>
-      <c r="B691" s="6" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C691" s="6" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="692" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A692" s="6" t="s">
-        <v>2375</v>
-      </c>
-      <c r="B692" s="6" t="s">
-        <v>2376</v>
-      </c>
-      <c r="C692" s="6" t="s">
-        <v>2377</v>
-      </c>
-    </row>
-    <row r="693" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A693" s="6" t="s">
-        <v>2378</v>
-      </c>
-      <c r="B693" s="6" t="s">
-        <v>2379</v>
-      </c>
-      <c r="C693" s="6" t="s">
-        <v>2380</v>
-      </c>
-    </row>
-    <row r="694" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A694" s="6" t="s">
-        <v>2381</v>
-      </c>
-      <c r="B694" s="6" t="s">
-        <v>2382</v>
-      </c>
-      <c r="C694" s="6" t="s">
-        <v>2383</v>
-      </c>
-    </row>
-    <row r="695" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A695" s="6" t="s">
-        <v>2384</v>
-      </c>
-      <c r="B695" s="6" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C695" s="6" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="696" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A696" s="6" t="s">
-        <v>2385</v>
-      </c>
-      <c r="B696" s="6" t="s">
-        <v>2386</v>
-      </c>
-      <c r="C696" s="6" t="s">
-        <v>2387</v>
-      </c>
-    </row>
-    <row r="697" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A697" s="6" t="s">
-        <v>2388</v>
-      </c>
-      <c r="B697" s="6" t="s">
-        <v>2389</v>
-      </c>
-      <c r="C697" s="6" t="s">
-        <v>2390</v>
-      </c>
-    </row>
-    <row r="698" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A698" s="6" t="s">
-        <v>2391</v>
-      </c>
-      <c r="B698" s="6" t="s">
-        <v>2392</v>
-      </c>
-      <c r="C698" s="6" t="s">
-        <v>2393</v>
-      </c>
-    </row>
-    <row r="699" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A699" s="6" t="s">
-        <v>2394</v>
-      </c>
-      <c r="B699" s="6" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C699" s="6" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="700" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A700" s="6" t="s">
-        <v>2395</v>
-      </c>
-      <c r="B700" s="6" t="s">
-        <v>2396</v>
-      </c>
-      <c r="C700" s="6" t="s">
-        <v>2397</v>
-      </c>
-    </row>
-    <row r="701" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A701" s="6" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B701" s="6" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C701" s="6" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="702" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A702" s="6" t="s">
-        <v>2399</v>
-      </c>
-      <c r="B702" s="6" t="s">
-        <v>2400</v>
-      </c>
-      <c r="C702" s="6" t="s">
-        <v>2401</v>
-      </c>
-    </row>
-    <row r="703" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A703" s="6" t="s">
-        <v>2402</v>
-      </c>
-      <c r="B703" s="6" t="s">
-        <v>2403</v>
-      </c>
-      <c r="C703" s="6" t="s">
-        <v>2404</v>
-      </c>
-    </row>
-    <row r="704" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A704" s="6" t="s">
-        <v>2405</v>
-      </c>
-      <c r="B704" s="6" t="s">
-        <v>2406</v>
-      </c>
-      <c r="C704" s="6" t="s">
-        <v>2407</v>
-      </c>
-    </row>
-    <row r="705" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A705" s="6" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B705" s="6" t="s">
-        <v>2409</v>
-      </c>
-      <c r="C705" s="6" t="s">
-        <v>2410</v>
-      </c>
-    </row>
-    <row r="706" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A706" s="6" t="s">
-        <v>2411</v>
-      </c>
-      <c r="B706" s="6" t="s">
-        <v>2412</v>
-      </c>
-      <c r="C706" s="6" t="s">
-        <v>2413</v>
-      </c>
-    </row>
-    <row r="707" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A707" s="6" t="s">
-        <v>2414</v>
-      </c>
-      <c r="B707" s="6" t="s">
-        <v>2415</v>
-      </c>
-      <c r="C707" s="6" t="s">
+    <row r="841" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A841" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B841" s="5" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C841" s="5" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="842" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A842" s="5" t="s">
         <v>2416</v>
       </c>
-    </row>
-    <row r="708" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A708" s="6" t="s">
+      <c r="B842" s="4" t="s">
         <v>2417</v>
       </c>
-      <c r="B708" s="6" t="s">
-        <v>2418</v>
-      </c>
-      <c r="C708" s="6" t="s">
+      <c r="C842" s="4" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="843" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A843" s="5" t="s">
         <v>2419</v>
       </c>
-    </row>
-    <row r="709" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A709" s="6" t="s">
+      <c r="B843" s="4" t="s">
         <v>2420</v>
       </c>
-      <c r="B709" s="6" t="s">
-        <v>2421</v>
-      </c>
-      <c r="C709" s="6" t="s">
+      <c r="C843" s="4" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="844" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A844" s="5" t="s">
         <v>2422</v>
       </c>
-    </row>
-    <row r="710" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A710" s="6" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B710" s="6" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C710" s="6" t="s">
+      <c r="B844" s="4" t="s">
         <v>2423</v>
       </c>
-    </row>
-    <row r="711" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A711" s="6" t="s">
+      <c r="C844" s="4" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="845" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A845" s="5" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B845" s="4" t="s">
+        <v>2515</v>
+      </c>
+      <c r="C845" s="4" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="846" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A846" s="5" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B846" s="4" t="s">
+        <v>2518</v>
+      </c>
+      <c r="C846" s="4" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="847" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A847" s="5" t="s">
         <v>1268</v>
       </c>
-      <c r="B711" s="6" t="s">
+      <c r="B847" s="5" t="s">
         <v>1269</v>
       </c>
-      <c r="C711" s="6" t="s">
+      <c r="C847" s="5" t="s">
         <v>1270</v>
       </c>
     </row>
-    <row r="712" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A712" s="6" t="s">
-        <v>2424</v>
-      </c>
-      <c r="B712" s="6" t="s">
-        <v>2425</v>
-      </c>
-      <c r="C712" s="6" t="s">
-        <v>2426</v>
-      </c>
-    </row>
-    <row r="713" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A713" s="6" t="s">
+    <row r="848" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A848" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B848" s="5" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C848" s="5" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="849" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A849" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B849" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C849" s="5" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="850" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A850" s="5" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B850" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C850" s="5" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="851" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A851" s="5" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B851" s="4" t="s">
+        <v>2521</v>
+      </c>
+      <c r="C851" s="4" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="852" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A852" s="5" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B852" s="5" t="s">
+        <v>2524</v>
+      </c>
+      <c r="C852" s="5" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="853" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A853" s="5" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B853" s="4" t="s">
+        <v>2527</v>
+      </c>
+      <c r="C853" s="4" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="854" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A854" s="5" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B854" s="5" t="s">
+        <v>2530</v>
+      </c>
+      <c r="C854" s="5" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="855" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A855" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B855" s="5" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C855" s="5" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="856" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A856" s="5" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B856" s="5" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C856" s="5" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="857" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A857" s="5" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B857" s="5" t="s">
+        <v>2534</v>
+      </c>
+      <c r="C857" s="5" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="858" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A858" s="5" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B858" s="5" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C858" s="5" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="859" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A859" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B859" s="5" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C859" s="5" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="860" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A860" s="5" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B860" s="5" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C860" s="5" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="861" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A861" s="5" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B861" s="5" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C861" s="5" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="862" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A862" s="5" t="s">
         <v>2427</v>
       </c>
-      <c r="B713" s="6" t="s">
-        <v>2428</v>
-      </c>
-      <c r="C713" s="6" t="s">
-        <v>2429</v>
-      </c>
-    </row>
-    <row r="714" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A714" s="6" t="s">
+      <c r="B862" s="4" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C862" s="4" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="863" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A863" s="5" t="s">
         <v>2430</v>
       </c>
-      <c r="B714" s="6" t="s">
-        <v>2431</v>
-      </c>
-      <c r="C714" s="6" t="s">
-        <v>2432</v>
-      </c>
-    </row>
-    <row r="715" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A715" s="6" t="s">
-        <v>1296</v>
-      </c>
-      <c r="B715" s="6" t="s">
+      <c r="B863" s="4" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C863" s="4" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="864" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A864" s="5" t="s">
         <v>2433</v>
       </c>
-      <c r="C715" s="6" t="s">
-        <v>2434</v>
-      </c>
-    </row>
-    <row r="716" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A716" s="6" t="s">
+      <c r="B864" s="4" t="s">
+        <v>2543</v>
+      </c>
+      <c r="C864" s="4" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="865" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A865" s="5" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B865" s="4" t="s">
+        <v>2545</v>
+      </c>
+      <c r="C865" s="4" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="866" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A866" s="5" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B866" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="C866" s="4" t="s">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="867" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A867" s="5" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B867" s="4" t="s">
+        <v>2549</v>
+      </c>
+      <c r="C867" s="4" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="868" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A868" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B868" s="4" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C868" s="4" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="869" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A869" s="5" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B869" s="4" t="s">
+        <v>2553</v>
+      </c>
+      <c r="C869" s="4" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="870" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A870" s="5" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B870" s="4" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C870" s="4" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="871" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A871" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B871" s="4" t="s">
+        <v>2568</v>
+      </c>
+      <c r="C871" s="4" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="872" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A872" s="5" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B872" s="4" t="s">
+        <v>2559</v>
+      </c>
+      <c r="C872" s="4" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="873" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A873" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B873" s="4" t="s">
+        <v>2561</v>
+      </c>
+      <c r="C873" s="4" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="874" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A874" s="5" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B874" s="4" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C874" s="4" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="875" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A875" s="5" t="s">
         <v>1300</v>
       </c>
-      <c r="B716" s="6" t="s">
-        <v>1301</v>
-      </c>
-      <c r="C716" s="6" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="717" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A717" s="6" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B717" s="6" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C717" s="6" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="718" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A718" s="6" t="s">
-        <v>2435</v>
-      </c>
-      <c r="B718" s="6" t="s">
-        <v>2436</v>
-      </c>
-      <c r="C718" s="6" t="s">
-        <v>2437</v>
-      </c>
-    </row>
-    <row r="719" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A719" s="6" t="s">
-        <v>2438</v>
-      </c>
-      <c r="B719" s="6" t="s">
-        <v>2439</v>
-      </c>
-      <c r="C719" s="6" t="s">
-        <v>2440</v>
-      </c>
-    </row>
-    <row r="720" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A720" s="6" t="s">
-        <v>2441</v>
-      </c>
-      <c r="B720" s="6" t="s">
-        <v>2442</v>
-      </c>
-      <c r="C720" s="6" t="s">
-        <v>2443</v>
-      </c>
-    </row>
-    <row r="721" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A721" s="6" t="s">
-        <v>2444</v>
-      </c>
-      <c r="B721" s="6" t="s">
-        <v>2445</v>
-      </c>
-      <c r="C721" s="6" t="s">
-        <v>2446</v>
-      </c>
-    </row>
-    <row r="722" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A722" s="6" t="s">
-        <v>2447</v>
-      </c>
-      <c r="B722" s="6" t="s">
-        <v>2448</v>
-      </c>
-      <c r="C722" s="6" t="s">
-        <v>2449</v>
-      </c>
-    </row>
-    <row r="723" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A723" s="6" t="s">
-        <v>2450</v>
-      </c>
-      <c r="B723" s="6" t="s">
-        <v>2451</v>
-      </c>
-      <c r="C723" s="6" t="s">
-        <v>2452</v>
-      </c>
-    </row>
-    <row r="724" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A724" s="6" t="s">
-        <v>2453</v>
-      </c>
-      <c r="B724" s="6" t="s">
-        <v>2454</v>
-      </c>
-      <c r="C724" s="6" t="s">
-        <v>2455</v>
-      </c>
-    </row>
-    <row r="725" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A725" s="6" t="s">
-        <v>2456</v>
-      </c>
-      <c r="B725" s="6" t="s">
-        <v>2457</v>
-      </c>
-      <c r="C725" s="6" t="s">
-        <v>2458</v>
-      </c>
-    </row>
-    <row r="726" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A726" s="6" t="s">
-        <v>2459</v>
-      </c>
-      <c r="B726" s="6" t="s">
-        <v>2460</v>
-      </c>
-      <c r="C726" s="6" t="s">
-        <v>2461</v>
-      </c>
-    </row>
-    <row r="727" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A727" s="6" t="s">
-        <v>2462</v>
-      </c>
-      <c r="B727" s="6" t="s">
-        <v>2463</v>
-      </c>
-      <c r="C727" s="6" t="s">
-        <v>2464</v>
-      </c>
-    </row>
-    <row r="728" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A728" s="6" t="s">
-        <v>2465</v>
-      </c>
-      <c r="B728" s="6" t="s">
-        <v>2466</v>
-      </c>
-      <c r="C728" s="6" t="s">
-        <v>2467</v>
-      </c>
-    </row>
-    <row r="729" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A729" s="6" t="s">
-        <v>2468</v>
-      </c>
-      <c r="B729" s="6" t="s">
-        <v>2469</v>
-      </c>
-      <c r="C729" s="6" t="s">
-        <v>2470</v>
-      </c>
-    </row>
-    <row r="730" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A730" s="6" t="s">
-        <v>2471</v>
-      </c>
-      <c r="B730" s="6" t="s">
-        <v>2472</v>
-      </c>
-      <c r="C730" s="6" t="s">
-        <v>2473</v>
-      </c>
-    </row>
-    <row r="731" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A731" s="6" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B731" s="6" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C731" s="6" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="732" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A732" s="6" t="s">
-        <v>2474</v>
-      </c>
-      <c r="B732" s="6" t="s">
-        <v>2475</v>
-      </c>
-      <c r="C732" s="6" t="s">
-        <v>2476</v>
-      </c>
-    </row>
-    <row r="733" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A733" s="6" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B733" s="6" t="s">
-        <v>1146</v>
-      </c>
-      <c r="C733" s="6" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="734" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A734" s="6" t="s">
-        <v>1149</v>
-      </c>
-      <c r="B734" s="6" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C734" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="735" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A735" s="6" t="s">
-        <v>2477</v>
-      </c>
-      <c r="B735" s="6" t="s">
-        <v>2478</v>
-      </c>
-      <c r="C735" s="6" t="s">
-        <v>2479</v>
-      </c>
-    </row>
-    <row r="736" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A736" s="6" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B736" s="6" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C736" s="6" t="s">
-        <v>2480</v>
-      </c>
-    </row>
-    <row r="737" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A737" s="6" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B737" s="6" t="s">
-        <v>2481</v>
-      </c>
-      <c r="C737" s="6" t="s">
-        <v>2482</v>
-      </c>
-    </row>
-    <row r="738" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A738" s="6" t="s">
-        <v>2483</v>
-      </c>
-      <c r="B738" s="6" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C738" s="6" t="s">
-        <v>2485</v>
-      </c>
-    </row>
-    <row r="739" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A739" s="6" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B739" s="6" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C739" s="6" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="740" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A740" s="6" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B740" s="6" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C740" s="6" t="s">
-        <v>2486</v>
-      </c>
-    </row>
-    <row r="741" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A741" s="6" t="s">
-        <v>2487</v>
-      </c>
-      <c r="B741" s="6" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C741" s="6" t="s">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="742" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A742" s="6" t="s">
-        <v>2490</v>
-      </c>
-      <c r="B742" s="6" t="s">
-        <v>2491</v>
-      </c>
-      <c r="C742" s="6" t="s">
-        <v>2492</v>
-      </c>
-    </row>
-    <row r="743" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A743" s="6" t="s">
-        <v>2493</v>
-      </c>
-      <c r="B743" s="6" t="s">
-        <v>2494</v>
-      </c>
-      <c r="C743" s="6" t="s">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="744" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A744" s="6" t="s">
-        <v>1169</v>
-      </c>
-      <c r="B744" s="6" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C744" s="6" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="745" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A745" s="6" t="s">
-        <v>2496</v>
-      </c>
-      <c r="B745" s="6" t="s">
-        <v>2497</v>
-      </c>
-      <c r="C745" s="6" t="s">
-        <v>2498</v>
-      </c>
-    </row>
-    <row r="746" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A746" s="6" t="s">
-        <v>2499</v>
-      </c>
-      <c r="B746" s="6" t="s">
-        <v>2500</v>
-      </c>
-      <c r="C746" s="6" t="s">
-        <v>2501</v>
-      </c>
-    </row>
+      <c r="B875" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C875" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="876" customFormat="false" ht="1278.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A876" s="5" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B876" s="5" t="s">
+        <v>2570</v>
+      </c>
+      <c r="C876" s="5" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/multi.xlsx
+++ b/multi.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3302" uniqueCount="2572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3311" uniqueCount="2581">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -7764,9 +7764,9 @@
 DESCRIPCION,PESO modificando ambos campos
 ,PESO manteniendo descripción
 • Sin IA: Comidas precargadas y actividad física:
-*DESAYUNO: menú completo
-*PIZZA (porcion),4: 4 porciones de pizza
-*TORTA (fraccion x 100g),1.5: 150 g de torta
+`*DESAYUNO`: menú completo
+`*PIZZA` (porcion),4: 4 porciones de pizza
+`*TORTA` (fraccion x 100g),1.5: 150 g de torta
 📌 Métodos de Registro de actividades:
 • Con IA: Texto, 🎤 Notas de voz.
 • Modificación parcial: Editar ingresando calorias
@@ -7804,9 +7804,9 @@
 DESCRIPTION,WEIGHT modifying both fields
 ,WEIGHT keeping description
 • Without AI: Preloaded meals and physical activity:
-*BREAKFAST: full menu
-*PIZZA (portion),4: 4 pizza portions
-*CAKE (fraction x 100g),1.5: 150 g of cake
+`*BREAKFAST`: full menu
+`*PIZZA` (portion),4: 4 pizza portions
+`*CAKE` (fraction x 100g),1.5: 150 g of cake
 📌 Activity Registration Methods:
 • With AI: Text, 🎤 Voice notes.
 • Partial modification: Edit by entering calories.
@@ -7814,6 +7814,33 @@
 • With AI: 📸 Photos.
 • Confirmation: entering clarifying note.
 📄 Attached is the complete User Manual in PDF format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">btn_edit_altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📏 Altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📏 Height</t>
+  </si>
+  <si>
+    <t xml:space="preserve">btn_edit_ocup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏃 Ocupación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏃 Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">btn_edit_nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👤 Nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👤 Name</t>
   </si>
 </sst>
 </file>
@@ -7921,7 +7948,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -18316,10 +18343,10 @@
       <c r="A671" s="4" t="s">
         <v>2345</v>
       </c>
-      <c r="B671" s="5" t="s">
+      <c r="B671" s="3" t="s">
         <v>2173</v>
       </c>
-      <c r="C671" s="5" t="s">
+      <c r="C671" s="3" t="s">
         <v>2174</v>
       </c>
     </row>
@@ -18327,10 +18354,10 @@
       <c r="A672" s="4" t="s">
         <v>2346</v>
       </c>
-      <c r="B672" s="5" t="s">
+      <c r="B672" s="3" t="s">
         <v>2177</v>
       </c>
-      <c r="C672" s="5" t="s">
+      <c r="C672" s="3" t="s">
         <v>2178</v>
       </c>
     </row>
@@ -18338,10 +18365,10 @@
       <c r="A673" s="4" t="s">
         <v>2347</v>
       </c>
-      <c r="B673" s="5" t="s">
+      <c r="B673" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="C673" s="5" t="s">
+      <c r="C673" s="3" t="s">
         <v>2182</v>
       </c>
     </row>
@@ -18349,10 +18376,10 @@
       <c r="A674" s="4" t="s">
         <v>2348</v>
       </c>
-      <c r="B674" s="5" t="s">
+      <c r="B674" s="3" t="s">
         <v>2185</v>
       </c>
-      <c r="C674" s="5" t="s">
+      <c r="C674" s="3" t="s">
         <v>2186</v>
       </c>
     </row>
@@ -18360,10 +18387,10 @@
       <c r="A675" s="4" t="s">
         <v>2349</v>
       </c>
-      <c r="B675" s="5" t="s">
+      <c r="B675" s="3" t="s">
         <v>2350</v>
       </c>
-      <c r="C675" s="5" t="s">
+      <c r="C675" s="3" t="s">
         <v>2351</v>
       </c>
     </row>
@@ -18371,10 +18398,10 @@
       <c r="A676" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="B676" s="5" t="s">
+      <c r="B676" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="C676" s="5" t="s">
+      <c r="C676" s="3" t="s">
         <v>464</v>
       </c>
     </row>
@@ -18382,796 +18409,796 @@
       <c r="A677" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="B677" s="5" t="s">
+      <c r="B677" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C677" s="5" t="s">
+      <c r="C677" s="3" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="678" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A678" s="5" t="s">
+      <c r="A678" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="B678" s="5" t="s">
+      <c r="B678" s="3" t="s">
         <v>1242</v>
       </c>
-      <c r="C678" s="5" t="s">
+      <c r="C678" s="3" t="s">
         <v>1243</v>
       </c>
     </row>
     <row r="679" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A679" s="5" t="s">
+      <c r="A679" s="3" t="s">
         <v>1245</v>
       </c>
-      <c r="B679" s="5" t="s">
+      <c r="B679" s="3" t="s">
         <v>1246</v>
       </c>
-      <c r="C679" s="5" t="s">
+      <c r="C679" s="3" t="s">
         <v>1247</v>
       </c>
     </row>
     <row r="680" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A680" s="5" t="s">
+      <c r="A680" s="3" t="s">
         <v>1249</v>
       </c>
-      <c r="B680" s="5" t="s">
+      <c r="B680" s="3" t="s">
         <v>1250</v>
       </c>
-      <c r="C680" s="5" t="s">
+      <c r="C680" s="3" t="s">
         <v>1251</v>
       </c>
     </row>
     <row r="681" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A681" s="5" t="s">
+      <c r="A681" s="3" t="s">
         <v>1253</v>
       </c>
-      <c r="B681" s="5" t="s">
+      <c r="B681" s="3" t="s">
         <v>1254</v>
       </c>
-      <c r="C681" s="5" t="s">
+      <c r="C681" s="3" t="s">
         <v>1255</v>
       </c>
     </row>
     <row r="682" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A682" s="5" t="s">
+      <c r="A682" s="3" t="s">
         <v>1256</v>
       </c>
-      <c r="B682" s="5" t="s">
+      <c r="B682" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="C682" s="5" t="s">
+      <c r="C682" s="3" t="s">
         <v>1258</v>
       </c>
     </row>
     <row r="683" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A683" s="5" t="s">
+      <c r="A683" s="3" t="s">
         <v>2352</v>
       </c>
-      <c r="B683" s="5" t="s">
+      <c r="B683" s="3" t="s">
         <v>2353</v>
       </c>
-      <c r="C683" s="5" t="s">
+      <c r="C683" s="3" t="s">
         <v>2354</v>
       </c>
     </row>
     <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A684" s="5" t="s">
+      <c r="A684" s="3" t="s">
         <v>2355</v>
       </c>
-      <c r="B684" s="5" t="s">
+      <c r="B684" s="3" t="s">
         <v>2356</v>
       </c>
-      <c r="C684" s="5" t="s">
+      <c r="C684" s="3" t="s">
         <v>1102</v>
       </c>
     </row>
     <row r="685" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A685" s="5" t="s">
+      <c r="A685" s="3" t="s">
         <v>2357</v>
       </c>
-      <c r="B685" s="5" t="s">
+      <c r="B685" s="3" t="s">
         <v>2358</v>
       </c>
-      <c r="C685" s="5" t="s">
+      <c r="C685" s="3" t="s">
         <v>2359</v>
       </c>
     </row>
     <row r="686" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A686" s="5" t="s">
+      <c r="A686" s="3" t="s">
         <v>2360</v>
       </c>
-      <c r="B686" s="5" t="s">
+      <c r="B686" s="3" t="s">
         <v>2361</v>
       </c>
-      <c r="C686" s="5" t="s">
+      <c r="C686" s="3" t="s">
         <v>2362</v>
       </c>
     </row>
     <row r="687" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A687" s="5" t="s">
+      <c r="A687" s="3" t="s">
         <v>2363</v>
       </c>
-      <c r="B687" s="5" t="s">
+      <c r="B687" s="3" t="s">
         <v>2364</v>
       </c>
-      <c r="C687" s="5" t="s">
+      <c r="C687" s="3" t="s">
         <v>2365</v>
       </c>
     </row>
     <row r="688" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A688" s="5" t="s">
+      <c r="A688" s="3" t="s">
         <v>2366</v>
       </c>
-      <c r="B688" s="5" t="s">
+      <c r="B688" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="C688" s="5" t="s">
+      <c r="C688" s="3" t="s">
         <v>1073</v>
       </c>
     </row>
     <row r="689" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A689" s="5" t="s">
+      <c r="A689" s="3" t="s">
         <v>2367</v>
       </c>
-      <c r="B689" s="5" t="s">
+      <c r="B689" s="3" t="s">
         <v>2368</v>
       </c>
-      <c r="C689" s="5" t="s">
+      <c r="C689" s="3" t="s">
         <v>2369</v>
       </c>
     </row>
     <row r="690" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A690" s="5" t="s">
+      <c r="A690" s="3" t="s">
         <v>2370</v>
       </c>
-      <c r="B690" s="5" t="s">
+      <c r="B690" s="3" t="s">
         <v>2371</v>
       </c>
-      <c r="C690" s="5" t="s">
+      <c r="C690" s="3" t="s">
         <v>2372</v>
       </c>
     </row>
     <row r="691" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A691" s="5" t="s">
+      <c r="A691" s="3" t="s">
         <v>2373</v>
       </c>
-      <c r="B691" s="5" t="s">
+      <c r="B691" s="3" t="s">
         <v>2374</v>
       </c>
-      <c r="C691" s="5" t="s">
+      <c r="C691" s="3" t="s">
         <v>2375</v>
       </c>
     </row>
     <row r="692" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A692" s="5" t="s">
+      <c r="A692" s="3" t="s">
         <v>2376</v>
       </c>
-      <c r="B692" s="5" t="s">
+      <c r="B692" s="3" t="s">
         <v>1081</v>
       </c>
-      <c r="C692" s="5" t="s">
+      <c r="C692" s="3" t="s">
         <v>1082</v>
       </c>
     </row>
     <row r="693" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A693" s="5" t="s">
+      <c r="A693" s="3" t="s">
         <v>2377</v>
       </c>
-      <c r="B693" s="5" t="s">
+      <c r="B693" s="3" t="s">
         <v>2378</v>
       </c>
-      <c r="C693" s="5" t="s">
+      <c r="C693" s="3" t="s">
         <v>2379</v>
       </c>
     </row>
     <row r="694" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A694" s="5" t="s">
+      <c r="A694" s="3" t="s">
         <v>2380</v>
       </c>
-      <c r="B694" s="5" t="s">
+      <c r="B694" s="3" t="s">
         <v>2381</v>
       </c>
-      <c r="C694" s="5" t="s">
+      <c r="C694" s="3" t="s">
         <v>2382</v>
       </c>
     </row>
     <row r="695" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A695" s="5" t="s">
+      <c r="A695" s="3" t="s">
         <v>2383</v>
       </c>
-      <c r="B695" s="5" t="s">
+      <c r="B695" s="3" t="s">
         <v>2384</v>
       </c>
-      <c r="C695" s="5" t="s">
+      <c r="C695" s="3" t="s">
         <v>2385</v>
       </c>
     </row>
     <row r="696" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A696" s="5" t="s">
+      <c r="A696" s="3" t="s">
         <v>2386</v>
       </c>
-      <c r="B696" s="5" t="s">
+      <c r="B696" s="3" t="s">
         <v>1085</v>
       </c>
-      <c r="C696" s="5" t="s">
+      <c r="C696" s="3" t="s">
         <v>1086</v>
       </c>
     </row>
     <row r="697" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A697" s="5" t="s">
+      <c r="A697" s="3" t="s">
         <v>2387</v>
       </c>
-      <c r="B697" s="5" t="s">
+      <c r="B697" s="3" t="s">
         <v>2388</v>
       </c>
-      <c r="C697" s="5" t="s">
+      <c r="C697" s="3" t="s">
         <v>2389</v>
       </c>
     </row>
     <row r="698" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A698" s="5" t="s">
+      <c r="A698" s="3" t="s">
         <v>2390</v>
       </c>
-      <c r="B698" s="5" t="s">
+      <c r="B698" s="3" t="s">
         <v>1089</v>
       </c>
-      <c r="C698" s="5" t="s">
+      <c r="C698" s="3" t="s">
         <v>1090</v>
       </c>
     </row>
     <row r="699" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A699" s="5" t="s">
+      <c r="A699" s="3" t="s">
         <v>2391</v>
       </c>
-      <c r="B699" s="5" t="s">
+      <c r="B699" s="3" t="s">
         <v>2392</v>
       </c>
-      <c r="C699" s="5" t="s">
+      <c r="C699" s="3" t="s">
         <v>2393</v>
       </c>
     </row>
     <row r="700" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A700" s="5" t="s">
+      <c r="A700" s="3" t="s">
         <v>2394</v>
       </c>
-      <c r="B700" s="5" t="s">
+      <c r="B700" s="3" t="s">
         <v>2395</v>
       </c>
-      <c r="C700" s="5" t="s">
+      <c r="C700" s="3" t="s">
         <v>2396</v>
       </c>
     </row>
     <row r="701" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A701" s="5" t="s">
+      <c r="A701" s="3" t="s">
         <v>2397</v>
       </c>
-      <c r="B701" s="5" t="s">
+      <c r="B701" s="3" t="s">
         <v>2398</v>
       </c>
-      <c r="C701" s="5" t="s">
+      <c r="C701" s="3" t="s">
         <v>2399</v>
       </c>
     </row>
     <row r="702" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A702" s="5" t="s">
+      <c r="A702" s="3" t="s">
         <v>2400</v>
       </c>
-      <c r="B702" s="5" t="s">
+      <c r="B702" s="3" t="s">
         <v>2401</v>
       </c>
-      <c r="C702" s="5" t="s">
+      <c r="C702" s="3" t="s">
         <v>2402</v>
       </c>
     </row>
     <row r="703" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A703" s="5" t="s">
+      <c r="A703" s="3" t="s">
         <v>2403</v>
       </c>
-      <c r="B703" s="5" t="s">
+      <c r="B703" s="3" t="s">
         <v>2404</v>
       </c>
-      <c r="C703" s="5" t="s">
+      <c r="C703" s="3" t="s">
         <v>2405</v>
       </c>
     </row>
     <row r="704" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A704" s="5" t="s">
+      <c r="A704" s="3" t="s">
         <v>2406</v>
       </c>
-      <c r="B704" s="5" t="s">
+      <c r="B704" s="3" t="s">
         <v>2407</v>
       </c>
-      <c r="C704" s="5" t="s">
+      <c r="C704" s="3" t="s">
         <v>2408</v>
       </c>
     </row>
     <row r="705" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A705" s="5" t="s">
+      <c r="A705" s="3" t="s">
         <v>2409</v>
       </c>
-      <c r="B705" s="5" t="s">
+      <c r="B705" s="3" t="s">
         <v>2410</v>
       </c>
-      <c r="C705" s="5" t="s">
+      <c r="C705" s="3" t="s">
         <v>2411</v>
       </c>
     </row>
     <row r="706" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A706" s="5" t="s">
+      <c r="A706" s="3" t="s">
         <v>2412</v>
       </c>
-      <c r="B706" s="5" t="s">
+      <c r="B706" s="3" t="s">
         <v>2413</v>
       </c>
-      <c r="C706" s="5" t="s">
+      <c r="C706" s="3" t="s">
         <v>2414</v>
       </c>
     </row>
     <row r="707" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A707" s="5" t="s">
+      <c r="A707" s="3" t="s">
         <v>1260</v>
       </c>
-      <c r="B707" s="5" t="s">
+      <c r="B707" s="3" t="s">
         <v>1261</v>
       </c>
-      <c r="C707" s="5" t="s">
+      <c r="C707" s="3" t="s">
         <v>2415</v>
       </c>
     </row>
     <row r="708" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A708" s="5" t="s">
+      <c r="A708" s="3" t="s">
         <v>1264</v>
       </c>
-      <c r="B708" s="5" t="s">
+      <c r="B708" s="3" t="s">
         <v>1265</v>
       </c>
-      <c r="C708" s="5" t="s">
+      <c r="C708" s="3" t="s">
         <v>1266</v>
       </c>
     </row>
     <row r="709" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A709" s="5" t="s">
+      <c r="A709" s="3" t="s">
         <v>2416</v>
       </c>
-      <c r="B709" s="5" t="s">
+      <c r="B709" s="3" t="s">
         <v>2417</v>
       </c>
-      <c r="C709" s="5" t="s">
+      <c r="C709" s="3" t="s">
         <v>2418</v>
       </c>
     </row>
     <row r="710" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A710" s="5" t="s">
+      <c r="A710" s="3" t="s">
         <v>2419</v>
       </c>
-      <c r="B710" s="5" t="s">
+      <c r="B710" s="3" t="s">
         <v>2420</v>
       </c>
-      <c r="C710" s="5" t="s">
+      <c r="C710" s="3" t="s">
         <v>2421</v>
       </c>
     </row>
     <row r="711" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A711" s="5" t="s">
+      <c r="A711" s="3" t="s">
         <v>2422</v>
       </c>
-      <c r="B711" s="5" t="s">
+      <c r="B711" s="3" t="s">
         <v>2423</v>
       </c>
-      <c r="C711" s="5" t="s">
+      <c r="C711" s="3" t="s">
         <v>2424</v>
       </c>
     </row>
     <row r="712" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A712" s="5" t="s">
+      <c r="A712" s="3" t="s">
         <v>1292</v>
       </c>
-      <c r="B712" s="5" t="s">
+      <c r="B712" s="3" t="s">
         <v>2425</v>
       </c>
-      <c r="C712" s="5" t="s">
+      <c r="C712" s="3" t="s">
         <v>2426</v>
       </c>
     </row>
     <row r="713" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A713" s="5" t="s">
+      <c r="A713" s="3" t="s">
         <v>1296</v>
       </c>
-      <c r="B713" s="5" t="s">
+      <c r="B713" s="3" t="s">
         <v>1297</v>
       </c>
-      <c r="C713" s="5" t="s">
+      <c r="C713" s="3" t="s">
         <v>1298</v>
       </c>
     </row>
     <row r="714" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A714" s="5" t="s">
+      <c r="A714" s="3" t="s">
         <v>1299</v>
       </c>
-      <c r="B714" s="5" t="s">
+      <c r="B714" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="C714" s="5" t="s">
+      <c r="C714" s="3" t="s">
         <v>1258</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A715" s="5" t="s">
+      <c r="A715" s="3" t="s">
         <v>2427</v>
       </c>
-      <c r="B715" s="5" t="s">
+      <c r="B715" s="3" t="s">
         <v>2428</v>
       </c>
-      <c r="C715" s="5" t="s">
+      <c r="C715" s="3" t="s">
         <v>2429</v>
       </c>
     </row>
     <row r="716" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A716" s="5" t="s">
+      <c r="A716" s="3" t="s">
         <v>2430</v>
       </c>
-      <c r="B716" s="5" t="s">
+      <c r="B716" s="3" t="s">
         <v>2431</v>
       </c>
-      <c r="C716" s="5" t="s">
+      <c r="C716" s="3" t="s">
         <v>2432</v>
       </c>
     </row>
     <row r="717" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A717" s="5" t="s">
+      <c r="A717" s="3" t="s">
         <v>2433</v>
       </c>
-      <c r="B717" s="5" t="s">
+      <c r="B717" s="3" t="s">
         <v>2434</v>
       </c>
-      <c r="C717" s="5" t="s">
+      <c r="C717" s="3" t="s">
         <v>2435</v>
       </c>
     </row>
     <row r="718" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A718" s="5" t="s">
+      <c r="A718" s="3" t="s">
         <v>2436</v>
       </c>
-      <c r="B718" s="5" t="s">
+      <c r="B718" s="3" t="s">
         <v>2437</v>
       </c>
-      <c r="C718" s="5" t="s">
+      <c r="C718" s="3" t="s">
         <v>2438</v>
       </c>
     </row>
     <row r="719" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A719" s="5" t="s">
+      <c r="A719" s="3" t="s">
         <v>2439</v>
       </c>
-      <c r="B719" s="5" t="s">
+      <c r="B719" s="3" t="s">
         <v>2440</v>
       </c>
-      <c r="C719" s="5" t="s">
+      <c r="C719" s="3" t="s">
         <v>2441</v>
       </c>
     </row>
     <row r="720" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A720" s="5" t="s">
+      <c r="A720" s="3" t="s">
         <v>2442</v>
       </c>
-      <c r="B720" s="5" t="s">
+      <c r="B720" s="3" t="s">
         <v>2443</v>
       </c>
-      <c r="C720" s="5" t="s">
+      <c r="C720" s="3" t="s">
         <v>2444</v>
       </c>
     </row>
     <row r="721" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A721" s="5" t="s">
+      <c r="A721" s="3" t="s">
         <v>2445</v>
       </c>
-      <c r="B721" s="5" t="s">
+      <c r="B721" s="3" t="s">
         <v>2446</v>
       </c>
-      <c r="C721" s="5" t="s">
+      <c r="C721" s="3" t="s">
         <v>2447</v>
       </c>
     </row>
     <row r="722" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A722" s="5" t="s">
+      <c r="A722" s="3" t="s">
         <v>2448</v>
       </c>
-      <c r="B722" s="5" t="s">
+      <c r="B722" s="3" t="s">
         <v>2449</v>
       </c>
-      <c r="C722" s="5" t="s">
+      <c r="C722" s="3" t="s">
         <v>2450</v>
       </c>
     </row>
     <row r="723" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A723" s="5" t="s">
+      <c r="A723" s="3" t="s">
         <v>2451</v>
       </c>
-      <c r="B723" s="5" t="s">
+      <c r="B723" s="3" t="s">
         <v>2452</v>
       </c>
-      <c r="C723" s="5" t="s">
+      <c r="C723" s="3" t="s">
         <v>2453</v>
       </c>
     </row>
     <row r="724" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A724" s="5" t="s">
+      <c r="A724" s="3" t="s">
         <v>2454</v>
       </c>
-      <c r="B724" s="5" t="s">
+      <c r="B724" s="3" t="s">
         <v>2455</v>
       </c>
-      <c r="C724" s="5" t="s">
+      <c r="C724" s="3" t="s">
         <v>2456</v>
       </c>
     </row>
     <row r="725" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A725" s="5" t="s">
+      <c r="A725" s="3" t="s">
         <v>2457</v>
       </c>
-      <c r="B725" s="5" t="s">
+      <c r="B725" s="3" t="s">
         <v>2458</v>
       </c>
-      <c r="C725" s="5" t="s">
+      <c r="C725" s="3" t="s">
         <v>2459</v>
       </c>
     </row>
     <row r="726" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A726" s="5" t="s">
+      <c r="A726" s="3" t="s">
         <v>2460</v>
       </c>
-      <c r="B726" s="5" t="s">
+      <c r="B726" s="3" t="s">
         <v>2461</v>
       </c>
-      <c r="C726" s="5" t="s">
+      <c r="C726" s="3" t="s">
         <v>2462</v>
       </c>
     </row>
     <row r="727" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A727" s="5" t="s">
+      <c r="A727" s="3" t="s">
         <v>2463</v>
       </c>
-      <c r="B727" s="5" t="s">
+      <c r="B727" s="3" t="s">
         <v>2464</v>
       </c>
-      <c r="C727" s="5" t="s">
+      <c r="C727" s="3" t="s">
         <v>2465</v>
       </c>
     </row>
     <row r="728" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A728" s="5" t="s">
+      <c r="A728" s="3" t="s">
         <v>1141</v>
       </c>
-      <c r="B728" s="5" t="s">
+      <c r="B728" s="3" t="s">
         <v>1142</v>
       </c>
-      <c r="C728" s="5" t="s">
+      <c r="C728" s="3" t="s">
         <v>1143</v>
       </c>
     </row>
     <row r="729" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A729" s="5" t="s">
+      <c r="A729" s="3" t="s">
         <v>2466</v>
       </c>
-      <c r="B729" s="5" t="s">
+      <c r="B729" s="3" t="s">
         <v>2467</v>
       </c>
-      <c r="C729" s="5" t="s">
+      <c r="C729" s="3" t="s">
         <v>2468</v>
       </c>
     </row>
     <row r="730" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A730" s="5" t="s">
+      <c r="A730" s="3" t="s">
         <v>1145</v>
       </c>
-      <c r="B730" s="5" t="s">
+      <c r="B730" s="3" t="s">
         <v>1146</v>
       </c>
-      <c r="C730" s="5" t="s">
+      <c r="C730" s="3" t="s">
         <v>1147</v>
       </c>
     </row>
     <row r="731" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A731" s="5" t="s">
+      <c r="A731" s="3" t="s">
         <v>1149</v>
       </c>
-      <c r="B731" s="5" t="s">
+      <c r="B731" s="3" t="s">
         <v>1150</v>
       </c>
-      <c r="C731" s="5" t="s">
+      <c r="C731" s="3" t="s">
         <v>1151</v>
       </c>
     </row>
     <row r="732" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A732" s="5" t="s">
+      <c r="A732" s="3" t="s">
         <v>2469</v>
       </c>
-      <c r="B732" s="5" t="s">
+      <c r="B732" s="3" t="s">
         <v>2470</v>
       </c>
-      <c r="C732" s="5" t="s">
+      <c r="C732" s="3" t="s">
         <v>2471</v>
       </c>
     </row>
     <row r="733" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A733" s="5" t="s">
+      <c r="A733" s="3" t="s">
         <v>1161</v>
       </c>
-      <c r="B733" s="5" t="s">
+      <c r="B733" s="3" t="s">
         <v>1162</v>
       </c>
-      <c r="C733" s="5" t="s">
+      <c r="C733" s="3" t="s">
         <v>2472</v>
       </c>
     </row>
     <row r="734" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A734" s="5" t="s">
+      <c r="A734" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="B734" s="5" t="s">
+      <c r="B734" s="3" t="s">
         <v>2473</v>
       </c>
-      <c r="C734" s="5" t="s">
+      <c r="C734" s="3" t="s">
         <v>2474</v>
       </c>
     </row>
     <row r="735" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A735" s="5" t="s">
+      <c r="A735" s="3" t="s">
         <v>2475</v>
       </c>
-      <c r="B735" s="5" t="s">
+      <c r="B735" s="3" t="s">
         <v>2476</v>
       </c>
-      <c r="C735" s="5" t="s">
+      <c r="C735" s="3" t="s">
         <v>2477</v>
       </c>
     </row>
     <row r="736" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A736" s="5" t="s">
+      <c r="A736" s="3" t="s">
         <v>1157</v>
       </c>
-      <c r="B736" s="5" t="s">
+      <c r="B736" s="3" t="s">
         <v>1158</v>
       </c>
-      <c r="C736" s="5" t="s">
+      <c r="C736" s="3" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="737" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A737" s="5" t="s">
+      <c r="A737" s="3" t="s">
         <v>1165</v>
       </c>
-      <c r="B737" s="5" t="s">
+      <c r="B737" s="3" t="s">
         <v>1166</v>
       </c>
-      <c r="C737" s="5" t="s">
+      <c r="C737" s="3" t="s">
         <v>2478</v>
       </c>
     </row>
     <row r="738" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A738" s="5" t="s">
+      <c r="A738" s="3" t="s">
         <v>2479</v>
       </c>
-      <c r="B738" s="5" t="s">
+      <c r="B738" s="3" t="s">
         <v>2480</v>
       </c>
-      <c r="C738" s="5" t="s">
+      <c r="C738" s="3" t="s">
         <v>2481</v>
       </c>
     </row>
     <row r="739" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A739" s="5" t="s">
+      <c r="A739" s="3" t="s">
         <v>2482</v>
       </c>
-      <c r="B739" s="5" t="s">
+      <c r="B739" s="3" t="s">
         <v>2483</v>
       </c>
-      <c r="C739" s="5" t="s">
+      <c r="C739" s="3" t="s">
         <v>2484</v>
       </c>
     </row>
     <row r="740" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A740" s="5" t="s">
+      <c r="A740" s="3" t="s">
         <v>2485</v>
       </c>
-      <c r="B740" s="5" t="s">
+      <c r="B740" s="3" t="s">
         <v>2486</v>
       </c>
-      <c r="C740" s="5" t="s">
+      <c r="C740" s="3" t="s">
         <v>2487</v>
       </c>
     </row>
     <row r="741" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A741" s="5" t="s">
+      <c r="A741" s="3" t="s">
         <v>1169</v>
       </c>
-      <c r="B741" s="5" t="s">
+      <c r="B741" s="3" t="s">
         <v>1170</v>
       </c>
-      <c r="C741" s="5" t="s">
+      <c r="C741" s="3" t="s">
         <v>1171</v>
       </c>
     </row>
     <row r="742" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A742" s="5" t="s">
+      <c r="A742" s="3" t="s">
         <v>2488</v>
       </c>
-      <c r="B742" s="5" t="s">
+      <c r="B742" s="3" t="s">
         <v>2489</v>
       </c>
-      <c r="C742" s="5" t="s">
+      <c r="C742" s="3" t="s">
         <v>2490</v>
       </c>
     </row>
     <row r="743" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A743" s="5" t="s">
+      <c r="A743" s="3" t="s">
         <v>2491</v>
       </c>
-      <c r="B743" s="5" t="s">
+      <c r="B743" s="3" t="s">
         <v>2492</v>
       </c>
-      <c r="C743" s="5" t="s">
+      <c r="C743" s="3" t="s">
         <v>2493</v>
       </c>
     </row>
     <row r="744" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A744" s="5" t="s">
+      <c r="A744" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="B744" s="5" t="s">
+      <c r="B744" s="3" t="s">
         <v>1242</v>
       </c>
-      <c r="C744" s="5" t="s">
+      <c r="C744" s="3" t="s">
         <v>1243</v>
       </c>
     </row>
     <row r="745" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A745" s="5" t="s">
+      <c r="A745" s="3" t="s">
         <v>1245</v>
       </c>
-      <c r="B745" s="5" t="s">
+      <c r="B745" s="3" t="s">
         <v>1246</v>
       </c>
-      <c r="C745" s="5" t="s">
+      <c r="C745" s="3" t="s">
         <v>1247</v>
       </c>
     </row>
     <row r="746" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A746" s="5" t="s">
+      <c r="A746" s="3" t="s">
         <v>1249</v>
       </c>
-      <c r="B746" s="5" t="s">
+      <c r="B746" s="3" t="s">
         <v>1250</v>
       </c>
-      <c r="C746" s="5" t="s">
+      <c r="C746" s="3" t="s">
         <v>1251</v>
       </c>
     </row>
     <row r="747" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A747" s="5" t="s">
+      <c r="A747" s="3" t="s">
         <v>1253</v>
       </c>
-      <c r="B747" s="5" t="s">
+      <c r="B747" s="3" t="s">
         <v>1254</v>
       </c>
-      <c r="C747" s="5" t="s">
+      <c r="C747" s="3" t="s">
         <v>1255</v>
       </c>
     </row>
     <row r="748" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A748" s="5" t="s">
+      <c r="A748" s="3" t="s">
         <v>1256</v>
       </c>
-      <c r="B748" s="5" t="s">
+      <c r="B748" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="C748" s="5" t="s">
+      <c r="C748" s="3" t="s">
         <v>1258</v>
       </c>
     </row>
     <row r="749" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A749" s="5" t="s">
+      <c r="A749" s="3" t="s">
         <v>2352</v>
       </c>
       <c r="B749" s="4" t="s">
@@ -19182,18 +19209,18 @@
       </c>
     </row>
     <row r="750" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A750" s="5" t="s">
+      <c r="A750" s="3" t="s">
         <v>2355</v>
       </c>
-      <c r="B750" s="5" t="s">
+      <c r="B750" s="3" t="s">
         <v>2356</v>
       </c>
-      <c r="C750" s="5" t="s">
+      <c r="C750" s="3" t="s">
         <v>1102</v>
       </c>
     </row>
     <row r="751" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A751" s="5" t="s">
+      <c r="A751" s="3" t="s">
         <v>2357</v>
       </c>
       <c r="B751" s="4" t="s">
@@ -19204,18 +19231,18 @@
       </c>
     </row>
     <row r="752" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A752" s="5" t="s">
+      <c r="A752" s="3" t="s">
         <v>2360</v>
       </c>
-      <c r="B752" s="5" t="s">
+      <c r="B752" s="3" t="s">
         <v>2361</v>
       </c>
-      <c r="C752" s="5" t="s">
+      <c r="C752" s="3" t="s">
         <v>2497</v>
       </c>
     </row>
     <row r="753" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A753" s="5" t="s">
+      <c r="A753" s="3" t="s">
         <v>2363</v>
       </c>
       <c r="B753" s="4" t="s">
@@ -19226,18 +19253,18 @@
       </c>
     </row>
     <row r="754" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A754" s="5" t="s">
+      <c r="A754" s="3" t="s">
         <v>2366</v>
       </c>
-      <c r="B754" s="5" t="s">
+      <c r="B754" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="C754" s="5" t="s">
+      <c r="C754" s="3" t="s">
         <v>1073</v>
       </c>
     </row>
     <row r="755" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A755" s="5" t="s">
+      <c r="A755" s="3" t="s">
         <v>2367</v>
       </c>
       <c r="B755" s="4" t="s">
@@ -19248,18 +19275,18 @@
       </c>
     </row>
     <row r="756" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A756" s="5" t="s">
+      <c r="A756" s="3" t="s">
         <v>2370</v>
       </c>
-      <c r="B756" s="5" t="s">
+      <c r="B756" s="3" t="s">
         <v>2371</v>
       </c>
-      <c r="C756" s="5" t="s">
+      <c r="C756" s="3" t="s">
         <v>2372</v>
       </c>
     </row>
     <row r="757" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A757" s="5" t="s">
+      <c r="A757" s="3" t="s">
         <v>2373</v>
       </c>
       <c r="B757" s="4" t="s">
@@ -19270,18 +19297,18 @@
       </c>
     </row>
     <row r="758" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A758" s="5" t="s">
+      <c r="A758" s="3" t="s">
         <v>2376</v>
       </c>
-      <c r="B758" s="5" t="s">
+      <c r="B758" s="3" t="s">
         <v>1081</v>
       </c>
-      <c r="C758" s="5" t="s">
+      <c r="C758" s="3" t="s">
         <v>1082</v>
       </c>
     </row>
     <row r="759" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A759" s="5" t="s">
+      <c r="A759" s="3" t="s">
         <v>2377</v>
       </c>
       <c r="B759" s="4" t="s">
@@ -19292,18 +19319,18 @@
       </c>
     </row>
     <row r="760" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A760" s="5" t="s">
+      <c r="A760" s="3" t="s">
         <v>2380</v>
       </c>
-      <c r="B760" s="5" t="s">
+      <c r="B760" s="3" t="s">
         <v>2381</v>
       </c>
-      <c r="C760" s="5" t="s">
+      <c r="C760" s="3" t="s">
         <v>2382</v>
       </c>
     </row>
     <row r="761" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A761" s="5" t="s">
+      <c r="A761" s="3" t="s">
         <v>2383</v>
       </c>
       <c r="B761" s="4" t="s">
@@ -19314,18 +19341,18 @@
       </c>
     </row>
     <row r="762" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A762" s="5" t="s">
+      <c r="A762" s="3" t="s">
         <v>2386</v>
       </c>
-      <c r="B762" s="5" t="s">
+      <c r="B762" s="3" t="s">
         <v>1085</v>
       </c>
-      <c r="C762" s="5" t="s">
+      <c r="C762" s="3" t="s">
         <v>1086</v>
       </c>
     </row>
     <row r="763" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A763" s="5" t="s">
+      <c r="A763" s="3" t="s">
         <v>2387</v>
       </c>
       <c r="B763" s="4" t="s">
@@ -19336,18 +19363,18 @@
       </c>
     </row>
     <row r="764" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A764" s="5" t="s">
+      <c r="A764" s="3" t="s">
         <v>2390</v>
       </c>
-      <c r="B764" s="5" t="s">
+      <c r="B764" s="3" t="s">
         <v>1089</v>
       </c>
-      <c r="C764" s="5" t="s">
+      <c r="C764" s="3" t="s">
         <v>1090</v>
       </c>
     </row>
     <row r="765" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A765" s="5" t="s">
+      <c r="A765" s="3" t="s">
         <v>2391</v>
       </c>
       <c r="B765" s="4" t="s">
@@ -19358,18 +19385,18 @@
       </c>
     </row>
     <row r="766" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A766" s="5" t="s">
+      <c r="A766" s="3" t="s">
         <v>2394</v>
       </c>
-      <c r="B766" s="5" t="s">
+      <c r="B766" s="3" t="s">
         <v>2395</v>
       </c>
-      <c r="C766" s="5" t="s">
+      <c r="C766" s="3" t="s">
         <v>2505</v>
       </c>
     </row>
     <row r="767" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A767" s="5" t="s">
+      <c r="A767" s="3" t="s">
         <v>2397</v>
       </c>
       <c r="B767" s="4" t="s">
@@ -19380,18 +19407,18 @@
       </c>
     </row>
     <row r="768" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A768" s="5" t="s">
+      <c r="A768" s="3" t="s">
         <v>2400</v>
       </c>
-      <c r="B768" s="5" t="s">
+      <c r="B768" s="3" t="s">
         <v>2401</v>
       </c>
-      <c r="C768" s="5" t="s">
+      <c r="C768" s="3" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="769" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A769" s="5" t="s">
+      <c r="A769" s="3" t="s">
         <v>2403</v>
       </c>
       <c r="B769" s="4" t="s">
@@ -19402,18 +19429,18 @@
       </c>
     </row>
     <row r="770" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A770" s="5" t="s">
+      <c r="A770" s="3" t="s">
         <v>2406</v>
       </c>
-      <c r="B770" s="5" t="s">
+      <c r="B770" s="3" t="s">
         <v>2407</v>
       </c>
-      <c r="C770" s="5" t="s">
+      <c r="C770" s="3" t="s">
         <v>2408</v>
       </c>
     </row>
     <row r="771" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A771" s="5" t="s">
+      <c r="A771" s="3" t="s">
         <v>2409</v>
       </c>
       <c r="B771" s="4" t="s">
@@ -19424,7 +19451,7 @@
       </c>
     </row>
     <row r="772" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A772" s="5" t="s">
+      <c r="A772" s="3" t="s">
         <v>2412</v>
       </c>
       <c r="B772" s="4" t="s">
@@ -19435,29 +19462,29 @@
       </c>
     </row>
     <row r="773" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A773" s="5" t="s">
+      <c r="A773" s="3" t="s">
         <v>1260</v>
       </c>
-      <c r="B773" s="5" t="s">
+      <c r="B773" s="3" t="s">
         <v>1261</v>
       </c>
-      <c r="C773" s="5" t="s">
+      <c r="C773" s="3" t="s">
         <v>1262</v>
       </c>
     </row>
     <row r="774" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A774" s="5" t="s">
+      <c r="A774" s="3" t="s">
         <v>1264</v>
       </c>
-      <c r="B774" s="5" t="s">
+      <c r="B774" s="3" t="s">
         <v>1265</v>
       </c>
-      <c r="C774" s="5" t="s">
+      <c r="C774" s="3" t="s">
         <v>1266</v>
       </c>
     </row>
     <row r="775" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A775" s="5" t="s">
+      <c r="A775" s="3" t="s">
         <v>2416</v>
       </c>
       <c r="B775" s="4" t="s">
@@ -19468,7 +19495,7 @@
       </c>
     </row>
     <row r="776" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A776" s="5" t="s">
+      <c r="A776" s="3" t="s">
         <v>2419</v>
       </c>
       <c r="B776" s="4" t="s">
@@ -19479,7 +19506,7 @@
       </c>
     </row>
     <row r="777" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A777" s="5" t="s">
+      <c r="A777" s="3" t="s">
         <v>2422</v>
       </c>
       <c r="B777" s="4" t="s">
@@ -19490,7 +19517,7 @@
       </c>
     </row>
     <row r="778" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A778" s="5" t="s">
+      <c r="A778" s="3" t="s">
         <v>2514</v>
       </c>
       <c r="B778" s="4" t="s">
@@ -19501,7 +19528,7 @@
       </c>
     </row>
     <row r="779" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A779" s="5" t="s">
+      <c r="A779" s="3" t="s">
         <v>2517</v>
       </c>
       <c r="B779" s="4" t="s">
@@ -19512,51 +19539,51 @@
       </c>
     </row>
     <row r="780" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A780" s="5" t="s">
+      <c r="A780" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="B780" s="5" t="s">
+      <c r="B780" s="3" t="s">
         <v>1269</v>
       </c>
-      <c r="C780" s="5" t="s">
+      <c r="C780" s="3" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="781" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A781" s="5" t="s">
+      <c r="A781" s="3" t="s">
         <v>1272</v>
       </c>
-      <c r="B781" s="5" t="s">
+      <c r="B781" s="3" t="s">
         <v>1273</v>
       </c>
-      <c r="C781" s="5" t="s">
+      <c r="C781" s="3" t="s">
         <v>1274</v>
       </c>
     </row>
     <row r="782" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A782" s="5" t="s">
+      <c r="A782" s="3" t="s">
         <v>1276</v>
       </c>
-      <c r="B782" s="5" t="s">
+      <c r="B782" s="3" t="s">
         <v>1277</v>
       </c>
-      <c r="C782" s="5" t="s">
+      <c r="C782" s="3" t="s">
         <v>1278</v>
       </c>
     </row>
     <row r="783" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A783" s="5" t="s">
+      <c r="A783" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="B783" s="5" t="s">
+      <c r="B783" s="3" t="s">
         <v>1281</v>
       </c>
-      <c r="C783" s="5" t="s">
+      <c r="C783" s="3" t="s">
         <v>1282</v>
       </c>
     </row>
     <row r="784" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A784" s="5" t="s">
+      <c r="A784" s="3" t="s">
         <v>2520</v>
       </c>
       <c r="B784" s="4" t="s">
@@ -19567,18 +19594,18 @@
       </c>
     </row>
     <row r="785" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A785" s="5" t="s">
+      <c r="A785" s="3" t="s">
         <v>2523</v>
       </c>
-      <c r="B785" s="5" t="s">
+      <c r="B785" s="3" t="s">
         <v>2524</v>
       </c>
-      <c r="C785" s="5" t="s">
+      <c r="C785" s="3" t="s">
         <v>2525</v>
       </c>
     </row>
     <row r="786" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A786" s="5" t="s">
+      <c r="A786" s="3" t="s">
         <v>2526</v>
       </c>
       <c r="B786" s="4" t="s">
@@ -19589,95 +19616,95 @@
       </c>
     </row>
     <row r="787" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A787" s="5" t="s">
+      <c r="A787" s="3" t="s">
         <v>2529</v>
       </c>
-      <c r="B787" s="5" t="s">
+      <c r="B787" s="3" t="s">
         <v>2530</v>
       </c>
-      <c r="C787" s="5" t="s">
+      <c r="C787" s="3" t="s">
         <v>2531</v>
       </c>
     </row>
     <row r="788" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A788" s="5" t="s">
+      <c r="A788" s="3" t="s">
         <v>1284</v>
       </c>
-      <c r="B788" s="5" t="s">
+      <c r="B788" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="C788" s="5" t="s">
+      <c r="C788" s="3" t="s">
         <v>1286</v>
       </c>
     </row>
     <row r="789" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A789" s="5" t="s">
+      <c r="A789" s="3" t="s">
         <v>1288</v>
       </c>
-      <c r="B789" s="5" t="s">
+      <c r="B789" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="C789" s="5" t="s">
+      <c r="C789" s="3" t="s">
         <v>2532</v>
       </c>
     </row>
     <row r="790" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A790" s="5" t="s">
+      <c r="A790" s="3" t="s">
         <v>2533</v>
       </c>
-      <c r="B790" s="5" t="s">
+      <c r="B790" s="3" t="s">
         <v>2534</v>
       </c>
-      <c r="C790" s="5" t="s">
+      <c r="C790" s="3" t="s">
         <v>2535</v>
       </c>
     </row>
     <row r="791" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A791" s="5" t="s">
+      <c r="A791" s="3" t="s">
         <v>2536</v>
       </c>
-      <c r="B791" s="5" t="s">
+      <c r="B791" s="3" t="s">
         <v>2537</v>
       </c>
-      <c r="C791" s="5" t="s">
+      <c r="C791" s="3" t="s">
         <v>2538</v>
       </c>
     </row>
     <row r="792" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A792" s="5" t="s">
+      <c r="A792" s="3" t="s">
         <v>1292</v>
       </c>
-      <c r="B792" s="5" t="s">
+      <c r="B792" s="3" t="s">
         <v>1293</v>
       </c>
-      <c r="C792" s="5" t="s">
+      <c r="C792" s="3" t="s">
         <v>1294</v>
       </c>
     </row>
     <row r="793" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A793" s="5" t="s">
+      <c r="A793" s="3" t="s">
         <v>1296</v>
       </c>
-      <c r="B793" s="5" t="s">
+      <c r="B793" s="3" t="s">
         <v>1297</v>
       </c>
-      <c r="C793" s="5" t="s">
+      <c r="C793" s="3" t="s">
         <v>1298</v>
       </c>
     </row>
     <row r="794" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A794" s="5" t="s">
+      <c r="A794" s="3" t="s">
         <v>1299</v>
       </c>
-      <c r="B794" s="5" t="s">
+      <c r="B794" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="C794" s="5" t="s">
+      <c r="C794" s="3" t="s">
         <v>1258</v>
       </c>
     </row>
     <row r="795" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A795" s="5" t="s">
+      <c r="A795" s="3" t="s">
         <v>2427</v>
       </c>
       <c r="B795" s="4" t="s">
@@ -19688,7 +19715,7 @@
       </c>
     </row>
     <row r="796" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A796" s="5" t="s">
+      <c r="A796" s="3" t="s">
         <v>2430</v>
       </c>
       <c r="B796" s="4" t="s">
@@ -19699,7 +19726,7 @@
       </c>
     </row>
     <row r="797" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A797" s="5" t="s">
+      <c r="A797" s="3" t="s">
         <v>2433</v>
       </c>
       <c r="B797" s="4" t="s">
@@ -19710,7 +19737,7 @@
       </c>
     </row>
     <row r="798" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A798" s="5" t="s">
+      <c r="A798" s="3" t="s">
         <v>2436</v>
       </c>
       <c r="B798" s="4" t="s">
@@ -19721,7 +19748,7 @@
       </c>
     </row>
     <row r="799" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A799" s="5" t="s">
+      <c r="A799" s="3" t="s">
         <v>2439</v>
       </c>
       <c r="B799" s="4" t="s">
@@ -19732,7 +19759,7 @@
       </c>
     </row>
     <row r="800" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A800" s="5" t="s">
+      <c r="A800" s="3" t="s">
         <v>2442</v>
       </c>
       <c r="B800" s="4" t="s">
@@ -19743,7 +19770,7 @@
       </c>
     </row>
     <row r="801" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A801" s="5" t="s">
+      <c r="A801" s="3" t="s">
         <v>2445</v>
       </c>
       <c r="B801" s="4" t="s">
@@ -19754,7 +19781,7 @@
       </c>
     </row>
     <row r="802" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A802" s="5" t="s">
+      <c r="A802" s="3" t="s">
         <v>2448</v>
       </c>
       <c r="B802" s="4" t="s">
@@ -19765,7 +19792,7 @@
       </c>
     </row>
     <row r="803" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A803" s="5" t="s">
+      <c r="A803" s="3" t="s">
         <v>2451</v>
       </c>
       <c r="B803" s="4" t="s">
@@ -19776,7 +19803,7 @@
       </c>
     </row>
     <row r="804" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A804" s="5" t="s">
+      <c r="A804" s="3" t="s">
         <v>2454</v>
       </c>
       <c r="B804" s="4" t="s">
@@ -19787,7 +19814,7 @@
       </c>
     </row>
     <row r="805" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A805" s="5" t="s">
+      <c r="A805" s="3" t="s">
         <v>2457</v>
       </c>
       <c r="B805" s="4" t="s">
@@ -19798,7 +19825,7 @@
       </c>
     </row>
     <row r="806" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A806" s="5" t="s">
+      <c r="A806" s="3" t="s">
         <v>2460</v>
       </c>
       <c r="B806" s="4" t="s">
@@ -19809,7 +19836,7 @@
       </c>
     </row>
     <row r="807" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A807" s="5" t="s">
+      <c r="A807" s="3" t="s">
         <v>2463</v>
       </c>
       <c r="B807" s="4" t="s">
@@ -19820,13 +19847,13 @@
       </c>
     </row>
     <row r="808" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A808" s="5" t="s">
+      <c r="A808" s="3" t="s">
         <v>1300</v>
       </c>
-      <c r="B808" s="5" t="s">
+      <c r="B808" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C808" s="5" t="s">
+      <c r="C808" s="3" t="s">
         <v>87</v>
       </c>
     </row>
@@ -19842,62 +19869,62 @@
       </c>
     </row>
     <row r="811" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A811" s="5" t="s">
+      <c r="A811" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="B811" s="5" t="s">
+      <c r="B811" s="3" t="s">
         <v>1242</v>
       </c>
-      <c r="C811" s="5" t="s">
+      <c r="C811" s="3" t="s">
         <v>1243</v>
       </c>
     </row>
     <row r="812" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A812" s="5" t="s">
+      <c r="A812" s="3" t="s">
         <v>1245</v>
       </c>
-      <c r="B812" s="5" t="s">
+      <c r="B812" s="3" t="s">
         <v>1246</v>
       </c>
-      <c r="C812" s="5" t="s">
+      <c r="C812" s="3" t="s">
         <v>1247</v>
       </c>
     </row>
     <row r="813" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A813" s="5" t="s">
+      <c r="A813" s="3" t="s">
         <v>1249</v>
       </c>
-      <c r="B813" s="5" t="s">
+      <c r="B813" s="3" t="s">
         <v>1250</v>
       </c>
-      <c r="C813" s="5" t="s">
+      <c r="C813" s="3" t="s">
         <v>1251</v>
       </c>
     </row>
     <row r="814" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A814" s="5" t="s">
+      <c r="A814" s="3" t="s">
         <v>1253</v>
       </c>
-      <c r="B814" s="5" t="s">
+      <c r="B814" s="3" t="s">
         <v>1254</v>
       </c>
-      <c r="C814" s="5" t="s">
+      <c r="C814" s="3" t="s">
         <v>1255</v>
       </c>
     </row>
     <row r="815" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A815" s="5" t="s">
+      <c r="A815" s="3" t="s">
         <v>1256</v>
       </c>
-      <c r="B815" s="5" t="s">
+      <c r="B815" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="C815" s="5" t="s">
+      <c r="C815" s="3" t="s">
         <v>1258</v>
       </c>
     </row>
     <row r="816" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A816" s="5" t="s">
+      <c r="A816" s="3" t="s">
         <v>2352</v>
       </c>
       <c r="B816" s="4" t="s">
@@ -19908,18 +19935,18 @@
       </c>
     </row>
     <row r="817" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A817" s="5" t="s">
+      <c r="A817" s="3" t="s">
         <v>2355</v>
       </c>
-      <c r="B817" s="5" t="s">
+      <c r="B817" s="3" t="s">
         <v>2356</v>
       </c>
-      <c r="C817" s="5" t="s">
+      <c r="C817" s="3" t="s">
         <v>1102</v>
       </c>
     </row>
     <row r="818" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A818" s="5" t="s">
+      <c r="A818" s="3" t="s">
         <v>2357</v>
       </c>
       <c r="B818" s="4" t="s">
@@ -19930,18 +19957,18 @@
       </c>
     </row>
     <row r="819" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A819" s="5" t="s">
+      <c r="A819" s="3" t="s">
         <v>2360</v>
       </c>
-      <c r="B819" s="5" t="s">
+      <c r="B819" s="3" t="s">
         <v>2361</v>
       </c>
-      <c r="C819" s="5" t="s">
+      <c r="C819" s="3" t="s">
         <v>2497</v>
       </c>
     </row>
     <row r="820" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A820" s="5" t="s">
+      <c r="A820" s="3" t="s">
         <v>2363</v>
       </c>
       <c r="B820" s="4" t="s">
@@ -19952,18 +19979,18 @@
       </c>
     </row>
     <row r="821" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A821" s="5" t="s">
+      <c r="A821" s="3" t="s">
         <v>2366</v>
       </c>
-      <c r="B821" s="5" t="s">
+      <c r="B821" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="C821" s="5" t="s">
+      <c r="C821" s="3" t="s">
         <v>1073</v>
       </c>
     </row>
     <row r="822" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A822" s="5" t="s">
+      <c r="A822" s="3" t="s">
         <v>2367</v>
       </c>
       <c r="B822" s="4" t="s">
@@ -19974,18 +20001,18 @@
       </c>
     </row>
     <row r="823" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A823" s="5" t="s">
+      <c r="A823" s="3" t="s">
         <v>2370</v>
       </c>
-      <c r="B823" s="5" t="s">
+      <c r="B823" s="3" t="s">
         <v>2371</v>
       </c>
-      <c r="C823" s="5" t="s">
+      <c r="C823" s="3" t="s">
         <v>2372</v>
       </c>
     </row>
     <row r="824" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A824" s="5" t="s">
+      <c r="A824" s="3" t="s">
         <v>2373</v>
       </c>
       <c r="B824" s="4" t="s">
@@ -19996,18 +20023,18 @@
       </c>
     </row>
     <row r="825" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A825" s="5" t="s">
+      <c r="A825" s="3" t="s">
         <v>2376</v>
       </c>
-      <c r="B825" s="5" t="s">
+      <c r="B825" s="3" t="s">
         <v>1081</v>
       </c>
-      <c r="C825" s="5" t="s">
+      <c r="C825" s="3" t="s">
         <v>1082</v>
       </c>
     </row>
     <row r="826" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A826" s="5" t="s">
+      <c r="A826" s="3" t="s">
         <v>2377</v>
       </c>
       <c r="B826" s="4" t="s">
@@ -20018,18 +20045,18 @@
       </c>
     </row>
     <row r="827" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A827" s="5" t="s">
+      <c r="A827" s="3" t="s">
         <v>2380</v>
       </c>
-      <c r="B827" s="5" t="s">
+      <c r="B827" s="3" t="s">
         <v>2381</v>
       </c>
-      <c r="C827" s="5" t="s">
+      <c r="C827" s="3" t="s">
         <v>2382</v>
       </c>
     </row>
     <row r="828" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A828" s="5" t="s">
+      <c r="A828" s="3" t="s">
         <v>2383</v>
       </c>
       <c r="B828" s="4" t="s">
@@ -20040,18 +20067,18 @@
       </c>
     </row>
     <row r="829" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A829" s="5" t="s">
+      <c r="A829" s="3" t="s">
         <v>2386</v>
       </c>
-      <c r="B829" s="5" t="s">
+      <c r="B829" s="3" t="s">
         <v>1085</v>
       </c>
-      <c r="C829" s="5" t="s">
+      <c r="C829" s="3" t="s">
         <v>1086</v>
       </c>
     </row>
     <row r="830" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A830" s="5" t="s">
+      <c r="A830" s="3" t="s">
         <v>2387</v>
       </c>
       <c r="B830" s="4" t="s">
@@ -20062,18 +20089,18 @@
       </c>
     </row>
     <row r="831" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A831" s="5" t="s">
+      <c r="A831" s="3" t="s">
         <v>2390</v>
       </c>
-      <c r="B831" s="5" t="s">
+      <c r="B831" s="3" t="s">
         <v>1089</v>
       </c>
-      <c r="C831" s="5" t="s">
+      <c r="C831" s="3" t="s">
         <v>1090</v>
       </c>
     </row>
     <row r="832" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A832" s="5" t="s">
+      <c r="A832" s="3" t="s">
         <v>2391</v>
       </c>
       <c r="B832" s="4" t="s">
@@ -20084,18 +20111,18 @@
       </c>
     </row>
     <row r="833" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A833" s="5" t="s">
+      <c r="A833" s="3" t="s">
         <v>2394</v>
       </c>
-      <c r="B833" s="5" t="s">
+      <c r="B833" s="3" t="s">
         <v>2395</v>
       </c>
-      <c r="C833" s="5" t="s">
+      <c r="C833" s="3" t="s">
         <v>2505</v>
       </c>
     </row>
     <row r="834" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A834" s="5" t="s">
+      <c r="A834" s="3" t="s">
         <v>2397</v>
       </c>
       <c r="B834" s="4" t="s">
@@ -20106,18 +20133,18 @@
       </c>
     </row>
     <row r="835" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A835" s="5" t="s">
+      <c r="A835" s="3" t="s">
         <v>2400</v>
       </c>
-      <c r="B835" s="5" t="s">
+      <c r="B835" s="3" t="s">
         <v>2401</v>
       </c>
-      <c r="C835" s="5" t="s">
+      <c r="C835" s="3" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="836" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A836" s="5" t="s">
+      <c r="A836" s="3" t="s">
         <v>2403</v>
       </c>
       <c r="B836" s="4" t="s">
@@ -20128,18 +20155,18 @@
       </c>
     </row>
     <row r="837" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A837" s="5" t="s">
+      <c r="A837" s="3" t="s">
         <v>2406</v>
       </c>
-      <c r="B837" s="5" t="s">
+      <c r="B837" s="3" t="s">
         <v>2407</v>
       </c>
-      <c r="C837" s="5" t="s">
+      <c r="C837" s="3" t="s">
         <v>2408</v>
       </c>
     </row>
     <row r="838" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A838" s="5" t="s">
+      <c r="A838" s="3" t="s">
         <v>2409</v>
       </c>
       <c r="B838" s="4" t="s">
@@ -20150,7 +20177,7 @@
       </c>
     </row>
     <row r="839" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A839" s="5" t="s">
+      <c r="A839" s="3" t="s">
         <v>2412</v>
       </c>
       <c r="B839" s="4" t="s">
@@ -20161,29 +20188,29 @@
       </c>
     </row>
     <row r="840" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A840" s="5" t="s">
+      <c r="A840" s="3" t="s">
         <v>1260</v>
       </c>
-      <c r="B840" s="5" t="s">
+      <c r="B840" s="3" t="s">
         <v>1261</v>
       </c>
-      <c r="C840" s="5" t="s">
+      <c r="C840" s="3" t="s">
         <v>1262</v>
       </c>
     </row>
     <row r="841" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A841" s="5" t="s">
+      <c r="A841" s="3" t="s">
         <v>1264</v>
       </c>
-      <c r="B841" s="5" t="s">
+      <c r="B841" s="3" t="s">
         <v>1265</v>
       </c>
-      <c r="C841" s="5" t="s">
+      <c r="C841" s="3" t="s">
         <v>1266</v>
       </c>
     </row>
     <row r="842" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A842" s="5" t="s">
+      <c r="A842" s="3" t="s">
         <v>2416</v>
       </c>
       <c r="B842" s="4" t="s">
@@ -20194,7 +20221,7 @@
       </c>
     </row>
     <row r="843" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A843" s="5" t="s">
+      <c r="A843" s="3" t="s">
         <v>2419</v>
       </c>
       <c r="B843" s="4" t="s">
@@ -20205,7 +20232,7 @@
       </c>
     </row>
     <row r="844" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A844" s="5" t="s">
+      <c r="A844" s="3" t="s">
         <v>2422</v>
       </c>
       <c r="B844" s="4" t="s">
@@ -20216,7 +20243,7 @@
       </c>
     </row>
     <row r="845" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A845" s="5" t="s">
+      <c r="A845" s="3" t="s">
         <v>2514</v>
       </c>
       <c r="B845" s="4" t="s">
@@ -20227,7 +20254,7 @@
       </c>
     </row>
     <row r="846" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A846" s="5" t="s">
+      <c r="A846" s="3" t="s">
         <v>2517</v>
       </c>
       <c r="B846" s="4" t="s">
@@ -20238,51 +20265,51 @@
       </c>
     </row>
     <row r="847" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A847" s="5" t="s">
+      <c r="A847" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="B847" s="5" t="s">
+      <c r="B847" s="3" t="s">
         <v>1269</v>
       </c>
-      <c r="C847" s="5" t="s">
+      <c r="C847" s="3" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="848" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A848" s="5" t="s">
+      <c r="A848" s="3" t="s">
         <v>1272</v>
       </c>
-      <c r="B848" s="5" t="s">
+      <c r="B848" s="3" t="s">
         <v>1273</v>
       </c>
-      <c r="C848" s="5" t="s">
+      <c r="C848" s="3" t="s">
         <v>1274</v>
       </c>
     </row>
     <row r="849" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A849" s="5" t="s">
+      <c r="A849" s="3" t="s">
         <v>1276</v>
       </c>
-      <c r="B849" s="5" t="s">
+      <c r="B849" s="3" t="s">
         <v>1277</v>
       </c>
-      <c r="C849" s="5" t="s">
+      <c r="C849" s="3" t="s">
         <v>1278</v>
       </c>
     </row>
     <row r="850" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A850" s="5" t="s">
+      <c r="A850" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="B850" s="5" t="s">
+      <c r="B850" s="3" t="s">
         <v>1281</v>
       </c>
-      <c r="C850" s="5" t="s">
+      <c r="C850" s="3" t="s">
         <v>1282</v>
       </c>
     </row>
     <row r="851" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A851" s="5" t="s">
+      <c r="A851" s="3" t="s">
         <v>2520</v>
       </c>
       <c r="B851" s="4" t="s">
@@ -20293,18 +20320,18 @@
       </c>
     </row>
     <row r="852" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A852" s="5" t="s">
+      <c r="A852" s="3" t="s">
         <v>2523</v>
       </c>
-      <c r="B852" s="5" t="s">
+      <c r="B852" s="3" t="s">
         <v>2524</v>
       </c>
-      <c r="C852" s="5" t="s">
+      <c r="C852" s="3" t="s">
         <v>2525</v>
       </c>
     </row>
     <row r="853" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A853" s="5" t="s">
+      <c r="A853" s="3" t="s">
         <v>2526</v>
       </c>
       <c r="B853" s="4" t="s">
@@ -20315,95 +20342,95 @@
       </c>
     </row>
     <row r="854" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A854" s="5" t="s">
+      <c r="A854" s="3" t="s">
         <v>2529</v>
       </c>
-      <c r="B854" s="5" t="s">
+      <c r="B854" s="3" t="s">
         <v>2530</v>
       </c>
-      <c r="C854" s="5" t="s">
+      <c r="C854" s="3" t="s">
         <v>2531</v>
       </c>
     </row>
     <row r="855" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A855" s="5" t="s">
+      <c r="A855" s="3" t="s">
         <v>1284</v>
       </c>
-      <c r="B855" s="5" t="s">
+      <c r="B855" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="C855" s="5" t="s">
+      <c r="C855" s="3" t="s">
         <v>1286</v>
       </c>
     </row>
     <row r="856" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A856" s="5" t="s">
+      <c r="A856" s="3" t="s">
         <v>1288</v>
       </c>
-      <c r="B856" s="5" t="s">
+      <c r="B856" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="C856" s="5" t="s">
+      <c r="C856" s="3" t="s">
         <v>2532</v>
       </c>
     </row>
     <row r="857" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A857" s="5" t="s">
+      <c r="A857" s="3" t="s">
         <v>2533</v>
       </c>
-      <c r="B857" s="5" t="s">
+      <c r="B857" s="3" t="s">
         <v>2534</v>
       </c>
-      <c r="C857" s="5" t="s">
+      <c r="C857" s="3" t="s">
         <v>2535</v>
       </c>
     </row>
     <row r="858" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A858" s="5" t="s">
+      <c r="A858" s="3" t="s">
         <v>2536</v>
       </c>
-      <c r="B858" s="5" t="s">
+      <c r="B858" s="3" t="s">
         <v>2537</v>
       </c>
-      <c r="C858" s="5" t="s">
+      <c r="C858" s="3" t="s">
         <v>2538</v>
       </c>
     </row>
     <row r="859" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A859" s="5" t="s">
+      <c r="A859" s="3" t="s">
         <v>1292</v>
       </c>
-      <c r="B859" s="5" t="s">
+      <c r="B859" s="3" t="s">
         <v>1293</v>
       </c>
-      <c r="C859" s="5" t="s">
+      <c r="C859" s="3" t="s">
         <v>1294</v>
       </c>
     </row>
     <row r="860" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A860" s="5" t="s">
+      <c r="A860" s="3" t="s">
         <v>1296</v>
       </c>
-      <c r="B860" s="5" t="s">
+      <c r="B860" s="3" t="s">
         <v>1297</v>
       </c>
-      <c r="C860" s="5" t="s">
+      <c r="C860" s="3" t="s">
         <v>1298</v>
       </c>
     </row>
     <row r="861" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A861" s="5" t="s">
+      <c r="A861" s="3" t="s">
         <v>1299</v>
       </c>
-      <c r="B861" s="5" t="s">
+      <c r="B861" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="C861" s="5" t="s">
+      <c r="C861" s="3" t="s">
         <v>1258</v>
       </c>
     </row>
     <row r="862" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A862" s="5" t="s">
+      <c r="A862" s="3" t="s">
         <v>2427</v>
       </c>
       <c r="B862" s="4" t="s">
@@ -20414,7 +20441,7 @@
       </c>
     </row>
     <row r="863" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A863" s="5" t="s">
+      <c r="A863" s="3" t="s">
         <v>2430</v>
       </c>
       <c r="B863" s="4" t="s">
@@ -20425,7 +20452,7 @@
       </c>
     </row>
     <row r="864" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A864" s="5" t="s">
+      <c r="A864" s="3" t="s">
         <v>2433</v>
       </c>
       <c r="B864" s="4" t="s">
@@ -20436,7 +20463,7 @@
       </c>
     </row>
     <row r="865" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A865" s="5" t="s">
+      <c r="A865" s="3" t="s">
         <v>2436</v>
       </c>
       <c r="B865" s="4" t="s">
@@ -20447,7 +20474,7 @@
       </c>
     </row>
     <row r="866" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A866" s="5" t="s">
+      <c r="A866" s="3" t="s">
         <v>2439</v>
       </c>
       <c r="B866" s="4" t="s">
@@ -20458,7 +20485,7 @@
       </c>
     </row>
     <row r="867" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A867" s="5" t="s">
+      <c r="A867" s="3" t="s">
         <v>2442</v>
       </c>
       <c r="B867" s="4" t="s">
@@ -20469,7 +20496,7 @@
       </c>
     </row>
     <row r="868" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A868" s="5" t="s">
+      <c r="A868" s="3" t="s">
         <v>2445</v>
       </c>
       <c r="B868" s="4" t="s">
@@ -20480,7 +20507,7 @@
       </c>
     </row>
     <row r="869" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A869" s="5" t="s">
+      <c r="A869" s="3" t="s">
         <v>2448</v>
       </c>
       <c r="B869" s="4" t="s">
@@ -20491,7 +20518,7 @@
       </c>
     </row>
     <row r="870" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A870" s="5" t="s">
+      <c r="A870" s="3" t="s">
         <v>2451</v>
       </c>
       <c r="B870" s="4" t="s">
@@ -20502,7 +20529,7 @@
       </c>
     </row>
     <row r="871" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A871" s="5" t="s">
+      <c r="A871" s="3" t="s">
         <v>2454</v>
       </c>
       <c r="B871" s="4" t="s">
@@ -20513,7 +20540,7 @@
       </c>
     </row>
     <row r="872" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A872" s="5" t="s">
+      <c r="A872" s="3" t="s">
         <v>2457</v>
       </c>
       <c r="B872" s="4" t="s">
@@ -20524,7 +20551,7 @@
       </c>
     </row>
     <row r="873" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A873" s="5" t="s">
+      <c r="A873" s="3" t="s">
         <v>2460</v>
       </c>
       <c r="B873" s="4" t="s">
@@ -20535,7 +20562,7 @@
       </c>
     </row>
     <row r="874" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A874" s="5" t="s">
+      <c r="A874" s="3" t="s">
         <v>2463</v>
       </c>
       <c r="B874" s="4" t="s">
@@ -20546,13 +20573,13 @@
       </c>
     </row>
     <row r="875" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A875" s="5" t="s">
+      <c r="A875" s="3" t="s">
         <v>1300</v>
       </c>
-      <c r="B875" s="5" t="s">
+      <c r="B875" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C875" s="5" t="s">
+      <c r="C875" s="3" t="s">
         <v>87</v>
       </c>
     </row>
@@ -20567,6 +20594,41 @@
         <v>2571</v>
       </c>
     </row>
+    <row r="877" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A877" s="5" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B877" s="5" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C877" s="5" t="s">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="878" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A878" s="5" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B878" s="5" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C878" s="5" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="879" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A879" s="5" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B879" s="5" t="s">
+        <v>2579</v>
+      </c>
+      <c r="C879" s="5" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/multi.xlsx
+++ b/multi.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3311" uniqueCount="2581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3338" uniqueCount="2591">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -7733,47 +7733,104 @@
     <t xml:space="preserve">Actualización del peso: Actualiza el peso registrado para el mes en curso.</t>
   </si>
   <si>
+    <t xml:space="preserve">btn_edit_altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📏 Altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📏 Height</t>
+  </si>
+  <si>
+    <t xml:space="preserve">btn_edit_ocup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏃 Ocupación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏃 Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">btn_edit_nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👤 Nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👤 Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perfil_lbl_nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perfil_lbl_ocupacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocupación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🪑 Nivel 1 (Sedentario/Ligero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🪑 Level 1 (Sedentary/Light)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🚶 Nivel 2 (Moderado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🚶 Level 2 (Moderate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏃 Nivel 3 (Intenso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏃 Level 3 (Intense)</t>
+  </si>
+  <si>
     <t xml:space="preserve">start_mensaje_bienvenida</t>
   </si>
   <si>
     <t xml:space="preserve">👋 ¡Bienvenido a tu Bot Nutricional Personalizado!
 Guía rápida de comandos e ingestas disponibles:
 📌 Comandos Principales:
-• /inicio: Resumen de los comando y PDF del manual.
-• /alta: Apertura de cuenta ingresando los datos.
-• /presi: Registro y consulta de presión arterial.
+• /inicio: Resumen de comandos y PDF del manual.
+• /alta: Apertura de cuenta.
+• /presi: Registro de presión arterial.
 /presi 120,80,70,nota (Completo)
 /presi 120,80,70 (Sin nota)
 /presi 120,80 (Solo presión)
 /presi AAAA-MM Promedio mensual y PDF.
-• /diario: Ingestas del día detalle nutricional y PDF.
-• /semanal: Estadística semanal (calorías, fibras, etc).
-• /mensual: Reporte con estimación de peso y PDF.
-• /perfil: Actualizacion de datos biométricos.
+• /diario: Ingestas del día y PDF.
+• /semanal: Estadística semanal.
+• /mensual: Reporte de peso y PDF.
+• /perfil: Actualización de datos biométricos.
 • /peso: Actualiza el peso del mes /peso 90.
-• /GET: Actualiza el gasto calorico total /GET 2150.
-• /eliminar: Borra ingestas seleccionando dia.
-• /barra: ingreso x codigo de barras /barra Número.
-• /comidas: Listado predeterminadas y PDF.
-• /receta: Calculadora Web para registrar comidas.
+• /GET: Actualiza el gasto calórico /GET 2150.
+• /eliminar: Borra ingestas por día.
+• /barra: Ingreso por código de barras.
+• /comidas: Listado predeterminado y PDF.
+• /receta: Calculadora Web.
 • /borracomida: Borra comidas de la planilla.
 📌 Métodos de Registro de ingestas:
-• Con IA: Texto, 🎤 Notas de voz, 📸 Fotos .
-• Modificación parcial: Editar por item y reenvío a la IA
-DESCRIPCION manteniendo el peso
-DESCRIPCION,PESO modificando ambos campos
-,PESO manteniendo descripción
-• Sin IA: Comidas precargadas y actividad física:
+• Con IA: Texto, 🎤 Notas de voz, 📸 Fotos.
+• Modificación parcial:
+DESCRIPCION (mantiene peso)
+DESCRIPCION,PESO (modifica ambos)
+,PESO (mantiene descripción)
+• Sin IA (Precargadas):
 `*DESAYUNO`: menú completo
-`*PIZZA` (porcion),4: 4 porciones de pizza
-`*TORTA` (fraccion x 100g),1.5: 150 g de torta
-📌 Métodos de Registro de actividades:
+`*PIZZA` (porcion),4: 4 porciones
+`*TORTA` (fraccion x 100g),1.5: 150 g
+📌 Registro de Actividades:
 • Con IA: Texto, 🎤 Notas de voz.
-• Modificación parcial: Editar ingresando calorias
-📌 Métodos de Registro de Presion
-• Con IA: 📸 Fotos .
-• Confirmacion: ingresando nota aclaratoria
-📄 Te adjuntamos el Manual de Usuario completo en formato PDF.</t>
+• Modificación parcial: Editar ingresando calorias.
+📌 Registro de Presión:
+• Con IA: 📸 Fotos.
+• Confirmación: ingresando nota.
+📄 Te adjuntamos el Manual de Usuario en PDF.</t>
   </si>
   <si>
     <t xml:space="preserve">👋 Welcome to your Personalized Nutritional Bot!
@@ -7781,66 +7838,39 @@
 📌 Main Commands:
 • /start: Summary of commands and manual PDF.
 • /alta: Account opening by entering data.
-• /presi: Blood pressure registration and consultation.
+• /presi: Blood pressure registration.
 /presi 120,80,70,note (Complete)
 /presi 120,80,70 (Without note)
 /presi 120,80 (Pressure only)
 /presi YYYY-MM Monthly average and PDF.
-• /day: Daily food intake nutritional detail and PDF.
-• /week: Weekly statistics (calories, fiber, etc.).
+• /day: Daily food intake detail and PDF.
+• /week: Weekly statistics.
 • /month: Report with weight estimation and PDF.
 • /profile: Update biometric data.
 • /weight: Update monthly weight /peso 90.
 • /GET: Update total caloric expenditure /GET 2150.
 • /delete: Delete intakes by selecting a day.
-• /barcode: Barcode entry /barcode Number.
+• /barcode: Barcode entry.
 • /meals: Default list and PDF.
-• /recipe: Web calculator to log meals.
+• /recipe: Web calculator.
 • /delmeal: Delete meals from the sheet.
 📌 Intake Registration Methods:
 • With AI: Text, 🎤 Voice notes, 📸 Photos.
-• Partial modification: Edit by item and resend to AI
-DESCRIPTION keeping weight
-DESCRIPTION,WEIGHT modifying both fields
-,WEIGHT keeping description
-• Without AI: Preloaded meals and physical activity:
+• Partial modification:
+DESCRIPTION (keeping weight)
+DESCRIPTION,WEIGHT (modifying both)
+,WEIGHT (keeping description)
+• Without AI (Preloaded):
 `*BREAKFAST`: full menu
-`*PIZZA` (portion),4: 4 pizza portions
-`*CAKE` (fraction x 100g),1.5: 150 g of cake
+`*PIZZA` (portion),4: 4 portions
+`*CAKE` (fraction x 100g),1.5: 150 g
 📌 Activity Registration Methods:
 • With AI: Text, 🎤 Voice notes.
 • Partial modification: Edit by entering calories.
-📌 Blood Pressure Registration Methods
+📌 Blood Pressure Registration:
 • With AI: 📸 Photos.
 • Confirmation: entering clarifying note.
-📄 Attached is the complete User Manual in PDF format.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">btn_edit_altura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📏 Altura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📏 Height</t>
-  </si>
-  <si>
-    <t xml:space="preserve">btn_edit_ocup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🏃 Ocupación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🏃 Occupation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">btn_edit_nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👤 Nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👤 Name</t>
+📄 Attached is the complete User Manual in PDF.</t>
   </si>
 </sst>
 </file>
@@ -20583,7 +20613,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="876" customFormat="false" ht="1278.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="876" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A876" s="5" t="s">
         <v>2569</v>
       </c>
@@ -20621,12 +20651,114 @@
         <v>2578</v>
       </c>
       <c r="B879" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="C879" s="5" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="880" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A880" s="5" t="s">
         <v>2579</v>
       </c>
-      <c r="C879" s="5" t="s">
+      <c r="B880" s="5" t="s">
         <v>2580</v>
       </c>
-    </row>
+      <c r="C880" s="5" t="s">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="881" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A881" s="5" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B881" s="5" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C881" s="5" t="s">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="882" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A882" s="5" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B882" s="5" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C882" s="5" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="883" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A883" s="5" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B883" s="5" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C883" s="5" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="884" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A884" s="5" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B884" s="5" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C884" s="5" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="885" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A885" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B885" s="5" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C885" s="5" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="886" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A886" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B886" s="5" t="s">
+        <v>2584</v>
+      </c>
+      <c r="C886" s="5" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="887" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A887" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B887" s="5" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C887" s="5" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="888" customFormat="false" ht="1154.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A888" s="5" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B888" s="5" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C888" s="5" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/multi.xlsx
+++ b/multi.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Bueno, ya creé la tabla. Se lla" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Bueno, ya creé la tabla. Se lla" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3338" uniqueCount="2591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="2624">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -7871,6 +7871,105 @@
 • With AI: 📸 Photos.
 • Confirmation: entering clarifying note.
 📄 Attached is the complete User Manual in PDF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable (variables)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Español (ES)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inglés (EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herramienta avanzada para registrar y calcular recetas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced tool to record and calculate recipes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usuario Conectado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connected User</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingredientes y Cantidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingredients and Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gramos Totales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Grams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculando macronutrientes...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculating macronutrients...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ Peso (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ Weight (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔥 Calorías</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔥 Calories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥩 Proteínas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥩 Proteins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥑 Grasas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥑 Fats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍞 Carbos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍞 Carbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🌾 Fibras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🌾 Fibers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_th_totales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual_pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espanol.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English.pdf</t>
   </si>
 </sst>
 </file>
@@ -7961,7 +8060,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7986,6 +8085,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7998,119 +8101,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18A303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369A3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A33E03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8E03A3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="C99C00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="C9211E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000EE"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551A8B"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AMJ1048576"/>
-  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.796875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.95"/>
@@ -20756,6 +20753,270 @@
         <v>2590</v>
       </c>
     </row>
+    <row r="889" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A889" s="6" t="s">
+        <v>2591</v>
+      </c>
+      <c r="B889" s="6" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C889" s="6" t="s">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="890" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A890" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B890" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C890" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="891" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A891" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B891" s="5" t="s">
+        <v>2594</v>
+      </c>
+      <c r="C891" s="5" t="s">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="892" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A892" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B892" s="5" t="s">
+        <v>2596</v>
+      </c>
+      <c r="C892" s="5" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="893" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A893" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B893" s="5" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C893" s="5" t="s">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="894" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A894" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B894" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="C894" s="5" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="895" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A895" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B895" s="5" t="s">
+        <v>2600</v>
+      </c>
+      <c r="C895" s="5" t="s">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="896" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A896" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B896" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C896" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="897" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A897" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B897" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C897" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="898" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A898" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B898" s="5" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C898" s="5" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="899" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A899" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B899" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C899" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="900" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A900" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B900" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C900" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="901" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A901" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B901" s="5" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C901" s="5" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="902" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A902" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B902" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="C902" s="5" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="903" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A903" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B903" s="5" t="s">
+        <v>2606</v>
+      </c>
+      <c r="C903" s="5" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="904" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A904" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B904" s="5" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C904" s="5" t="s">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="905" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A905" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B905" s="5" t="s">
+        <v>2610</v>
+      </c>
+      <c r="C905" s="5" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="906" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A906" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B906" s="5" t="s">
+        <v>2612</v>
+      </c>
+      <c r="C906" s="5" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="907" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A907" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B907" s="5" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C907" s="5" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="908" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A908" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B908" s="5" t="s">
+        <v>2616</v>
+      </c>
+      <c r="C908" s="5" t="s">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="909" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A909" s="5" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B909" s="5" t="s">
+        <v>2619</v>
+      </c>
+      <c r="C909" s="5" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="910" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A910" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B910" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C910" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="911" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A911" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B911" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C911" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="912" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A912" s="5" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B912" s="5" t="s">
+        <v>2622</v>
+      </c>
+      <c r="C912" s="5" t="s">
+        <v>2623</v>
+      </c>
+    </row>
     <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/multi.xlsx
+++ b/multi.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="720">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -28,10 +28,22 @@
     <t xml:space="preserve">ES</t>
   </si>
   <si>
+    <t xml:space="preserve">EN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT</t>
+  </si>
+  <si>
     <t xml:space="preserve">lenguajes</t>
   </si>
   <si>
     <t xml:space="preserve">Español</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italiano</t>
   </si>
   <si>
     <t xml:space="preserve">banderas</t>
@@ -2255,40 +2267,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2304,2960 +2312,3078 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D368"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.7"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>2</v>
+      <c r="A2" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>4</v>
+      <c r="A3" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B49" s="3" t="s">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
+      <c r="B47" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B52" s="6" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
+      <c r="B50" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B51" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B52" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B53" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B55" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B59" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B60" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B65" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="s">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B66" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="s">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B67" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5" t="s">
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B68" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B69" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5" t="s">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B70" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5" t="s">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B71" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5" t="s">
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B72" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5" t="s">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B73" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5" t="s">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B74" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5" t="s">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B75" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="5" t="s">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B76" s="5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5" t="s">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B77" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="5" t="s">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B78" s="5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5" t="s">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B79" s="5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="5" t="s">
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B80" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="5" t="s">
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B81" s="5" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="s">
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B82" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5" t="s">
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B83" s="5" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="5" t="s">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B84" s="5" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5" t="s">
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B85" s="5" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5" t="s">
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B86" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5" t="s">
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B87" s="5" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5" t="s">
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B88" s="5" t="s">
         <v>174</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>50</v>
+        <v>191</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>35</v>
+        <v>192</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>126</v>
+        <v>235</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>114</v>
+        <v>280</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>192</v>
+        <v>285</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>273</v>
+        <v>356</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B188" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B192" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B193" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B195" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>116</v>
+        <v>385</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B198" s="3" t="s">
-        <v>118</v>
+        <v>386</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>122</v>
+        <v>391</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B211" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B212" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B219" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="B220" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="B221" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B223" s="3" t="s">
-        <v>431</v>
+        <v>434</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="B230" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="B235" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B236" s="3" t="s">
-        <v>457</v>
+        <v>460</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B237" s="3" t="s">
-        <v>459</v>
+        <v>462</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B238" s="3" t="s">
-        <v>461</v>
+        <v>464</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="B239" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="B240" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="B241" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>471</v>
+        <v>474</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>473</v>
+        <v>476</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>475</v>
+        <v>478</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="B246" s="3" t="s">
-        <v>477</v>
+        <v>480</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>479</v>
+        <v>482</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B249" s="3" t="s">
-        <v>483</v>
+        <v>486</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>485</v>
+        <v>488</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B251" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="B253" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B256" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>501</v>
+        <v>504</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="B259" s="3" t="s">
-        <v>503</v>
+        <v>506</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>505</v>
+        <v>508</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="B261" s="3" t="s">
-        <v>507</v>
+        <v>510</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="B262" s="3" t="s">
-        <v>509</v>
+        <v>512</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B263" s="3" t="s">
-        <v>511</v>
+        <v>514</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="B264" s="3" t="s">
-        <v>513</v>
+        <v>516</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="B265" s="3" t="s">
-        <v>515</v>
+        <v>518</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>517</v>
+        <v>520</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="B267" s="3" t="s">
-        <v>427</v>
+        <v>522</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="B268" s="3" t="s">
-        <v>520</v>
+        <v>523</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="B269" s="3" t="s">
-        <v>522</v>
+        <v>525</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B270" s="3" t="s">
-        <v>524</v>
+        <v>527</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="B271" s="3" t="s">
-        <v>526</v>
+        <v>529</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="B272" s="3" t="s">
-        <v>528</v>
+        <v>531</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="B273" s="3" t="s">
-        <v>530</v>
+        <v>533</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="B274" s="3" t="s">
-        <v>532</v>
+        <v>535</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B275" s="3" t="s">
-        <v>534</v>
+        <v>537</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="B276" s="3" t="s">
-        <v>536</v>
+        <v>539</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="B277" s="3" t="s">
-        <v>538</v>
+        <v>541</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="B278" s="3" t="s">
-        <v>540</v>
+        <v>543</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="B279" s="3" t="s">
-        <v>542</v>
+        <v>545</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="B280" s="3" t="s">
-        <v>544</v>
+        <v>547</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="B281" s="3" t="s">
-        <v>546</v>
+        <v>549</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>548</v>
+        <v>551</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>550</v>
+        <v>553</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="B284" s="3" t="s">
-        <v>552</v>
+        <v>555</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="B285" s="3" t="s">
-        <v>554</v>
+        <v>557</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="B286" s="3" t="s">
-        <v>556</v>
+        <v>559</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="B287" s="3" t="s">
-        <v>50</v>
+        <v>561</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="B288" s="3" t="s">
-        <v>559</v>
+        <v>562</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="B289" s="3" t="s">
-        <v>561</v>
+        <v>564</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="B290" s="3" t="s">
-        <v>280</v>
+        <v>566</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B291" s="3" t="s">
-        <v>564</v>
+        <v>567</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="B292" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="B293" s="3" t="s">
-        <v>568</v>
+        <v>571</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="B294" s="3" t="s">
-        <v>570</v>
+        <v>573</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="B295" s="3" t="s">
-        <v>572</v>
+        <v>575</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B296" s="3" t="s">
-        <v>574</v>
+        <v>577</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="B297" s="3" t="s">
-        <v>576</v>
+        <v>579</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="B298" s="3" t="s">
-        <v>578</v>
+        <v>581</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="B299" s="3" t="s">
-        <v>580</v>
+        <v>583</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="B300" s="3" t="s">
-        <v>582</v>
+        <v>585</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="B301" s="3" t="s">
-        <v>584</v>
+        <v>587</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="B302" s="3" t="s">
-        <v>586</v>
+        <v>589</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="B303" s="3" t="s">
-        <v>588</v>
+        <v>591</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="B304" s="3" t="s">
-        <v>590</v>
+        <v>593</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="B305" s="3" t="s">
-        <v>592</v>
+        <v>595</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="B306" s="3" t="s">
-        <v>594</v>
+        <v>597</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="B307" s="3" t="s">
-        <v>596</v>
+        <v>599</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="B308" s="3" t="s">
-        <v>598</v>
+        <v>601</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="B309" s="3" t="s">
-        <v>600</v>
+        <v>603</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="B310" s="3" t="s">
-        <v>602</v>
+        <v>605</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="B311" s="3" t="s">
-        <v>604</v>
+        <v>607</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="B312" s="3" t="s">
-        <v>606</v>
+        <v>609</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="B313" s="3" t="s">
-        <v>608</v>
+        <v>611</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="B314" s="3" t="s">
-        <v>610</v>
+        <v>613</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="B315" s="3" t="s">
-        <v>612</v>
+        <v>615</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="B316" s="3" t="s">
-        <v>614</v>
+        <v>617</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="B317" s="3" t="s">
-        <v>616</v>
+        <v>619</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="B318" s="3" t="s">
-        <v>618</v>
+        <v>621</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="B319" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="B320" s="3" t="s">
-        <v>622</v>
+        <v>625</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="B321" s="3" t="s">
-        <v>624</v>
+        <v>627</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="B322" s="3" t="s">
-        <v>626</v>
+        <v>629</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="B323" s="3" t="s">
-        <v>628</v>
+        <v>631</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="B324" s="3" t="s">
-        <v>630</v>
+        <v>633</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="B325" s="3" t="s">
-        <v>632</v>
+        <v>635</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="B326" s="3" t="s">
-        <v>634</v>
+        <v>637</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="B327" s="3" t="s">
-        <v>636</v>
+        <v>639</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="B328" s="3" t="s">
-        <v>638</v>
+        <v>641</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="B329" s="3" t="s">
-        <v>640</v>
+        <v>643</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="B330" s="3" t="s">
-        <v>642</v>
+        <v>645</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="B331" s="3" t="s">
-        <v>644</v>
+        <v>647</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="B332" s="3" t="s">
-        <v>646</v>
+        <v>649</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="B333" s="3" t="s">
-        <v>648</v>
+        <v>651</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="B334" s="3" t="s">
-        <v>650</v>
+        <v>653</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="B335" s="3" t="s">
-        <v>652</v>
+        <v>655</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="B336" s="3" t="s">
-        <v>654</v>
+        <v>657</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="B337" s="3" t="s">
-        <v>656</v>
+        <v>659</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="B338" s="3" t="s">
-        <v>658</v>
+        <v>661</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="B339" s="3" t="s">
-        <v>660</v>
+        <v>663</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="B340" s="3" t="s">
-        <v>662</v>
+        <v>665</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="B341" s="3" t="s">
-        <v>664</v>
+        <v>667</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="B342" s="3" t="s">
-        <v>666</v>
+        <v>669</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="B343" s="3" t="s">
-        <v>668</v>
+        <v>671</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="B344" s="3" t="s">
-        <v>273</v>
+        <v>673</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="B345" s="3" t="s">
-        <v>671</v>
+        <v>674</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="B346" s="3" t="s">
-        <v>673</v>
+        <v>676</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="B347" s="3" t="s">
-        <v>675</v>
+        <v>678</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="B348" s="3" t="s">
-        <v>677</v>
+        <v>680</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="B349" s="3" t="s">
-        <v>652</v>
+        <v>682</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="B350" s="3" t="s">
-        <v>680</v>
+        <v>683</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="B351" s="3" t="s">
-        <v>682</v>
+        <v>685</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="B352" s="3" t="s">
-        <v>652</v>
+        <v>687</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="B353" s="3" t="s">
-        <v>685</v>
+        <v>688</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="B354" s="3" t="s">
-        <v>687</v>
+        <v>690</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="B355" s="3" t="s">
-        <v>689</v>
+        <v>692</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="B356" s="3" t="s">
-        <v>691</v>
+        <v>694</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="B357" s="3" t="s">
-        <v>693</v>
+        <v>696</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="B358" s="3" t="s">
-        <v>695</v>
+        <v>698</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="B359" s="3" t="s">
-        <v>697</v>
+        <v>700</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="B360" s="3" t="s">
-        <v>699</v>
+        <v>702</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="B361" s="3" t="s">
-        <v>701</v>
+        <v>704</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="B362" s="3" t="s">
-        <v>703</v>
+        <v>706</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>707</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="B363" s="3" t="s">
-        <v>705</v>
+        <v>708</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="B364" s="3" t="s">
-        <v>707</v>
+        <v>710</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="B365" s="3" t="s">
-        <v>709</v>
+        <v>712</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>713</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="B366" s="3" t="s">
-        <v>711</v>
+        <v>714</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="B367" s="3" t="s">
-        <v>713</v>
+        <v>716</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="B368" s="3" t="s">
-        <v>715</v>
+        <v>718</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>719</v>
       </c>
     </row>
   </sheetData>

--- a/multi.xlsx
+++ b/multi.xlsx
@@ -8,19 +8,20 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="traduccion" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="diccionario_vars" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="493">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -28,24 +29,99 @@
     <t xml:space="preserve">ES</t>
   </si>
   <si>
+    <t xml:space="preserve">EN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA</t>
+  </si>
+  <si>
     <t xml:space="preserve">lenguajes</t>
   </si>
   <si>
     <t xml:space="preserve">Español</t>
   </si>
   <si>
+    <t xml:space="preserve">English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italiano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deutsch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Français</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Português</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Català</t>
+  </si>
+  <si>
     <t xml:space="preserve">banderas</t>
   </si>
   <si>
     <t xml:space="preserve">🇪🇸</t>
   </si>
   <si>
+    <t xml:space="preserve">🇺🇸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🇮🇹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🇩🇪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🇫🇷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🇵🇹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🤖 IA NutriBot</t>
+  </si>
+  <si>
     <t xml:space="preserve">guia</t>
   </si>
   <si>
     <t xml:space="preserve">Bienvenido a la audioguía de IA NutriBot, tu asistente nutricional inteligente.</t>
   </si>
   <si>
+    <t xml:space="preserve">Welcome to the NutriBot AI audio guide, your smart nutrition assistant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benvenuti nella guida audio NutriBot AI, il vostro assistente nutrizionale intelligente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willkommen beim NutriBot AI-Audioguide, Ihrem intelligenten Ernährungsassistenten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bienvenue dans le guide audio NutriBot AI, votre assistant nutritionnel intelligent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bem-vindo ao guia de áudio com IA NutriBot, seu assistente inteligente de nutrição.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benvingut a l'audioguia de IA NutriBot, el teu assistent nutricional intel·ligent.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_titulo_web</t>
   </si>
   <si>
@@ -58,124 +134,451 @@
     <t xml:space="preserve">⏳ Cargando idioma...</t>
   </si>
   <si>
+    <t xml:space="preserve">⏳ Loading language...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⏳ Caricamento lingua...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⏳ Sprache wird geladen...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⏳ Chargement de la langue...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⏳ Carregando idioma...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⏳ Carregant idioma...</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_logo</t>
   </si>
   <si>
-    <t xml:space="preserve">🤖 IA NutriBot</t>
-  </si>
-  <si>
     <t xml:space="preserve">_02_menu_inicio</t>
   </si>
   <si>
     <t xml:space="preserve">Inicio</t>
   </si>
   <si>
+    <t xml:space="preserve">Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inizio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commencer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Começar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inici</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_menu_ingreso</t>
   </si>
   <si>
     <t xml:space="preserve">Ingreso</t>
   </si>
   <si>
+    <t xml:space="preserve">Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reddito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einkommen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingrés</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_menu_alta</t>
   </si>
   <si>
     <t xml:space="preserve">Alta</t>
   </si>
   <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haut</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_menu_comandos</t>
   </si>
   <si>
     <t xml:space="preserve">Comandos</t>
   </si>
   <si>
+    <t xml:space="preserve">Commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comandi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Befehle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commandes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordres</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_menu_faq</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ</t>
   </si>
   <si>
+    <t xml:space="preserve">Häufig gestellte Fragen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perguntas frequentes</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_menu_calculadora</t>
   </si>
   <si>
     <t xml:space="preserve">Calculadora</t>
   </si>
   <si>
+    <t xml:space="preserve">Calculator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcolatrice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalkulator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculatrice</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_titulo_inicio</t>
   </si>
   <si>
     <t xml:space="preserve">Bienvenido a IA NutriBot</t>
   </si>
   <si>
+    <t xml:space="preserve">Welcome to AI NutriBot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benvenuti in AI NutriBot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willkommen bei AI NutriBot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bienvenue dans AI NutriBot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bem-vindo ao AI NutriBot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benvingut a IA NutriBot</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_cap_inicio</t>
   </si>
   <si>
     <t xml:space="preserve">Tu asistente nutricional inteligente en Telegram</t>
   </si>
   <si>
+    <t xml:space="preserve">Your smart nutrition assistant on Telegram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il tuo assistente nutrizionale intelligente su Telegram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dein intelligenter Ernährungsassistent auf Telegram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Votre assistant nutritionnel intelligent sur Telegram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seu assistente inteligente de nutrição no Telegram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El teu assistent nutricional intel·ligent a Telegram</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_texto_inicio</t>
   </si>
   <si>
     <t xml:space="preserve">IA NutriBot es tu compañero diario para llevar un registro simple, rápido y preciso de tu alimentación y evolución física directamente desde Telegram.</t>
   </si>
   <si>
+    <t xml:space="preserve">AI NutriBot is your daily companion to keep a simple, fast and accurate record of your diet and physical evolution directly from Telegram.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI NutriBot è il tuo compagno quotidiano per tenere traccia in modo semplice, rapido e preciso della tua dieta e dei tuoi progressi fisici, direttamente da Telegram.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI NutriBot ist Ihr täglicher Begleiter, mit dem Sie Ihre Ernährung und körperliche Entwicklung einfach, schnell und präzise direkt über Telegram dokumentieren können.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI NutriBot est votre compagnon quotidien pour tenir un registre simple, rapide et précis de votre alimentation et de votre évolution physique directement depuis Telegram.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O AI NutriBot é seu companheiro diário para manter um registro simples, rápido e preciso de sua dieta e evolução física diretamente do Telegram.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA NutriBot és el teu company diari per portar un registre simple, ràpid i precís de la teva alimentació i evolució física directament des de Telegram.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_titulo_ingreso</t>
   </si>
   <si>
     <t xml:space="preserve">Cómo ingresar tus comidas</t>
   </si>
   <si>
+    <t xml:space="preserve">How to enter your meals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Come inserire i pasti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So geben Sie Ihre Mahlzeiten ein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment saisir vos repas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como registrar suas refeições</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Com ingressar els teus àpats</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_cap_ingreso</t>
   </si>
   <si>
     <t xml:space="preserve">Registro por texto, audio o foto</t>
   </si>
   <si>
+    <t xml:space="preserve">Registration by text, audio or photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrazione tramite testo, audio o foto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anmeldung per Text, Audio oder Foto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inscription par texte, audio ou photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadastro por mensagem de texto, áudio ou foto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registre per text, àudio o foto</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_texto_ingreso</t>
   </si>
   <si>
     <t xml:space="preserve">Podés registrar tus comidas enviando un mensaje de texto, un audio de voz describiendo tu plato o una fotografía de lo que estás por comer.</t>
   </si>
   <si>
+    <t xml:space="preserve">You can register your meals by sending a text message, a voice audio describing your dish, or a photograph of what you are about to eat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">È possibile registrare i propri pasti inviando un SMS, un messaggio vocale che descriva il piatto o una fotografia di ciò che si sta per mangiare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sie können Ihre Mahlzeiten registrieren, indem Sie eine SMS, eine Sprachnachricht mit einer Beschreibung Ihres Gerichts oder ein Foto von dem, was Sie essen werden, senden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous pouvez enregistrer vos repas en envoyant un SMS, un message vocal décrivant votre plat ou une photo de ce que vous allez manger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Você pode registrar suas refeições enviando uma mensagem de texto, um áudio descrevendo o prato ou uma foto do que vai comer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podeu registrar els vostres àpats enviant un missatge de text, un àudio de veu descrivint el vostre plat o una fotografia del que esteu per menjar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_titulo_alta</t>
   </si>
   <si>
     <t xml:space="preserve">Proceso de Alta y Perfil</t>
   </si>
   <si>
+    <t xml:space="preserve">Registration and Profile Process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processo di registrazione e creazione del profilo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrierungs- und Profilprozess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processus d'inscription et de profil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processo de registro e perfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procés d'alta i perfil</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_cap_alta</t>
   </si>
   <si>
     <t xml:space="preserve">Configuración biométrica personalizada</t>
   </si>
   <si>
+    <t xml:space="preserve">Custom biometric configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurazione biometrica personalizzata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benutzerdefinierte biometrische Konfiguration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuration biométrique personnalisée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuração biométrica personalizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuració biomètrica personalitzada</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_texto_alta</t>
   </si>
   <si>
     <t xml:space="preserve">Al iniciar el bot por primera vez, configuraremos tu perfil biométrico (edad, altura, peso, cintura y cuello) para calcular tus requerimientos diarios con exactitud.</t>
   </si>
   <si>
+    <t xml:space="preserve">When you start the bot for the first time, we will configure your biometric profile (age, height, weight, waist and neck) to accurately calculate your daily requirements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando avvii il bot per la prima volta, configureremo il tuo profilo biometrico (età, altezza, peso, circonferenza vita e collo) per calcolare con precisione il tuo fabbisogno giornaliero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wenn Sie den Bot zum ersten Mal starten, konfigurieren wir Ihr biometrisches Profil (Alter, Größe, Gewicht, Taillen- und Halsumfang), um Ihren täglichen Bedarf genau zu berechnen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lors du premier lancement du bot, nous configurerons votre profil biométrique (âge, taille, poids, tour de taille et tour de cou) afin de calculer avec précision vos besoins quotidiens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ao iniciar o bot pela primeira vez, configuraremos seu perfil biométrico (idade, altura, peso, circunferência da cintura e do pescoço) para calcular com precisão suas necessidades diárias.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En iniciar el bot per primer cop, configurarem el teu perfil biomètric (edat, alçada, pes, cintura i coll) per calcular els teus requeriments diaris amb exactitud.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_titulo_comandos</t>
   </si>
   <si>
     <t xml:space="preserve">Comandos disponibles</t>
   </si>
   <si>
+    <t xml:space="preserve">Available commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comandi disponibili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verfügbare Befehle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commandes disponibles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comandos disponíveis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordres disponibles</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_cap_comandos</t>
   </si>
   <si>
     <t xml:space="preserve">Control total desde el menú</t>
   </si>
   <si>
+    <t xml:space="preserve">Full control from the menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controllo completo dal menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volle Kontrolle über das Menü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrôle total depuis le menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controle total a partir do menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control total des del menú</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_texto_comandos</t>
   </si>
   <si>
     <t xml:space="preserve">Utilizá los comandos del bot para consultar tu resumen diario, historial mensual, reportes en PDF, editar registros o acceder a esta calculadora de recetas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Use the bot's commands to view your daily summary, monthly history, PDF reports, edit records, or access this recipe calculator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilizza i comandi del bot per visualizzare il riepilogo giornaliero, la cronologia mensile, i report in PDF, modificare i record o accedere a questo calcolatore di ricette.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nutzen Sie die Befehle des Bots, um Ihre Tageszusammenfassung, Monatshistorie und PDF-Berichte anzuzeigen, Datensätze zu bearbeiten oder auf diesen Rezeptrechner zuzugreifen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilisez les commandes du bot pour consulter votre résumé quotidien, votre historique mensuel, vos rapports PDF, modifier des enregistrements ou accéder à ce calculateur de recettes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilize os comandos do bot para visualizar seu resumo diário, histórico mensal, relatórios em PDF, editar registros ou acessar esta calculadora de receitas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilitzeu les ordres del bot per consultar el vostre resum diari, historial mensual, reports en PDF, editar registres o accedir a aquesta calculadora de receptes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_titulo_faq</t>
   </si>
   <si>
     <t xml:space="preserve">Preguntas Frecuentes (FAQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequently Asked Questions (FAQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domande frequenti (FAQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Häufig gestellte Fragen (FAQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foire aux questions (FAQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perguntas frequentes (FAQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preguntes Freqüents (FAQ)</t>
   </si>
   <si>
     <t xml:space="preserve">_02_texto_faq</t>
@@ -185,78 +588,300 @@
 Desde la pestaña Calculadora podés ingresar todos los ingredientes de tu preparación, dividir por porciones y guardarla con un código único.</t>
   </si>
   <si>
+    <t xml:space="preserve">How do I calculate a homemade recipe?
+From the Calculator tab, you can enter all the ingredients for your recipe, divide it into portions, and save it with a unique code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Come si calcola una ricetta fatta in casa?
+Dalla scheda Calcolatrice, puoi inserire tutti gli ingredienti della tua ricetta, dividerla in porzioni e salvarla con un codice univoco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie berechne ich die Zutaten für ein selbstgemachtes Rezept?
+Im Reiter „Rechner“ können Sie alle Zutaten für Ihr Rezept eingeben, es portionieren und mit einem individuellen Code speichern.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment calculer les quantités d'une recette maison ?
+Dans l'onglet Calculatrice, vous pouvez saisir tous les ingrédients de votre recette, la diviser en portions et l'enregistrer avec un code unique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como faço para calcular uma receita caseira?
+Na aba Calculadora, você pode inserir todos os ingredientes da sua receita, dividi-la em porções e salvá-la com um código único.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Com calculo una recepta casolana?
+Des de la pestanya Calculadora podeu ingressar tots els ingredients de la vostra preparació, dividir per porcions i guardar-la amb un codi únic.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_titulo_calc</t>
   </si>
   <si>
     <t xml:space="preserve">Calculadora Web</t>
   </si>
   <si>
+    <t xml:space="preserve">Web Calculator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcolatrice Web</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web-Rechner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculatrice en ligne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculadora online</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_desc_calc</t>
   </si>
   <si>
     <t xml:space="preserve">Herramienta avanzada para registrar y calcular recetas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Advanced tool for recording and calculating recipes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strumento avanzato per registrare e calcolare le ricette.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortschrittliches Tool zum Aufzeichnen und Berechnen von Rezepten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outil avancé pour l'enregistrement et le calcul des recettes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferramenta avançada para registrar e calcular receitas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eina avançada per registrar i calcular receptes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_user_conectado</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario Conectado</t>
   </si>
   <si>
+    <t xml:space="preserve">User Connected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utente connesso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benutzer verbunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilisateur connecté</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usuário conectado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usuari Connectat</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_label_codigo</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
   </si>
   <si>
+    <t xml:space="preserve">Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codi</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_ph_codigo</t>
   </si>
   <si>
     <t xml:space="preserve">Ej: PASCUALINAP</t>
   </si>
   <si>
+    <t xml:space="preserve">Example: PASCUALINAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esempio: PASCUALINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beispiel: PASCUALINAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exemple : PASCUALINAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exemplo: PASCUALINAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ex: PASCUALINAP</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_label_descripcion</t>
   </si>
   <si>
     <t xml:space="preserve">Descripción</t>
   </si>
   <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descrizione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beschreibung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descrição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descripció</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_ph_descripcion</t>
   </si>
   <si>
     <t xml:space="preserve">Ej: Porción de pascualina de atún</t>
   </si>
   <si>
+    <t xml:space="preserve">Example: Portion of tuna pascualina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esempio: Porzione di tonno pascualina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beispiel: Portion Thunfisch-Pascualina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exemple : Portion de thon pascualina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exemplo: Porção de atum pascualina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ex: Porció de pasqualina de tonyina</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_label_ingredientes</t>
   </si>
   <si>
     <t xml:space="preserve">Ingredientes y Cantidad</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingredients and Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingredienti e quantità</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zutaten und Menge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingrédients et quantité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingredientes e quantidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingredients i Quantitat</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_ph_ingredientes</t>
   </si>
   <si>
     <t xml:space="preserve">Ej: 1 kg de harina, 6 huevos, 200 g de manteca</t>
   </si>
   <si>
+    <t xml:space="preserve">Example: 1 kg of flour, 6 eggs, 200 g of butter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esempio: 1 kg di farina, 6 uova, 200 g di burro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beispiel: 1 kg Mehl, 6 Eier, 200 g Butter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exemple : 1 kg de farine, 6 œufs, 200 g de beurre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exemplo: 1 kg de farinha, 6 ovos, 200 g de manteiga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ex: 1 kg de farina, 6 ous, 200 g de llard</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_label_criterio</t>
   </si>
   <si>
     <t xml:space="preserve">Criterio de División</t>
   </si>
   <si>
+    <t xml:space="preserve">Division Criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criteri di divisione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teilungskriterien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critères de division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critérios de divisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criteri de Divisió</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_opt_porciones</t>
   </si>
   <si>
     <t xml:space="preserve">Porciones</t>
   </si>
   <si>
+    <t xml:space="preserve">Portions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porzioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portionen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porções</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porcions</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_opt_gramos</t>
   </si>
   <si>
     <t xml:space="preserve">Gramos Totales</t>
   </si>
   <si>
+    <t xml:space="preserve">Total Grams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grammi totali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesamtgramm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grammes totales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total de gramas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grams Totals</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_label_porciones</t>
   </si>
   <si>
@@ -266,166 +891,622 @@
     <t xml:space="preserve">✨ Calcular Fila con IA</t>
   </si>
   <si>
+    <t xml:space="preserve">✨ Calculate Row with AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✨ Calcola la riga con l'IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✨ Zeile mit KI berechnen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✨ Calculer une ligne avec l'IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✨ Calcular linha com IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✨ Calcular Fila amb IA</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_loading_ia</t>
   </si>
   <si>
     <t xml:space="preserve">Calculando macronutrientes...</t>
   </si>
   <si>
+    <t xml:space="preserve">Calculating macronutrients...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcolo dei macronutrienti...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berechnung der Makronährstoffe...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul des macronutriments...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculo de macronutrientes...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculant macronutrients...</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_th_nombre</t>
   </si>
   <si>
     <t xml:space="preserve">Nombre</t>
   </si>
   <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nom</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_th_peso</t>
   </si>
   <si>
     <t xml:space="preserve">⚖️ Peso (g)</t>
   </si>
   <si>
+    <t xml:space="preserve">⚖️ Weight (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ Gewicht (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ Poids (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ Pes (g)</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_th_calorias</t>
   </si>
   <si>
     <t xml:space="preserve">🔥 Calorías</t>
   </si>
   <si>
+    <t xml:space="preserve">🔥 Calories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔥 Calorie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔥 Kalorien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔥 Calorias</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_th_proteinas</t>
   </si>
   <si>
     <t xml:space="preserve">🥩 Proteínas</t>
   </si>
   <si>
+    <t xml:space="preserve">🥩 Proteins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥩 Proteine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥩 Protéines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥩 Proteïnes</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_th_grasas</t>
   </si>
   <si>
     <t xml:space="preserve">🥑 Grasas</t>
   </si>
   <si>
+    <t xml:space="preserve">🥑 Fats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥑 Grassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥑 Fette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥑 Matières grasses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥑 Gorduras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥑 Greixos</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_th_carbohidratos</t>
   </si>
   <si>
     <t xml:space="preserve">🍞 Carbos</t>
   </si>
   <si>
+    <t xml:space="preserve">🍞 Carbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍞 Carboidrati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍞 Kohlenhydrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍞 Glucides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍞 Carboidratos</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_th_fibras</t>
   </si>
   <si>
     <t xml:space="preserve">🌾 Fibras</t>
   </si>
   <si>
+    <t xml:space="preserve">🌾 Fibers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🌾 Fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🌾 Fasern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🌾 Fibres</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_th_totales</t>
   </si>
   <si>
     <t xml:space="preserve">Totales</t>
   </si>
   <si>
+    <t xml:space="preserve">Totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totais</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_btn_guardar</t>
   </si>
   <si>
     <t xml:space="preserve">💾 Guardar Directamente en Planilla</t>
   </si>
   <si>
+    <t xml:space="preserve">💾 Save Directly to Spreadsheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">💾 Salva direttamente nel foglio di calcolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">💾 Direkt in Tabellenkalkulation speichern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">💾 Enregistrer directement dans une feuille de calcul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">💾 Salvar diretamente na planilha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">💾 Desar Directament a Planilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_btn_copiar</t>
   </si>
   <si>
     <t xml:space="preserve">📋 Copiar Fila para Excel</t>
   </si>
   <si>
+    <t xml:space="preserve">📋 Copy Row for Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 Copia riga per Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 Zeile für Excel kopieren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 Copier la ligne pour Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 Copiar linha para o Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 Copiar Fila per a Excel</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_title_audioguia</t>
   </si>
   <si>
     <t xml:space="preserve">Audioguía</t>
   </si>
   <si>
+    <t xml:space="preserve">Audio guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audioguida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audioguide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide audio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guia de áudio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audioguia</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_title_manual</t>
   </si>
   <si>
     <t xml:space="preserve">Manual (PDF)</t>
   </si>
   <si>
+    <t xml:space="preserve">Manuale (PDF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handbuch (PDF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel (PDF)</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_footer_rights</t>
   </si>
   <si>
     <t xml:space="preserve">© 2026 IA NutriBot - Todos los derechos reservados.</t>
   </si>
   <si>
+    <t xml:space="preserve">© 2026 IA NutriBot - All rights reserved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">© 2026 IA NutriBot - Tutti i diritti riservati.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">© 2026 IA NutriBot - Alle Rechte vorbehalten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">© 2026 IA NutriBot - Tous droits réservés.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">© 2026 IA NutriBot - Todos os direitos reservados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">© 2026 IA NutriBot - Tots els drets reservats.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_no_registrado</t>
   </si>
   <si>
     <t xml:space="preserve">Acción no permitida para usuarios no registrados.</t>
   </si>
   <si>
+    <t xml:space="preserve">Action not allowed for unregistered users.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azione non consentita agli utenti non registrati.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aktionen sind für nicht registrierte Benutzer nicht zulässig.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action interdite aux utilisateurs non enregistrés.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A ação não é permitida para usuários não registrados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acció no permesa per a usuaris no registrats.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_campos_vacios</t>
   </si>
   <si>
     <t xml:space="preserve">Por favor completa el código, la descripción y los ingredientes.</t>
   </si>
   <si>
+    <t xml:space="preserve">Please complete the code, description, and ingredients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si prega di compilare il codice, la descrizione e gli ingredienti.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitte vervollständigen Sie den Code, die Beschreibung und die Zutatenliste.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veuillez compléter le code, la description et les ingrédients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por favor, preencha o código, a descrição e os ingredientes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si us plau completa el codi, la descripció i els ingredients.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_servidor</t>
   </si>
   <si>
     <t xml:space="preserve">❌ El servidor falló</t>
   </si>
   <si>
+    <t xml:space="preserve">❌ The server failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Il server non è riuscito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Der Server ist ausgefallen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Le serveur a échoué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ O servidor falhou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ El servidor va fallar</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_calcular</t>
   </si>
   <si>
     <t xml:space="preserve">❌ Error al calcular:</t>
   </si>
   <si>
+    <t xml:space="preserve">❌ Calculation error:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Errore di calcolo:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Berechnungsfehler:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Erreur de calcul :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Erro de cálculo:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error en calcular:</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_procesamiento</t>
   </si>
   <si>
     <t xml:space="preserve">❌ Error de procesamiento:</t>
   </si>
   <si>
+    <t xml:space="preserve">❌ Processing error:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Errore di elaborazione:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Verarbeitungsfehler:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Erreur de traitement :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Erro de processamento:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error de processament:</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_sin_datos</t>
   </si>
   <si>
     <t xml:space="preserve">No hay datos calculados para guardar.</t>
   </si>
   <si>
+    <t xml:space="preserve">There is no calculated data to save.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non ci sono dati calcolati da salvare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es sind keine berechneten Daten zum Speichern vorhanden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aucune donnée calculée n'est à enregistrer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não há dados calculados para salvar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No hi ha dades calculades per desar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_msg_exito_guardar</t>
   </si>
   <si>
     <t xml:space="preserve">✅ ¡Éxito!</t>
   </si>
   <si>
+    <t xml:space="preserve">✅ Success!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Successo!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Erfolg!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Succès !</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Sucesso!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Èxit!</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_guardar</t>
   </si>
   <si>
     <t xml:space="preserve">❌ Error al guardar:</t>
   </si>
   <si>
+    <t xml:space="preserve">❌ Error saving:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Errore durante il salvataggio:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Fehler beim Speichern:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Erreur d'enregistrement :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Erro ao salvar:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error en desar:</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_conexion_guardar</t>
   </si>
   <si>
     <t xml:space="preserve">Error de conexión al intentar guardar.</t>
   </si>
   <si>
+    <t xml:space="preserve">Connection error while trying to save.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Errore di connessione durante il tentativo di salvataggio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verbindungsfehler beim Speichern.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erreur de connexion lors de la tentative d'enregistrement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erro de conexão ao tentar salvar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error de connexió en intentar desar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_msg_copiado</t>
   </si>
   <si>
     <t xml:space="preserve">¡Fila total copiada! Podés pegarla en tu Excel con Ctrl + V.</t>
   </si>
   <si>
+    <t xml:space="preserve">Row total copied! You can paste it into your Excel with Ctrl + V.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totale riga copiato! Puoi incollarlo in Excel con Ctrl + V.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Zeilensumme wurde kopiert! Sie können sie mit Strg + V in Ihre Excel-Datei einfügen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le total de la ligne a été copié ! Vous pouvez le coller dans votre fichier Excel avec Ctrl + V.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total da linha copiado! Você pode colar no Excel usando Ctrl + V.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fila total copiada! Podeu enganxar-la al vostre Excel amb Ctrl + V.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_copiar</t>
   </si>
   <si>
     <t xml:space="preserve">Error al copiar al portapapeles.</t>
   </si>
   <si>
+    <t xml:space="preserve">Error copying to clipboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Errore durante la copia negli appunti.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fehler beim Kopieren in die Zwischenablage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erreur lors de la copie dans le presse-papiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erro ao copiar para a área de transferência.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error en copiar al porta-retalls.</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_audioguia</t>
   </si>
   <si>
     <t xml:space="preserve">Error al reproducir la audioguía:</t>
   </si>
   <si>
+    <t xml:space="preserve">Error playing the audio guide:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Errore durante la riproduzione della guida audio:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fehler beim Abspielen des Audioguides:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erreur lors de la lecture du guide audio :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erro ao reproduzir o guia de áudio:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error en reproduir l'audioguia:</t>
+  </si>
+  <si>
     <t xml:space="preserve">_02_err_no_speech</t>
   </si>
   <si>
     <t xml:space="preserve">Tu navegador no soporta la función de lectura de voz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your browser does not support the text-to-speech function.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il tuo browser non supporta la funzione di sintesi vocale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ihr Browser unterstützt die Text-zu-Sprache-Funktion nicht.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Votre navigateur ne prend pas en charge la fonction de synthèse vocale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seu navegador não suporta a função de conversão de texto em fala.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El vostre navegador no suporta la funció de lectura de veu.</t>
   </si>
 </sst>
 </file>
@@ -435,11 +1516,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -455,17 +1538,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -515,12 +1587,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -540,560 +1612,5396 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H426"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="176.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="2" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="H7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="2" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="E9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="H9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="2" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="H10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="2" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="G11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="G12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+    <row r="13" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+      <c r="C13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="F13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="H13" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="G14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B46" s="2" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
+      <c r="H16" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="2" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="310.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="G17" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B54" s="2" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
+      <c r="H18" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B58" s="2" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+      <c r="H19" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B62" s="2" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="323.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
+      <c r="H20" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B66" s="2" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>134</v>
       </c>
+      <c r="F21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="350.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="364.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+    </row>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+    </row>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+    </row>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+    </row>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+    </row>
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+    </row>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+    </row>
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+    </row>
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+    </row>
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+    </row>
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+    </row>
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+    </row>
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+    </row>
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+    </row>
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+    </row>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+    </row>
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
+    </row>
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+      <c r="H124" s="2"/>
+    </row>
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+      <c r="H125" s="2"/>
+    </row>
+    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+    </row>
+    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+    </row>
+    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+      <c r="H128" s="2"/>
+    </row>
+    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+    </row>
+    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+      <c r="H130" s="2"/>
+    </row>
+    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
+    </row>
+    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2"/>
+    </row>
+    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+    </row>
+    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+    </row>
+    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+    </row>
+    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+    </row>
+    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+    </row>
+    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+    </row>
+    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+    </row>
+    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+    </row>
+    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+    </row>
+    <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="2"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+    </row>
+    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+    </row>
+    <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="2"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+      <c r="H144" s="2"/>
+    </row>
+    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="2"/>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2"/>
+      <c r="G145" s="2"/>
+      <c r="H145" s="2"/>
+    </row>
+    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
+    </row>
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2"/>
+    </row>
+    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+      <c r="H148" s="2"/>
+    </row>
+    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="2"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+    </row>
+    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
+    </row>
+    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
+    </row>
+    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+      <c r="H152" s="2"/>
+    </row>
+    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+    </row>
+    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+      <c r="H154" s="2"/>
+    </row>
+    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+      <c r="H155" s="2"/>
+    </row>
+    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+    </row>
+    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="2"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+    </row>
+    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="2"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+      <c r="H158" s="2"/>
+    </row>
+    <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="2"/>
+    </row>
+    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+    </row>
+    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+    </row>
+    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+    </row>
+    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2"/>
+    </row>
+    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="2"/>
+    </row>
+    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="2"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+    </row>
+    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="2"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="2"/>
+    </row>
+    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="2"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="2"/>
+    </row>
+    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+    </row>
+    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="2"/>
+    </row>
+    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+    </row>
+    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+    </row>
+    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+    </row>
+    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="2"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+    </row>
+    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+    </row>
+    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="2"/>
+    </row>
+    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="2"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+      <c r="H176" s="2"/>
+    </row>
+    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="2"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+    </row>
+    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="2"/>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="2"/>
+    </row>
+    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="2"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="2"/>
+    </row>
+    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+    </row>
+    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="2"/>
+    </row>
+    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="2"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2"/>
+      <c r="H182" s="2"/>
+    </row>
+    <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="2"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="2"/>
+    </row>
+    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="2"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
+      <c r="H184" s="2"/>
+    </row>
+    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="2"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="2"/>
+      <c r="H185" s="2"/>
+    </row>
+    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="2"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2"/>
+      <c r="H186" s="2"/>
+    </row>
+    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="2"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="2"/>
+      <c r="H187" s="2"/>
+    </row>
+    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="2"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
+      <c r="G188" s="2"/>
+      <c r="H188" s="2"/>
+    </row>
+    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="2"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="2"/>
+      <c r="H189" s="2"/>
+    </row>
+    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="2"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="2"/>
+      <c r="H190" s="2"/>
+    </row>
+    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="2"/>
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
+      <c r="E191" s="2"/>
+      <c r="F191" s="2"/>
+      <c r="G191" s="2"/>
+      <c r="H191" s="2"/>
+    </row>
+    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="2"/>
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
+      <c r="H192" s="2"/>
+    </row>
+    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="2"/>
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
+      <c r="G193" s="2"/>
+      <c r="H193" s="2"/>
+    </row>
+    <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="2"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
+      <c r="H194" s="2"/>
+    </row>
+    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="2"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+      <c r="E195" s="2"/>
+      <c r="F195" s="2"/>
+      <c r="G195" s="2"/>
+      <c r="H195" s="2"/>
+    </row>
+    <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="2"/>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
+      <c r="E196" s="2"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="2"/>
+      <c r="H196" s="2"/>
+    </row>
+    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="2"/>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+      <c r="E197" s="2"/>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+      <c r="H197" s="2"/>
+    </row>
+    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2"/>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+      <c r="E198" s="2"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
+      <c r="H198" s="2"/>
+    </row>
+    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2"/>
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="2"/>
+    </row>
+    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="2"/>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+    </row>
+    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="2"/>
+      <c r="B201" s="2"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+      <c r="H201" s="2"/>
+    </row>
+    <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="2"/>
+      <c r="B202" s="2"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
+      <c r="E202" s="2"/>
+      <c r="F202" s="2"/>
+      <c r="G202" s="2"/>
+      <c r="H202" s="2"/>
+    </row>
+    <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="2"/>
+      <c r="B203" s="2"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
+      <c r="H203" s="2"/>
+    </row>
+    <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="2"/>
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
+      <c r="H204" s="2"/>
+    </row>
+    <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2"/>
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+      <c r="E205" s="2"/>
+      <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
+      <c r="H205" s="2"/>
+    </row>
+    <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="2"/>
+      <c r="B206" s="2"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
+      <c r="E206" s="2"/>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
+      <c r="H206" s="2"/>
+    </row>
+    <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2"/>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+      <c r="E207" s="2"/>
+      <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
+      <c r="H207" s="2"/>
+    </row>
+    <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="2"/>
+      <c r="B208" s="2"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
+      <c r="E208" s="2"/>
+      <c r="F208" s="2"/>
+      <c r="G208" s="2"/>
+      <c r="H208" s="2"/>
+    </row>
+    <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="2"/>
+      <c r="B209" s="2"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
+      <c r="E209" s="2"/>
+      <c r="F209" s="2"/>
+      <c r="G209" s="2"/>
+      <c r="H209" s="2"/>
+    </row>
+    <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="2"/>
+      <c r="B210" s="2"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
+      <c r="E210" s="2"/>
+      <c r="F210" s="2"/>
+      <c r="G210" s="2"/>
+      <c r="H210" s="2"/>
+    </row>
+    <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="2"/>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
+      <c r="E211" s="2"/>
+      <c r="F211" s="2"/>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2"/>
+    </row>
+    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="2"/>
+      <c r="B212" s="2"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
+      <c r="E212" s="2"/>
+      <c r="F212" s="2"/>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2"/>
+    </row>
+    <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="2"/>
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2"/>
+      <c r="F213" s="2"/>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2"/>
+    </row>
+    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="2"/>
+      <c r="B214" s="2"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
+      <c r="E214" s="2"/>
+      <c r="F214" s="2"/>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2"/>
+    </row>
+    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+    </row>
+    <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="2"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="2"/>
+      <c r="H216" s="2"/>
+    </row>
+    <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
+      <c r="G217" s="2"/>
+      <c r="H217" s="2"/>
+    </row>
+    <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="2"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="2"/>
+      <c r="H218" s="2"/>
+    </row>
+    <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+    </row>
+    <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+    </row>
+    <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+    </row>
+    <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+    </row>
+    <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+    </row>
+    <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="2"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
+    </row>
+    <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="2"/>
+      <c r="B225" s="2"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
+      <c r="E225" s="2"/>
+      <c r="F225" s="2"/>
+      <c r="G225" s="2"/>
+      <c r="H225" s="2"/>
+    </row>
+    <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="2"/>
+      <c r="B226" s="2"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
+      <c r="E226" s="2"/>
+      <c r="F226" s="2"/>
+      <c r="G226" s="2"/>
+      <c r="H226" s="2"/>
+    </row>
+    <row r="227" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="2"/>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+      <c r="E227" s="2"/>
+      <c r="F227" s="2"/>
+      <c r="G227" s="2"/>
+      <c r="H227" s="2"/>
+    </row>
+    <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="2"/>
+      <c r="B228" s="2"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
+      <c r="E228" s="2"/>
+      <c r="F228" s="2"/>
+      <c r="G228" s="2"/>
+      <c r="H228" s="2"/>
+    </row>
+    <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="2"/>
+      <c r="B229" s="2"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="2"/>
+      <c r="E229" s="2"/>
+      <c r="F229" s="2"/>
+      <c r="G229" s="2"/>
+      <c r="H229" s="2"/>
+    </row>
+    <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="2"/>
+      <c r="B230" s="2"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
+      <c r="E230" s="2"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="2"/>
+      <c r="H230" s="2"/>
+    </row>
+    <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="2"/>
+      <c r="B231" s="2"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
+      <c r="E231" s="2"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="2"/>
+      <c r="H231" s="2"/>
+    </row>
+    <row r="232" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="2"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="2"/>
+      <c r="H232" s="2"/>
+    </row>
+    <row r="233" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="2"/>
+      <c r="B233" s="2"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
+      <c r="E233" s="2"/>
+      <c r="F233" s="2"/>
+      <c r="G233" s="2"/>
+      <c r="H233" s="2"/>
+    </row>
+    <row r="234" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="2"/>
+      <c r="B234" s="2"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="2"/>
+      <c r="H234" s="2"/>
+    </row>
+    <row r="235" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="2"/>
+      <c r="B235" s="2"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
+      <c r="E235" s="2"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="2"/>
+      <c r="H235" s="2"/>
+    </row>
+    <row r="236" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="2"/>
+      <c r="B236" s="2"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
+      <c r="E236" s="2"/>
+      <c r="F236" s="2"/>
+      <c r="G236" s="2"/>
+      <c r="H236" s="2"/>
+    </row>
+    <row r="237" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="2"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
+      <c r="E237" s="2"/>
+      <c r="F237" s="2"/>
+      <c r="G237" s="2"/>
+      <c r="H237" s="2"/>
+    </row>
+    <row r="238" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="2"/>
+      <c r="B238" s="2"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
+      <c r="E238" s="2"/>
+      <c r="F238" s="2"/>
+      <c r="G238" s="2"/>
+      <c r="H238" s="2"/>
+    </row>
+    <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="2"/>
+    </row>
+    <row r="240" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="2"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="2"/>
+      <c r="H240" s="2"/>
+    </row>
+    <row r="241" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="2"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
+      <c r="E241" s="2"/>
+      <c r="F241" s="2"/>
+      <c r="G241" s="2"/>
+      <c r="H241" s="2"/>
+    </row>
+    <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="2"/>
+      <c r="B242" s="2"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
+      <c r="E242" s="2"/>
+      <c r="F242" s="2"/>
+      <c r="G242" s="2"/>
+      <c r="H242" s="2"/>
+    </row>
+    <row r="243" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="2"/>
+      <c r="B243" s="2"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="2"/>
+      <c r="H243" s="2"/>
+    </row>
+    <row r="244" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="2"/>
+      <c r="B244" s="2"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+      <c r="F244" s="2"/>
+      <c r="G244" s="2"/>
+      <c r="H244" s="2"/>
+    </row>
+    <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="2"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="2"/>
+      <c r="H245" s="2"/>
+    </row>
+    <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="2"/>
+      <c r="B246" s="2"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+      <c r="F246" s="2"/>
+      <c r="G246" s="2"/>
+      <c r="H246" s="2"/>
+    </row>
+    <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="2"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+      <c r="F247" s="2"/>
+      <c r="G247" s="2"/>
+      <c r="H247" s="2"/>
+    </row>
+    <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="2"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="2"/>
+      <c r="H248" s="2"/>
+    </row>
+    <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="2"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="2"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="2"/>
+      <c r="H249" s="2"/>
+    </row>
+    <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="2"/>
+      <c r="B250" s="2"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="2"/>
+      <c r="H250" s="2"/>
+    </row>
+    <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="2"/>
+      <c r="B251" s="2"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
+      <c r="E251" s="2"/>
+      <c r="F251" s="2"/>
+      <c r="G251" s="2"/>
+      <c r="H251" s="2"/>
+    </row>
+    <row r="252" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="2"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="2"/>
+      <c r="H252" s="2"/>
+    </row>
+    <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="2"/>
+      <c r="B253" s="2"/>
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
+      <c r="E253" s="2"/>
+      <c r="F253" s="2"/>
+      <c r="G253" s="2"/>
+      <c r="H253" s="2"/>
+    </row>
+    <row r="254" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="2"/>
+      <c r="B254" s="2"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
+      <c r="E254" s="2"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="2"/>
+      <c r="H254" s="2"/>
+    </row>
+    <row r="255" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="2"/>
+      <c r="B255" s="2"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
+      <c r="E255" s="2"/>
+      <c r="F255" s="2"/>
+      <c r="G255" s="2"/>
+      <c r="H255" s="2"/>
+    </row>
+    <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="2"/>
+      <c r="B256" s="2"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
+      <c r="E256" s="2"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="2"/>
+      <c r="H256" s="2"/>
+    </row>
+    <row r="257" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="2"/>
+      <c r="B257" s="2"/>
+      <c r="C257" s="2"/>
+      <c r="D257" s="2"/>
+      <c r="E257" s="2"/>
+      <c r="F257" s="2"/>
+      <c r="G257" s="2"/>
+      <c r="H257" s="2"/>
+    </row>
+    <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="2"/>
+      <c r="B258" s="2"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
+      <c r="E258" s="2"/>
+      <c r="F258" s="2"/>
+      <c r="G258" s="2"/>
+      <c r="H258" s="2"/>
+    </row>
+    <row r="259" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="2"/>
+      <c r="B259" s="2"/>
+      <c r="C259" s="2"/>
+      <c r="D259" s="2"/>
+      <c r="E259" s="2"/>
+      <c r="F259" s="2"/>
+      <c r="G259" s="2"/>
+      <c r="H259" s="2"/>
+    </row>
+    <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="2"/>
+      <c r="B260" s="2"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="2"/>
+      <c r="G260" s="2"/>
+      <c r="H260" s="2"/>
+    </row>
+    <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="2"/>
+      <c r="B261" s="2"/>
+      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
+      <c r="E261" s="2"/>
+      <c r="F261" s="2"/>
+      <c r="G261" s="2"/>
+      <c r="H261" s="2"/>
+    </row>
+    <row r="262" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="2"/>
+      <c r="B262" s="2"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
+      <c r="E262" s="2"/>
+      <c r="F262" s="2"/>
+      <c r="G262" s="2"/>
+      <c r="H262" s="2"/>
+    </row>
+    <row r="263" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="2"/>
+      <c r="B263" s="2"/>
+      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
+      <c r="E263" s="2"/>
+      <c r="F263" s="2"/>
+      <c r="G263" s="2"/>
+      <c r="H263" s="2"/>
+    </row>
+    <row r="264" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="2"/>
+      <c r="B264" s="2"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
+      <c r="E264" s="2"/>
+      <c r="F264" s="2"/>
+      <c r="G264" s="2"/>
+      <c r="H264" s="2"/>
+    </row>
+    <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="2"/>
+      <c r="B265" s="2"/>
+      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
+      <c r="E265" s="2"/>
+      <c r="F265" s="2"/>
+      <c r="G265" s="2"/>
+      <c r="H265" s="2"/>
+    </row>
+    <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="2"/>
+      <c r="B266" s="2"/>
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
+      <c r="E266" s="2"/>
+      <c r="F266" s="2"/>
+      <c r="G266" s="2"/>
+      <c r="H266" s="2"/>
+    </row>
+    <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="2"/>
+      <c r="B267" s="2"/>
+      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
+      <c r="E267" s="2"/>
+      <c r="F267" s="2"/>
+      <c r="G267" s="2"/>
+      <c r="H267" s="2"/>
+    </row>
+    <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="2"/>
+      <c r="B268" s="2"/>
+      <c r="C268" s="2"/>
+      <c r="D268" s="2"/>
+      <c r="E268" s="2"/>
+      <c r="F268" s="2"/>
+      <c r="G268" s="2"/>
+      <c r="H268" s="2"/>
+    </row>
+    <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="2"/>
+      <c r="B269" s="2"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
+      <c r="E269" s="2"/>
+      <c r="F269" s="2"/>
+      <c r="G269" s="2"/>
+      <c r="H269" s="2"/>
+    </row>
+    <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="2"/>
+      <c r="B270" s="2"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
+      <c r="E270" s="2"/>
+      <c r="F270" s="2"/>
+      <c r="G270" s="2"/>
+      <c r="H270" s="2"/>
+    </row>
+    <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="2"/>
+      <c r="B271" s="2"/>
+      <c r="C271" s="2"/>
+      <c r="D271" s="2"/>
+      <c r="E271" s="2"/>
+      <c r="F271" s="2"/>
+      <c r="G271" s="2"/>
+      <c r="H271" s="2"/>
+    </row>
+    <row r="272" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="2"/>
+      <c r="B272" s="2"/>
+      <c r="C272" s="2"/>
+      <c r="D272" s="2"/>
+      <c r="E272" s="2"/>
+      <c r="F272" s="2"/>
+      <c r="G272" s="2"/>
+      <c r="H272" s="2"/>
+    </row>
+    <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="2"/>
+      <c r="B273" s="2"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="2"/>
+      <c r="E273" s="2"/>
+      <c r="F273" s="2"/>
+      <c r="G273" s="2"/>
+      <c r="H273" s="2"/>
+    </row>
+    <row r="274" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="2"/>
+      <c r="B274" s="2"/>
+      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
+      <c r="E274" s="2"/>
+      <c r="F274" s="2"/>
+      <c r="G274" s="2"/>
+      <c r="H274" s="2"/>
+    </row>
+    <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="2"/>
+      <c r="B275" s="2"/>
+      <c r="C275" s="2"/>
+      <c r="D275" s="2"/>
+      <c r="E275" s="2"/>
+      <c r="F275" s="2"/>
+      <c r="G275" s="2"/>
+      <c r="H275" s="2"/>
+    </row>
+    <row r="276" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="2"/>
+      <c r="B276" s="2"/>
+      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
+      <c r="E276" s="2"/>
+      <c r="F276" s="2"/>
+      <c r="G276" s="2"/>
+      <c r="H276" s="2"/>
+    </row>
+    <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="2"/>
+      <c r="B277" s="2"/>
+      <c r="C277" s="2"/>
+      <c r="D277" s="2"/>
+      <c r="E277" s="2"/>
+      <c r="F277" s="2"/>
+      <c r="G277" s="2"/>
+      <c r="H277" s="2"/>
+    </row>
+    <row r="278" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="2"/>
+      <c r="B278" s="2"/>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2"/>
+      <c r="E278" s="2"/>
+      <c r="F278" s="2"/>
+      <c r="G278" s="2"/>
+      <c r="H278" s="2"/>
+    </row>
+    <row r="279" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="2"/>
+      <c r="B279" s="2"/>
+      <c r="C279" s="2"/>
+      <c r="D279" s="2"/>
+      <c r="E279" s="2"/>
+      <c r="F279" s="2"/>
+      <c r="G279" s="2"/>
+      <c r="H279" s="2"/>
+    </row>
+    <row r="280" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="2"/>
+      <c r="B280" s="2"/>
+      <c r="C280" s="2"/>
+      <c r="D280" s="2"/>
+      <c r="E280" s="2"/>
+      <c r="F280" s="2"/>
+      <c r="G280" s="2"/>
+      <c r="H280" s="2"/>
+    </row>
+    <row r="281" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="2"/>
+      <c r="B281" s="2"/>
+      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
+      <c r="E281" s="2"/>
+      <c r="F281" s="2"/>
+      <c r="G281" s="2"/>
+      <c r="H281" s="2"/>
+    </row>
+    <row r="282" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="2"/>
+      <c r="B282" s="2"/>
+      <c r="C282" s="2"/>
+      <c r="D282" s="2"/>
+      <c r="E282" s="2"/>
+      <c r="F282" s="2"/>
+      <c r="G282" s="2"/>
+      <c r="H282" s="2"/>
+    </row>
+    <row r="283" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="2"/>
+      <c r="B283" s="2"/>
+      <c r="C283" s="2"/>
+      <c r="D283" s="2"/>
+      <c r="E283" s="2"/>
+      <c r="F283" s="2"/>
+      <c r="G283" s="2"/>
+      <c r="H283" s="2"/>
+    </row>
+    <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="2"/>
+      <c r="B284" s="2"/>
+      <c r="C284" s="2"/>
+      <c r="D284" s="2"/>
+      <c r="E284" s="2"/>
+      <c r="F284" s="2"/>
+      <c r="G284" s="2"/>
+      <c r="H284" s="2"/>
+    </row>
+    <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="2"/>
+      <c r="B285" s="2"/>
+      <c r="C285" s="2"/>
+      <c r="D285" s="2"/>
+      <c r="E285" s="2"/>
+      <c r="F285" s="2"/>
+      <c r="G285" s="2"/>
+      <c r="H285" s="2"/>
+    </row>
+    <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="2"/>
+      <c r="B286" s="2"/>
+      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
+      <c r="E286" s="2"/>
+      <c r="F286" s="2"/>
+      <c r="G286" s="2"/>
+      <c r="H286" s="2"/>
+    </row>
+    <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="2"/>
+      <c r="B287" s="2"/>
+      <c r="C287" s="2"/>
+      <c r="D287" s="2"/>
+      <c r="E287" s="2"/>
+      <c r="F287" s="2"/>
+      <c r="G287" s="2"/>
+      <c r="H287" s="2"/>
+    </row>
+    <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="2"/>
+      <c r="B288" s="2"/>
+      <c r="C288" s="2"/>
+      <c r="D288" s="2"/>
+      <c r="E288" s="2"/>
+      <c r="F288" s="2"/>
+      <c r="G288" s="2"/>
+      <c r="H288" s="2"/>
+    </row>
+    <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="2"/>
+      <c r="B289" s="2"/>
+      <c r="C289" s="2"/>
+      <c r="D289" s="2"/>
+      <c r="E289" s="2"/>
+      <c r="F289" s="2"/>
+      <c r="G289" s="2"/>
+      <c r="H289" s="2"/>
+    </row>
+    <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="2"/>
+      <c r="B290" s="2"/>
+      <c r="C290" s="2"/>
+      <c r="D290" s="2"/>
+      <c r="E290" s="2"/>
+      <c r="F290" s="2"/>
+      <c r="G290" s="2"/>
+      <c r="H290" s="2"/>
+    </row>
+    <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="2"/>
+      <c r="B291" s="2"/>
+      <c r="C291" s="2"/>
+      <c r="D291" s="2"/>
+      <c r="E291" s="2"/>
+      <c r="F291" s="2"/>
+      <c r="G291" s="2"/>
+      <c r="H291" s="2"/>
+    </row>
+    <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="2"/>
+      <c r="B292" s="2"/>
+      <c r="C292" s="2"/>
+      <c r="D292" s="2"/>
+      <c r="E292" s="2"/>
+      <c r="F292" s="2"/>
+      <c r="G292" s="2"/>
+      <c r="H292" s="2"/>
+    </row>
+    <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="2"/>
+      <c r="B293" s="2"/>
+      <c r="C293" s="2"/>
+      <c r="D293" s="2"/>
+      <c r="E293" s="2"/>
+      <c r="F293" s="2"/>
+      <c r="G293" s="2"/>
+      <c r="H293" s="2"/>
+    </row>
+    <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="2"/>
+      <c r="B294" s="2"/>
+      <c r="C294" s="2"/>
+      <c r="D294" s="2"/>
+      <c r="E294" s="2"/>
+      <c r="F294" s="2"/>
+      <c r="G294" s="2"/>
+      <c r="H294" s="2"/>
+    </row>
+    <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="2"/>
+      <c r="B295" s="2"/>
+      <c r="C295" s="2"/>
+      <c r="D295" s="2"/>
+      <c r="E295" s="2"/>
+      <c r="F295" s="2"/>
+      <c r="G295" s="2"/>
+      <c r="H295" s="2"/>
+    </row>
+    <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="2"/>
+      <c r="B296" s="2"/>
+      <c r="C296" s="2"/>
+      <c r="D296" s="2"/>
+      <c r="E296" s="2"/>
+      <c r="F296" s="2"/>
+      <c r="G296" s="2"/>
+      <c r="H296" s="2"/>
+    </row>
+    <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="2"/>
+      <c r="B297" s="2"/>
+      <c r="C297" s="2"/>
+      <c r="D297" s="2"/>
+      <c r="E297" s="2"/>
+      <c r="F297" s="2"/>
+      <c r="G297" s="2"/>
+      <c r="H297" s="2"/>
+    </row>
+    <row r="298" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="2"/>
+      <c r="B298" s="2"/>
+      <c r="C298" s="2"/>
+      <c r="D298" s="2"/>
+      <c r="E298" s="2"/>
+      <c r="F298" s="2"/>
+      <c r="G298" s="2"/>
+      <c r="H298" s="2"/>
+    </row>
+    <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="2"/>
+      <c r="B299" s="2"/>
+      <c r="C299" s="2"/>
+      <c r="D299" s="2"/>
+      <c r="E299" s="2"/>
+      <c r="F299" s="2"/>
+      <c r="G299" s="2"/>
+      <c r="H299" s="2"/>
+    </row>
+    <row r="300" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="2"/>
+      <c r="B300" s="2"/>
+      <c r="C300" s="2"/>
+      <c r="D300" s="2"/>
+      <c r="E300" s="2"/>
+      <c r="F300" s="2"/>
+      <c r="G300" s="2"/>
+      <c r="H300" s="2"/>
+    </row>
+    <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="2"/>
+      <c r="B301" s="2"/>
+      <c r="C301" s="2"/>
+      <c r="D301" s="2"/>
+      <c r="E301" s="2"/>
+      <c r="F301" s="2"/>
+      <c r="G301" s="2"/>
+      <c r="H301" s="2"/>
+    </row>
+    <row r="302" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="2"/>
+      <c r="B302" s="2"/>
+      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
+      <c r="E302" s="2"/>
+      <c r="F302" s="2"/>
+      <c r="G302" s="2"/>
+      <c r="H302" s="2"/>
+    </row>
+    <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="2"/>
+      <c r="B303" s="2"/>
+      <c r="C303" s="2"/>
+      <c r="D303" s="2"/>
+      <c r="E303" s="2"/>
+      <c r="F303" s="2"/>
+      <c r="G303" s="2"/>
+      <c r="H303" s="2"/>
+    </row>
+    <row r="304" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="2"/>
+      <c r="B304" s="2"/>
+      <c r="C304" s="2"/>
+      <c r="D304" s="2"/>
+      <c r="E304" s="2"/>
+      <c r="F304" s="2"/>
+      <c r="G304" s="2"/>
+      <c r="H304" s="2"/>
+    </row>
+    <row r="305" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="2"/>
+      <c r="B305" s="2"/>
+      <c r="C305" s="2"/>
+      <c r="D305" s="2"/>
+      <c r="E305" s="2"/>
+      <c r="F305" s="2"/>
+      <c r="G305" s="2"/>
+      <c r="H305" s="2"/>
+    </row>
+    <row r="306" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="2"/>
+      <c r="B306" s="2"/>
+      <c r="C306" s="2"/>
+      <c r="D306" s="2"/>
+      <c r="E306" s="2"/>
+      <c r="F306" s="2"/>
+      <c r="G306" s="2"/>
+      <c r="H306" s="2"/>
+    </row>
+    <row r="307" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="2"/>
+      <c r="B307" s="2"/>
+      <c r="C307" s="2"/>
+      <c r="D307" s="2"/>
+      <c r="E307" s="2"/>
+      <c r="F307" s="2"/>
+      <c r="G307" s="2"/>
+      <c r="H307" s="2"/>
+    </row>
+    <row r="308" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="2"/>
+      <c r="B308" s="2"/>
+      <c r="C308" s="2"/>
+      <c r="D308" s="2"/>
+      <c r="E308" s="2"/>
+      <c r="F308" s="2"/>
+      <c r="G308" s="2"/>
+      <c r="H308" s="2"/>
+    </row>
+    <row r="309" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="2"/>
+      <c r="B309" s="2"/>
+      <c r="C309" s="2"/>
+      <c r="D309" s="2"/>
+      <c r="E309" s="2"/>
+      <c r="F309" s="2"/>
+      <c r="G309" s="2"/>
+      <c r="H309" s="2"/>
+    </row>
+    <row r="310" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="2"/>
+      <c r="B310" s="2"/>
+      <c r="C310" s="2"/>
+      <c r="D310" s="2"/>
+      <c r="E310" s="2"/>
+      <c r="F310" s="2"/>
+      <c r="G310" s="2"/>
+      <c r="H310" s="2"/>
+    </row>
+    <row r="311" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="2"/>
+      <c r="B311" s="2"/>
+      <c r="C311" s="2"/>
+      <c r="D311" s="2"/>
+      <c r="E311" s="2"/>
+      <c r="F311" s="2"/>
+      <c r="G311" s="2"/>
+      <c r="H311" s="2"/>
+    </row>
+    <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="2"/>
+      <c r="B312" s="2"/>
+      <c r="C312" s="2"/>
+      <c r="D312" s="2"/>
+      <c r="E312" s="2"/>
+      <c r="F312" s="2"/>
+      <c r="G312" s="2"/>
+      <c r="H312" s="2"/>
+    </row>
+    <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="2"/>
+      <c r="B313" s="2"/>
+      <c r="C313" s="2"/>
+      <c r="D313" s="2"/>
+      <c r="E313" s="2"/>
+      <c r="F313" s="2"/>
+      <c r="G313" s="2"/>
+      <c r="H313" s="2"/>
+    </row>
+    <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="2"/>
+      <c r="B314" s="2"/>
+      <c r="C314" s="2"/>
+      <c r="D314" s="2"/>
+      <c r="E314" s="2"/>
+      <c r="F314" s="2"/>
+      <c r="G314" s="2"/>
+      <c r="H314" s="2"/>
+    </row>
+    <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="2"/>
+      <c r="B315" s="2"/>
+      <c r="C315" s="2"/>
+      <c r="D315" s="2"/>
+      <c r="E315" s="2"/>
+      <c r="F315" s="2"/>
+      <c r="G315" s="2"/>
+      <c r="H315" s="2"/>
+    </row>
+    <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="2"/>
+      <c r="B316" s="2"/>
+      <c r="C316" s="2"/>
+      <c r="D316" s="2"/>
+      <c r="E316" s="2"/>
+      <c r="F316" s="2"/>
+      <c r="G316" s="2"/>
+      <c r="H316" s="2"/>
+    </row>
+    <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="2"/>
+      <c r="B317" s="2"/>
+      <c r="C317" s="2"/>
+      <c r="D317" s="2"/>
+      <c r="E317" s="2"/>
+      <c r="F317" s="2"/>
+      <c r="G317" s="2"/>
+      <c r="H317" s="2"/>
+    </row>
+    <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="2"/>
+      <c r="B318" s="2"/>
+      <c r="C318" s="2"/>
+      <c r="D318" s="2"/>
+      <c r="E318" s="2"/>
+      <c r="F318" s="2"/>
+      <c r="G318" s="2"/>
+      <c r="H318" s="2"/>
+    </row>
+    <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="2"/>
+      <c r="B319" s="2"/>
+      <c r="C319" s="2"/>
+      <c r="D319" s="2"/>
+      <c r="E319" s="2"/>
+      <c r="F319" s="2"/>
+      <c r="G319" s="2"/>
+      <c r="H319" s="2"/>
+    </row>
+    <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="2"/>
+      <c r="B320" s="2"/>
+      <c r="C320" s="2"/>
+      <c r="D320" s="2"/>
+      <c r="E320" s="2"/>
+      <c r="F320" s="2"/>
+      <c r="G320" s="2"/>
+      <c r="H320" s="2"/>
+    </row>
+    <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="2"/>
+      <c r="B321" s="2"/>
+      <c r="C321" s="2"/>
+      <c r="D321" s="2"/>
+      <c r="E321" s="2"/>
+      <c r="F321" s="2"/>
+      <c r="G321" s="2"/>
+      <c r="H321" s="2"/>
+    </row>
+    <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="2"/>
+      <c r="B322" s="2"/>
+      <c r="C322" s="2"/>
+      <c r="D322" s="2"/>
+      <c r="E322" s="2"/>
+      <c r="F322" s="2"/>
+      <c r="G322" s="2"/>
+      <c r="H322" s="2"/>
+    </row>
+    <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="2"/>
+      <c r="B323" s="2"/>
+      <c r="C323" s="2"/>
+      <c r="D323" s="2"/>
+      <c r="E323" s="2"/>
+      <c r="F323" s="2"/>
+      <c r="G323" s="2"/>
+      <c r="H323" s="2"/>
+    </row>
+    <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A324" s="2"/>
+      <c r="B324" s="2"/>
+      <c r="C324" s="2"/>
+      <c r="D324" s="2"/>
+      <c r="E324" s="2"/>
+      <c r="F324" s="2"/>
+      <c r="G324" s="2"/>
+      <c r="H324" s="2"/>
+    </row>
+    <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="2"/>
+      <c r="B325" s="2"/>
+      <c r="C325" s="2"/>
+      <c r="D325" s="2"/>
+      <c r="E325" s="2"/>
+      <c r="F325" s="2"/>
+      <c r="G325" s="2"/>
+      <c r="H325" s="2"/>
+    </row>
+    <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="2"/>
+      <c r="B326" s="2"/>
+      <c r="C326" s="2"/>
+      <c r="D326" s="2"/>
+      <c r="E326" s="2"/>
+      <c r="F326" s="2"/>
+      <c r="G326" s="2"/>
+      <c r="H326" s="2"/>
+    </row>
+    <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="2"/>
+      <c r="B327" s="2"/>
+      <c r="C327" s="2"/>
+      <c r="D327" s="2"/>
+      <c r="E327" s="2"/>
+      <c r="F327" s="2"/>
+      <c r="G327" s="2"/>
+      <c r="H327" s="2"/>
+    </row>
+    <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="2"/>
+      <c r="B328" s="2"/>
+      <c r="C328" s="2"/>
+      <c r="D328" s="2"/>
+      <c r="E328" s="2"/>
+      <c r="F328" s="2"/>
+      <c r="G328" s="2"/>
+      <c r="H328" s="2"/>
+    </row>
+    <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A329" s="2"/>
+      <c r="B329" s="2"/>
+      <c r="C329" s="2"/>
+      <c r="D329" s="2"/>
+      <c r="E329" s="2"/>
+      <c r="F329" s="2"/>
+      <c r="G329" s="2"/>
+      <c r="H329" s="2"/>
+    </row>
+    <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="2"/>
+      <c r="B330" s="2"/>
+      <c r="C330" s="2"/>
+      <c r="D330" s="2"/>
+      <c r="E330" s="2"/>
+      <c r="F330" s="2"/>
+      <c r="G330" s="2"/>
+      <c r="H330" s="2"/>
+    </row>
+    <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="2"/>
+      <c r="B331" s="2"/>
+      <c r="C331" s="2"/>
+      <c r="D331" s="2"/>
+      <c r="E331" s="2"/>
+      <c r="F331" s="2"/>
+      <c r="G331" s="2"/>
+      <c r="H331" s="2"/>
+    </row>
+    <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="2"/>
+      <c r="B332" s="2"/>
+      <c r="C332" s="2"/>
+      <c r="D332" s="2"/>
+      <c r="E332" s="2"/>
+      <c r="F332" s="2"/>
+      <c r="G332" s="2"/>
+      <c r="H332" s="2"/>
+    </row>
+    <row r="333" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="2"/>
+      <c r="B333" s="2"/>
+      <c r="C333" s="2"/>
+      <c r="D333" s="2"/>
+      <c r="E333" s="2"/>
+      <c r="F333" s="2"/>
+      <c r="G333" s="2"/>
+      <c r="H333" s="2"/>
+    </row>
+    <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="2"/>
+      <c r="B334" s="2"/>
+      <c r="C334" s="2"/>
+      <c r="D334" s="2"/>
+      <c r="E334" s="2"/>
+      <c r="F334" s="2"/>
+      <c r="G334" s="2"/>
+      <c r="H334" s="2"/>
+    </row>
+    <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="2"/>
+      <c r="B335" s="2"/>
+      <c r="C335" s="2"/>
+      <c r="D335" s="2"/>
+      <c r="E335" s="2"/>
+      <c r="F335" s="2"/>
+      <c r="G335" s="2"/>
+      <c r="H335" s="2"/>
+    </row>
+    <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="2"/>
+      <c r="B336" s="2"/>
+      <c r="C336" s="2"/>
+      <c r="D336" s="2"/>
+      <c r="E336" s="2"/>
+      <c r="F336" s="2"/>
+      <c r="G336" s="2"/>
+      <c r="H336" s="2"/>
+    </row>
+    <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="2"/>
+      <c r="B337" s="2"/>
+      <c r="C337" s="2"/>
+      <c r="D337" s="2"/>
+      <c r="E337" s="2"/>
+      <c r="F337" s="2"/>
+      <c r="G337" s="2"/>
+      <c r="H337" s="2"/>
+    </row>
+    <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="2"/>
+      <c r="B338" s="2"/>
+      <c r="C338" s="2"/>
+      <c r="D338" s="2"/>
+      <c r="E338" s="2"/>
+      <c r="F338" s="2"/>
+      <c r="G338" s="2"/>
+      <c r="H338" s="2"/>
+    </row>
+    <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="2"/>
+      <c r="B339" s="2"/>
+      <c r="C339" s="2"/>
+      <c r="D339" s="2"/>
+      <c r="E339" s="2"/>
+      <c r="F339" s="2"/>
+      <c r="G339" s="2"/>
+      <c r="H339" s="2"/>
+    </row>
+    <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="2"/>
+      <c r="B340" s="2"/>
+      <c r="C340" s="2"/>
+      <c r="D340" s="2"/>
+      <c r="E340" s="2"/>
+      <c r="F340" s="2"/>
+      <c r="G340" s="2"/>
+      <c r="H340" s="2"/>
+    </row>
+    <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="2"/>
+      <c r="B341" s="2"/>
+      <c r="C341" s="2"/>
+      <c r="D341" s="2"/>
+      <c r="E341" s="2"/>
+      <c r="F341" s="2"/>
+      <c r="G341" s="2"/>
+      <c r="H341" s="2"/>
+    </row>
+    <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="2"/>
+      <c r="B342" s="2"/>
+      <c r="C342" s="2"/>
+      <c r="D342" s="2"/>
+      <c r="E342" s="2"/>
+      <c r="F342" s="2"/>
+      <c r="G342" s="2"/>
+      <c r="H342" s="2"/>
+    </row>
+    <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="2"/>
+      <c r="B343" s="2"/>
+      <c r="C343" s="2"/>
+      <c r="D343" s="2"/>
+      <c r="E343" s="2"/>
+      <c r="F343" s="2"/>
+      <c r="G343" s="2"/>
+      <c r="H343" s="2"/>
+    </row>
+    <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="2"/>
+      <c r="B344" s="2"/>
+      <c r="C344" s="2"/>
+      <c r="D344" s="2"/>
+      <c r="E344" s="2"/>
+      <c r="F344" s="2"/>
+      <c r="G344" s="2"/>
+      <c r="H344" s="2"/>
+    </row>
+    <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="2"/>
+      <c r="B345" s="2"/>
+      <c r="C345" s="2"/>
+      <c r="D345" s="2"/>
+      <c r="E345" s="2"/>
+      <c r="F345" s="2"/>
+      <c r="G345" s="2"/>
+      <c r="H345" s="2"/>
+    </row>
+    <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="2"/>
+      <c r="B346" s="2"/>
+      <c r="C346" s="2"/>
+      <c r="D346" s="2"/>
+      <c r="E346" s="2"/>
+      <c r="F346" s="2"/>
+      <c r="G346" s="2"/>
+      <c r="H346" s="2"/>
+    </row>
+    <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="2"/>
+      <c r="B347" s="2"/>
+      <c r="C347" s="2"/>
+      <c r="D347" s="2"/>
+      <c r="E347" s="2"/>
+      <c r="F347" s="2"/>
+      <c r="G347" s="2"/>
+      <c r="H347" s="2"/>
+    </row>
+    <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="2"/>
+      <c r="B348" s="2"/>
+      <c r="C348" s="2"/>
+      <c r="D348" s="2"/>
+      <c r="E348" s="2"/>
+      <c r="F348" s="2"/>
+      <c r="G348" s="2"/>
+      <c r="H348" s="2"/>
+    </row>
+    <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="2"/>
+      <c r="B349" s="2"/>
+      <c r="C349" s="2"/>
+      <c r="D349" s="2"/>
+      <c r="E349" s="2"/>
+      <c r="F349" s="2"/>
+      <c r="G349" s="2"/>
+      <c r="H349" s="2"/>
+    </row>
+    <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="2"/>
+      <c r="B350" s="2"/>
+      <c r="C350" s="2"/>
+      <c r="D350" s="2"/>
+      <c r="E350" s="2"/>
+      <c r="F350" s="2"/>
+      <c r="G350" s="2"/>
+      <c r="H350" s="2"/>
+    </row>
+    <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="2"/>
+      <c r="B351" s="2"/>
+      <c r="C351" s="2"/>
+      <c r="D351" s="2"/>
+      <c r="E351" s="2"/>
+      <c r="F351" s="2"/>
+      <c r="G351" s="2"/>
+      <c r="H351" s="2"/>
+    </row>
+    <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="2"/>
+      <c r="B352" s="2"/>
+      <c r="C352" s="2"/>
+      <c r="D352" s="2"/>
+      <c r="E352" s="2"/>
+      <c r="F352" s="2"/>
+      <c r="G352" s="2"/>
+      <c r="H352" s="2"/>
+    </row>
+    <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="2"/>
+      <c r="B353" s="2"/>
+      <c r="C353" s="2"/>
+      <c r="D353" s="2"/>
+      <c r="E353" s="2"/>
+      <c r="F353" s="2"/>
+      <c r="G353" s="2"/>
+      <c r="H353" s="2"/>
+    </row>
+    <row r="354" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A354" s="2"/>
+      <c r="B354" s="2"/>
+      <c r="C354" s="2"/>
+      <c r="D354" s="2"/>
+      <c r="E354" s="2"/>
+      <c r="F354" s="2"/>
+      <c r="G354" s="2"/>
+      <c r="H354" s="2"/>
+    </row>
+    <row r="355" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A355" s="2"/>
+      <c r="B355" s="2"/>
+      <c r="C355" s="2"/>
+      <c r="D355" s="2"/>
+      <c r="E355" s="2"/>
+      <c r="F355" s="2"/>
+      <c r="G355" s="2"/>
+      <c r="H355" s="2"/>
+    </row>
+    <row r="356" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="2"/>
+      <c r="B356" s="2"/>
+      <c r="C356" s="2"/>
+      <c r="D356" s="2"/>
+      <c r="E356" s="2"/>
+      <c r="F356" s="2"/>
+      <c r="G356" s="2"/>
+      <c r="H356" s="2"/>
+    </row>
+    <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="2"/>
+      <c r="B357" s="2"/>
+      <c r="C357" s="2"/>
+      <c r="D357" s="2"/>
+      <c r="E357" s="2"/>
+      <c r="F357" s="2"/>
+      <c r="G357" s="2"/>
+      <c r="H357" s="2"/>
+    </row>
+    <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="2"/>
+      <c r="B358" s="2"/>
+      <c r="C358" s="2"/>
+      <c r="D358" s="2"/>
+      <c r="E358" s="2"/>
+      <c r="F358" s="2"/>
+      <c r="G358" s="2"/>
+      <c r="H358" s="2"/>
+    </row>
+    <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A359" s="2"/>
+      <c r="B359" s="2"/>
+      <c r="C359" s="2"/>
+      <c r="D359" s="2"/>
+      <c r="E359" s="2"/>
+      <c r="F359" s="2"/>
+      <c r="G359" s="2"/>
+      <c r="H359" s="2"/>
+    </row>
+    <row r="360" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="2"/>
+      <c r="B360" s="2"/>
+      <c r="C360" s="2"/>
+      <c r="D360" s="2"/>
+      <c r="E360" s="2"/>
+      <c r="F360" s="2"/>
+      <c r="G360" s="2"/>
+      <c r="H360" s="2"/>
+    </row>
+    <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="2"/>
+      <c r="B361" s="2"/>
+      <c r="C361" s="2"/>
+      <c r="D361" s="2"/>
+      <c r="E361" s="2"/>
+      <c r="F361" s="2"/>
+      <c r="G361" s="2"/>
+      <c r="H361" s="2"/>
+    </row>
+    <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="2"/>
+      <c r="B362" s="2"/>
+      <c r="C362" s="2"/>
+      <c r="D362" s="2"/>
+      <c r="E362" s="2"/>
+      <c r="F362" s="2"/>
+      <c r="G362" s="2"/>
+      <c r="H362" s="2"/>
+    </row>
+    <row r="363" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A363" s="2"/>
+      <c r="B363" s="2"/>
+      <c r="C363" s="2"/>
+      <c r="D363" s="2"/>
+      <c r="E363" s="2"/>
+      <c r="F363" s="2"/>
+      <c r="G363" s="2"/>
+      <c r="H363" s="2"/>
+    </row>
+    <row r="364" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="2"/>
+      <c r="B364" s="2"/>
+      <c r="C364" s="2"/>
+      <c r="D364" s="2"/>
+      <c r="E364" s="2"/>
+      <c r="F364" s="2"/>
+      <c r="G364" s="2"/>
+      <c r="H364" s="2"/>
+    </row>
+    <row r="365" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A365" s="2"/>
+      <c r="B365" s="2"/>
+      <c r="C365" s="2"/>
+      <c r="D365" s="2"/>
+      <c r="E365" s="2"/>
+      <c r="F365" s="2"/>
+      <c r="G365" s="2"/>
+      <c r="H365" s="2"/>
+    </row>
+    <row r="366" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A366" s="2"/>
+      <c r="B366" s="2"/>
+      <c r="C366" s="2"/>
+      <c r="D366" s="2"/>
+      <c r="E366" s="2"/>
+      <c r="F366" s="2"/>
+      <c r="G366" s="2"/>
+      <c r="H366" s="2"/>
+    </row>
+    <row r="367" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A367" s="2"/>
+      <c r="B367" s="2"/>
+      <c r="C367" s="2"/>
+      <c r="D367" s="2"/>
+      <c r="E367" s="2"/>
+      <c r="F367" s="2"/>
+      <c r="G367" s="2"/>
+      <c r="H367" s="2"/>
+    </row>
+    <row r="368" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A368" s="2"/>
+      <c r="B368" s="2"/>
+      <c r="C368" s="2"/>
+      <c r="D368" s="2"/>
+      <c r="E368" s="2"/>
+      <c r="F368" s="2"/>
+      <c r="G368" s="2"/>
+      <c r="H368" s="2"/>
+    </row>
+    <row r="369" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A369" s="2"/>
+      <c r="B369" s="2"/>
+      <c r="C369" s="2"/>
+      <c r="D369" s="2"/>
+      <c r="E369" s="2"/>
+      <c r="F369" s="2"/>
+      <c r="G369" s="2"/>
+      <c r="H369" s="2"/>
+    </row>
+    <row r="370" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A370" s="2"/>
+      <c r="B370" s="2"/>
+      <c r="C370" s="2"/>
+      <c r="D370" s="2"/>
+      <c r="E370" s="2"/>
+      <c r="F370" s="2"/>
+      <c r="G370" s="2"/>
+      <c r="H370" s="2"/>
+    </row>
+    <row r="371" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A371" s="2"/>
+      <c r="B371" s="2"/>
+      <c r="C371" s="2"/>
+      <c r="D371" s="2"/>
+      <c r="E371" s="2"/>
+      <c r="F371" s="2"/>
+      <c r="G371" s="2"/>
+      <c r="H371" s="2"/>
+    </row>
+    <row r="372" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A372" s="2"/>
+      <c r="B372" s="2"/>
+      <c r="C372" s="2"/>
+      <c r="D372" s="2"/>
+      <c r="E372" s="2"/>
+      <c r="F372" s="2"/>
+      <c r="G372" s="2"/>
+      <c r="H372" s="2"/>
+    </row>
+    <row r="373" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A373" s="2"/>
+      <c r="B373" s="2"/>
+      <c r="C373" s="2"/>
+      <c r="D373" s="2"/>
+      <c r="E373" s="2"/>
+      <c r="F373" s="2"/>
+      <c r="G373" s="2"/>
+      <c r="H373" s="2"/>
+    </row>
+    <row r="374" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A374" s="2"/>
+      <c r="B374" s="2"/>
+      <c r="C374" s="2"/>
+      <c r="D374" s="2"/>
+      <c r="E374" s="2"/>
+      <c r="F374" s="2"/>
+      <c r="G374" s="2"/>
+      <c r="H374" s="2"/>
+    </row>
+    <row r="375" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A375" s="2"/>
+      <c r="B375" s="2"/>
+      <c r="C375" s="2"/>
+      <c r="D375" s="2"/>
+      <c r="E375" s="2"/>
+      <c r="F375" s="2"/>
+      <c r="G375" s="2"/>
+      <c r="H375" s="2"/>
+    </row>
+    <row r="376" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A376" s="2"/>
+      <c r="B376" s="2"/>
+      <c r="C376" s="2"/>
+      <c r="D376" s="2"/>
+      <c r="E376" s="2"/>
+      <c r="F376" s="2"/>
+      <c r="G376" s="2"/>
+      <c r="H376" s="2"/>
+    </row>
+    <row r="377" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A377" s="2"/>
+      <c r="B377" s="2"/>
+      <c r="C377" s="2"/>
+      <c r="D377" s="2"/>
+      <c r="E377" s="2"/>
+      <c r="F377" s="2"/>
+      <c r="G377" s="2"/>
+      <c r="H377" s="2"/>
+    </row>
+    <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A378" s="2"/>
+      <c r="B378" s="2"/>
+      <c r="C378" s="2"/>
+      <c r="D378" s="2"/>
+      <c r="E378" s="2"/>
+      <c r="F378" s="2"/>
+      <c r="G378" s="2"/>
+      <c r="H378" s="2"/>
+    </row>
+    <row r="379" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A379" s="2"/>
+      <c r="B379" s="2"/>
+      <c r="C379" s="2"/>
+      <c r="D379" s="2"/>
+      <c r="E379" s="2"/>
+      <c r="F379" s="2"/>
+      <c r="G379" s="2"/>
+      <c r="H379" s="2"/>
+    </row>
+    <row r="380" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A380" s="2"/>
+      <c r="B380" s="2"/>
+      <c r="C380" s="2"/>
+      <c r="D380" s="2"/>
+      <c r="E380" s="2"/>
+      <c r="F380" s="2"/>
+      <c r="G380" s="2"/>
+      <c r="H380" s="2"/>
+    </row>
+    <row r="381" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="2"/>
+      <c r="B381" s="2"/>
+      <c r="C381" s="2"/>
+      <c r="D381" s="2"/>
+      <c r="E381" s="2"/>
+      <c r="F381" s="2"/>
+      <c r="G381" s="2"/>
+      <c r="H381" s="2"/>
+    </row>
+    <row r="382" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A382" s="2"/>
+      <c r="B382" s="2"/>
+      <c r="C382" s="2"/>
+      <c r="D382" s="2"/>
+      <c r="E382" s="2"/>
+      <c r="F382" s="2"/>
+      <c r="G382" s="2"/>
+      <c r="H382" s="2"/>
+    </row>
+    <row r="383" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A383" s="2"/>
+      <c r="B383" s="2"/>
+      <c r="C383" s="2"/>
+      <c r="D383" s="2"/>
+      <c r="E383" s="2"/>
+      <c r="F383" s="2"/>
+      <c r="G383" s="2"/>
+      <c r="H383" s="2"/>
+    </row>
+    <row r="384" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A384" s="2"/>
+      <c r="B384" s="2"/>
+      <c r="C384" s="2"/>
+      <c r="D384" s="2"/>
+      <c r="E384" s="2"/>
+      <c r="F384" s="2"/>
+      <c r="G384" s="2"/>
+      <c r="H384" s="2"/>
+    </row>
+    <row r="385" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="2"/>
+      <c r="B385" s="2"/>
+      <c r="C385" s="2"/>
+      <c r="D385" s="2"/>
+      <c r="E385" s="2"/>
+      <c r="F385" s="2"/>
+      <c r="G385" s="2"/>
+      <c r="H385" s="2"/>
+    </row>
+    <row r="386" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A386" s="2"/>
+      <c r="B386" s="2"/>
+      <c r="C386" s="2"/>
+      <c r="D386" s="2"/>
+      <c r="E386" s="2"/>
+      <c r="F386" s="2"/>
+      <c r="G386" s="2"/>
+      <c r="H386" s="2"/>
+    </row>
+    <row r="387" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="2"/>
+      <c r="B387" s="2"/>
+      <c r="C387" s="2"/>
+      <c r="D387" s="2"/>
+      <c r="E387" s="2"/>
+      <c r="F387" s="2"/>
+      <c r="G387" s="2"/>
+      <c r="H387" s="2"/>
+    </row>
+    <row r="388" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A388" s="2"/>
+      <c r="B388" s="2"/>
+      <c r="C388" s="2"/>
+      <c r="D388" s="2"/>
+      <c r="E388" s="2"/>
+      <c r="F388" s="2"/>
+      <c r="G388" s="2"/>
+      <c r="H388" s="2"/>
+    </row>
+    <row r="389" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A389" s="2"/>
+      <c r="B389" s="2"/>
+      <c r="C389" s="2"/>
+      <c r="D389" s="2"/>
+      <c r="E389" s="2"/>
+      <c r="F389" s="2"/>
+      <c r="G389" s="2"/>
+      <c r="H389" s="2"/>
+    </row>
+    <row r="390" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A390" s="2"/>
+      <c r="B390" s="2"/>
+      <c r="C390" s="2"/>
+      <c r="D390" s="2"/>
+      <c r="E390" s="2"/>
+      <c r="F390" s="2"/>
+      <c r="G390" s="2"/>
+      <c r="H390" s="2"/>
+    </row>
+    <row r="391" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A391" s="2"/>
+      <c r="B391" s="2"/>
+      <c r="C391" s="2"/>
+      <c r="D391" s="2"/>
+      <c r="E391" s="2"/>
+      <c r="F391" s="2"/>
+      <c r="G391" s="2"/>
+      <c r="H391" s="2"/>
+    </row>
+    <row r="392" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A392" s="2"/>
+      <c r="B392" s="2"/>
+      <c r="C392" s="2"/>
+      <c r="D392" s="2"/>
+      <c r="E392" s="2"/>
+      <c r="F392" s="2"/>
+      <c r="G392" s="2"/>
+      <c r="H392" s="2"/>
+    </row>
+    <row r="393" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A393" s="2"/>
+      <c r="B393" s="2"/>
+      <c r="C393" s="2"/>
+      <c r="D393" s="2"/>
+      <c r="E393" s="2"/>
+      <c r="F393" s="2"/>
+      <c r="G393" s="2"/>
+      <c r="H393" s="2"/>
+    </row>
+    <row r="394" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A394" s="2"/>
+      <c r="B394" s="2"/>
+      <c r="C394" s="2"/>
+      <c r="D394" s="2"/>
+      <c r="E394" s="2"/>
+      <c r="F394" s="2"/>
+      <c r="G394" s="2"/>
+      <c r="H394" s="2"/>
+    </row>
+    <row r="395" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A395" s="2"/>
+      <c r="B395" s="2"/>
+      <c r="C395" s="2"/>
+      <c r="D395" s="2"/>
+      <c r="E395" s="2"/>
+      <c r="F395" s="2"/>
+      <c r="G395" s="2"/>
+      <c r="H395" s="2"/>
+    </row>
+    <row r="396" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A396" s="2"/>
+      <c r="B396" s="2"/>
+      <c r="C396" s="2"/>
+      <c r="D396" s="2"/>
+      <c r="E396" s="2"/>
+      <c r="F396" s="2"/>
+      <c r="G396" s="2"/>
+      <c r="H396" s="2"/>
+    </row>
+    <row r="397" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A397" s="2"/>
+      <c r="B397" s="2"/>
+      <c r="C397" s="2"/>
+      <c r="D397" s="2"/>
+      <c r="E397" s="2"/>
+      <c r="F397" s="2"/>
+      <c r="G397" s="2"/>
+      <c r="H397" s="2"/>
+    </row>
+    <row r="398" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A398" s="2"/>
+      <c r="B398" s="2"/>
+      <c r="C398" s="2"/>
+      <c r="D398" s="2"/>
+      <c r="E398" s="2"/>
+      <c r="F398" s="2"/>
+      <c r="G398" s="2"/>
+      <c r="H398" s="2"/>
+    </row>
+    <row r="399" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A399" s="2"/>
+      <c r="B399" s="2"/>
+      <c r="C399" s="2"/>
+      <c r="D399" s="2"/>
+      <c r="E399" s="2"/>
+      <c r="F399" s="2"/>
+      <c r="G399" s="2"/>
+      <c r="H399" s="2"/>
+    </row>
+    <row r="400" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A400" s="2"/>
+      <c r="B400" s="2"/>
+      <c r="C400" s="2"/>
+      <c r="D400" s="2"/>
+      <c r="E400" s="2"/>
+      <c r="F400" s="2"/>
+      <c r="G400" s="2"/>
+      <c r="H400" s="2"/>
+    </row>
+    <row r="401" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A401" s="2"/>
+      <c r="B401" s="2"/>
+      <c r="C401" s="2"/>
+      <c r="D401" s="2"/>
+      <c r="E401" s="2"/>
+      <c r="F401" s="2"/>
+      <c r="G401" s="2"/>
+      <c r="H401" s="2"/>
+    </row>
+    <row r="402" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A402" s="2"/>
+      <c r="B402" s="2"/>
+      <c r="C402" s="2"/>
+      <c r="D402" s="2"/>
+      <c r="E402" s="2"/>
+      <c r="F402" s="2"/>
+      <c r="G402" s="2"/>
+      <c r="H402" s="2"/>
+    </row>
+    <row r="403" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A403" s="2"/>
+      <c r="B403" s="2"/>
+      <c r="C403" s="2"/>
+      <c r="D403" s="2"/>
+      <c r="E403" s="2"/>
+      <c r="F403" s="2"/>
+      <c r="G403" s="2"/>
+      <c r="H403" s="2"/>
+    </row>
+    <row r="404" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A404" s="2"/>
+      <c r="B404" s="2"/>
+      <c r="C404" s="2"/>
+      <c r="D404" s="2"/>
+      <c r="E404" s="2"/>
+      <c r="F404" s="2"/>
+      <c r="G404" s="2"/>
+      <c r="H404" s="2"/>
+    </row>
+    <row r="405" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A405" s="2"/>
+      <c r="B405" s="2"/>
+      <c r="C405" s="2"/>
+      <c r="D405" s="2"/>
+      <c r="E405" s="2"/>
+      <c r="F405" s="2"/>
+      <c r="G405" s="2"/>
+      <c r="H405" s="2"/>
+    </row>
+    <row r="406" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A406" s="2"/>
+      <c r="B406" s="2"/>
+      <c r="C406" s="2"/>
+      <c r="D406" s="2"/>
+      <c r="E406" s="2"/>
+      <c r="F406" s="2"/>
+      <c r="G406" s="2"/>
+      <c r="H406" s="2"/>
+    </row>
+    <row r="407" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A407" s="2"/>
+      <c r="B407" s="2"/>
+      <c r="C407" s="2"/>
+      <c r="D407" s="2"/>
+      <c r="E407" s="2"/>
+      <c r="F407" s="2"/>
+      <c r="G407" s="2"/>
+      <c r="H407" s="2"/>
+    </row>
+    <row r="408" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A408" s="2"/>
+      <c r="B408" s="2"/>
+      <c r="C408" s="2"/>
+      <c r="D408" s="2"/>
+      <c r="E408" s="2"/>
+      <c r="F408" s="2"/>
+      <c r="G408" s="2"/>
+      <c r="H408" s="2"/>
+    </row>
+    <row r="409" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A409" s="2"/>
+      <c r="B409" s="2"/>
+      <c r="C409" s="2"/>
+      <c r="D409" s="2"/>
+      <c r="E409" s="2"/>
+      <c r="F409" s="2"/>
+      <c r="G409" s="2"/>
+      <c r="H409" s="2"/>
+    </row>
+    <row r="410" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A410" s="2"/>
+      <c r="B410" s="2"/>
+      <c r="C410" s="2"/>
+      <c r="D410" s="2"/>
+      <c r="E410" s="2"/>
+      <c r="F410" s="2"/>
+      <c r="G410" s="2"/>
+      <c r="H410" s="2"/>
+    </row>
+    <row r="411" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A411" s="2"/>
+      <c r="B411" s="2"/>
+      <c r="C411" s="2"/>
+      <c r="D411" s="2"/>
+      <c r="E411" s="2"/>
+      <c r="F411" s="2"/>
+      <c r="G411" s="2"/>
+      <c r="H411" s="2"/>
+    </row>
+    <row r="412" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A412" s="2"/>
+      <c r="B412" s="2"/>
+      <c r="C412" s="2"/>
+      <c r="D412" s="2"/>
+      <c r="E412" s="2"/>
+      <c r="F412" s="2"/>
+      <c r="G412" s="2"/>
+      <c r="H412" s="2"/>
+    </row>
+    <row r="413" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A413" s="2"/>
+      <c r="B413" s="2"/>
+      <c r="C413" s="2"/>
+      <c r="D413" s="2"/>
+      <c r="E413" s="2"/>
+      <c r="F413" s="2"/>
+      <c r="G413" s="2"/>
+      <c r="H413" s="2"/>
+    </row>
+    <row r="414" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A414" s="2"/>
+      <c r="B414" s="2"/>
+      <c r="C414" s="2"/>
+      <c r="D414" s="2"/>
+      <c r="E414" s="2"/>
+      <c r="F414" s="2"/>
+      <c r="G414" s="2"/>
+      <c r="H414" s="2"/>
+    </row>
+    <row r="415" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A415" s="2"/>
+      <c r="B415" s="2"/>
+      <c r="C415" s="2"/>
+      <c r="D415" s="2"/>
+      <c r="E415" s="2"/>
+      <c r="F415" s="2"/>
+      <c r="G415" s="2"/>
+      <c r="H415" s="2"/>
+    </row>
+    <row r="416" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A416" s="2"/>
+      <c r="B416" s="2"/>
+      <c r="C416" s="2"/>
+      <c r="D416" s="2"/>
+      <c r="E416" s="2"/>
+      <c r="F416" s="2"/>
+      <c r="G416" s="2"/>
+      <c r="H416" s="2"/>
+    </row>
+    <row r="417" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A417" s="2"/>
+      <c r="B417" s="2"/>
+      <c r="C417" s="2"/>
+      <c r="D417" s="2"/>
+      <c r="E417" s="2"/>
+      <c r="F417" s="2"/>
+      <c r="G417" s="2"/>
+      <c r="H417" s="2"/>
+    </row>
+    <row r="418" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A418" s="2"/>
+      <c r="B418" s="2"/>
+      <c r="C418" s="2"/>
+      <c r="D418" s="2"/>
+      <c r="E418" s="2"/>
+      <c r="F418" s="2"/>
+      <c r="G418" s="2"/>
+      <c r="H418" s="2"/>
+    </row>
+    <row r="419" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A419" s="2"/>
+      <c r="B419" s="2"/>
+      <c r="C419" s="2"/>
+      <c r="D419" s="2"/>
+      <c r="E419" s="2"/>
+      <c r="F419" s="2"/>
+      <c r="G419" s="2"/>
+      <c r="H419" s="2"/>
+    </row>
+    <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A420" s="2"/>
+      <c r="B420" s="2"/>
+      <c r="C420" s="2"/>
+      <c r="D420" s="2"/>
+      <c r="E420" s="2"/>
+      <c r="F420" s="2"/>
+      <c r="G420" s="2"/>
+      <c r="H420" s="2"/>
+    </row>
+    <row r="421" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A421" s="2"/>
+      <c r="B421" s="2"/>
+      <c r="C421" s="2"/>
+      <c r="D421" s="2"/>
+      <c r="E421" s="2"/>
+      <c r="F421" s="2"/>
+      <c r="G421" s="2"/>
+      <c r="H421" s="2"/>
+    </row>
+    <row r="422" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A422" s="2"/>
+      <c r="B422" s="2"/>
+      <c r="C422" s="2"/>
+      <c r="D422" s="2"/>
+      <c r="E422" s="2"/>
+      <c r="F422" s="2"/>
+      <c r="G422" s="2"/>
+      <c r="H422" s="2"/>
+    </row>
+    <row r="423" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A423" s="2"/>
+      <c r="B423" s="2"/>
+      <c r="C423" s="2"/>
+      <c r="D423" s="2"/>
+      <c r="E423" s="2"/>
+      <c r="F423" s="2"/>
+      <c r="G423" s="2"/>
+      <c r="H423" s="2"/>
+    </row>
+    <row r="424" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A424" s="2"/>
+      <c r="B424" s="2"/>
+      <c r="C424" s="2"/>
+      <c r="D424" s="2"/>
+      <c r="E424" s="2"/>
+      <c r="F424" s="2"/>
+      <c r="G424" s="2"/>
+      <c r="H424" s="2"/>
+    </row>
+    <row r="425" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A425" s="2"/>
+      <c r="B425" s="2"/>
+      <c r="C425" s="2"/>
+      <c r="D425" s="2"/>
+      <c r="E425" s="2"/>
+      <c r="F425" s="2"/>
+      <c r="G425" s="2"/>
+      <c r="H425" s="2"/>
+    </row>
+    <row r="426" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A426" s="2"/>
+      <c r="B426" s="2"/>
+      <c r="C426" s="2"/>
+      <c r="D426" s="2"/>
+      <c r="E426" s="2"/>
+      <c r="F426" s="2"/>
+      <c r="G426" s="2"/>
+      <c r="H426" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/multi.xlsx
+++ b/multi.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="936">
   <si>
     <t xml:space="preserve">variables</t>
   </si>
@@ -450,7 +450,7 @@
     <t xml:space="preserve">_03_control_quincenal_ok</t>
   </si>
   <si>
-    <t xml:space="preserve">✅ ¡Control quincenal guardado y factor calibrado!
+    <t xml:space="preserve">✅ ¡Control quincenal guardado y GET calibrado!
 • Variación detectada: {variacion} kg
 • Nuevo factor de actividad: {factor}</t>
   </si>
@@ -477,7 +477,7 @@
     <t xml:space="preserve">✅ ¡Peso base del mes registrado correctamente!\n\n• Peso inicial ({mes}): {peso} kg</t>
   </si>
   <si>
-    <t xml:space="preserve">✅ ¡Control quincenal guardado y factor calibrado!\n\n• Variación detectada: {variacion} kg\n• Nuevo factor de actividad: {factor}</t>
+    <t xml:space="preserve">✅ ¡Control quincenal guardado y GET calibrado!\n\n• Variación detectada: {variacion} kg\n• Nuevo GET de actividad: {factor}</t>
   </si>
   <si>
     <t xml:space="preserve">✅ ¡Cierre de mes registrado impecable!\n\nEl balance del período se ha consolidado y ya configuramos automáticamente tu perfil base para el inicio del próximo mes con {peso} kg.</t>
@@ -669,6 +669,42 @@
     <t xml:space="preserve">ℹ️ Orientación General del Sistema:</t>
   </si>
   <si>
+    <t xml:space="preserve">bot_analizando_actividad_ia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🤖 Analizando actividad con IA...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_err_procesar_actividad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error al procesar actividad: {e}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_reanalizando_desc_ia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🤖 Re-analizando descripción con IA...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_err_reanalizar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error al re-analizar: {e}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bot_err_procesar_act_fisica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Error al procesar la actividad física: {e}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">del_no_registros_momento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ No se encontraron registros para este momento en la fecha {fecha}.</t>
+  </si>
+  <si>
     <t xml:space="preserve">06_bot_reg_actividad</t>
   </si>
   <si>
@@ -789,9 +825,6 @@
     <t xml:space="preserve">06_bot_error_proc_act</t>
   </si>
   <si>
-    <t xml:space="preserve">❌ Error al procesar actividad: {e}</t>
-  </si>
-  <si>
     <t xml:space="preserve">06_bot_error_fecha_inv</t>
   </si>
   <si>
@@ -933,6 +966,18 @@
     <t xml:space="preserve">✅ ¡Presión arterial registrada con éxito!\n\n• Presión Alta: {alta} mmHg\n• Presión Baja: {baja} mmHg{pul_txt}</t>
   </si>
   <si>
+    <t xml:space="preserve">06_bot_conf_ingesta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📝 &lt;b&gt;Confirmación de Ingesta:&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">del_titulo_eliminar_registros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🗑️ **Eliminar Registros**\n📅 Fecha: {fecha} | Momento: {momento}\n\n</t>
+  </si>
+  <si>
     <t xml:space="preserve">07_bot_no_comidas_precargadas</t>
   </si>
   <si>
@@ -1269,6 +1314,18 @@
     <t xml:space="preserve">✅ ¡Presión arterial registrada con éxito!\n\n• Presión Alta: {alta} mmHg\n• Presión Baja: {baja} mmHg{pul_txt}\n📝 Nota: {nota}</t>
   </si>
   <si>
+    <t xml:space="preserve">bot_operacion_cancelada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Operación cancelada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_bot_producto_desconocido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Producto desconocido</t>
+  </si>
+  <si>
     <t xml:space="preserve">08_inf_diario_titulo</t>
   </si>
   <si>
@@ -1830,6 +1887,24 @@
     <t xml:space="preserve">❌ Período de prueba finalizado.\nNo alcanzaste el objetivo mínimo de constancia (20 días) para mantener la cuenta gratuita y el seguimiento fue pausado.\n\nPara reactivarlo y usar el bot sin interrupciones hasta fin de mes, hemos emitido una factura proporcional por los días restantes (aprox. {costo_usd} USD / {estrellas} ⭐️).\n\nA fin de mes podrás elegir tu plan definitivo.</t>
   </si>
   <si>
+    <t xml:space="preserve">08_notif_de_anteayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de anteayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08_notif_de_ayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de ayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08_notif_de_hoy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de hoy</t>
+  </si>
+  <si>
     <t xml:space="preserve">09_ing_error_usuario_deshabilitado</t>
   </si>
   <si>
@@ -2187,196 +2262,433 @@
     <t xml:space="preserve">09_get_error_datos_expirados</t>
   </si>
   <si>
+    <t xml:space="preserve">⚠️ Los datos temporales expiraron. Por favor, volvé a enviar el comando /GET.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_calibracion_exito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ ¡Gasto energético actualizado con éxito!\n\n• Nuevo Gasto Diario asignado: {get_final:.0f} kcal\n• Período actualizado: {mes_actual}\n• Estado: Calibración mensual registrada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_error_guardar_db</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠ Ocurrió un error al guardar en la base de datos: {e}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reloj_actualizado_mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Período en formato YYYY-MM que registra si el usuario ya realizó su calibración mensual del GET mediante reloj inteligente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profesional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID de Telegram del médico o profesional de la salud asociado al seguimiento del paciente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ritmo_preferido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ritmo de avance seleccionado por el usuario (tranquilo, moderado, intenso) para definir el déficit o superávit calórico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cintura_cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perímetro de la cintura medido en centímetros para el cálculo de masa magra de alta precisión.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cuello_cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perímetro del cuello medido en centímetros para la estimación de composición corporal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cadera_cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perímetro de la cadera medido en centímetros (específico para perfiles femeninos).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valores_Clinicos_Profesional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabla relacional de supremacía clínica donde el médico almacena los topes personalizados de calorías y macronutrientes por período.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_perfil_lbl_cintura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cintura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_perfil_lbl_cuello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_perfil_lbl_cadera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_perfil_lbl_meta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_perfil_lbl_act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_perfil_fecha_no_reg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No registrada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_perfil_mod_pediatrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modalidad Pediátrica/Juvenil (Cálculo OMS sin circunferencias)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_perfil_alerta_medidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Atención: Tenés 18 años o más. Actualizá tus medidas con los botones de abajo para activar el cálculo de masa magra de alta precisión clínica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_btn_ritmo_tranquilo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟢 Tranquilo / Lento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_btn_ritmo_moderado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟡 Moderado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_btn_ritmo_intenso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔴 Intenso / Rápido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_presi_resumen_titulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 Resumen de Presión Arterial ({mes}):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_presi_mediciones_reg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Mediciones registradas: {cant}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_presi_prom_alta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_presi_prom_baja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_presi_prom_pulso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_presi_foto_err_rango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Lectura de presión atípica o errónea\n\nLos valores detectados en la imagen ({alta:.0f}/{baja:.0f} mmHg) están fuera de los rangos biológicos lógicos.\n\nPor favor, registrala manualmente usando:\n/presi [alta],[baja],[pulsaciones] (ej: /presi 120,80,75).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_btn_presi_agregar_nota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_btn_presi_guardar_directo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_btn_cancelar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_presi_foto_detectada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 Tensiómetro detectado en la imagen:\n\n• Presión Alta: {alta:.0f} mmHg\n• Presión Baja: {baja:.0f} mmHg{pul_txt}\n\nSeleccioná una opción para continuar:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_presi_generando_pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generando PDF de presión... ⏳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_presi_pdf_caption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🩺 Reporte de Presión Arterial - Período {mes}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_bloqueo_medico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👨‍⚕️ &lt;b&gt;Acción denegada:&lt;/b&gt; Tenés un profesional asignado. Por favor, contactalo directamente para realizar modificaciones en tu plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_start_mensaje_bienvenida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👋 *¡Bienvenido a tu Bot Nutricional Personalizado!*\n\nGuía rápida de comandos e ingresos disponibles:\n\n📌 *Comandos Principales:*\n• /alta: Apertura de cuenta ingresando los datos.\n• /barra: Ingresa por código de barras un comestible.\n• /borracomida: Borra una comida de la Planilla.\n• /comidas: Planilla de comidas precargadas y PDF.\n• /dia: Ingestas seleccionando por teclado y PDF.\n• /eliminar: Borra ingestas y actividades.\n• /GET: Actualiza GET por reloj inteligente .\n• /inicio: Resumen de comandos y manual en PDF.\n• /pagar: Elegir el plan o promoción de pago vigente.\n• /perfil: Actualización de datos biométricos.\n• /peso: Registro o control de peso mensual \n• /presi: Registro y consulta de presión arterial.\n• /receta: Calculadora Web para registrar comidas.\n• /mes: Reporte mensual de calorías y PDF .\n• /semana: Estadística semanal (calorías, fibras, etc.).\n• /x: Cancelar comando.\n\n📌 *Métodos de Registro y consultas directas:*\n• *Ingestas con IA:* 📝 Texto, 🎤 Notas de voz, 📸 Fotos.\n• *Ingestas con IA:* 📸 Fotos de un código de barras\n• *Ingestas sin IA:* 📝 Planilla precargada *COMIDA.\n• *Presión arterial:* 📸 Fotos del tensiómetro digital\n• *Actividad física:* 📝 Texto o 🎤 Notas de voz.\n• *Resumen diario:* 🎤 Notas de voz: Consumos del dia 5. \n• *Resumen semanal:* 🎤 Notas de voz: Detalle de la semana \n• *Resumen mensual:* 🎤 Notas de voz: resumen de agosto. \n\n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_btn_descargar_manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📄 Descargar Manual Completo en PDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_peso_base_reg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ **Peso base registrado ({mes}):** {peso:.1f} kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_peso_ingreso_quincenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\nPara ingresar tu control quincenal y calibrar tu factor, escribí:\n/peso [nuevo_peso] (ejemplo: /peso 96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_peso_ingreso_cierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\nPara ingresar tu peso de cierre de mes, escribí:\n/peso [nuevo_peso] (ejemplo: /peso 96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_peso_prox_quincena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\n⏳ *Tu próximo control de peso se habilitará a partir del día 15.*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_manual_usuario_caption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📄 **Manual de Usuario**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_manual_err_no_encontrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ El archivo {pdf_filename} no se encuentra en el servidor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_manual_err_envio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">❌ Ocurrió un error al intentar enviar el manual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_calibracion_no_disp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⏳ **Calibración no disponible:** Para mantener la estabilidad de los cálculos, la calibración de gasto con reloj inteligente se habilita únicamente a partir del **día 15** de cada mes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_err_calorias_realistas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Ingresá un valor de calorías realista (entre 1000 y 4000 kcal).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_err_perfil_inactivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_err_tmb_base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_nota_seguridad_tope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\n⚠️ *Nota de seguridad:* El valor del reloj superaba el 20% de variación respecto a tu tendencia habitual. Se aplicó el tope máximo permitido del 20%.\n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_resumen_calibracion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📊 **Calibración de Gasto Energético (Reloj):**\n\n• Calorías reportadas por el reloj: {calorias_reloj:.0f} kcal\n• TMB Base estimada: {tmb:.0f} kcal\n\n• **Gasto Diario Anterior:** {get_anterior:.0f} kcal\n• **Nuevo Gasto Diario Ajustado:** {get_nuevo:.0f} kcal\n\n{aviso_tope}¿Deseás actualizar tu gasto diario con este valor?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_err_formato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_err_procesar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_operacion_cancelada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_datos_expirados</t>
+  </si>
+  <si>
     <t xml:space="preserve">⚠️ Los datos temporales expiraron. Por favor, volvé a enviar el comando /factor.</t>
   </si>
   <si>
-    <t xml:space="preserve">09_get_calibracion_exito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✅ ¡Gasto energético actualizado con éxito!\n\n• Nuevo Gasto Diario asignado: {get_final:.0f} kcal\n• Período actualizado: {mes_actual}\n• Estado: Calibración mensual registrada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_get_error_guardar_db</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠ Ocurrió un error al guardar en la base de datos: {e}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reloj_actualizado_mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Período en formato YYYY-MM que registra si el usuario ya realizó su calibración mensual del GET mediante reloj inteligente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">profesional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID de Telegram del médico o profesional de la salud asociado al seguimiento del paciente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ritmo_preferido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ritmo de avance seleccionado por el usuario (tranquilo, moderado, intenso) para definir el déficit o superávit calórico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cintura_cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perímetro de la cintura medido en centímetros para el cálculo de masa magra de alta precisión.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cuello_cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perímetro del cuello medido en centímetros para la estimación de composición corporal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cadera_cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perímetro de la cadera medido en centímetros (específico para perfiles femeninos).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valores_Clinicos_Profesional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabla relacional de supremacía clínica donde el médico almacena los topes personalizados de calorías y macronutrientes por período.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_perfil_lbl_cintura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cintura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_perfil_lbl_cuello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_perfil_lbl_cadera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cadera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_perfil_lbl_meta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_perfil_lbl_act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_perfil_fecha_no_reg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No registrada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_perfil_mod_pediatrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modalidad Pediátrica/Juvenil (Cálculo OMS sin circunferencias)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_perfil_alerta_medidas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ Atención: Tenés 18 años o más. Actualizá tus medidas con los botones de abajo para activar el cálculo de masa magra de alta precisión clínica.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_btn_ritmo_tranquilo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🟢 Tranquilo / Lento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_btn_ritmo_moderado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🟡 Moderado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_btn_ritmo_intenso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🔴 Intenso / Rápido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_presi_resumen_titulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🩺 Resumen de Presión Arterial ({mes}):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_presi_mediciones_reg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Mediciones registradas: {cant}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_presi_prom_alta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_presi_prom_baja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_presi_prom_pulso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_presi_foto_err_rango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ Lectura de presión atípica o errónea\n\nLos valores detectados en la imagen ({alta:.0f}/{baja:.0f} mmHg) están fuera de los rangos biológicos lógicos.\n\nPor favor, registrala manualmente usando:\n/presi [alta],[baja],[pulsaciones] (ej: /presi 120,80,75).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_btn_presi_agregar_nota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_btn_presi_guardar_directo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_btn_cancelar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_presi_foto_detectada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🩺 Tensiómetro detectado en la imagen:\n\n• Presión Alta: {alta:.0f} mmHg\n• Presión Baja: {baja:.0f} mmHg{pul_txt}\n\nSeleccioná una opción para continuar:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_presi_generando_pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generando PDF de presión... ⏳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_presi_pdf_caption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🩺 Reporte de Presión Arterial - Período {mes}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_get_bloqueo_medico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👨‍⚕️ &lt;b&gt;Acción denegada:&lt;/b&gt; Tenés un profesional asignado. Por favor, contactalo directamente para realizar modificaciones en tu plan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_start_mensaje_bienvenida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">👋 *¡Bienvenido a tu Bot Nutricional Personalizado!*\n\nGuía rápida de comandos e ingresos disponibles:\n\n📌 *Comandos Principales:*\n• /alta: Apertura de cuenta ingresando los datos.\n• /barra: Ingresa por código de barras un comestible.\n• /borracomida: Borra una comida de la Planilla.\n• /comidas: Planilla de comidas precargadas y PDF.\n• /diario: Ingestas seleccionando por teclado y PDF.\n• /eliminar: Borra ingestas y actividades.\n• /GET: Actualiza GET por reloj inteligente .\n• /inicio: Resumen de comandos y manual en PDF.\n• /pago: Elegir el plan o promoción de pago vigente.\n• /perfil: Actualización de datos biométricos.\n• /peso: Registro o control de peso mensual \n• /presi: Registro y consulta de presión arterial.\n• /receta: Calculadora Web para registrar comidas.\n• /resumen: Reporte mensual de calorías y PDF .\n• /semana: Estadística semanal (calorías, fibras, etc.).\n\n• /x: Cancelar comando.\n\n📌 *Métodos de Registro y consultas directas:*\n• *Ingestas con IA:* 📝 Texto, 🎤 Notas de voz, 📸 Fotos.\n• *Ingestas con IA:* 📸 Fotos de un código de barras\n• *Ingestas sin IA:* 📝 Planilla precargada *COMIDA.\n• *Presión arterial:* 📸 Fotos del tensiómetro digital\n• *Actividad física:* 📝 Texto o 🎤 Notas de voz.\n• *Resumen diario:* 🎤 Notas de voz: Consumos del dia 5. \n• *Resumen semanal:* 🎤 Notas de voz: Detalle de la semana \n• *Resumen mensual:* 🎤 Notas de voz: resumen de agosto. \n\n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_btn_descargar_manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📄 Descargar Manual Completo en PDF</t>
+    <t xml:space="preserve">09_get_exito_actualizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ **¡Gasto energético actualizado con éxito!**\n\n• Nuevo Gasto Diario asignado: {get_final:.0f} kcal\n• Período actualizado: {mes_actual}\n• Estado: Calibración mensual registrada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_get_err_guardar_db</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_selecciona_idioma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🌐 Seleccioná tu **idioma preferido**:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_err_cadera_valida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Ingresá un perímetro de cadera válido en cm (ejemplo: 100).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_selecciona_ritmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seleccioná el **ritmo para tu plan**. Esto define el déficit/superávit de tus calorías:\n• *🟢 Tranquilo (Cambios muy graduales, súper fácil de sostener).*\n• *🟡 Moderado (Equilibrio ideal entre resultados y adherencia).*\n• *🔴 Intenso (Exigente, para resultados más rápidos).*\n\n🎯 Seleccioná tu ritmo deseado:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_selecciona_movimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seleccioná tu **nivel de movimiento diario** (el ejercicio deportivo se registra aparte):\n• *🪑 Ligero (Trabajo de oficina / Mayormente sentado).*\n• *🚶 Moderado (De pie muchas horas, ej: docentes, vendedores).*\n• *🏃 Intenso (Trabajo físico pesado, ej: albañilería, carga).*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_ingresa_peso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingresá tu **peso actual en kg** (ejemplo: 82.5):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_prueba_finalizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ **Tu período de prueba gratuito ha finalizado.**\n\nPara seguir usando todas las funciones del asistente, podés activar tu cuenta abonando los días que restan hasta fin de mes.\n\nUna vez abonado, volverás a tener acceso total y tu ciclo de facturación se alineará al día 1 del mes próximo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_btn_activar_mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_terminos_ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ **Términos aceptados correctamente.**\n\n🔑 **Apertura de Ficha - Validación de Profesional**\n\nPara comenzar el registro, por favor ingresá el **ID de Telegram del profesional**.\n*(Si no tenés un profesional asignado y querés usar el asistente de forma independiente, ingresá 123456789)*:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_err_prof_invalido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ **ID de profesional no válido**\n\nEl número ingresado no figura en la lista de profesionales autorizados. Por favor, verificá el ID con tu profesional e intentalo nuevamente o escribí /cancelar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_solicita_nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ **Profesional verificado correctamente.**\n\n📝 **Apertura de Ficha Nutricional**\nPor favor, indicá tu **Nombre y Apellido / Apodo**:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_err_fecha_cumple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Formato de fecha inválido. Usá el formato AAAA-MM-DD (ejemplo: 1990-08-25).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_perfil_pediatrico_ritmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👶 **Perfil pediátrico/juvenil detectado ({edad_calculada} años).**\nSe adaptarán los cálculos a los estándares pediátricos de la OMS sin requerir medidas corporales.\n\nSeleccioná el **ritmo para tu plan**. Esto define el déficit/superávit de tus calorías:\n• *🟢 Tranquilo (Cambios muy graduales, súper fácil de sostener).*\n• *🟡 Moderado (Equilibrio ideal entre resultados y adherencia).*\n• *🔴 Intenso (Exigente, para resultados más rápidos).*\n\n🎯 Seleccioná tu ritmo deseado:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_ingresa_cintura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingresá el **perímetro de tu cintura en cm** (ejemplo: 85):\n\n{tip_cintura}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_err_cintura_valida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Ingresá un perímetro de cintura válido en cm (ejemplo: 85).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_ingresa_cuello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingresá el **perímetro de tu cuello en cm** (ejemplo: 38):\n\n{tip_cuello}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_err_cuello_valido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Ingresá un perímetro de cuello válido en cm (ejemplo: 38).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_ingresa_cadera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingresá el **perímetro de tu cadera en cm** (ejemplo: 100):\n\n{tip_cadera}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_err_nombre_valido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Por favor, ingresá un nombre válido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_btn_masculino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masculino 👨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_btn_femenino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Femenino 👩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_selecciona_sexo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seleccioná tu **sexo biológico**:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_ingresa_cumple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahora ingresá tu **fecha de nacimiento** en formato AAAA-MM-DD (ejemplo: 1985-04-12):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_err_peso_valido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ Ingresá un peso válido en kg (ejemplo: 75.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_ing_ingresa_altura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingresá tu **altura en centímetros** (ejemplo: 175 para 1,75 m):</t>
   </si>
   <si>
     <t xml:space="preserve">10_pagar_sin_planes</t>
@@ -2412,7 +2724,7 @@
     <t xml:space="preserve">10_pagar_enviado</t>
   </si>
   <si>
-    <t xml:space="preserve">✅ Has seleccionado: {descripcion} ({estrellas} Estrellas).\nTe hemos enviado la factura para abonar en el chat.</t>
+    <t xml:space="preserve">✅ Has seleccionado: {descripcion} ({estrellas} Estrellas).\nTe enviaremos la factura para abonar en el chat el dia 1.</t>
   </si>
   <si>
     <t xml:space="preserve">10_pagar_error_proc</t>
@@ -2595,17 +2907,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2731,7 +3047,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B973"/>
+  <dimension ref="A1:B1009"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3706,107 +4022,107 @@
         <v>213</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2"/>
-      <c r="B124" s="2"/>
-    </row>
-    <row r="125" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="s">
+    <row r="124" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B124" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1" t="s">
+    <row r="125" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B125" s="3" t="s">
         <v>217</v>
       </c>
     </row>
+    <row r="126" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
     <row r="127" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="s">
+      <c r="A127" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B127" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1" t="s">
+    <row r="128" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B128" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1" t="s">
+    <row r="129" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="B129" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
     </row>
     <row r="131" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="292.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
         <v>237</v>
       </c>
@@ -3814,7 +4130,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
         <v>239</v>
       </c>
@@ -3822,7 +4138,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="292.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
         <v>241</v>
       </c>
@@ -3830,7 +4146,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
         <v>243</v>
       </c>
@@ -3838,7 +4154,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
         <v>245</v>
       </c>
@@ -3846,7 +4162,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
         <v>247</v>
       </c>
@@ -3854,7 +4170,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
         <v>249</v>
       </c>
@@ -3862,7 +4178,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
         <v>251</v>
       </c>
@@ -3870,7 +4186,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
         <v>253</v>
       </c>
@@ -3878,7 +4194,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
         <v>255</v>
       </c>
@@ -3894,7 +4210,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
         <v>259</v>
       </c>
@@ -3902,7 +4218,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
         <v>261</v>
       </c>
@@ -3910,7 +4226,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
         <v>263</v>
       </c>
@@ -3918,539 +4234,539 @@
         <v>264</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
         <v>265</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="152" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="1" t="s">
+      <c r="B152" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B152" s="1" t="s">
+    </row>
+    <row r="153" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="153" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
+      <c r="B153" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B153" s="1" t="s">
+    </row>
+    <row r="154" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="154" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="s">
+      <c r="B154" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B155" s="1" t="s">
+    </row>
+    <row r="156" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="156" customFormat="false" ht="214.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="s">
+      <c r="B156" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B156" s="1" t="s">
+    </row>
+    <row r="157" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="157" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="1" t="s">
+      <c r="B157" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B157" s="1" t="s">
+    </row>
+    <row r="158" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="158" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="s">
+      <c r="B158" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B158" s="1" t="s">
+    </row>
+    <row r="159" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="159" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="1" t="s">
+      <c r="B159" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B159" s="1" t="s">
+    </row>
+    <row r="160" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="160" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1" t="s">
+      <c r="B160" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B160" s="1" t="s">
+    </row>
+    <row r="161" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="161" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1" t="s">
+      <c r="B161" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B161" s="1" t="s">
+    </row>
+    <row r="162" customFormat="false" ht="214.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="162" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="1" t="s">
+      <c r="B162" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B162" s="1" t="s">
+    </row>
+    <row r="163" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="163" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="1" t="s">
+      <c r="B163" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B163" s="1" t="s">
+    </row>
+    <row r="164" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="164" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1" t="s">
+      <c r="B164" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B164" s="1" t="s">
+    </row>
+    <row r="165" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="165" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1" t="s">
+      <c r="B165" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B165" s="1" t="s">
+    </row>
+    <row r="166" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="166" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="1" t="s">
+      <c r="B166" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B166" s="1" t="s">
+    </row>
+    <row r="167" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="167" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="1" t="s">
+      <c r="B167" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B167" s="1" t="s">
+    </row>
+    <row r="168" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="168" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="1" t="s">
+      <c r="B168" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B168" s="1" t="s">
+    </row>
+    <row r="169" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="s">
         <v>300</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>235</v>
+        <v>302</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>239</v>
+        <v>306</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="2"/>
-      <c r="B173" s="2"/>
-    </row>
-    <row r="174" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="175" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>304</v>
+        <v>245</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>306</v>
+        <v>247</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>307</v>
+        <v>248</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>308</v>
+        <v>249</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>310</v>
+        <v>251</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>311</v>
+        <v>252</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B179" s="1" t="s">
+      <c r="A179" s="3" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="180" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="1" t="s">
+      <c r="B179" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B180" s="1" t="s">
+    </row>
+    <row r="180" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="3" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="181" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="1" t="s">
+      <c r="B180" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B181" s="1" t="s">
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2"/>
+      <c r="B181" s="2"/>
+    </row>
+    <row r="182" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="182" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="1" t="s">
+      <c r="B182" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="183" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="183" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
         <v>319</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="184" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="185" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="186" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="188" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
         <v>334</v>
       </c>
       <c r="B191" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="1" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="192" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="1" t="s">
+      <c r="B192" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B192" s="1" t="s">
+    </row>
+    <row r="193" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="1" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="193" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="1" t="s">
+      <c r="B193" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B193" s="1" t="s">
+    </row>
+    <row r="194" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="1" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="194" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="1" t="s">
+      <c r="B194" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B194" s="1" t="s">
+    </row>
+    <row r="195" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="195" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="s">
+      <c r="B195" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B195" s="1" t="s">
+    </row>
+    <row r="196" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="196" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1" t="s">
+      <c r="B196" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B196" s="1" t="s">
+    </row>
+    <row r="197" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="197" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="1" t="s">
+      <c r="B197" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B197" s="1" t="s">
+    </row>
+    <row r="198" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="1" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="198" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="1" t="s">
+      <c r="B198" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B198" s="1" t="s">
+    </row>
+    <row r="199" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="1" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="199" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="1" t="s">
+      <c r="B199" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B200" s="1" t="s">
+    </row>
+    <row r="201" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="1" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="201" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="1" t="s">
+      <c r="B201" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B201" s="1" t="s">
+    </row>
+    <row r="202" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="1" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="202" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="1" t="s">
+      <c r="B202" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B202" s="1" t="s">
+    </row>
+    <row r="203" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="1" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="203" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="1" t="s">
+      <c r="B203" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B203" s="1" t="s">
+    </row>
+    <row r="204" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="1" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="204" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="1" t="s">
+      <c r="B204" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B204" s="1" t="s">
+    </row>
+    <row r="205" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="1" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="205" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="1" t="s">
+      <c r="B205" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B205" s="1" t="s">
+    </row>
+    <row r="206" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="1" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="206" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="1" t="s">
+      <c r="B206" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B206" s="1" t="s">
+    </row>
+    <row r="207" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="1" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="207" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="1" t="s">
+      <c r="B207" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B207" s="1" t="s">
+    </row>
+    <row r="208" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="1" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="208" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="1" t="s">
+      <c r="B208" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B208" s="1" t="s">
+    </row>
+    <row r="209" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="1" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="209" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="1" t="s">
+      <c r="B209" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B210" s="1" t="s">
+    </row>
+    <row r="211" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="211" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="1" t="s">
+      <c r="B211" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B211" s="1" t="s">
+    </row>
+    <row r="212" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="1" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="212" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="1" t="s">
+      <c r="B212" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B212" s="1" t="s">
+    </row>
+    <row r="213" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="1" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="213" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="1" t="s">
+      <c r="B213" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B213" s="1" t="s">
+    </row>
+    <row r="214" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="1" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="214" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="1" t="s">
+      <c r="B214" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B214" s="1" t="s">
+    </row>
+    <row r="215" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="1" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="215" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="1" t="s">
+      <c r="B215" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B215" s="1" t="s">
+    </row>
+    <row r="216" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="1" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="216" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="1" t="s">
+      <c r="B216" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B216" s="1" t="s">
+    </row>
+    <row r="217" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="1" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="217" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="1" t="s">
+      <c r="B217" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="218" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
         <v>387</v>
       </c>
@@ -4463,422 +4779,422 @@
         <v>389</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>268</v>
+        <v>394</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="225" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="226" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="228" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="230" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>304</v>
+        <v>407</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>306</v>
+        <v>409</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>308</v>
+        <v>411</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>310</v>
+        <v>413</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>311</v>
+        <v>414</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>312</v>
+        <v>415</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="235" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>346</v>
+        <v>417</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="236" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>348</v>
+        <v>419</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="238" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="240" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>368</v>
+        <v>325</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>369</v>
+        <v>326</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="244" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="245" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="246" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="247" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>383</v>
+        <v>426</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="249" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="250" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="250" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="251" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="2"/>
-      <c r="B253" s="2"/>
-    </row>
-    <row r="254" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="255" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="259" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="B261" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="3" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="262" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="1" t="s">
+      <c r="B261" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B262" s="1" t="s">
+    </row>
+    <row r="262" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="3" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="263" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="1" t="s">
+      <c r="B262" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="B263" s="1" t="s">
+    </row>
+    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="2"/>
+      <c r="B263" s="2"/>
+    </row>
+    <row r="264" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="264" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="1" t="s">
+      <c r="B264" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B264" s="1" t="s">
+    </row>
+    <row r="265" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="1" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="265" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="1" t="s">
+      <c r="B265" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B265" s="1" t="s">
+    </row>
+    <row r="266" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="1" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="266" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="1" t="s">
+      <c r="B266" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B266" s="1" t="s">
+    </row>
+    <row r="267" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="1" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="267" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="1" t="s">
+      <c r="B267" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="272" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="272" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
         <v>449</v>
       </c>
@@ -4899,63 +5215,63 @@
         <v>453</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="275" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="277" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="278" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="279" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="280" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="281" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>467</v>
+        <v>233</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4966,7 +5282,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
         <v>470</v>
       </c>
@@ -4974,239 +5290,239 @@
         <v>471</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
         <v>472</v>
       </c>
       <c r="B284" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="1" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="285" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="1" t="s">
+      <c r="B285" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B285" s="1" t="s">
+    </row>
+    <row r="286" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="1" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="286" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="1" t="s">
+      <c r="B286" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B286" s="1" t="s">
+    </row>
+    <row r="287" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="1" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="287" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="1" t="s">
+      <c r="B287" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B287" s="1" t="s">
+    </row>
+    <row r="288" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="1" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="288" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="1" t="s">
+      <c r="B288" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B288" s="1" t="s">
+    </row>
+    <row r="289" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="1" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="289" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="1" t="s">
+      <c r="B289" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B289" s="1" t="s">
+    </row>
+    <row r="290" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="1" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="290" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="1" t="s">
+      <c r="B290" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B290" s="1" t="s">
+    </row>
+    <row r="291" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="1" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="291" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="1" t="s">
+      <c r="B291" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="B291" s="1" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B292" s="1" t="s">
+    </row>
+    <row r="293" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="1" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="293" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="1" t="s">
+      <c r="B293" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B293" s="1" t="s">
+    </row>
+    <row r="294" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="1" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="294" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="1" t="s">
+      <c r="B294" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B294" s="1" t="s">
+    </row>
+    <row r="295" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="1" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="295" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="1" t="s">
+      <c r="B295" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B295" s="1" t="s">
+    </row>
+    <row r="296" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="1" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="296" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="1" t="s">
+      <c r="B296" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B296" s="1" t="s">
+    </row>
+    <row r="297" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="1" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="297" customFormat="false" ht="516.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="1" t="s">
+      <c r="B297" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B298" s="1" t="s">
+    </row>
+    <row r="299" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="1" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="299" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="1" t="s">
+      <c r="B299" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B299" s="1" t="s">
+    </row>
+    <row r="300" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="1" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="300" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="1" t="s">
+      <c r="B300" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B300" s="1" t="s">
+    </row>
+    <row r="301" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="1" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="301" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="1" t="s">
+      <c r="B301" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B301" s="1" t="s">
+    </row>
+    <row r="302" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="1" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="302" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="1" t="s">
+      <c r="B302" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B302" s="1" t="s">
+    </row>
+    <row r="303" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="1" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="303" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="1" t="s">
+      <c r="B303" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B304" s="1" t="s">
+    </row>
+    <row r="305" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="1" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="305" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="1" t="s">
+      <c r="B305" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B305" s="1" t="s">
+    </row>
+    <row r="306" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="1" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="306" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="1" t="s">
+      <c r="B306" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B306" s="1" t="s">
+    </row>
+    <row r="307" customFormat="false" ht="516.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="1" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="307" customFormat="false" ht="695.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="1" t="s">
+      <c r="B307" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B307" s="1" t="s">
+    </row>
+    <row r="308" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="1" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="308" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="1" t="s">
+      <c r="B308" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B308" s="1" t="s">
+    </row>
+    <row r="309" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="1" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="309" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="1" t="s">
+      <c r="B309" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="B309" s="1" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B310" s="1" t="s">
+    </row>
+    <row r="311" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="1" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="311" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="1" t="s">
+      <c r="B311" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B311" s="1" t="s">
+    </row>
+    <row r="312" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="1" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="312" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="1" t="s">
+      <c r="B312" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="313" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="313" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
         <v>529</v>
       </c>
@@ -5214,7 +5530,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
         <v>531</v>
       </c>
@@ -5222,7 +5538,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
         <v>533</v>
       </c>
@@ -5230,7 +5546,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
         <v>535</v>
       </c>
@@ -5238,7 +5554,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="695.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
         <v>537</v>
       </c>
@@ -5246,7 +5562,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
         <v>539</v>
       </c>
@@ -5254,7 +5570,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
         <v>541</v>
       </c>
@@ -5262,7 +5578,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
         <v>543</v>
       </c>
@@ -5270,7 +5586,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
         <v>545</v>
       </c>
@@ -5283,55 +5599,55 @@
         <v>547</v>
       </c>
       <c r="B322" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="1" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="323" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="1" t="s">
+      <c r="B323" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="B323" s="1" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>551</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="B325" s="1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="B326" s="1" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="B327" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5339,90 +5655,90 @@
         <v>560</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>205</v>
+        <v>561</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>228</v>
+        <v>565</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="333" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="334" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="335" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="336" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="337" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="338" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="339" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="340" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
         <v>580</v>
       </c>
@@ -5430,211 +5746,203 @@
         <v>581</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
         <v>582</v>
       </c>
       <c r="B341" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="1" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="342" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="1" t="s">
+      <c r="B342" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="B342" s="1" t="s">
+    </row>
+    <row r="343" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="1" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="343" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="1" t="s">
+      <c r="B343" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="B343" s="1" t="s">
+    </row>
+    <row r="344" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="1" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="344" customFormat="false" ht="348.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="1" t="s">
+      <c r="B344" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="B344" s="1" t="s">
+    </row>
+    <row r="345" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="1" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="345" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="1" t="s">
+      <c r="B345" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="B345" s="1" t="s">
+    </row>
+    <row r="346" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="1" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="346" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="1" t="s">
+      <c r="B346" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="B346" s="1" t="s">
+    </row>
+    <row r="347" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="1" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="347" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="1" t="s">
+      <c r="B347" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="B347" s="1" t="s">
+    </row>
+    <row r="348" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="1" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="348" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="1" t="s">
+      <c r="B348" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="B348" s="1" t="s">
+    </row>
+    <row r="349" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="1" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="349" customFormat="false" ht="348.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="1" t="s">
+      <c r="B349" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="B349" s="1" t="s">
+    </row>
+    <row r="350" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="1" t="s">
         <v>599</v>
-      </c>
-    </row>
-    <row r="350" customFormat="false" ht="404.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="1" t="s">
-        <v>598</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="2"/>
-      <c r="B351" s="2"/>
-    </row>
-    <row r="352" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="352" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="353" customFormat="false" ht="214.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="354" customFormat="false" ht="449.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="354" customFormat="false" ht="348.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="355" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="356" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="357" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="358" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="359" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="359" customFormat="false" ht="348.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="360" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="404.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
         <v>617</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="B361" s="1" t="s">
-        <v>84</v>
+      <c r="A361" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="B362" s="1" t="s">
-        <v>185</v>
+      <c r="A362" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="B363" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="364" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="B364" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="365" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="B365" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="366" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="1" t="s">
+      <c r="A363" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="B366" s="1" t="s">
+      <c r="B363" s="3" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="367" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="3"/>
+      <c r="B364" s="3"/>
+    </row>
+    <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A365" s="3"/>
+      <c r="B365" s="3"/>
+    </row>
+    <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A366" s="2"/>
+      <c r="B366" s="2"/>
+    </row>
+    <row r="367" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
         <v>626</v>
       </c>
@@ -5642,7 +5950,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="368" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="214.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
         <v>628</v>
       </c>
@@ -5650,7 +5958,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="369" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="449.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
         <v>630</v>
       </c>
@@ -5658,7 +5966,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="370" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
         <v>632</v>
       </c>
@@ -5666,7 +5974,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
         <v>634</v>
       </c>
@@ -5674,7 +5982,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="372" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
         <v>636</v>
       </c>
@@ -5682,7 +5990,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
         <v>638</v>
       </c>
@@ -5698,7 +6006,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="375" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
         <v>642</v>
       </c>
@@ -5706,447 +6014,447 @@
         <v>643</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
         <v>644</v>
       </c>
       <c r="B376" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A377" s="1" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="377" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="1" t="s">
+      <c r="B377" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A378" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B377" s="1" t="s">
+      <c r="B378" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A379" s="1" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="378" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="1" t="s">
+      <c r="B379" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A380" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B378" s="1" t="s">
+      <c r="B380" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="1" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="379" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="1" t="s">
+      <c r="B381" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B379" s="1" t="s">
+    </row>
+    <row r="382" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A382" s="1" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="380" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="1" t="s">
+      <c r="B382" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B380" s="1" t="s">
+    </row>
+    <row r="383" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A383" s="1" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="381" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="1" t="s">
+      <c r="B383" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="B381" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="382" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="B382" s="1" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="383" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="B383" s="1" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="385" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="385" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="387" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="389" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A389" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="390" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A390" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B390" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B388" s="1" t="s">
+    </row>
+    <row r="391" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A391" s="1" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="389" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="1" t="s">
+      <c r="B391" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B389" s="1" t="s">
+    </row>
+    <row r="392" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A392" s="1" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="390" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="1" t="s">
+      <c r="B392" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="B390" s="1" t="s">
+    </row>
+    <row r="393" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A393" s="1" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="391" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="1" t="s">
+      <c r="B393" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="B391" s="1" t="s">
+    </row>
+    <row r="394" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A394" s="1" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="392" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="1" t="s">
+      <c r="B394" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="B392" s="1" t="s">
+    </row>
+    <row r="395" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A395" s="1" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="393" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="1" t="s">
+      <c r="B395" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B393" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="394" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="1" t="s">
+    </row>
+    <row r="396" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A396" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B394" s="1" t="s">
+      <c r="B396" s="1" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="1" t="s">
+    <row r="397" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A397" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="B395" s="1" t="s">
+      <c r="B397" s="1" t="s">
         <v>682</v>
-      </c>
-    </row>
-    <row r="396" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="B396" s="1" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="397" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="B397" s="1" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>661</v>
+        <v>684</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="400" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A400" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B400" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="B399" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="400" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="B400" s="1" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>661</v>
+        <v>690</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="403" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A403" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="B402" s="1" t="s">
+      <c r="B403" s="1" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="403" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A403" s="1" t="s">
+    <row r="404" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A404" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="B403" s="1" t="s">
+      <c r="B404" s="1" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="404" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A404" s="1" t="s">
+    <row r="405" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A405" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="B404" s="1" t="s">
+      <c r="B405" s="1" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="405" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A405" s="1" t="s">
+    <row r="406" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A406" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="B405" s="1" t="s">
+      <c r="B406" s="1" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="406" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A406" s="1" t="s">
+    <row r="407" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A407" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="B406" s="1" t="s">
+      <c r="B407" s="1" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A407" s="1" t="s">
+    <row r="408" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A408" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B407" s="1" t="s">
+      <c r="B408" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="409" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A409" s="1" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="408" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A408" s="1" t="s">
+      <c r="B409" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B408" s="1" t="s">
+    </row>
+    <row r="410" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A410" s="1" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="409" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A409" s="1" t="s">
+      <c r="B410" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="B409" s="1" t="s">
+    </row>
+    <row r="411" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A411" s="1" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="410" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A410" s="1" t="s">
+      <c r="B411" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="B410" s="1" t="s">
+    </row>
+    <row r="412" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A412" s="1" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="411" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A411" s="1" t="s">
+      <c r="B412" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="B411" s="1" t="s">
+    </row>
+    <row r="413" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A413" s="1" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="412" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A412" s="1" t="s">
+      <c r="B413" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="414" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A414" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="B412" s="1" t="s">
+      <c r="B414" s="1" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="413" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A413" s="1" t="s">
+    <row r="415" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A415" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="B413" s="1" t="s">
+      <c r="B415" s="1" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="414" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A414" s="1" t="s">
+    <row r="416" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A416" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B414" s="1" t="s">
+      <c r="B416" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="417" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A417" s="1" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="415" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A415" s="1" t="s">
+      <c r="B417" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B415" s="1" t="s">
+    </row>
+    <row r="418" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A418" s="1" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="416" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A416" s="1" t="s">
+      <c r="B418" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B416" s="1" t="s">
+    </row>
+    <row r="419" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A419" s="1" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="417" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A417" s="1" t="s">
+      <c r="B419" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B417" s="1" t="s">
+    </row>
+    <row r="420" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A420" s="1" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="418" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A418" s="1" t="s">
+      <c r="B420" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B418" s="1" t="s">
+    </row>
+    <row r="421" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A421" s="1" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="419" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A419" s="1" t="s">
+      <c r="B421" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B419" s="1" t="s">
+    </row>
+    <row r="422" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A422" s="1" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="420" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A420" s="1" t="s">
+      <c r="B422" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="B420" s="1" t="s">
+    </row>
+    <row r="423" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A423" s="1" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="421" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A421" s="1" t="s">
+      <c r="B423" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="B421" s="1" t="s">
+    </row>
+    <row r="424" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A424" s="1" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="422" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A422" s="1" t="s">
+      <c r="B424" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="B422" s="1" t="s">
+    </row>
+    <row r="425" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A425" s="1" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="423" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A423" s="1" t="s">
+      <c r="B425" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="B423" s="1" t="s">
+    </row>
+    <row r="426" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A426" s="1" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="424" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A424" s="1" t="s">
+      <c r="B426" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="B424" s="1" t="s">
+    </row>
+    <row r="427" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A427" s="1" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="425" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A425" s="1" t="s">
+      <c r="B427" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="B425" s="1" t="s">
+    </row>
+    <row r="428" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A428" s="1" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="426" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A426" s="1" t="s">
+      <c r="B428" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B426" s="1" t="s">
+    </row>
+    <row r="429" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A429" s="1" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="427" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A427" s="1" t="s">
+      <c r="B429" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B427" s="1" t="s">
+    </row>
+    <row r="430" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A430" s="1" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="428" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A428" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="B428" s="1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="429" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A429" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="B429" s="1" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="430" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A430" s="1" t="s">
+      <c r="B430" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B430" s="1" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="431" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="431" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
         <v>746</v>
       </c>
@@ -6154,7 +6462,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="432" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
         <v>748</v>
       </c>
@@ -6162,7 +6470,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
         <v>750</v>
       </c>
@@ -6170,7 +6478,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="434" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
         <v>752</v>
       </c>
@@ -6178,7 +6486,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
         <v>754</v>
       </c>
@@ -6186,7 +6494,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
         <v>756</v>
       </c>
@@ -6194,7 +6502,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
         <v>758</v>
       </c>
@@ -6202,7 +6510,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
         <v>760</v>
       </c>
@@ -6210,7 +6518,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="439" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
         <v>762</v>
       </c>
@@ -6218,729 +6526,793 @@
         <v>763</v>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
         <v>764</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="441" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="441" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B441" s="1" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="442" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A442" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="443" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A443" s="1" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="442" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A442" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="B442" s="1" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="443" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A443" s="1" t="s">
-        <v>767</v>
-      </c>
       <c r="B443" s="1" t="s">
-        <v>768</v>
+        <v>656</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>692</v>
+        <v>657</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="445" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="445" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="446" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="446" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>673</v>
+        <v>772</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="448" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="448" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="449" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="449" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="450" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="450" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="451" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="451" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="452" customFormat="false" ht="1457.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="452" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A454" s="2"/>
-      <c r="B454" s="2"/>
-    </row>
-    <row r="455" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="454" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A454" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B454" s="1" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="455" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="456" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="456" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="457" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="457" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="458" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="458" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>792</v>
+        <v>717</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="460" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="460" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
         <v>794</v>
       </c>
       <c r="B460" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="461" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A461" s="1" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="461" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A461" s="1" t="s">
+      <c r="B461" s="1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="462" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A462" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="B461" s="1" t="s">
+      <c r="B462" s="1" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="463" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A463" s="1" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="462" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A462" s="1" t="s">
+      <c r="B463" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="B462" s="1" t="s">
+    </row>
+    <row r="464" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A464" s="1" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="463" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A463" s="1" t="s">
+      <c r="B464" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="B463" s="1" t="s">
+    </row>
+    <row r="465" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A465" s="1" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="464" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A464" s="1" t="s">
+      <c r="B465" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="B464" s="1" t="s">
+    </row>
+    <row r="466" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A466" s="1" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="465" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A465" s="1" t="s">
+      <c r="B466" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="B465" s="1" t="s">
+    </row>
+    <row r="467" customFormat="false" ht="1446.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A467" s="1" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="466" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A466" s="1" t="s">
+      <c r="B467" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="B466" s="1" t="s">
+    </row>
+    <row r="468" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A468" s="1" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="467" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A467" s="1" t="s">
+      <c r="B468" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="B467" s="1" t="s">
+    </row>
+    <row r="469" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A469" s="3" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="468" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A468" s="1" t="s">
+      <c r="B469" s="3" t="s">
         <v>810</v>
       </c>
-      <c r="B468" s="1" t="s">
+    </row>
+    <row r="470" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A470" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="B470" s="3" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="471" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A471" s="3" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="469" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A469" s="1" t="s">
+      <c r="B471" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="B469" s="1" t="s">
+    </row>
+    <row r="472" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A472" s="3" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="470" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A470" s="1" t="s">
+      <c r="B472" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="B470" s="1" t="s">
+    </row>
+    <row r="473" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A473" s="3" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="471" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A471" s="1" t="s">
+      <c r="B473" s="3" t="s">
         <v>816</v>
       </c>
-      <c r="B471" s="1" t="s">
+    </row>
+    <row r="474" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A474" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="B474" s="3" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="475" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A475" s="3" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="472" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A472" s="1" t="s">
+      <c r="B475" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="B472" s="1" t="s">
+    </row>
+    <row r="476" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A476" s="3" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="473" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A473" s="1" t="s">
+      <c r="B476" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="B473" s="1" t="s">
+    </row>
+    <row r="477" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A477" s="3" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="474" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A474" s="1" t="s">
+      <c r="B477" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="B474" s="1" t="s">
+    </row>
+    <row r="478" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A478" s="3" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="475" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A475" s="1" t="s">
+      <c r="B478" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="B475" s="1" t="s">
+    </row>
+    <row r="479" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A479" s="3" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="476" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A476" s="1" t="s">
+      <c r="B479" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="B476" s="1" t="s">
+    </row>
+    <row r="480" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A480" s="3" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="477" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A477" s="1" t="s">
+      <c r="B480" s="3" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="481" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A481" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="B477" s="1" t="s">
+      <c r="B481" s="3" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="482" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A482" s="3" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="478" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A478" s="1" t="s">
+      <c r="B482" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="B478" s="1" t="s">
+    </row>
+    <row r="483" customFormat="false" ht="348.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A483" s="3" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A479" s="2"/>
-      <c r="B479" s="2"/>
-    </row>
-    <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A480" s="2"/>
-      <c r="B480" s="2"/>
-    </row>
-    <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A481" s="2"/>
-      <c r="B481" s="2"/>
-    </row>
-    <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A482" s="2"/>
-      <c r="B482" s="2"/>
-    </row>
-    <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A483" s="2"/>
-      <c r="B483" s="2"/>
-    </row>
-    <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A484" s="2"/>
-      <c r="B484" s="2"/>
-    </row>
-    <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A485" s="2"/>
-      <c r="B485" s="2"/>
-    </row>
-    <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A486" s="2"/>
-      <c r="B486" s="2"/>
-    </row>
-    <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A487" s="2"/>
-      <c r="B487" s="2"/>
-    </row>
-    <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A488" s="2"/>
-      <c r="B488" s="2"/>
-    </row>
-    <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A489" s="2"/>
-      <c r="B489" s="2"/>
-    </row>
-    <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A490" s="2"/>
-      <c r="B490" s="2"/>
-    </row>
-    <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A491" s="2"/>
-      <c r="B491" s="2"/>
-    </row>
-    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A492" s="2"/>
-      <c r="B492" s="2"/>
-    </row>
-    <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A493" s="2"/>
-      <c r="B493" s="2"/>
-    </row>
-    <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A494" s="2"/>
-      <c r="B494" s="2"/>
-    </row>
-    <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A495" s="2"/>
-      <c r="B495" s="2"/>
-    </row>
-    <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A496" s="2"/>
-      <c r="B496" s="2"/>
-    </row>
-    <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A497" s="2"/>
-      <c r="B497" s="2"/>
-    </row>
-    <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A498" s="2"/>
-      <c r="B498" s="2"/>
-    </row>
-    <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A499" s="2"/>
-      <c r="B499" s="2"/>
-    </row>
-    <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A500" s="2"/>
-      <c r="B500" s="2"/>
-    </row>
-    <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A501" s="2"/>
-      <c r="B501" s="2"/>
-    </row>
-    <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A502" s="2"/>
-      <c r="B502" s="2"/>
-    </row>
-    <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A503" s="2"/>
-      <c r="B503" s="2"/>
-    </row>
-    <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A504" s="2"/>
-      <c r="B504" s="2"/>
-    </row>
-    <row r="505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A505" s="2"/>
-      <c r="B505" s="2"/>
-    </row>
-    <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A506" s="2"/>
-      <c r="B506" s="2"/>
-    </row>
-    <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A507" s="2"/>
-      <c r="B507" s="2"/>
-    </row>
-    <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A508" s="2"/>
-      <c r="B508" s="2"/>
-    </row>
-    <row r="509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A509" s="2"/>
-      <c r="B509" s="2"/>
-    </row>
-    <row r="510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A510" s="2"/>
-      <c r="B510" s="2"/>
-    </row>
-    <row r="511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A511" s="2"/>
-      <c r="B511" s="2"/>
-    </row>
-    <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A512" s="2"/>
-      <c r="B512" s="2"/>
-    </row>
-    <row r="513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A513" s="2"/>
-      <c r="B513" s="2"/>
+      <c r="B483" s="3" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="484" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A484" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="B484" s="3" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="485" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A485" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="B485" s="3" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="486" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A486" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="B486" s="3" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="487" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A487" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="B487" s="3" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="488" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A488" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="B488" s="3" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="489" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A489" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="490" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A490" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="491" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A491" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B491" s="3" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="492" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A492" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="B492" s="3" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="493" customFormat="false" ht="303.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A493" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="B493" s="3" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="494" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A494" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="B494" s="3" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="495" customFormat="false" ht="281.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A495" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="B495" s="3" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="496" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A496" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="B496" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="497" customFormat="false" ht="292.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A497" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="B497" s="3" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="498" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A498" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="B498" s="3" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="499" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A499" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="B499" s="3" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="500" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A500" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="B500" s="3" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="501" customFormat="false" ht="516.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A501" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="B501" s="3" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="502" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A502" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="B502" s="3" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="503" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A503" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="B503" s="3" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="504" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A504" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="B504" s="3" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="505" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A505" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="B505" s="3" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="506" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A506" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="B506" s="3" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="507" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A507" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="B507" s="3" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="508" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A508" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="B508" s="3" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="509" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A509" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="B509" s="3" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="510" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A510" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="B510" s="3" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="511" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A511" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="B511" s="3" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="512" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A512" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="B512" s="3" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="513" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A513" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="B513" s="3" t="s">
+        <v>887</v>
+      </c>
     </row>
     <row r="514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A514" s="2"/>
-      <c r="B514" s="2"/>
-    </row>
-    <row r="515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A515" s="2"/>
-      <c r="B515" s="2"/>
-    </row>
-    <row r="516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A516" s="2"/>
-      <c r="B516" s="2"/>
-    </row>
-    <row r="517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A517" s="2"/>
-      <c r="B517" s="2"/>
-    </row>
-    <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A518" s="2"/>
-      <c r="B518" s="2"/>
-    </row>
-    <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A519" s="2"/>
-      <c r="B519" s="2"/>
-    </row>
-    <row r="520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A520" s="2"/>
-      <c r="B520" s="2"/>
-    </row>
-    <row r="521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A521" s="2"/>
-      <c r="B521" s="2"/>
-    </row>
-    <row r="522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A522" s="2"/>
-      <c r="B522" s="2"/>
-    </row>
-    <row r="523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A523" s="2"/>
-      <c r="B523" s="2"/>
-    </row>
-    <row r="524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A524" s="2"/>
-      <c r="B524" s="2"/>
-    </row>
-    <row r="525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A525" s="2"/>
-      <c r="B525" s="2"/>
-    </row>
-    <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A526" s="2"/>
-      <c r="B526" s="2"/>
-    </row>
-    <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A527" s="2"/>
-      <c r="B527" s="2"/>
-    </row>
-    <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A528" s="2"/>
-      <c r="B528" s="2"/>
-    </row>
-    <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A529" s="2"/>
-      <c r="B529" s="2"/>
-    </row>
-    <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A530" s="2"/>
-      <c r="B530" s="2"/>
-    </row>
-    <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A531" s="2"/>
-      <c r="B531" s="2"/>
-    </row>
-    <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A532" s="2"/>
-      <c r="B532" s="2"/>
-    </row>
-    <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A533" s="2"/>
-      <c r="B533" s="2"/>
-    </row>
-    <row r="534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A534" s="2"/>
-      <c r="B534" s="2"/>
-    </row>
-    <row r="535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A535" s="2"/>
-      <c r="B535" s="2"/>
-    </row>
-    <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A536" s="2"/>
-      <c r="B536" s="2"/>
-    </row>
-    <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A537" s="2"/>
-      <c r="B537" s="2"/>
-    </row>
-    <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A538" s="2"/>
-      <c r="B538" s="2"/>
-    </row>
-    <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A539" s="2"/>
-      <c r="B539" s="2"/>
-    </row>
-    <row r="540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A540" s="2"/>
-      <c r="B540" s="2"/>
-    </row>
-    <row r="541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A541" s="2"/>
-      <c r="B541" s="2"/>
-    </row>
-    <row r="542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A542" s="2"/>
-      <c r="B542" s="2"/>
-    </row>
-    <row r="543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A543" s="2"/>
-      <c r="B543" s="2"/>
-    </row>
-    <row r="544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A544" s="2"/>
-      <c r="B544" s="2"/>
-    </row>
-    <row r="545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A545" s="2"/>
-      <c r="B545" s="2"/>
-    </row>
-    <row r="546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A546" s="2"/>
-      <c r="B546" s="2"/>
-    </row>
-    <row r="547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A547" s="2"/>
-      <c r="B547" s="2"/>
-    </row>
-    <row r="548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A548" s="2"/>
-      <c r="B548" s="2"/>
-    </row>
-    <row r="549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A549" s="2"/>
-      <c r="B549" s="2"/>
-    </row>
-    <row r="550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A550" s="2"/>
-      <c r="B550" s="2"/>
-    </row>
-    <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A551" s="2"/>
-      <c r="B551" s="2"/>
-    </row>
-    <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A552" s="2"/>
-      <c r="B552" s="2"/>
-    </row>
-    <row r="553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A553" s="2"/>
-      <c r="B553" s="2"/>
-    </row>
-    <row r="554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A554" s="2"/>
-      <c r="B554" s="2"/>
-    </row>
-    <row r="555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A555" s="2"/>
-      <c r="B555" s="2"/>
-    </row>
-    <row r="556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A556" s="2"/>
-      <c r="B556" s="2"/>
-    </row>
-    <row r="557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A557" s="2"/>
-      <c r="B557" s="2"/>
-    </row>
-    <row r="558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A558" s="2"/>
-      <c r="B558" s="2"/>
-    </row>
-    <row r="559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="2"/>
-      <c r="B559" s="2"/>
-    </row>
-    <row r="560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="2"/>
-      <c r="B560" s="2"/>
-    </row>
-    <row r="561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A561" s="2"/>
-      <c r="B561" s="2"/>
-    </row>
-    <row r="562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A562" s="2"/>
-      <c r="B562" s="2"/>
-    </row>
-    <row r="563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A563" s="2"/>
-      <c r="B563" s="2"/>
-    </row>
-    <row r="564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A564" s="2"/>
-      <c r="B564" s="2"/>
-    </row>
-    <row r="565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A565" s="2"/>
-      <c r="B565" s="2"/>
-    </row>
-    <row r="566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A566" s="2"/>
-      <c r="B566" s="2"/>
-    </row>
-    <row r="567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A567" s="2"/>
-      <c r="B567" s="2"/>
-    </row>
-    <row r="568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A568" s="2"/>
-      <c r="B568" s="2"/>
-    </row>
-    <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A569" s="2"/>
-      <c r="B569" s="2"/>
-    </row>
-    <row r="570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A570" s="2"/>
-      <c r="B570" s="2"/>
-    </row>
-    <row r="571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A571" s="2"/>
-      <c r="B571" s="2"/>
-    </row>
-    <row r="572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A572" s="2"/>
-      <c r="B572" s="2"/>
-    </row>
-    <row r="573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A573" s="2"/>
-      <c r="B573" s="2"/>
-    </row>
-    <row r="574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A574" s="2"/>
-      <c r="B574" s="2"/>
-    </row>
-    <row r="575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A575" s="2"/>
-      <c r="B575" s="2"/>
-    </row>
-    <row r="576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A576" s="2"/>
-      <c r="B576" s="2"/>
-    </row>
-    <row r="577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A577" s="2"/>
-      <c r="B577" s="2"/>
-    </row>
-    <row r="578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A578" s="2"/>
-      <c r="B578" s="2"/>
-    </row>
-    <row r="579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A579" s="2"/>
-      <c r="B579" s="2"/>
-    </row>
-    <row r="580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A580" s="2"/>
-      <c r="B580" s="2"/>
-    </row>
-    <row r="581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A581" s="2"/>
-      <c r="B581" s="2"/>
-    </row>
-    <row r="582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A582" s="2"/>
-      <c r="B582" s="2"/>
+      <c r="A514" s="3"/>
+      <c r="B514" s="3"/>
+    </row>
+    <row r="515" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A515" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="516" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A516" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="517" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A517" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="518" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A518" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="519" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A519" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="520" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A520" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="521" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A521" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="522" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A522" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="523" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A523" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="524" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A524" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="525" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A525" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="526" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A526" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="527" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A527" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="528" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A528" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="529" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A529" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="530" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A530" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="531" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A531" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="532" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A532" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="533" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A533" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="534" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A534" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="535" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A535" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="536" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A536" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="537" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A537" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="538" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A538" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>935</v>
+      </c>
     </row>
     <row r="583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="2"/>
@@ -8505,6 +8877,150 @@
     <row r="973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
+    </row>
+    <row r="974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A974" s="2"/>
+      <c r="B974" s="2"/>
+    </row>
+    <row r="975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A975" s="2"/>
+      <c r="B975" s="2"/>
+    </row>
+    <row r="976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A976" s="2"/>
+      <c r="B976" s="2"/>
+    </row>
+    <row r="977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A977" s="2"/>
+      <c r="B977" s="2"/>
+    </row>
+    <row r="978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A978" s="2"/>
+      <c r="B978" s="2"/>
+    </row>
+    <row r="979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A979" s="2"/>
+      <c r="B979" s="2"/>
+    </row>
+    <row r="980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A980" s="2"/>
+      <c r="B980" s="2"/>
+    </row>
+    <row r="981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A981" s="2"/>
+      <c r="B981" s="2"/>
+    </row>
+    <row r="982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A982" s="2"/>
+      <c r="B982" s="2"/>
+    </row>
+    <row r="983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A983" s="2"/>
+      <c r="B983" s="2"/>
+    </row>
+    <row r="984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A984" s="2"/>
+      <c r="B984" s="2"/>
+    </row>
+    <row r="985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A985" s="2"/>
+      <c r="B985" s="2"/>
+    </row>
+    <row r="986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A986" s="2"/>
+      <c r="B986" s="2"/>
+    </row>
+    <row r="987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A987" s="2"/>
+      <c r="B987" s="2"/>
+    </row>
+    <row r="988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A988" s="2"/>
+      <c r="B988" s="2"/>
+    </row>
+    <row r="989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A989" s="2"/>
+      <c r="B989" s="2"/>
+    </row>
+    <row r="990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A990" s="2"/>
+      <c r="B990" s="2"/>
+    </row>
+    <row r="991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A991" s="2"/>
+      <c r="B991" s="2"/>
+    </row>
+    <row r="992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A992" s="2"/>
+      <c r="B992" s="2"/>
+    </row>
+    <row r="993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A993" s="2"/>
+      <c r="B993" s="2"/>
+    </row>
+    <row r="994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A994" s="2"/>
+      <c r="B994" s="2"/>
+    </row>
+    <row r="995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A995" s="2"/>
+      <c r="B995" s="2"/>
+    </row>
+    <row r="996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A996" s="2"/>
+      <c r="B996" s="2"/>
+    </row>
+    <row r="997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A997" s="2"/>
+      <c r="B997" s="2"/>
+    </row>
+    <row r="998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A998" s="2"/>
+      <c r="B998" s="2"/>
+    </row>
+    <row r="999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A999" s="2"/>
+      <c r="B999" s="2"/>
+    </row>
+    <row r="1000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1000" s="2"/>
+      <c r="B1000" s="2"/>
+    </row>
+    <row r="1001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1001" s="2"/>
+      <c r="B1001" s="2"/>
+    </row>
+    <row r="1002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1002" s="2"/>
+      <c r="B1002" s="2"/>
+    </row>
+    <row r="1003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1003" s="2"/>
+      <c r="B1003" s="2"/>
+    </row>
+    <row r="1004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1004" s="2"/>
+      <c r="B1004" s="2"/>
+    </row>
+    <row r="1005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1005" s="2"/>
+      <c r="B1005" s="2"/>
+    </row>
+    <row r="1006" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1006" s="2"/>
+      <c r="B1006" s="2"/>
+    </row>
+    <row r="1007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1007" s="2"/>
+      <c r="B1007" s="2"/>
+    </row>
+    <row r="1008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1008" s="2"/>
+      <c r="B1008" s="2"/>
+    </row>
+    <row r="1009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1009" s="2"/>
+      <c r="B1009" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
